--- a/forensic_xr_book.xlsx
+++ b/forensic_xr_book.xlsx
@@ -741,35 +741,35 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>023590.KS</t>
+          <t>0538.HK</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Daou Technology Inc.</t>
+          <t>Ajisen (China) Holdings Limite</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t xml:space="preserve">Hotels, Restaurants &amp; </t>
         </is>
       </c>
       <c r="G9" s="11" t="n">
-        <v>1148709798.626002</v>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>110731994.1818532</v>
+      </c>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="I9" s="13" t="n">
@@ -804,15 +804,13 @@
         </is>
       </c>
       <c r="P9" s="13" t="n">
-        <v>-12.852</v>
+        <v>-4.256074644466831</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>0.4782027784698607</v>
-      </c>
-      <c r="R9" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.27059576</v>
+      </c>
+      <c r="R9" s="14" t="n">
+        <v>66.45259291149884</v>
       </c>
     </row>
     <row r="10">
@@ -821,17 +819,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>0538.HK</t>
+          <t>005710.KQ</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Ajisen (China) Holdings Limite</t>
+          <t>Daewon Sanup Co., Ltd</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -841,15 +839,15 @@
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hotels, Restaurants &amp; </t>
+          <t>nan</t>
         </is>
       </c>
       <c r="G10" s="11" t="n">
-        <v>110731994.1818532</v>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>138531094.1027808</v>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="I10" s="13" t="n">
@@ -884,13 +882,13 @@
         </is>
       </c>
       <c r="P10" s="13" t="n">
-        <v>-4.256074644466831</v>
+        <v>-3.801</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0.27059576</v>
+        <v>0.3695059829823844</v>
       </c>
       <c r="R10" s="14" t="n">
-        <v>66.45259291149884</v>
+        <v>30.46226708553826</v>
       </c>
     </row>
     <row r="11">
@@ -899,31 +897,31 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>3700.HK</t>
+          <t>042420.KQ</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Inke Limited</t>
+          <t>Z Holdings Corporation</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>Diversified Telecommun</t>
+          <t>Internet &amp; Direct Mark</t>
         </is>
       </c>
       <c r="G11" s="11" t="n">
-        <v>241787776.6746577</v>
+        <v>96779704.39330758</v>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
@@ -961,16 +959,14 @@
           <t>–</t>
         </is>
       </c>
-      <c r="P11" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P11" s="13" t="n">
+        <v>3.135</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0.28567517</v>
+        <v>0.3895122570757942</v>
       </c>
       <c r="R11" s="14" t="n">
-        <v>-32.71958452610624</v>
+        <v>41.66640904663798</v>
       </c>
     </row>
     <row r="12">
@@ -979,31 +975,31 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>UIS</t>
+          <t>CCL.AX</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Unisys Corporation</t>
+          <t>Coca-Cola Amatil Limited</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Consumer Stapl</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="G12" s="11" t="n">
-        <v>176456608</v>
+        <v>757397297.131691</v>
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
@@ -1021,8 +1017,10 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L12" s="14" t="n">
-        <v>664.1859510299552</v>
+      <c r="L12" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M12" s="15" t="inlineStr">
         <is>
@@ -1034,19 +1032,19 @@
           <t>–</t>
         </is>
       </c>
-      <c r="O12" s="14" t="n">
-        <v>41.02353725449977</v>
+      <c r="O12" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="P12" s="13" t="n">
-        <v>14.07767730337079</v>
-      </c>
-      <c r="Q12" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-8.710000000000001</v>
+      </c>
+      <c r="Q12" s="13" t="n">
+        <v>2.487333</v>
       </c>
       <c r="R12" s="14" t="n">
-        <v>43.41950981183043</v>
+        <v>41.63159677303595</v>
       </c>
     </row>
     <row r="13">
@@ -1055,12 +1053,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>IH</t>
+          <t>UIS</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Ihuman Inc.</t>
+          <t>Unisys Corporation</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -1070,16 +1068,16 @@
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>Consumer Stapl</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>Household Products</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G13" s="11" t="n">
-        <v>61335440</v>
+        <v>176456608</v>
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
@@ -1098,7 +1096,7 @@
         </is>
       </c>
       <c r="L13" s="14" t="n">
-        <v>36.21397352003996</v>
+        <v>664.1859510299552</v>
       </c>
       <c r="M13" s="15" t="inlineStr">
         <is>
@@ -1110,19 +1108,19 @@
           <t>–</t>
         </is>
       </c>
-      <c r="O13" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="O13" s="14" t="n">
+        <v>41.02353725449977</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>-16.30325301502349</v>
-      </c>
-      <c r="Q13" s="13" t="n">
-        <v>0.42920363</v>
+        <v>14.07767730337079</v>
+      </c>
+      <c r="Q13" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="R13" s="14" t="n">
-        <v>0.03494303267047</v>
+        <v>43.41950981183043</v>
       </c>
     </row>
     <row r="14">
@@ -1131,12 +1129,12 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>SOHU</t>
+          <t>MOMO</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Sohu.Com Limited</t>
+          <t>Hello Group Inc.</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -1155,7 +1153,7 @@
         </is>
       </c>
       <c r="G14" s="11" t="n">
-        <v>407085504</v>
+        <v>723205632</v>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
@@ -1173,8 +1171,10 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L14" s="14" t="n">
-        <v>105.7831821002401</v>
+      <c r="L14" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M14" s="15" t="inlineStr">
         <is>
@@ -1191,16 +1191,14 @@
           <t>–</t>
         </is>
       </c>
-      <c r="P14" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P14" s="13" t="n">
+        <v>-2.728782876763296</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.2684324</v>
+        <v>0.46039647</v>
       </c>
       <c r="R14" s="14" t="n">
-        <v>-1.49828078875518</v>
+        <v>20.94380126436537</v>
       </c>
     </row>
     <row r="15">
@@ -1209,31 +1207,31 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>MGP1.SG</t>
+          <t>XRX</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Marfrig Global Foods S.A.</t>
+          <t>Xerox Holdings Corporation</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>Consumer Stapl</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>Food &amp; Staples Retaili</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G15" s="11" t="n">
-        <v>4373527361.245239</v>
+        <v>450408800</v>
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
@@ -1251,34 +1249,28 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L15" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L15" s="14" t="n">
+        <v>429.1656823756551</v>
       </c>
       <c r="M15" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N15" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O15" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N15" s="14" t="n">
+        <v>10.2129443296845</v>
+      </c>
+      <c r="O15" s="14" t="n">
+        <v>8.487610367416689</v>
       </c>
       <c r="P15" s="13" t="n">
-        <v>-3.937537876354913</v>
+        <v>8.554</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>1.9623438</v>
+        <v>1.3937424</v>
       </c>
       <c r="R15" s="14" t="n">
-        <v>21.13548885797807</v>
+        <v>37.65473555194727</v>
       </c>
     </row>
     <row r="16">
@@ -1287,12 +1279,12 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>005710.KQ</t>
+          <t>036030.KQ</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Daewon Sanup Co., Ltd</t>
+          <t>KT Hitel Corporation., Limited</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -1302,7 +1294,7 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
@@ -1311,7 +1303,7 @@
         </is>
       </c>
       <c r="G16" s="11" t="n">
-        <v>138531094.1027808</v>
+        <v>150050732.0442173</v>
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
@@ -1350,13 +1342,13 @@
         </is>
       </c>
       <c r="P16" s="13" t="n">
-        <v>-3.801</v>
+        <v>-615.858919062507</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0.3695059829823844</v>
+        <v>0.7595988387147542</v>
       </c>
       <c r="R16" s="14" t="n">
-        <v>30.46226708553826</v>
+        <v>19.5455356272729</v>
       </c>
     </row>
     <row r="17">
@@ -1443,31 +1435,31 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>2355.HK</t>
+          <t>032190.KQ</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Baoye Group Company Limited</t>
+          <t>Daou Data Corp.</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>Construction &amp; Enginee</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="G18" s="11" t="n">
-        <v>195982093.9629554</v>
+        <v>512293310.7061763</v>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
@@ -1506,13 +1498,15 @@
         </is>
       </c>
       <c r="P18" s="13" t="n">
-        <v>-4.899369514150129</v>
+        <v>-11.053</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.101864375</v>
-      </c>
-      <c r="R18" s="14" t="n">
-        <v>39.63325301600989</v>
+        <v>0.4656302080321993</v>
+      </c>
+      <c r="R18" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1521,31 +1515,31 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>GDHG</t>
+          <t>214180.KQ</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Golden Heaven Group Holdings L</t>
+          <t>Minwise Co., Ltd</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hotels, Restaurants &amp; </t>
+          <t>nan</t>
         </is>
       </c>
       <c r="G19" s="11" t="n">
-        <v>69901808</v>
+        <v>118767246.4195844</v>
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
@@ -1563,8 +1557,10 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L19" s="14" t="n">
-        <v>4.844947644272663</v>
+      <c r="L19" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M19" s="15" t="inlineStr">
         <is>
@@ -1582,13 +1578,13 @@
         </is>
       </c>
       <c r="P19" s="13" t="n">
-        <v>-76.425</v>
+        <v>-0.323</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.3869456205617164</v>
+        <v>0.9486322725013556</v>
       </c>
       <c r="R19" s="14" t="n">
-        <v>5.41869452105689</v>
+        <v>37.04623266917117</v>
       </c>
     </row>
     <row r="20">
@@ -1597,12 +1593,12 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>MOMO</t>
+          <t>FBIO</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Hello Group Inc.</t>
+          <t>Fortress Biotech, Inc.</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
@@ -1612,16 +1608,16 @@
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>Diversified Telecommun</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G20" s="11" t="n">
-        <v>723205632</v>
+        <v>85712048</v>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
@@ -1639,34 +1635,34 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L20" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L20" s="14" t="n">
+        <v>343.1034572875916</v>
       </c>
       <c r="M20" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N20" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N20" s="14" t="n">
+        <v>1.220365193000639</v>
       </c>
       <c r="O20" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="P20" s="13" t="n">
-        <v>-2.728782876763296</v>
+      <c r="P20" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.46039647</v>
-      </c>
-      <c r="R20" s="14" t="n">
-        <v>20.94380126436537</v>
+        <v>0.52161556</v>
+      </c>
+      <c r="R20" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1675,12 +1671,12 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>SOGP</t>
+          <t>SOHU</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Sound Group Inc.</t>
+          <t>Sohu.Com Limited</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
@@ -1699,7 +1695,7 @@
         </is>
       </c>
       <c r="G21" s="11" t="n">
-        <v>50852788</v>
+        <v>407085504</v>
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
@@ -1717,10 +1713,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L21" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L21" s="14" t="n">
+        <v>105.7831821002401</v>
       </c>
       <c r="M21" s="15" t="inlineStr">
         <is>
@@ -1737,14 +1731,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="P21" s="13" t="n">
-        <v>-1.272959469710062</v>
+      <c r="P21" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.85055774</v>
+        <v>0.2684324</v>
       </c>
       <c r="R21" s="14" t="n">
-        <v>0.25686856401089</v>
+        <v>-1.49828078875518</v>
       </c>
     </row>
     <row r="22">
@@ -1753,12 +1749,12 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>042420.KQ</t>
+          <t>081000.KS</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Z Holdings Corporation</t>
+          <t>Iljin Diamond Co. Ltd.</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
@@ -1768,16 +1764,16 @@
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>Internet &amp; Direct Mark</t>
+          <t>Building Products</t>
         </is>
       </c>
       <c r="G22" s="11" t="n">
-        <v>96779704.39330758</v>
+        <v>92123282.75923637</v>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
@@ -1816,13 +1812,13 @@
         </is>
       </c>
       <c r="P22" s="13" t="n">
-        <v>3.135</v>
+        <v>-3.399252068290597</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.3895122570757942</v>
+        <v>0.3975017324830632</v>
       </c>
       <c r="R22" s="14" t="n">
-        <v>41.66640904663798</v>
+        <v>-11.56907985022138</v>
       </c>
     </row>
     <row r="23">
@@ -1831,31 +1827,31 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>036030.KQ</t>
+          <t>2355.HK</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>KT Hitel Corporation., Limited</t>
+          <t>Baoye Group Company Limited</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Construction &amp; Enginee</t>
         </is>
       </c>
       <c r="G23" s="11" t="n">
-        <v>150050732.0442173</v>
+        <v>195982093.9629554</v>
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
@@ -1894,13 +1890,13 @@
         </is>
       </c>
       <c r="P23" s="13" t="n">
-        <v>-615.858919062507</v>
+        <v>-4.899369514150129</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.7595988387147542</v>
+        <v>0.101864375</v>
       </c>
       <c r="R23" s="14" t="n">
-        <v>19.5455356272729</v>
+        <v>39.63325301600989</v>
       </c>
     </row>
     <row r="24">
@@ -1909,31 +1905,31 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>FBIO</t>
+          <t>MGP1.SG</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Fortress Biotech, Inc.</t>
+          <t>Marfrig Global Foods S.A.</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Stapl</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Food &amp; Staples Retaili</t>
         </is>
       </c>
       <c r="G24" s="11" t="n">
-        <v>85712048</v>
+        <v>4373527361.245239</v>
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
@@ -1951,34 +1947,34 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L24" s="14" t="n">
-        <v>343.1034572875916</v>
+      <c r="L24" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M24" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N24" s="14" t="n">
-        <v>1.220365193000639</v>
+      <c r="N24" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O24" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="P24" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P24" s="13" t="n">
+        <v>-3.937537876354913</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.52161556</v>
-      </c>
-      <c r="R24" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.9623438</v>
+      </c>
+      <c r="R24" s="14" t="n">
+        <v>21.13548885797807</v>
       </c>
     </row>
     <row r="25">
@@ -1987,31 +1983,31 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>214180.KQ</t>
+          <t>IH</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Minwise Co., Ltd</t>
+          <t>Ihuman Inc.</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Consumer Stapl</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Household Products</t>
         </is>
       </c>
       <c r="G25" s="11" t="n">
-        <v>118767246.4195844</v>
+        <v>61335440</v>
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
@@ -2029,10 +2025,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L25" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L25" s="14" t="n">
+        <v>36.21397352003996</v>
       </c>
       <c r="M25" s="15" t="inlineStr">
         <is>
@@ -2050,13 +2044,13 @@
         </is>
       </c>
       <c r="P25" s="13" t="n">
-        <v>-0.323</v>
+        <v>-16.30325301502349</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0.9486322725013556</v>
+        <v>0.42920363</v>
       </c>
       <c r="R25" s="14" t="n">
-        <v>37.04623266917117</v>
+        <v>0.03494303267047</v>
       </c>
     </row>
     <row r="26">
@@ -2065,31 +2059,31 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>CCL.AX</t>
+          <t>SOGP</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Coca-Cola Amatil Limited</t>
+          <t>Sound Group Inc.</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>Consumer Stapl</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Diversified Telecommun</t>
         </is>
       </c>
       <c r="G26" s="11" t="n">
-        <v>757397297.131691</v>
+        <v>50852788</v>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
@@ -2128,13 +2122,13 @@
         </is>
       </c>
       <c r="P26" s="13" t="n">
-        <v>-8.710000000000001</v>
+        <v>-1.272959469710062</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>2.487333</v>
+        <v>0.85055774</v>
       </c>
       <c r="R26" s="14" t="n">
-        <v>41.63159677303595</v>
+        <v>0.25686856401089</v>
       </c>
     </row>
     <row r="27">
@@ -2143,31 +2137,31 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>032190.KQ</t>
+          <t>3700.HK</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Daou Data Corp.</t>
+          <t>Inke Limited</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Diversified Telecommun</t>
         </is>
       </c>
       <c r="G27" s="11" t="n">
-        <v>512293310.7061763</v>
+        <v>241787776.6746577</v>
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
@@ -2205,16 +2199,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="P27" s="13" t="n">
-        <v>-11.053</v>
+      <c r="P27" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0.4656302080321993</v>
-      </c>
-      <c r="R27" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.28567517</v>
+      </c>
+      <c r="R27" s="14" t="n">
+        <v>-32.71958452610624</v>
       </c>
     </row>
     <row r="28">
@@ -2223,12 +2217,12 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>081000.KS</t>
+          <t>023590.KS</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Iljin Diamond Co. Ltd.</t>
+          <t>Daou Technology Inc.</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
@@ -2238,16 +2232,16 @@
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>Building Products</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G28" s="11" t="n">
-        <v>92123282.75923637</v>
+        <v>1148709798.626002</v>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
@@ -2286,13 +2280,15 @@
         </is>
       </c>
       <c r="P28" s="13" t="n">
-        <v>-3.399252068290597</v>
+        <v>-12.852</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0.3975017324830632</v>
-      </c>
-      <c r="R28" s="14" t="n">
-        <v>-11.56907985022138</v>
+        <v>0.4782027784698607</v>
+      </c>
+      <c r="R28" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -2301,31 +2297,31 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>XRX</t>
+          <t>3348.HK</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Xerox Holdings Corporation</t>
+          <t>China PengFei Group Limited</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Machinery</t>
         </is>
       </c>
       <c r="G29" s="11" t="n">
-        <v>450408800</v>
+        <v>86771221.75693507</v>
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
@@ -2333,38 +2329,44 @@
         </is>
       </c>
       <c r="I29" s="13" t="n">
-        <v>3</v>
+        <v>2.9872</v>
       </c>
       <c r="J29" s="14" t="n">
-        <v>200</v>
+        <v>199.15</v>
       </c>
       <c r="K29" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L29" s="14" t="n">
-        <v>429.1656823756551</v>
+      <c r="L29" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M29" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N29" s="14" t="n">
-        <v>10.2129443296845</v>
-      </c>
-      <c r="O29" s="14" t="n">
-        <v>8.487610367416689</v>
+      <c r="N29" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O29" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="P29" s="13" t="n">
-        <v>8.554</v>
+        <v>-4.705337784371387</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>1.3937424</v>
+        <v>0.56547403</v>
       </c>
       <c r="R29" s="14" t="n">
-        <v>37.65473555194727</v>
+        <v>22.38999653955031</v>
       </c>
     </row>
     <row r="30">
@@ -2373,12 +2375,12 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>3348.HK</t>
+          <t>3983.HK</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>China PengFei Group Limited</t>
+          <t>China Bluechemical Ltd.</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
@@ -2388,16 +2390,16 @@
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>Machinery</t>
+          <t>Construction Materials</t>
         </is>
       </c>
       <c r="G30" s="11" t="n">
-        <v>86771221.75693507</v>
+        <v>1161809182.068069</v>
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
@@ -2405,10 +2407,10 @@
         </is>
       </c>
       <c r="I30" s="13" t="n">
-        <v>2.9872</v>
+        <v>2.9631</v>
       </c>
       <c r="J30" s="14" t="n">
-        <v>199.15</v>
+        <v>197.54</v>
       </c>
       <c r="K30" s="15" t="inlineStr">
         <is>
@@ -2436,13 +2438,13 @@
         </is>
       </c>
       <c r="P30" s="13" t="n">
-        <v>-4.705337784371387</v>
+        <v>-4.723304615477501</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>0.56547403</v>
+        <v>0.4139531</v>
       </c>
       <c r="R30" s="14" t="n">
-        <v>22.38999653955031</v>
+        <v>16.48902767594668</v>
       </c>
     </row>
     <row r="31">
@@ -2451,12 +2453,12 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>3983.HK</t>
+          <t>1786.HK</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>China Bluechemical Ltd.</t>
+          <t>CRCC High-Tech Equipment Corpo</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
@@ -2466,16 +2468,16 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Machinery</t>
         </is>
       </c>
       <c r="G31" s="11" t="n">
-        <v>1161809182.068069</v>
+        <v>137700514.4040183</v>
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
@@ -2483,10 +2485,10 @@
         </is>
       </c>
       <c r="I31" s="13" t="n">
-        <v>2.9631</v>
+        <v>2.936</v>
       </c>
       <c r="J31" s="14" t="n">
-        <v>197.54</v>
+        <v>195.73</v>
       </c>
       <c r="K31" s="15" t="inlineStr">
         <is>
@@ -2514,13 +2516,13 @@
         </is>
       </c>
       <c r="P31" s="13" t="n">
-        <v>-4.723304615477501</v>
+        <v>-3.301667715802051</v>
       </c>
       <c r="Q31" s="13" t="n">
-        <v>0.4139531</v>
+        <v>0.14562407</v>
       </c>
       <c r="R31" s="14" t="n">
-        <v>16.48902767594668</v>
+        <v>2.61472718142236</v>
       </c>
     </row>
     <row r="32">
@@ -2529,31 +2531,31 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>1786.HK</t>
+          <t>LKFT</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>CRCC High-Tech Equipment Corpo</t>
+          <t>Lakefront Biotherapeutics Amer</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>Machinery</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="G32" s="11" t="n">
-        <v>137700514.4040183</v>
+        <v>1758263424</v>
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
@@ -2561,10 +2563,10 @@
         </is>
       </c>
       <c r="I32" s="13" t="n">
-        <v>2.936</v>
+        <v>2.9274</v>
       </c>
       <c r="J32" s="14" t="n">
-        <v>195.73</v>
+        <v>195.16</v>
       </c>
       <c r="K32" s="15" t="inlineStr">
         <is>
@@ -2592,13 +2594,13 @@
         </is>
       </c>
       <c r="P32" s="13" t="n">
-        <v>-3.301667715802051</v>
+        <v>-1.913960800643914</v>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>0.14562407</v>
+        <v>9.299113</v>
       </c>
       <c r="R32" s="14" t="n">
-        <v>2.61472718142236</v>
+        <v>-16.63386108701237</v>
       </c>
     </row>
     <row r="33">
@@ -2607,31 +2609,31 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>226320.KS</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Lakefront Biotherapeutics Amer</t>
+          <t>It'S Hanbul Co., Ltd.</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Consumer Stapl</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Household Products</t>
         </is>
       </c>
       <c r="G33" s="11" t="n">
-        <v>1758263424</v>
+        <v>119950341.1843873</v>
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
@@ -2639,10 +2641,10 @@
         </is>
       </c>
       <c r="I33" s="13" t="n">
-        <v>2.9274</v>
+        <v>2.8872</v>
       </c>
       <c r="J33" s="14" t="n">
-        <v>195.16</v>
+        <v>192.48</v>
       </c>
       <c r="K33" s="15" t="inlineStr">
         <is>
@@ -2670,13 +2672,13 @@
         </is>
       </c>
       <c r="P33" s="13" t="n">
-        <v>-1.913960800643914</v>
+        <v>-2.358</v>
       </c>
       <c r="Q33" s="13" t="n">
-        <v>9.299113</v>
+        <v>0.4867003249801732</v>
       </c>
       <c r="R33" s="14" t="n">
-        <v>-16.63386108701237</v>
+        <v>8.273822214057889</v>
       </c>
     </row>
     <row r="34">
@@ -2685,31 +2687,31 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>226320.KS</t>
+          <t>LAB</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>It'S Hanbul Co., Ltd.</t>
+          <t xml:space="preserve">Standard BioTools Inc. Common </t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>Consumer Stapl</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>Household Products</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G34" s="11" t="n">
-        <v>119950341.1843873</v>
+        <v>270879392</v>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
@@ -2717,20 +2719,18 @@
         </is>
       </c>
       <c r="I34" s="13" t="n">
-        <v>2.8872</v>
+        <v>2.8569</v>
       </c>
       <c r="J34" s="14" t="n">
-        <v>192.48</v>
+        <v>190.46</v>
       </c>
       <c r="K34" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L34" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L34" s="14" t="n">
+        <v>106.8416455984957</v>
       </c>
       <c r="M34" s="15" t="inlineStr">
         <is>
@@ -2742,19 +2742,19 @@
           <t>–</t>
         </is>
       </c>
-      <c r="O34" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P34" s="13" t="n">
-        <v>-2.358</v>
+      <c r="O34" s="14" t="n">
+        <v>16.15047590270434</v>
+      </c>
+      <c r="P34" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>0.4867003249801732</v>
+        <v>0.50108933</v>
       </c>
       <c r="R34" s="14" t="n">
-        <v>8.273822214057889</v>
+        <v>-32.50904453448516</v>
       </c>
     </row>
     <row r="35">
@@ -2763,31 +2763,31 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>1075.HK</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Standard BioTools Inc. Common </t>
+          <t>Capinfo Company Limited</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G35" s="11" t="n">
-        <v>270879392</v>
+        <v>63422331.40438554</v>
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
@@ -2795,18 +2795,20 @@
         </is>
       </c>
       <c r="I35" s="13" t="n">
-        <v>2.8569</v>
+        <v>2.8346</v>
       </c>
       <c r="J35" s="14" t="n">
-        <v>190.46</v>
+        <v>188.97</v>
       </c>
       <c r="K35" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L35" s="14" t="n">
-        <v>106.8416455984957</v>
+      <c r="L35" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M35" s="15" t="inlineStr">
         <is>
@@ -2818,19 +2820,19 @@
           <t>–</t>
         </is>
       </c>
-      <c r="O35" s="14" t="n">
-        <v>16.15047590270434</v>
-      </c>
-      <c r="P35" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="O35" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P35" s="13" t="n">
+        <v>-3.644595643513037</v>
       </c>
       <c r="Q35" s="13" t="n">
-        <v>0.50108933</v>
+        <v>0.36235</v>
       </c>
       <c r="R35" s="14" t="n">
-        <v>-32.50904453448516</v>
+        <v>74.56133863205552</v>
       </c>
     </row>
     <row r="36">
@@ -2839,12 +2841,12 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>1075.HK</t>
+          <t>2877.HK</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Capinfo Company Limited</t>
+          <t xml:space="preserve">China Shineway Pharmaceutical </t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
@@ -2854,16 +2856,16 @@
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G36" s="11" t="n">
-        <v>63422331.40438554</v>
+        <v>766321290.3686138</v>
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
@@ -2871,10 +2873,10 @@
         </is>
       </c>
       <c r="I36" s="13" t="n">
-        <v>2.8346</v>
+        <v>2.8092</v>
       </c>
       <c r="J36" s="14" t="n">
-        <v>188.97</v>
+        <v>187.28</v>
       </c>
       <c r="K36" s="15" t="inlineStr">
         <is>
@@ -2902,13 +2904,13 @@
         </is>
       </c>
       <c r="P36" s="13" t="n">
-        <v>-3.644595643513037</v>
+        <v>-4.560352717033771</v>
       </c>
       <c r="Q36" s="13" t="n">
-        <v>0.36235</v>
+        <v>0.63750666</v>
       </c>
       <c r="R36" s="14" t="n">
-        <v>74.56133863205552</v>
+        <v>21.53375486044041</v>
       </c>
     </row>
     <row r="37">
@@ -2917,12 +2919,12 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>2877.HK</t>
+          <t>2348.HK</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">China Shineway Pharmaceutical </t>
+          <t>Dawnrays Pharmaceutical (Holdi</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
@@ -2941,7 +2943,7 @@
         </is>
       </c>
       <c r="G37" s="11" t="n">
-        <v>766321290.3686138</v>
+        <v>190876303.7740096</v>
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
@@ -2949,10 +2951,10 @@
         </is>
       </c>
       <c r="I37" s="13" t="n">
-        <v>2.8092</v>
+        <v>2.8059</v>
       </c>
       <c r="J37" s="14" t="n">
-        <v>187.28</v>
+        <v>187.06</v>
       </c>
       <c r="K37" s="15" t="inlineStr">
         <is>
@@ -2980,13 +2982,13 @@
         </is>
       </c>
       <c r="P37" s="13" t="n">
-        <v>-4.560352717033771</v>
+        <v>-2.262957359369161</v>
       </c>
       <c r="Q37" s="13" t="n">
-        <v>0.63750666</v>
+        <v>0.37324485</v>
       </c>
       <c r="R37" s="14" t="n">
-        <v>21.53375486044041</v>
+        <v>21.16964636477932</v>
       </c>
     </row>
     <row r="38">
@@ -2995,31 +2997,31 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>2348.HK</t>
+          <t>MAPS</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Dawnrays Pharmaceutical (Holdi</t>
+          <t>WM Technology Inc. Class A Com</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G38" s="11" t="n">
-        <v>190876303.7740096</v>
+        <v>62173400</v>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
@@ -3027,20 +3029,18 @@
         </is>
       </c>
       <c r="I38" s="13" t="n">
-        <v>2.8059</v>
+        <v>2.7458</v>
       </c>
       <c r="J38" s="14" t="n">
-        <v>187.06</v>
+        <v>183.05</v>
       </c>
       <c r="K38" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L38" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L38" s="14" t="n">
+        <v>299.0072925077284</v>
       </c>
       <c r="M38" s="15" t="inlineStr">
         <is>
@@ -3058,13 +3058,13 @@
         </is>
       </c>
       <c r="P38" s="13" t="n">
-        <v>-2.262957359369161</v>
+        <v>6.91978925548454</v>
       </c>
       <c r="Q38" s="13" t="n">
-        <v>0.37324485</v>
+        <v>0.9897228545503748</v>
       </c>
       <c r="R38" s="14" t="n">
-        <v>21.16964636477932</v>
+        <v>4.71491443732356</v>
       </c>
     </row>
     <row r="39">
@@ -3073,31 +3073,31 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>MAPS</t>
+          <t>CTT.LS</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>WM Technology Inc. Class A Com</t>
+          <t>CTT - Correios de Portugal SA</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Air Freight &amp; Logistic</t>
         </is>
       </c>
       <c r="G39" s="11" t="n">
-        <v>62173400</v>
+        <v>955064808.3495485</v>
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
@@ -3105,18 +3105,20 @@
         </is>
       </c>
       <c r="I39" s="13" t="n">
-        <v>2.7458</v>
+        <v>2.735</v>
       </c>
       <c r="J39" s="14" t="n">
-        <v>183.05</v>
+        <v>182.33</v>
       </c>
       <c r="K39" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L39" s="14" t="n">
-        <v>299.0072925077284</v>
+      <c r="L39" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M39" s="15" t="inlineStr">
         <is>
@@ -3134,13 +3136,13 @@
         </is>
       </c>
       <c r="P39" s="13" t="n">
-        <v>6.91978925548454</v>
+        <v>-6.721</v>
       </c>
       <c r="Q39" s="13" t="n">
-        <v>0.9897228545503748</v>
+        <v>2.673729</v>
       </c>
       <c r="R39" s="14" t="n">
-        <v>4.71491443732356</v>
+        <v>33.75258674992358</v>
       </c>
     </row>
     <row r="40">
@@ -3149,31 +3151,31 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>CTT.LS</t>
+          <t>003240.KS</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>CTT - Correios de Portugal SA</t>
+          <t>Taekwang Industrial Co., Ltd.</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>Air Freight &amp; Logistic</t>
+          <t xml:space="preserve">Oil, Gas &amp; Consumable </t>
         </is>
       </c>
       <c r="G40" s="11" t="n">
-        <v>955064808.3495485</v>
+        <v>499843622.960411</v>
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
@@ -3181,10 +3183,10 @@
         </is>
       </c>
       <c r="I40" s="13" t="n">
-        <v>2.735</v>
+        <v>2.72</v>
       </c>
       <c r="J40" s="14" t="n">
-        <v>182.33</v>
+        <v>181.33</v>
       </c>
       <c r="K40" s="15" t="inlineStr">
         <is>
@@ -3211,14 +3213,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="P40" s="13" t="n">
-        <v>-6.721</v>
+      <c r="P40" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q40" s="13" t="n">
-        <v>2.673729</v>
+        <v>0.2072827046246781</v>
       </c>
       <c r="R40" s="14" t="n">
-        <v>33.75258674992358</v>
+        <v>-53.84157050148208</v>
       </c>
     </row>
     <row r="41">
@@ -3227,12 +3231,12 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>003240.KS</t>
+          <t>092230.KS</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Taekwang Industrial Co., Ltd.</t>
+          <t>KPX Holdings Co.,Ltd.</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
@@ -3242,16 +3246,16 @@
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oil, Gas &amp; Consumable </t>
+          <t>Industrial Conglomerat</t>
         </is>
       </c>
       <c r="G41" s="11" t="n">
-        <v>499843622.960411</v>
+        <v>252340682.5422591</v>
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
@@ -3259,10 +3263,10 @@
         </is>
       </c>
       <c r="I41" s="13" t="n">
-        <v>2.72</v>
+        <v>2.7179</v>
       </c>
       <c r="J41" s="14" t="n">
-        <v>181.33</v>
+        <v>181.19</v>
       </c>
       <c r="K41" s="15" t="inlineStr">
         <is>
@@ -3289,16 +3293,14 @@
           <t>–</t>
         </is>
       </c>
-      <c r="P41" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P41" s="13" t="n">
+        <v>3.335</v>
       </c>
       <c r="Q41" s="13" t="n">
-        <v>0.2072827046246781</v>
+        <v>0.2935025148444605</v>
       </c>
       <c r="R41" s="14" t="n">
-        <v>-53.84157050148208</v>
+        <v>-23.09652103056119</v>
       </c>
     </row>
     <row r="42">
@@ -3307,31 +3309,31 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>092230.KS</t>
+          <t>0420.HK</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>KPX Holdings Co.,Ltd.</t>
+          <t>Fountain Set (Holdings) Limite</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>Industrial Conglomerat</t>
+          <t>Textiles, Apparel &amp; Lu</t>
         </is>
       </c>
       <c r="G42" s="11" t="n">
-        <v>252340682.5422591</v>
+        <v>102389102.5023126</v>
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
@@ -3339,10 +3341,10 @@
         </is>
       </c>
       <c r="I42" s="13" t="n">
-        <v>2.7179</v>
+        <v>2.7129</v>
       </c>
       <c r="J42" s="14" t="n">
-        <v>181.19</v>
+        <v>180.86</v>
       </c>
       <c r="K42" s="15" t="inlineStr">
         <is>
@@ -3370,13 +3372,13 @@
         </is>
       </c>
       <c r="P42" s="13" t="n">
-        <v>3.335</v>
+        <v>-1.252</v>
       </c>
       <c r="Q42" s="13" t="n">
-        <v>0.2935025148444605</v>
+        <v>0.24605559</v>
       </c>
       <c r="R42" s="14" t="n">
-        <v>-23.09652103056119</v>
+        <v>29.46091108514986</v>
       </c>
     </row>
     <row r="43">
@@ -3385,17 +3387,17 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>0420.HK</t>
+          <t>9726.T</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Fountain Set (Holdings) Limite</t>
+          <t>KNT-CT Holdings Co., Ltd.</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
@@ -3405,11 +3407,11 @@
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>Textiles, Apparel &amp; Lu</t>
+          <t xml:space="preserve">Hotels, Restaurants &amp; </t>
         </is>
       </c>
       <c r="G43" s="11" t="n">
-        <v>102389102.5023126</v>
+        <v>319008390.1582418</v>
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
@@ -3417,10 +3419,10 @@
         </is>
       </c>
       <c r="I43" s="13" t="n">
-        <v>2.7129</v>
+        <v>2.7099</v>
       </c>
       <c r="J43" s="14" t="n">
-        <v>180.86</v>
+        <v>180.66</v>
       </c>
       <c r="K43" s="15" t="inlineStr">
         <is>
@@ -3448,13 +3450,13 @@
         </is>
       </c>
       <c r="P43" s="13" t="n">
-        <v>-1.252</v>
+        <v>-2.993</v>
       </c>
       <c r="Q43" s="13" t="n">
-        <v>0.24605559</v>
+        <v>1.4868548</v>
       </c>
       <c r="R43" s="14" t="n">
-        <v>29.46091108514986</v>
+        <v>13.80142515922356</v>
       </c>
     </row>
     <row r="44">
@@ -3463,31 +3465,31 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>9726.T</t>
+          <t>GRR.AX</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>KNT-CT Holdings Co., Ltd.</t>
+          <t>Grange Resources Ltd.</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hotels, Restaurants &amp; </t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="G44" s="11" t="n">
-        <v>319008390.1582418</v>
+        <v>105611425.0404425</v>
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
@@ -3495,10 +3497,10 @@
         </is>
       </c>
       <c r="I44" s="13" t="n">
-        <v>2.7099</v>
+        <v>2.7096</v>
       </c>
       <c r="J44" s="14" t="n">
-        <v>180.66</v>
+        <v>180.64</v>
       </c>
       <c r="K44" s="15" t="inlineStr">
         <is>
@@ -3526,13 +3528,13 @@
         </is>
       </c>
       <c r="P44" s="13" t="n">
-        <v>-2.993</v>
+        <v>-1.02</v>
       </c>
       <c r="Q44" s="13" t="n">
-        <v>1.4868548</v>
+        <v>0.13569936</v>
       </c>
       <c r="R44" s="14" t="n">
-        <v>13.80142515922356</v>
+        <v>25.15386227734993</v>
       </c>
     </row>
     <row r="45">
@@ -3541,31 +3543,31 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>GRR.AX</t>
+          <t>ELOX</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Grange Resources Ltd.</t>
+          <t>Eloxx Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G45" s="11" t="n">
-        <v>105611425.0404425</v>
+        <v>54121944</v>
       </c>
       <c r="H45" s="12" t="inlineStr">
         <is>
@@ -3573,20 +3575,18 @@
         </is>
       </c>
       <c r="I45" s="13" t="n">
-        <v>2.7096</v>
+        <v>2.7009</v>
       </c>
       <c r="J45" s="14" t="n">
-        <v>180.64</v>
+        <v>180.06</v>
       </c>
       <c r="K45" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L45" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L45" s="14" t="n">
+        <v>174.871767355585</v>
       </c>
       <c r="M45" s="15" t="inlineStr">
         <is>
@@ -3603,14 +3603,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="P45" s="13" t="n">
-        <v>-1.02</v>
+      <c r="P45" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q45" s="13" t="n">
-        <v>0.13569936</v>
+        <v>1.3695652</v>
       </c>
       <c r="R45" s="14" t="n">
-        <v>25.15386227734993</v>
+        <v>-40.03902475970765</v>
       </c>
     </row>
     <row r="46">
@@ -3619,12 +3621,12 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>ELOX</t>
+          <t>SEAT</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Eloxx Pharmaceuticals, Inc.</t>
+          <t>Vivid Seats Inc. Class A Commo</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
@@ -3634,16 +3636,16 @@
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t xml:space="preserve">Electronic Equipment, </t>
         </is>
       </c>
       <c r="G46" s="11" t="n">
-        <v>54121944</v>
+        <v>55643912</v>
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
@@ -3651,10 +3653,10 @@
         </is>
       </c>
       <c r="I46" s="13" t="n">
-        <v>2.7009</v>
+        <v>2.6998</v>
       </c>
       <c r="J46" s="14" t="n">
-        <v>180.06</v>
+        <v>179.99</v>
       </c>
       <c r="K46" s="15" t="inlineStr">
         <is>
@@ -3662,7 +3664,7 @@
         </is>
       </c>
       <c r="L46" s="14" t="n">
-        <v>174.871767355585</v>
+        <v>359.9890676270209</v>
       </c>
       <c r="M46" s="15" t="inlineStr">
         <is>
@@ -3684,11 +3686,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q46" s="13" t="n">
-        <v>1.3695652</v>
+      <c r="Q46" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="R46" s="14" t="n">
-        <v>-40.03902475970765</v>
+        <v>10.10651828310898</v>
       </c>
     </row>
     <row r="47">
@@ -3697,12 +3701,12 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>SEAT</t>
+          <t>SNEX</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Vivid Seats Inc. Class A Commo</t>
+          <t>Stonex Group Inc.</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
@@ -3712,16 +3716,16 @@
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electronic Equipment, </t>
+          <t>nan</t>
         </is>
       </c>
       <c r="G47" s="11" t="n">
-        <v>55643912</v>
+        <v>8487799808</v>
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
@@ -3729,18 +3733,16 @@
         </is>
       </c>
       <c r="I47" s="13" t="n">
-        <v>2.6998</v>
+        <v>2.6523</v>
       </c>
       <c r="J47" s="14" t="n">
-        <v>179.99</v>
-      </c>
-      <c r="K47" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>176.82</v>
+      </c>
+      <c r="K47" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="L47" s="14" t="n">
-        <v>359.9890676270209</v>
+        <v>0.2179599003096563</v>
       </c>
       <c r="M47" s="15" t="inlineStr">
         <is>
@@ -3757,18 +3759,14 @@
           <t>–</t>
         </is>
       </c>
-      <c r="P47" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q47" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P47" s="13" t="n">
+        <v>-132.336558243513</v>
+      </c>
+      <c r="Q47" s="13" t="n">
+        <v>2.969073</v>
       </c>
       <c r="R47" s="14" t="n">
-        <v>10.10651828310898</v>
+        <v>45.17405957249845</v>
       </c>
     </row>
     <row r="48">
@@ -3777,31 +3775,31 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>SNEX</t>
+          <t>200625.SZ</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Stonex Group Inc.</t>
+          <t>Chongqing Changan Automobile C</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Automobiles</t>
         </is>
       </c>
       <c r="G48" s="11" t="n">
-        <v>8487799808</v>
+        <v>4136333262.592009</v>
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
@@ -3809,16 +3807,20 @@
         </is>
       </c>
       <c r="I48" s="13" t="n">
-        <v>2.6523</v>
+        <v>2.638</v>
       </c>
       <c r="J48" s="14" t="n">
-        <v>176.82</v>
-      </c>
-      <c r="K48" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="14" t="n">
-        <v>0.2179599003096563</v>
+        <v>175.87</v>
+      </c>
+      <c r="K48" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L48" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M48" s="15" t="inlineStr">
         <is>
@@ -3836,13 +3838,13 @@
         </is>
       </c>
       <c r="P48" s="13" t="n">
-        <v>-132.336558243513</v>
+        <v>-2.983771360959555</v>
       </c>
       <c r="Q48" s="13" t="n">
-        <v>2.969073</v>
+        <v>0.364986</v>
       </c>
       <c r="R48" s="14" t="n">
-        <v>45.17405957249845</v>
+        <v>-20.12284630158316</v>
       </c>
     </row>
     <row r="49">
@@ -3851,17 +3853,17 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>200625.SZ</t>
+          <t>TOUR</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Chongqing Changan Automobile C</t>
+          <t>Tuniu Corp</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
@@ -3871,11 +3873,11 @@
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t xml:space="preserve">Hotels, Restaurants &amp; </t>
         </is>
       </c>
       <c r="G49" s="11" t="n">
-        <v>4136333262.592009</v>
+        <v>55513800</v>
       </c>
       <c r="H49" s="12" t="inlineStr">
         <is>
@@ -3883,30 +3885,26 @@
         </is>
       </c>
       <c r="I49" s="13" t="n">
-        <v>2.638</v>
+        <v>2.6048</v>
       </c>
       <c r="J49" s="14" t="n">
-        <v>175.87</v>
+        <v>260.48</v>
       </c>
       <c r="K49" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L49" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L49" s="14" t="n">
+        <v>120.9519074536421</v>
       </c>
       <c r="M49" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N49" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N49" s="14" t="n">
+        <v>13.54978401766768</v>
       </c>
       <c r="O49" s="15" t="inlineStr">
         <is>
@@ -3914,13 +3912,13 @@
         </is>
       </c>
       <c r="P49" s="13" t="n">
-        <v>-2.983771360959555</v>
+        <v>-21.30402859359938</v>
       </c>
       <c r="Q49" s="13" t="n">
-        <v>0.364986</v>
+        <v>0.3666611</v>
       </c>
       <c r="R49" s="14" t="n">
-        <v>-20.12284630158316</v>
+        <v>-0.09665532574543001</v>
       </c>
     </row>
     <row r="50">
@@ -3929,17 +3927,17 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>TOUR</t>
+          <t>009680.KS</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Tuniu Corp</t>
+          <t>Motonic Corporation</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
@@ -3949,11 +3947,11 @@
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hotels, Restaurants &amp; </t>
+          <t>Auto Components</t>
         </is>
       </c>
       <c r="G50" s="11" t="n">
-        <v>55513800</v>
+        <v>147439191.8869889</v>
       </c>
       <c r="H50" s="12" t="inlineStr">
         <is>
@@ -3961,26 +3959,30 @@
         </is>
       </c>
       <c r="I50" s="13" t="n">
-        <v>2.6048</v>
+        <v>2.5809</v>
       </c>
       <c r="J50" s="14" t="n">
-        <v>260.48</v>
+        <v>172.06</v>
       </c>
       <c r="K50" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L50" s="14" t="n">
-        <v>120.9519074536421</v>
+      <c r="L50" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M50" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N50" s="14" t="n">
-        <v>13.54978401766768</v>
+      <c r="N50" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O50" s="15" t="inlineStr">
         <is>
@@ -3988,13 +3990,13 @@
         </is>
       </c>
       <c r="P50" s="13" t="n">
-        <v>-21.30402859359938</v>
+        <v>-6.133</v>
       </c>
       <c r="Q50" s="13" t="n">
-        <v>0.3666611</v>
+        <v>0.4671964590343672</v>
       </c>
       <c r="R50" s="14" t="n">
-        <v>-0.09665532574543001</v>
+        <v>18.28184430168729</v>
       </c>
     </row>
     <row r="51">
@@ -4003,12 +4005,12 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>009680.KS</t>
+          <t>047820.KQ</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Motonic Corporation</t>
+          <t>Chorokbaem Media Co., Ltd.</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
@@ -4018,16 +4020,16 @@
       </c>
       <c r="E51" s="10" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>Auto Components</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="G51" s="11" t="n">
-        <v>147439191.8869889</v>
+        <v>50871515.65890633</v>
       </c>
       <c r="H51" s="12" t="inlineStr">
         <is>
@@ -4035,10 +4037,10 @@
         </is>
       </c>
       <c r="I51" s="13" t="n">
-        <v>2.5809</v>
+        <v>2.5545</v>
       </c>
       <c r="J51" s="14" t="n">
-        <v>172.06</v>
+        <v>170.3</v>
       </c>
       <c r="K51" s="15" t="inlineStr">
         <is>
@@ -4066,13 +4068,13 @@
         </is>
       </c>
       <c r="P51" s="13" t="n">
-        <v>-6.133</v>
+        <v>-2.707</v>
       </c>
       <c r="Q51" s="13" t="n">
-        <v>0.4671964590343672</v>
+        <v>0.4029878150146366</v>
       </c>
       <c r="R51" s="14" t="n">
-        <v>18.28184430168729</v>
+        <v>15.09050592553209</v>
       </c>
     </row>
     <row r="52">
@@ -4081,31 +4083,31 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>047820.KQ</t>
+          <t>2386.HK</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Chorokbaem Media Co., Ltd.</t>
+          <t>SINOPEC Engineering (Group) Co</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Construction &amp; Enginee</t>
         </is>
       </c>
       <c r="G52" s="11" t="n">
-        <v>50871515.65890633</v>
+        <v>3091587172.546385</v>
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
@@ -4113,10 +4115,10 @@
         </is>
       </c>
       <c r="I52" s="13" t="n">
-        <v>2.5545</v>
+        <v>2.5214</v>
       </c>
       <c r="J52" s="14" t="n">
-        <v>170.3</v>
+        <v>168.09</v>
       </c>
       <c r="K52" s="15" t="inlineStr">
         <is>
@@ -4144,13 +4146,13 @@
         </is>
       </c>
       <c r="P52" s="13" t="n">
-        <v>-2.707</v>
+        <v>-5.660627950988354</v>
       </c>
       <c r="Q52" s="13" t="n">
-        <v>0.4029878150146366</v>
+        <v>0.64989513</v>
       </c>
       <c r="R52" s="14" t="n">
-        <v>15.09050592553209</v>
+        <v>19.70145509137191</v>
       </c>
     </row>
     <row r="53">
@@ -4159,31 +4161,31 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>2386.HK</t>
+          <t>002170.KS</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>SINOPEC Engineering (Group) Co</t>
+          <t>Samyang Tongsang Co., Ltd</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>Construction &amp; Enginee</t>
+          <t>Textiles, Apparel &amp; Lu</t>
         </is>
       </c>
       <c r="G53" s="11" t="n">
-        <v>3091587172.546385</v>
+        <v>92381342.96730712</v>
       </c>
       <c r="H53" s="12" t="inlineStr">
         <is>
@@ -4191,10 +4193,10 @@
         </is>
       </c>
       <c r="I53" s="13" t="n">
-        <v>2.5214</v>
+        <v>2.5068</v>
       </c>
       <c r="J53" s="14" t="n">
-        <v>168.09</v>
+        <v>167.12</v>
       </c>
       <c r="K53" s="15" t="inlineStr">
         <is>
@@ -4222,13 +4224,13 @@
         </is>
       </c>
       <c r="P53" s="13" t="n">
-        <v>-5.660627950988354</v>
+        <v>-6.005</v>
       </c>
       <c r="Q53" s="13" t="n">
-        <v>0.64989513</v>
+        <v>0.3129317990925645</v>
       </c>
       <c r="R53" s="14" t="n">
-        <v>19.70145509137191</v>
+        <v>19.77089345517098</v>
       </c>
     </row>
     <row r="54">
@@ -4237,31 +4239,31 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>002170.KS</t>
+          <t>MYPS</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Samyang Tongsang Co., Ltd</t>
+          <t>PLAYSTUDIOS Inc.  Class A Comm</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>Textiles, Apparel &amp; Lu</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G54" s="11" t="n">
-        <v>92381342.96730712</v>
+        <v>58871488</v>
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
@@ -4269,20 +4271,18 @@
         </is>
       </c>
       <c r="I54" s="13" t="n">
-        <v>2.5068</v>
+        <v>2.5028</v>
       </c>
       <c r="J54" s="14" t="n">
-        <v>167.12</v>
+        <v>166.85</v>
       </c>
       <c r="K54" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L54" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L54" s="14" t="n">
+        <v>47.41004677850167</v>
       </c>
       <c r="M54" s="15" t="inlineStr">
         <is>
@@ -4300,13 +4300,13 @@
         </is>
       </c>
       <c r="P54" s="13" t="n">
-        <v>-6.005</v>
+        <v>-3.963</v>
       </c>
       <c r="Q54" s="13" t="n">
-        <v>0.3129317990925645</v>
+        <v>0.2966707</v>
       </c>
       <c r="R54" s="14" t="n">
-        <v>19.77089345517098</v>
+        <v>20.88112286937462</v>
       </c>
     </row>
     <row r="55">
@@ -4315,31 +4315,31 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>MYPS</t>
+          <t>002795.KS</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>PLAYSTUDIOS Inc.  Class A Comm</t>
+          <t>AMOREPACIFIC Group</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Consumer Stapl</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Household Products</t>
         </is>
       </c>
       <c r="G55" s="11" t="n">
-        <v>58871488</v>
+        <v>645767395.6312668</v>
       </c>
       <c r="H55" s="12" t="inlineStr">
         <is>
@@ -4347,18 +4347,20 @@
         </is>
       </c>
       <c r="I55" s="13" t="n">
-        <v>2.5028</v>
+        <v>2.4921</v>
       </c>
       <c r="J55" s="14" t="n">
-        <v>166.85</v>
+        <v>166.14</v>
       </c>
       <c r="K55" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L55" s="14" t="n">
-        <v>47.41004677850167</v>
+      <c r="L55" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M55" s="15" t="inlineStr">
         <is>
@@ -4376,13 +4378,15 @@
         </is>
       </c>
       <c r="P55" s="13" t="n">
-        <v>-3.963</v>
-      </c>
-      <c r="Q55" s="13" t="n">
-        <v>0.2966707</v>
+        <v>4.595</v>
+      </c>
+      <c r="Q55" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="R55" s="14" t="n">
-        <v>20.88112286937462</v>
+        <v>42.0548197766043</v>
       </c>
     </row>
     <row r="56">
@@ -4391,31 +4395,31 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>002795.KS</t>
+          <t>6100.HK</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>AMOREPACIFIC Group</t>
+          <t>Tongdao Liepin Group</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>Consumer Stapl</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>Household Products</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G56" s="11" t="n">
-        <v>645767395.6312668</v>
+        <v>134208652.6063451</v>
       </c>
       <c r="H56" s="12" t="inlineStr">
         <is>
@@ -4423,10 +4427,10 @@
         </is>
       </c>
       <c r="I56" s="13" t="n">
-        <v>2.4921</v>
+        <v>2.4692</v>
       </c>
       <c r="J56" s="14" t="n">
-        <v>166.14</v>
+        <v>164.61</v>
       </c>
       <c r="K56" s="15" t="inlineStr">
         <is>
@@ -4454,15 +4458,13 @@
         </is>
       </c>
       <c r="P56" s="13" t="n">
-        <v>4.595</v>
-      </c>
-      <c r="Q56" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-3.273672284207612</v>
+      </c>
+      <c r="Q56" s="13" t="n">
+        <v>0.3498656</v>
       </c>
       <c r="R56" s="14" t="n">
-        <v>42.0548197766043</v>
+        <v>31.64514479457069</v>
       </c>
     </row>
     <row r="57">
@@ -4471,31 +4473,31 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>6100.HK</t>
+          <t>600104.SS</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>Tongdao Liepin Group</t>
+          <t>SAIC Motor Corporation Limited</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Automobiles</t>
         </is>
       </c>
       <c r="G57" s="11" t="n">
-        <v>134208652.6063451</v>
+        <v>19913480554.4624</v>
       </c>
       <c r="H57" s="12" t="inlineStr">
         <is>
@@ -4503,10 +4505,10 @@
         </is>
       </c>
       <c r="I57" s="13" t="n">
-        <v>2.4692</v>
+        <v>2.4688</v>
       </c>
       <c r="J57" s="14" t="n">
-        <v>164.61</v>
+        <v>164.59</v>
       </c>
       <c r="K57" s="15" t="inlineStr">
         <is>
@@ -4534,13 +4536,13 @@
         </is>
       </c>
       <c r="P57" s="13" t="n">
-        <v>-3.273672284207612</v>
+        <v>-0.903</v>
       </c>
       <c r="Q57" s="13" t="n">
-        <v>0.3498656</v>
+        <v>0.44818357</v>
       </c>
       <c r="R57" s="14" t="n">
-        <v>31.64514479457069</v>
+        <v>28.15266433787464</v>
       </c>
     </row>
     <row r="58">
@@ -4549,12 +4551,12 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>600104.SS</t>
+          <t>200570.SZ</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>SAIC Motor Corporation Limited</t>
+          <t>Changchai Company, Limited</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
@@ -4564,16 +4566,16 @@
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t>Machinery</t>
         </is>
       </c>
       <c r="G58" s="11" t="n">
-        <v>19913480554.4624</v>
+        <v>185502384.3848075</v>
       </c>
       <c r="H58" s="12" t="inlineStr">
         <is>
@@ -4581,10 +4583,10 @@
         </is>
       </c>
       <c r="I58" s="13" t="n">
-        <v>2.4688</v>
+        <v>2.4184</v>
       </c>
       <c r="J58" s="14" t="n">
-        <v>164.59</v>
+        <v>161.23</v>
       </c>
       <c r="K58" s="15" t="inlineStr">
         <is>
@@ -4612,13 +4614,13 @@
         </is>
       </c>
       <c r="P58" s="13" t="n">
-        <v>-0.903</v>
+        <v>-4.807063888047561</v>
       </c>
       <c r="Q58" s="13" t="n">
-        <v>0.44818357</v>
+        <v>0.35128185</v>
       </c>
       <c r="R58" s="14" t="n">
-        <v>28.15266433787464</v>
+        <v>20.07137064026483</v>
       </c>
     </row>
     <row r="59">
@@ -4627,31 +4629,31 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>200570.SZ</t>
+          <t>TK</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>Changchai Company, Limited</t>
+          <t>Teekay Corporation Ltd.</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>Machinery</t>
+          <t xml:space="preserve">Oil, Gas &amp; Consumable </t>
         </is>
       </c>
       <c r="G59" s="11" t="n">
-        <v>185502384.3848075</v>
+        <v>1238640512</v>
       </c>
       <c r="H59" s="12" t="inlineStr">
         <is>
@@ -4659,30 +4661,24 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>2.4184</v>
+        <v>2.4183</v>
       </c>
       <c r="J59" s="14" t="n">
-        <v>161.23</v>
-      </c>
-      <c r="K59" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L59" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>161.22</v>
+      </c>
+      <c r="K59" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="14" t="n">
+        <v>2.916988395742057</v>
       </c>
       <c r="M59" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N59" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N59" s="14" t="n">
+        <v>86.84448712751292</v>
       </c>
       <c r="O59" s="15" t="inlineStr">
         <is>
@@ -4690,13 +4686,13 @@
         </is>
       </c>
       <c r="P59" s="13" t="n">
-        <v>-4.807063888047561</v>
+        <v>4.305210340896252</v>
       </c>
       <c r="Q59" s="13" t="n">
-        <v>0.35128185</v>
+        <v>0.5727544593251743</v>
       </c>
       <c r="R59" s="14" t="n">
-        <v>20.07137064026483</v>
+        <v>26.51907448672242</v>
       </c>
     </row>
     <row r="60">
@@ -4705,31 +4701,31 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>TK</t>
+          <t>BCAP.JK</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Teekay Corporation Ltd.</t>
+          <t>PT MNC Kapital Indonesia Tbk</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oil, Gas &amp; Consumable </t>
+          <t>nan</t>
         </is>
       </c>
       <c r="G60" s="11" t="n">
-        <v>1238640512</v>
+        <v>117147191.336379</v>
       </c>
       <c r="H60" s="12" t="inlineStr">
         <is>
@@ -4737,24 +4733,30 @@
         </is>
       </c>
       <c r="I60" s="13" t="n">
-        <v>2.4183</v>
+        <v>2.4056</v>
       </c>
       <c r="J60" s="14" t="n">
-        <v>161.22</v>
-      </c>
-      <c r="K60" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="14" t="n">
-        <v>2.916988395742057</v>
+        <v>160.37</v>
+      </c>
+      <c r="K60" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L60" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N60" s="14" t="n">
-        <v>86.84448712751292</v>
+      <c r="N60" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O60" s="15" t="inlineStr">
         <is>
@@ -4762,13 +4764,13 @@
         </is>
       </c>
       <c r="P60" s="13" t="n">
-        <v>4.305210340896252</v>
+        <v>1.198371422064693</v>
       </c>
       <c r="Q60" s="13" t="n">
-        <v>0.5727544593251743</v>
+        <v>0.46965998</v>
       </c>
       <c r="R60" s="14" t="n">
-        <v>26.51907448672242</v>
+        <v>-6.288390804467669</v>
       </c>
     </row>
     <row r="61">
@@ -4777,31 +4779,31 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>BCAP.JK</t>
+          <t>MJS.V</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>PT MNC Kapital Indonesia Tbk</t>
+          <t>Majestic Gold Corp.</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="G61" s="11" t="n">
-        <v>117147191.336379</v>
+        <v>112030195.391613</v>
       </c>
       <c r="H61" s="12" t="inlineStr">
         <is>
@@ -4809,10 +4811,10 @@
         </is>
       </c>
       <c r="I61" s="13" t="n">
-        <v>2.4056</v>
+        <v>2.3894</v>
       </c>
       <c r="J61" s="14" t="n">
-        <v>160.37</v>
+        <v>159.29</v>
       </c>
       <c r="K61" s="15" t="inlineStr">
         <is>
@@ -4840,13 +4842,13 @@
         </is>
       </c>
       <c r="P61" s="13" t="n">
-        <v>1.198371422064693</v>
+        <v>-1.422066098475755</v>
       </c>
       <c r="Q61" s="13" t="n">
-        <v>0.46965998</v>
+        <v>0.5320235</v>
       </c>
       <c r="R61" s="14" t="n">
-        <v>-6.288390804467669</v>
+        <v>16.27984485454658</v>
       </c>
     </row>
     <row r="62">
@@ -4855,31 +4857,31 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>MJS.V</t>
+          <t>1202.HK</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Majestic Gold Corp.</t>
+          <t>Chengdu PUTIAN Telecommunicati</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Communications Equipme</t>
         </is>
       </c>
       <c r="G62" s="11" t="n">
-        <v>112030195.391613</v>
+        <v>75542004.82368466</v>
       </c>
       <c r="H62" s="12" t="inlineStr">
         <is>
@@ -4887,10 +4889,10 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>2.3894</v>
+        <v>2.3865</v>
       </c>
       <c r="J62" s="14" t="n">
-        <v>159.29</v>
+        <v>159.1</v>
       </c>
       <c r="K62" s="15" t="inlineStr">
         <is>
@@ -4918,13 +4920,13 @@
         </is>
       </c>
       <c r="P62" s="13" t="n">
-        <v>-1.422066098475755</v>
+        <v>-2.298482387345427</v>
       </c>
       <c r="Q62" s="13" t="n">
-        <v>0.5320235</v>
+        <v>0.6157307</v>
       </c>
       <c r="R62" s="14" t="n">
-        <v>16.27984485454658</v>
+        <v>-14.37127256435016</v>
       </c>
     </row>
     <row r="63">
@@ -4933,12 +4935,12 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>1202.HK</t>
+          <t>2660.HK</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>Chengdu PUTIAN Telecommunicati</t>
+          <t>Zengame Technology Holding Lim</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
@@ -4948,16 +4950,16 @@
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>Communications Equipme</t>
+          <t>Interactive Media &amp; Se</t>
         </is>
       </c>
       <c r="G63" s="11" t="n">
-        <v>75542004.82368466</v>
+        <v>308378176.4272841</v>
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
@@ -4965,10 +4967,10 @@
         </is>
       </c>
       <c r="I63" s="13" t="n">
-        <v>2.3865</v>
+        <v>2.3776</v>
       </c>
       <c r="J63" s="14" t="n">
-        <v>159.1</v>
+        <v>158.51</v>
       </c>
       <c r="K63" s="15" t="inlineStr">
         <is>
@@ -4996,13 +4998,13 @@
         </is>
       </c>
       <c r="P63" s="13" t="n">
-        <v>-2.298482387345427</v>
+        <v>-2.92879287770554</v>
       </c>
       <c r="Q63" s="13" t="n">
-        <v>0.6157307</v>
+        <v>0.8040437</v>
       </c>
       <c r="R63" s="14" t="n">
-        <v>-14.37127256435016</v>
+        <v>12.60271971358383</v>
       </c>
     </row>
     <row r="64">
@@ -5011,31 +5013,31 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>2660.HK</t>
+          <t>120030.KS</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Zengame Technology Holding Lim</t>
+          <t>CHOSUN WELDING POHANG Co., Ltd</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>Interactive Media &amp; Se</t>
+          <t>Building Products</t>
         </is>
       </c>
       <c r="G64" s="11" t="n">
-        <v>308378176.4272841</v>
+        <v>50782125.30029904</v>
       </c>
       <c r="H64" s="12" t="inlineStr">
         <is>
@@ -5043,10 +5045,10 @@
         </is>
       </c>
       <c r="I64" s="13" t="n">
-        <v>2.3776</v>
+        <v>2.3643</v>
       </c>
       <c r="J64" s="14" t="n">
-        <v>158.51</v>
+        <v>157.62</v>
       </c>
       <c r="K64" s="15" t="inlineStr">
         <is>
@@ -5074,13 +5076,13 @@
         </is>
       </c>
       <c r="P64" s="13" t="n">
-        <v>-2.92879287770554</v>
+        <v>-3.522247821266952</v>
       </c>
       <c r="Q64" s="13" t="n">
-        <v>0.8040437</v>
+        <v>0.5145270064046606</v>
       </c>
       <c r="R64" s="14" t="n">
-        <v>12.60271971358383</v>
+        <v>19.99107056150671</v>
       </c>
     </row>
     <row r="65">
@@ -5089,17 +5091,17 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>120030.KS</t>
+          <t>HGS.NS</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>CHOSUN WELDING POHANG Co., Ltd</t>
+          <t>Hinduja Global Solutions Limit</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
@@ -5109,11 +5111,11 @@
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>Building Products</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G65" s="11" t="n">
-        <v>50782125.30029904</v>
+        <v>185447570.923518</v>
       </c>
       <c r="H65" s="12" t="inlineStr">
         <is>
@@ -5121,10 +5123,10 @@
         </is>
       </c>
       <c r="I65" s="13" t="n">
-        <v>2.3643</v>
+        <v>2.3352</v>
       </c>
       <c r="J65" s="14" t="n">
-        <v>157.62</v>
+        <v>155.68</v>
       </c>
       <c r="K65" s="15" t="inlineStr">
         <is>
@@ -5152,13 +5154,13 @@
         </is>
       </c>
       <c r="P65" s="13" t="n">
-        <v>-3.522247821266952</v>
+        <v>-7.663</v>
       </c>
       <c r="Q65" s="13" t="n">
-        <v>0.5145270064046606</v>
+        <v>0.21361493</v>
       </c>
       <c r="R65" s="14" t="n">
-        <v>19.99107056150671</v>
+        <v>11.1128588832898</v>
       </c>
     </row>
     <row r="66">
@@ -5167,31 +5169,31 @@
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>HGS.NS</t>
+          <t>TTEC</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Hinduja Global Solutions Limit</t>
+          <t>Ttec Holdings, Inc.</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G66" s="11" t="n">
-        <v>185447570.923518</v>
+        <v>63345280</v>
       </c>
       <c r="H66" s="12" t="inlineStr">
         <is>
@@ -5199,20 +5201,18 @@
         </is>
       </c>
       <c r="I66" s="13" t="n">
-        <v>2.3352</v>
+        <v>2.3319</v>
       </c>
       <c r="J66" s="14" t="n">
-        <v>155.68</v>
+        <v>155.46</v>
       </c>
       <c r="K66" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L66" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L66" s="14" t="n">
+        <v>310.9229290643281</v>
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
@@ -5224,19 +5224,17 @@
           <t>–</t>
         </is>
       </c>
-      <c r="O66" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="O66" s="14" t="n">
+        <v>19.91161916653297</v>
       </c>
       <c r="P66" s="13" t="n">
-        <v>-7.663</v>
+        <v>5.332</v>
       </c>
       <c r="Q66" s="13" t="n">
-        <v>0.21361493</v>
+        <v>0.65628195</v>
       </c>
       <c r="R66" s="14" t="n">
-        <v>11.1128588832898</v>
+        <v>64.10263948586179</v>
       </c>
     </row>
     <row r="67">
@@ -5245,50 +5243,52 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>TTEC</t>
+          <t>0882.HK</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>Ttec Holdings, Inc.</t>
+          <t>Tianjin Development Holdings L</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="G67" s="11" t="n">
-        <v>63345280</v>
-      </c>
-      <c r="H67" s="12" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>284047901.5149878</v>
+      </c>
+      <c r="H67" s="17" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="I67" s="13" t="n">
-        <v>2.3319</v>
+        <v>2.3273</v>
       </c>
       <c r="J67" s="14" t="n">
-        <v>155.46</v>
+        <v>155.15</v>
       </c>
       <c r="K67" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L67" s="14" t="n">
-        <v>310.9229290643281</v>
+      <c r="L67" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M67" s="15" t="inlineStr">
         <is>
@@ -5300,17 +5300,19 @@
           <t>–</t>
         </is>
       </c>
-      <c r="O67" s="14" t="n">
-        <v>19.91161916653297</v>
+      <c r="O67" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="P67" s="13" t="n">
-        <v>5.332</v>
+        <v>31.946</v>
       </c>
       <c r="Q67" s="13" t="n">
-        <v>0.65628195</v>
+        <v>0.16383736</v>
       </c>
       <c r="R67" s="14" t="n">
-        <v>64.10263948586179</v>
+        <v>-1.36426494994613</v>
       </c>
     </row>
     <row r="68">
@@ -5319,22 +5321,22 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>0882.HK</t>
+          <t>600742.SS</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Tianjin Development Holdings L</t>
+          <t>Changchun FAWAY Group Automobi</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
@@ -5343,18 +5345,18 @@
         </is>
       </c>
       <c r="G68" s="11" t="n">
-        <v>284047901.5149878</v>
-      </c>
-      <c r="H68" s="17" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>829219825.0310974</v>
+      </c>
+      <c r="H68" s="12" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="I68" s="13" t="n">
-        <v>2.3273</v>
+        <v>2.3156</v>
       </c>
       <c r="J68" s="14" t="n">
-        <v>155.15</v>
+        <v>154.37</v>
       </c>
       <c r="K68" s="15" t="inlineStr">
         <is>
@@ -5382,13 +5384,13 @@
         </is>
       </c>
       <c r="P68" s="13" t="n">
-        <v>31.946</v>
+        <v>-1.882</v>
       </c>
       <c r="Q68" s="13" t="n">
-        <v>0.16383736</v>
+        <v>0.65464324</v>
       </c>
       <c r="R68" s="14" t="n">
-        <v>-1.36426494994613</v>
+        <v>20.31337854120659</v>
       </c>
     </row>
     <row r="69">
@@ -5397,31 +5399,31 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>600742.SS</t>
+          <t>0771.HK</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>Changchun FAWAY Group Automobi</t>
+          <t>Automated Systems Holdings Lim</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G69" s="11" t="n">
-        <v>829219825.0310974</v>
+        <v>79265237.49040219</v>
       </c>
       <c r="H69" s="12" t="inlineStr">
         <is>
@@ -5429,10 +5431,10 @@
         </is>
       </c>
       <c r="I69" s="13" t="n">
-        <v>2.3156</v>
+        <v>2.3128</v>
       </c>
       <c r="J69" s="14" t="n">
-        <v>154.37</v>
+        <v>154.19</v>
       </c>
       <c r="K69" s="15" t="inlineStr">
         <is>
@@ -5460,13 +5462,13 @@
         </is>
       </c>
       <c r="P69" s="13" t="n">
-        <v>-1.882</v>
+        <v>-3.762</v>
       </c>
       <c r="Q69" s="13" t="n">
-        <v>0.65464324</v>
+        <v>0.31786942</v>
       </c>
       <c r="R69" s="14" t="n">
-        <v>20.31337854120659</v>
+        <v>-12.1481312689599</v>
       </c>
     </row>
     <row r="70">
@@ -5475,12 +5477,12 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>0771.HK</t>
+          <t>2236.HK</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Automated Systems Holdings Lim</t>
+          <t>Wison Engineering Services Co.</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
@@ -5490,16 +5492,16 @@
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Construction &amp; Enginee</t>
         </is>
       </c>
       <c r="G70" s="11" t="n">
-        <v>79265237.49040219</v>
+        <v>254981771.7363948</v>
       </c>
       <c r="H70" s="12" t="inlineStr">
         <is>
@@ -5507,10 +5509,10 @@
         </is>
       </c>
       <c r="I70" s="13" t="n">
-        <v>2.3128</v>
+        <v>2.3034</v>
       </c>
       <c r="J70" s="14" t="n">
-        <v>154.19</v>
+        <v>153.56</v>
       </c>
       <c r="K70" s="15" t="inlineStr">
         <is>
@@ -5538,13 +5540,13 @@
         </is>
       </c>
       <c r="P70" s="13" t="n">
-        <v>-3.762</v>
+        <v>-11.30676141419331</v>
       </c>
       <c r="Q70" s="13" t="n">
-        <v>0.31786942</v>
+        <v>0.5922185</v>
       </c>
       <c r="R70" s="14" t="n">
-        <v>-12.1481312689599</v>
+        <v>-67.27614765804543</v>
       </c>
     </row>
     <row r="71">
@@ -5553,17 +5555,17 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>2236.HK</t>
+          <t>S19.SI</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>Wison Engineering Services Co.</t>
+          <t>Singapore Shipping Corporation</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="E71" s="10" t="inlineStr">
@@ -5573,11 +5575,11 @@
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t>Construction &amp; Enginee</t>
+          <t>Marine</t>
         </is>
       </c>
       <c r="G71" s="11" t="n">
-        <v>254981771.7363948</v>
+        <v>94740958.96377563</v>
       </c>
       <c r="H71" s="12" t="inlineStr">
         <is>
@@ -5585,10 +5587,10 @@
         </is>
       </c>
       <c r="I71" s="13" t="n">
-        <v>2.3034</v>
+        <v>2.2914</v>
       </c>
       <c r="J71" s="14" t="n">
-        <v>153.56</v>
+        <v>152.76</v>
       </c>
       <c r="K71" s="15" t="inlineStr">
         <is>
@@ -5616,13 +5618,13 @@
         </is>
       </c>
       <c r="P71" s="13" t="n">
-        <v>-11.30676141419331</v>
+        <v>-2.075237621765811</v>
       </c>
       <c r="Q71" s="13" t="n">
-        <v>0.5922185</v>
+        <v>0.67009014</v>
       </c>
       <c r="R71" s="14" t="n">
-        <v>-67.27614765804543</v>
+        <v>23.55565129475746</v>
       </c>
     </row>
     <row r="72">
@@ -5709,31 +5711,31 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>S19.SI</t>
+          <t>ACH</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>Singapore Shipping Corporation</t>
+          <t xml:space="preserve">Aluminum Corporation of China </t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t>Marine</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="G73" s="11" t="n">
-        <v>94740958.96377563</v>
+        <v>83057080</v>
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
@@ -5741,25 +5743,21 @@
         </is>
       </c>
       <c r="I73" s="13" t="n">
-        <v>2.2914</v>
+        <v>2.2874</v>
       </c>
       <c r="J73" s="14" t="n">
-        <v>152.76</v>
+        <v>228.74</v>
       </c>
       <c r="K73" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L73" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M73" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L73" s="14" t="n">
+        <v>57.48697161036723</v>
+      </c>
+      <c r="M73" s="14" t="n">
+        <v>792.226261746741</v>
       </c>
       <c r="N73" s="15" t="inlineStr">
         <is>
@@ -5772,13 +5770,17 @@
         </is>
       </c>
       <c r="P73" s="13" t="n">
-        <v>-2.075237621765811</v>
-      </c>
-      <c r="Q73" s="13" t="n">
-        <v>0.67009014</v>
-      </c>
-      <c r="R73" s="14" t="n">
-        <v>23.55565129475746</v>
+        <v>6.575</v>
+      </c>
+      <c r="Q73" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R73" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -5787,31 +5789,31 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>ACH</t>
+          <t>0623.HK</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aluminum Corporation of China </t>
+          <t>SinoMedia Holding Limited</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Diversified Telecommun</t>
         </is>
       </c>
       <c r="G74" s="11" t="n">
-        <v>83057080</v>
+        <v>123410890.7711315</v>
       </c>
       <c r="H74" s="12" t="inlineStr">
         <is>
@@ -5819,21 +5821,25 @@
         </is>
       </c>
       <c r="I74" s="13" t="n">
-        <v>2.2874</v>
+        <v>2.2828</v>
       </c>
       <c r="J74" s="14" t="n">
-        <v>228.74</v>
+        <v>152.19</v>
       </c>
       <c r="K74" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L74" s="14" t="n">
-        <v>57.48697161036723</v>
-      </c>
-      <c r="M74" s="14" t="n">
-        <v>792.226261746741</v>
+      <c r="L74" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M74" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N74" s="15" t="inlineStr">
         <is>
@@ -5846,17 +5852,13 @@
         </is>
       </c>
       <c r="P74" s="13" t="n">
-        <v>6.575</v>
-      </c>
-      <c r="Q74" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R74" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-4.665860510757919</v>
+      </c>
+      <c r="Q74" s="13" t="n">
+        <v>0.42375004</v>
+      </c>
+      <c r="R74" s="14" t="n">
+        <v>5.18977421651165</v>
       </c>
     </row>
     <row r="75">
@@ -5865,17 +5867,17 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>0623.HK</t>
+          <t>HMVL.NS</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>SinoMedia Holding Limited</t>
+          <t>Hindustan Media Ventures Limit</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="E75" s="10" t="inlineStr">
@@ -5889,7 +5891,7 @@
         </is>
       </c>
       <c r="G75" s="11" t="n">
-        <v>123410890.7711315</v>
+        <v>61515955.22155485</v>
       </c>
       <c r="H75" s="12" t="inlineStr">
         <is>
@@ -5897,10 +5899,10 @@
         </is>
       </c>
       <c r="I75" s="13" t="n">
-        <v>2.2828</v>
+        <v>2.2701</v>
       </c>
       <c r="J75" s="14" t="n">
-        <v>152.19</v>
+        <v>151.34</v>
       </c>
       <c r="K75" s="15" t="inlineStr">
         <is>
@@ -5928,13 +5930,13 @@
         </is>
       </c>
       <c r="P75" s="13" t="n">
-        <v>-4.665860510757919</v>
+        <v>-2.336</v>
       </c>
       <c r="Q75" s="13" t="n">
-        <v>0.42375004</v>
+        <v>0.3708259</v>
       </c>
       <c r="R75" s="14" t="n">
-        <v>5.18977421651165</v>
+        <v>5.40649792705699</v>
       </c>
     </row>
     <row r="76">
@@ -5943,31 +5945,31 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>HMVL.NS</t>
+          <t>0113.HK</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Hindustan Media Ventures Limit</t>
+          <t>Dickson Concepts (Internationa</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>Diversified Telecommun</t>
+          <t>Textiles, Apparel &amp; Lu</t>
         </is>
       </c>
       <c r="G76" s="11" t="n">
-        <v>61515955.22155485</v>
+        <v>293114804.1021651</v>
       </c>
       <c r="H76" s="12" t="inlineStr">
         <is>
@@ -5975,10 +5977,10 @@
         </is>
       </c>
       <c r="I76" s="13" t="n">
-        <v>2.2701</v>
+        <v>2.2082</v>
       </c>
       <c r="J76" s="14" t="n">
-        <v>151.34</v>
+        <v>147.21</v>
       </c>
       <c r="K76" s="15" t="inlineStr">
         <is>
@@ -6006,13 +6008,13 @@
         </is>
       </c>
       <c r="P76" s="13" t="n">
-        <v>-2.336</v>
+        <v>-2.87810589741739</v>
       </c>
       <c r="Q76" s="13" t="n">
-        <v>0.3708259</v>
+        <v>0.6222547</v>
       </c>
       <c r="R76" s="14" t="n">
-        <v>5.40649792705699</v>
+        <v>15.60904020523187</v>
       </c>
     </row>
     <row r="77">
@@ -6021,42 +6023,42 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>0113.HK</t>
+          <t>054800.KQ</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>Dickson Concepts (Internationa</t>
+          <t>IDIS Holdings Co., Ltd.</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>Textiles, Apparel &amp; Lu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="G77" s="11" t="n">
-        <v>293114804.1021651</v>
-      </c>
-      <c r="H77" s="12" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>86400269.06174681</v>
+      </c>
+      <c r="H77" s="17" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="I77" s="13" t="n">
-        <v>2.2082</v>
+        <v>2.2062</v>
       </c>
       <c r="J77" s="14" t="n">
-        <v>147.21</v>
+        <v>147.08</v>
       </c>
       <c r="K77" s="15" t="inlineStr">
         <is>
@@ -6084,13 +6086,13 @@
         </is>
       </c>
       <c r="P77" s="13" t="n">
-        <v>-2.87810589741739</v>
+        <v>3.238</v>
       </c>
       <c r="Q77" s="13" t="n">
-        <v>0.6222547</v>
+        <v>0.3329555299332747</v>
       </c>
       <c r="R77" s="14" t="n">
-        <v>15.60904020523187</v>
+        <v>54.59384882780623</v>
       </c>
     </row>
     <row r="78">
@@ -6099,12 +6101,12 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>054800.KQ</t>
+          <t>066620.KQ</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>IDIS Holdings Co., Ltd.</t>
+          <t>Kukbo Design Co., Ltd.</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
@@ -6114,7 +6116,7 @@
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
@@ -6123,18 +6125,18 @@
         </is>
       </c>
       <c r="G78" s="11" t="n">
-        <v>86400269.06174681</v>
-      </c>
-      <c r="H78" s="17" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>113745472.5711635</v>
+      </c>
+      <c r="H78" s="12" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="I78" s="13" t="n">
-        <v>2.2062</v>
+        <v>2.2059</v>
       </c>
       <c r="J78" s="14" t="n">
-        <v>147.08</v>
+        <v>147.06</v>
       </c>
       <c r="K78" s="15" t="inlineStr">
         <is>
@@ -6162,13 +6164,13 @@
         </is>
       </c>
       <c r="P78" s="13" t="n">
-        <v>3.238</v>
+        <v>-3.989</v>
       </c>
       <c r="Q78" s="13" t="n">
-        <v>0.3329555299332747</v>
+        <v>0.4726214978968569</v>
       </c>
       <c r="R78" s="14" t="n">
-        <v>54.59384882780623</v>
+        <v>39.22722041839523</v>
       </c>
     </row>
     <row r="79">
@@ -6177,31 +6179,31 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>066620.KQ</t>
+          <t>0710.HK</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>Kukbo Design Co., Ltd.</t>
+          <t>BOE Varitronix Ltd</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t xml:space="preserve">Electronic Equipment, </t>
         </is>
       </c>
       <c r="G79" s="11" t="n">
-        <v>113745472.5711635</v>
+        <v>376670631.4656752</v>
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
@@ -6209,10 +6211,10 @@
         </is>
       </c>
       <c r="I79" s="13" t="n">
-        <v>2.2059</v>
+        <v>2.2004</v>
       </c>
       <c r="J79" s="14" t="n">
-        <v>147.06</v>
+        <v>146.69</v>
       </c>
       <c r="K79" s="15" t="inlineStr">
         <is>
@@ -6240,13 +6242,13 @@
         </is>
       </c>
       <c r="P79" s="13" t="n">
-        <v>-3.989</v>
+        <v>-1.881012163576926</v>
       </c>
       <c r="Q79" s="13" t="n">
-        <v>0.4726214978968569</v>
+        <v>0.61516225</v>
       </c>
       <c r="R79" s="14" t="n">
-        <v>39.22722041839523</v>
+        <v>10.50849759768003</v>
       </c>
     </row>
     <row r="80">
@@ -6255,12 +6257,12 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>0710.HK</t>
+          <t>0366.HK</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>BOE Varitronix Ltd</t>
+          <t xml:space="preserve">Luks Group (Vietnam Holdings) </t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
@@ -6270,16 +6272,16 @@
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electronic Equipment, </t>
+          <t>Construction Materials</t>
         </is>
       </c>
       <c r="G80" s="11" t="n">
-        <v>376670631.4656752</v>
+        <v>53016211.98899076</v>
       </c>
       <c r="H80" s="12" t="inlineStr">
         <is>
@@ -6287,10 +6289,10 @@
         </is>
       </c>
       <c r="I80" s="13" t="n">
-        <v>2.2004</v>
+        <v>2.1546</v>
       </c>
       <c r="J80" s="14" t="n">
-        <v>146.69</v>
+        <v>143.64</v>
       </c>
       <c r="K80" s="15" t="inlineStr">
         <is>
@@ -6318,13 +6320,13 @@
         </is>
       </c>
       <c r="P80" s="13" t="n">
-        <v>-1.881012163576926</v>
+        <v>-2.78</v>
       </c>
       <c r="Q80" s="13" t="n">
-        <v>0.61516225</v>
+        <v>0.1810887</v>
       </c>
       <c r="R80" s="14" t="n">
-        <v>10.50849759768003</v>
+        <v>17.0180685132255</v>
       </c>
     </row>
     <row r="81">
@@ -6333,31 +6335,31 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>0366.HK</t>
+          <t>NBR</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luks Group (Vietnam Holdings) </t>
+          <t>Nabors Industries Ltd</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t xml:space="preserve">Oil, Gas &amp; Consumable </t>
         </is>
       </c>
       <c r="G81" s="11" t="n">
-        <v>53016211.98899076</v>
+        <v>1376357376</v>
       </c>
       <c r="H81" s="12" t="inlineStr">
         <is>
@@ -6365,30 +6367,26 @@
         </is>
       </c>
       <c r="I81" s="13" t="n">
-        <v>2.1546</v>
+        <v>2.1495</v>
       </c>
       <c r="J81" s="14" t="n">
-        <v>143.64</v>
+        <v>143.3</v>
       </c>
       <c r="K81" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L81" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L81" s="14" t="n">
+        <v>286.5995466572775</v>
       </c>
       <c r="M81" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N81" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N81" s="14" t="n">
+        <v>4.482847338626098</v>
       </c>
       <c r="O81" s="15" t="inlineStr">
         <is>
@@ -6396,13 +6394,13 @@
         </is>
       </c>
       <c r="P81" s="13" t="n">
-        <v>-2.78</v>
+        <v>4.362</v>
       </c>
       <c r="Q81" s="13" t="n">
-        <v>0.1810887</v>
+        <v>2.4644344</v>
       </c>
       <c r="R81" s="14" t="n">
-        <v>17.0180685132255</v>
+        <v>2.87339886762939</v>
       </c>
     </row>
     <row r="82">
@@ -6411,31 +6409,31 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>NBR</t>
+          <t>040300.KQ</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Nabors Industries Ltd</t>
+          <t>YTN Co.,Ltd.</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E82" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oil, Gas &amp; Consumable </t>
+          <t>nan</t>
         </is>
       </c>
       <c r="G82" s="11" t="n">
-        <v>1376357376</v>
+        <v>61464157.95320418</v>
       </c>
       <c r="H82" s="12" t="inlineStr">
         <is>
@@ -6443,26 +6441,30 @@
         </is>
       </c>
       <c r="I82" s="13" t="n">
-        <v>2.1495</v>
+        <v>2.1224</v>
       </c>
       <c r="J82" s="14" t="n">
-        <v>143.3</v>
+        <v>141.49</v>
       </c>
       <c r="K82" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L82" s="14" t="n">
-        <v>286.5995466572775</v>
+      <c r="L82" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M82" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N82" s="14" t="n">
-        <v>4.482847338626098</v>
+      <c r="N82" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O82" s="15" t="inlineStr">
         <is>
@@ -6470,13 +6472,13 @@
         </is>
       </c>
       <c r="P82" s="13" t="n">
-        <v>4.362</v>
+        <v>-5.048</v>
       </c>
       <c r="Q82" s="13" t="n">
-        <v>2.4644344</v>
+        <v>0.5790057077888011</v>
       </c>
       <c r="R82" s="14" t="n">
-        <v>2.87339886762939</v>
+        <v>-1.72639384540231</v>
       </c>
     </row>
     <row r="83">
@@ -6485,31 +6487,31 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>040300.KQ</t>
+          <t>0210.HK</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>YTN Co.,Ltd.</t>
+          <t xml:space="preserve">Daphne International Holdings </t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Textiles, Apparel &amp; Lu</t>
         </is>
       </c>
       <c r="G83" s="11" t="n">
-        <v>61464157.95320418</v>
+        <v>79526718.99423406</v>
       </c>
       <c r="H83" s="12" t="inlineStr">
         <is>
@@ -6517,10 +6519,10 @@
         </is>
       </c>
       <c r="I83" s="13" t="n">
-        <v>2.1224</v>
+        <v>2.0751</v>
       </c>
       <c r="J83" s="14" t="n">
-        <v>141.49</v>
+        <v>138.34</v>
       </c>
       <c r="K83" s="15" t="inlineStr">
         <is>
@@ -6548,13 +6550,13 @@
         </is>
       </c>
       <c r="P83" s="13" t="n">
-        <v>-5.048</v>
+        <v>-1.694106543804159</v>
       </c>
       <c r="Q83" s="13" t="n">
-        <v>0.5790057077888011</v>
+        <v>0.631315</v>
       </c>
       <c r="R83" s="14" t="n">
-        <v>-1.72639384540231</v>
+        <v>23.08105232049102</v>
       </c>
     </row>
     <row r="84">
@@ -6563,12 +6565,12 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>0210.HK</t>
+          <t>6820.HK</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daphne International Holdings </t>
+          <t>FriendTimes Inc.</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
@@ -6578,16 +6580,16 @@
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>Textiles, Apparel &amp; Lu</t>
+          <t>Interactive Media &amp; Se</t>
         </is>
       </c>
       <c r="G84" s="11" t="n">
-        <v>79526718.99423406</v>
+        <v>94713120.14146514</v>
       </c>
       <c r="H84" s="12" t="inlineStr">
         <is>
@@ -6595,10 +6597,10 @@
         </is>
       </c>
       <c r="I84" s="13" t="n">
-        <v>2.0751</v>
+        <v>2.069</v>
       </c>
       <c r="J84" s="14" t="n">
-        <v>138.34</v>
+        <v>137.93</v>
       </c>
       <c r="K84" s="15" t="inlineStr">
         <is>
@@ -6626,13 +6628,13 @@
         </is>
       </c>
       <c r="P84" s="13" t="n">
-        <v>-1.694106543804159</v>
+        <v>-10.65094536225466</v>
       </c>
       <c r="Q84" s="13" t="n">
-        <v>0.631315</v>
+        <v>0.49736303</v>
       </c>
       <c r="R84" s="14" t="n">
-        <v>23.08105232049102</v>
+        <v>20.77303497364105</v>
       </c>
     </row>
     <row r="85">
@@ -6641,31 +6643,31 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>6820.HK</t>
+          <t>AVAL</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>FriendTimes Inc.</t>
+          <t xml:space="preserve">Grupo Aval Acciones y Valores </t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>Interactive Media &amp; Se</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="G85" s="11" t="n">
-        <v>94713120.14146514</v>
+        <v>6351379456</v>
       </c>
       <c r="H85" s="12" t="inlineStr">
         <is>
@@ -6673,10 +6675,10 @@
         </is>
       </c>
       <c r="I85" s="13" t="n">
-        <v>2.069</v>
+        <v>2.064</v>
       </c>
       <c r="J85" s="14" t="n">
-        <v>137.93</v>
+        <v>137.6</v>
       </c>
       <c r="K85" s="15" t="inlineStr">
         <is>
@@ -6703,14 +6705,18 @@
           <t>–</t>
         </is>
       </c>
-      <c r="P85" s="13" t="n">
-        <v>-10.65094536225466</v>
+      <c r="P85" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q85" s="13" t="n">
-        <v>0.49736303</v>
-      </c>
-      <c r="R85" s="14" t="n">
-        <v>20.77303497364105</v>
+        <v>0.6983912402273952</v>
+      </c>
+      <c r="R85" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -6719,31 +6725,31 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>AVAL</t>
+          <t>200550.SZ</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grupo Aval Acciones y Valores </t>
+          <t xml:space="preserve">Jiangling Motors Corporation, </t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Automobiles</t>
         </is>
       </c>
       <c r="G86" s="11" t="n">
-        <v>6351379456</v>
+        <v>1042020893.846527</v>
       </c>
       <c r="H86" s="12" t="inlineStr">
         <is>
@@ -6751,10 +6757,10 @@
         </is>
       </c>
       <c r="I86" s="13" t="n">
-        <v>2.064</v>
+        <v>2.0625</v>
       </c>
       <c r="J86" s="14" t="n">
-        <v>137.6</v>
+        <v>137.5</v>
       </c>
       <c r="K86" s="15" t="inlineStr">
         <is>
@@ -6781,18 +6787,14 @@
           <t>–</t>
         </is>
       </c>
-      <c r="P86" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P86" s="13" t="n">
+        <v>-1.079871114907206</v>
       </c>
       <c r="Q86" s="13" t="n">
-        <v>0.6983912402273952</v>
-      </c>
-      <c r="R86" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.57824683</v>
+      </c>
+      <c r="R86" s="14" t="n">
+        <v>27.56625747476087</v>
       </c>
     </row>
     <row r="87">
@@ -6801,31 +6803,31 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>200550.SZ</t>
+          <t>0206.HK</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jiangling Motors Corporation, </t>
+          <t>CMIC Ocean En-Tech Holding Co.</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t>Energy Equipment &amp; Ser</t>
         </is>
       </c>
       <c r="G87" s="11" t="n">
-        <v>1042020893.846527</v>
+        <v>80976308.81652638</v>
       </c>
       <c r="H87" s="12" t="inlineStr">
         <is>
@@ -6833,10 +6835,10 @@
         </is>
       </c>
       <c r="I87" s="13" t="n">
-        <v>2.0625</v>
+        <v>2.0572</v>
       </c>
       <c r="J87" s="14" t="n">
-        <v>137.5</v>
+        <v>137.15</v>
       </c>
       <c r="K87" s="15" t="inlineStr">
         <is>
@@ -6863,14 +6865,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="P87" s="13" t="n">
-        <v>-1.079871114907206</v>
+      <c r="P87" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q87" s="13" t="n">
-        <v>0.57824683</v>
+        <v>0.4723148</v>
       </c>
       <c r="R87" s="14" t="n">
-        <v>27.56625747476087</v>
+        <v>82.43615074039568</v>
       </c>
     </row>
     <row r="88">
@@ -6879,12 +6883,12 @@
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>0206.HK</t>
+          <t>1568.HK</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>CMIC Ocean En-Tech Holding Co.</t>
+          <t>Sundart Holdings Limited</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
@@ -6894,16 +6898,16 @@
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>Energy Equipment &amp; Ser</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G88" s="11" t="n">
-        <v>80976308.81652638</v>
+        <v>179442298.5907096</v>
       </c>
       <c r="H88" s="12" t="inlineStr">
         <is>
@@ -6911,10 +6915,10 @@
         </is>
       </c>
       <c r="I88" s="13" t="n">
-        <v>2.0572</v>
+        <v>2.0512</v>
       </c>
       <c r="J88" s="14" t="n">
-        <v>137.15</v>
+        <v>136.75</v>
       </c>
       <c r="K88" s="15" t="inlineStr">
         <is>
@@ -6941,16 +6945,14 @@
           <t>–</t>
         </is>
       </c>
-      <c r="P88" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P88" s="13" t="n">
+        <v>-1.255</v>
       </c>
       <c r="Q88" s="13" t="n">
-        <v>0.4723148</v>
+        <v>0.37391302</v>
       </c>
       <c r="R88" s="14" t="n">
-        <v>82.43615074039568</v>
+        <v>-6.960172812293069</v>
       </c>
     </row>
     <row r="89">
@@ -6959,31 +6961,31 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>1568.HK</t>
+          <t>005990.KQ</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>Sundart Holdings Limited</t>
+          <t>Maeil Holdings Co., Ltd.</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E89" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Stapl</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="G89" s="11" t="n">
-        <v>179442298.5907096</v>
+        <v>88900659.32992949</v>
       </c>
       <c r="H89" s="12" t="inlineStr">
         <is>
@@ -6991,10 +6993,10 @@
         </is>
       </c>
       <c r="I89" s="13" t="n">
-        <v>2.0512</v>
+        <v>2.0194</v>
       </c>
       <c r="J89" s="14" t="n">
-        <v>136.75</v>
+        <v>134.63</v>
       </c>
       <c r="K89" s="15" t="inlineStr">
         <is>
@@ -7022,13 +7024,13 @@
         </is>
       </c>
       <c r="P89" s="13" t="n">
-        <v>-1.255</v>
+        <v>2.984</v>
       </c>
       <c r="Q89" s="13" t="n">
-        <v>0.37391302</v>
+        <v>0.3407681346875961</v>
       </c>
       <c r="R89" s="14" t="n">
-        <v>-6.960172812293069</v>
+        <v>76.53523134332552</v>
       </c>
     </row>
     <row r="90">
@@ -7037,12 +7039,12 @@
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>005990.KQ</t>
+          <t>035610.KQ</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Maeil Holdings Co., Ltd.</t>
+          <t>Solborn, Inc.</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
@@ -7052,7 +7054,7 @@
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>Consumer Stapl</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
@@ -7061,7 +7063,7 @@
         </is>
       </c>
       <c r="G90" s="11" t="n">
-        <v>88900659.32992949</v>
+        <v>90146910.85052596</v>
       </c>
       <c r="H90" s="12" t="inlineStr">
         <is>
@@ -7069,10 +7071,10 @@
         </is>
       </c>
       <c r="I90" s="13" t="n">
-        <v>2.0194</v>
+        <v>2.0163</v>
       </c>
       <c r="J90" s="14" t="n">
-        <v>134.63</v>
+        <v>134.42</v>
       </c>
       <c r="K90" s="15" t="inlineStr">
         <is>
@@ -7100,13 +7102,13 @@
         </is>
       </c>
       <c r="P90" s="13" t="n">
-        <v>2.984</v>
+        <v>0.499</v>
       </c>
       <c r="Q90" s="13" t="n">
-        <v>0.3407681346875961</v>
+        <v>0.4404573070670534</v>
       </c>
       <c r="R90" s="14" t="n">
-        <v>76.53523134332552</v>
+        <v>7.8330492148766</v>
       </c>
     </row>
     <row r="91">
@@ -7115,22 +7117,22 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>035610.KQ</t>
+          <t>AMJB</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>Solborn, Inc.</t>
+          <t>Jpmorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E91" s="10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
@@ -7139,7 +7141,7 @@
         </is>
       </c>
       <c r="G91" s="11" t="n">
-        <v>90146910.85052596</v>
+        <v>93126748000</v>
       </c>
       <c r="H91" s="12" t="inlineStr">
         <is>
@@ -7147,20 +7149,16 @@
         </is>
       </c>
       <c r="I91" s="13" t="n">
-        <v>2.0163</v>
+        <v>2</v>
       </c>
       <c r="J91" s="14" t="n">
-        <v>134.42</v>
-      </c>
-      <c r="K91" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L91" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>200</v>
+      </c>
+      <c r="K91" s="14" t="n">
+        <v>9.534317680673226</v>
+      </c>
+      <c r="L91" s="14" t="n">
+        <v>0.511131345421833</v>
       </c>
       <c r="M91" s="15" t="inlineStr">
         <is>
@@ -7177,14 +7175,18 @@
           <t>–</t>
         </is>
       </c>
-      <c r="P91" s="13" t="n">
-        <v>0.499</v>
+      <c r="P91" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q91" s="13" t="n">
-        <v>0.4404573070670534</v>
-      </c>
-      <c r="R91" s="14" t="n">
-        <v>7.8330492148766</v>
+        <v>0.2486044986892615</v>
+      </c>
+      <c r="R91" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -7193,12 +7195,12 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>ZH</t>
+          <t>VYLD</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Zhihu Inc.</t>
+          <t>Jpmorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
@@ -7208,16 +7210,16 @@
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>Diversified Telecommun</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="G92" s="11" t="n">
-        <v>241481968</v>
+        <v>79118101660</v>
       </c>
       <c r="H92" s="12" t="inlineStr">
         <is>
@@ -7230,15 +7232,11 @@
       <c r="J92" s="14" t="n">
         <v>200</v>
       </c>
-      <c r="K92" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L92" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="K92" s="14" t="n">
+        <v>11.22246339801778</v>
+      </c>
+      <c r="L92" s="14" t="n">
+        <v>0.6016322308206402</v>
       </c>
       <c r="M92" s="15" t="inlineStr">
         <is>
@@ -7261,10 +7259,12 @@
         </is>
       </c>
       <c r="Q92" s="13" t="n">
-        <v>0.39252138</v>
-      </c>
-      <c r="R92" s="14" t="n">
-        <v>-0.07052584403626</v>
+        <v>0.2112080194234886</v>
+      </c>
+      <c r="R92" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -7273,31 +7273,31 @@
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>0909.HK</t>
+          <t>001940.KS</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>Ming Yuan Cloud Group Holdings</t>
+          <t>KISCO Holdings Corp.</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E93" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="G93" s="11" t="n">
-        <v>256268599.1634292</v>
+        <v>202927291.1822295</v>
       </c>
       <c r="H93" s="12" t="inlineStr">
         <is>
@@ -7341,10 +7341,10 @@
         </is>
       </c>
       <c r="Q93" s="13" t="n">
-        <v>0.401683</v>
+        <v>0.2470810832653075</v>
       </c>
       <c r="R93" s="14" t="n">
-        <v>5.22212466905032</v>
+        <v>-5.36679090234641</v>
       </c>
     </row>
     <row r="94">
@@ -7353,12 +7353,12 @@
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>VYLD</t>
+          <t>CMCM</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Jpmorgan Chase &amp; Co</t>
+          <t>Cheetah Mobile Inc.</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
@@ -7368,16 +7368,16 @@
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G94" s="11" t="n">
-        <v>79118101660</v>
+        <v>99789184</v>
       </c>
       <c r="H94" s="12" t="inlineStr">
         <is>
@@ -7390,39 +7390,35 @@
       <c r="J94" s="14" t="n">
         <v>200</v>
       </c>
-      <c r="K94" s="14" t="n">
-        <v>11.22246339801778</v>
+      <c r="K94" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L94" s="14" t="n">
-        <v>0.6016322308206402</v>
+        <v>129.4819687071497</v>
       </c>
       <c r="M94" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N94" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N94" s="14" t="n">
+        <v>29.49718478507651</v>
       </c>
       <c r="O94" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="P94" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P94" s="13" t="n">
+        <v>-19.46430541052319</v>
       </c>
       <c r="Q94" s="13" t="n">
-        <v>0.2112080194234886</v>
-      </c>
-      <c r="R94" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.4287816</v>
+      </c>
+      <c r="R94" s="14" t="n">
+        <v>-0.08587525535886001</v>
       </c>
     </row>
     <row r="95">
@@ -7431,31 +7427,31 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>AMJB</t>
+          <t>2033.HK</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>Jpmorgan Chase &amp; Co</t>
+          <t>Time Watch Investments Limited</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E95" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Textiles, Apparel &amp; Lu</t>
         </is>
       </c>
       <c r="G95" s="11" t="n">
-        <v>93126748000</v>
+        <v>58301469.56463955</v>
       </c>
       <c r="H95" s="12" t="inlineStr">
         <is>
@@ -7468,11 +7464,15 @@
       <c r="J95" s="14" t="n">
         <v>200</v>
       </c>
-      <c r="K95" s="14" t="n">
-        <v>9.534317680673226</v>
-      </c>
-      <c r="L95" s="14" t="n">
-        <v>0.511131345421833</v>
+      <c r="K95" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L95" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M95" s="15" t="inlineStr">
         <is>
@@ -7495,12 +7495,10 @@
         </is>
       </c>
       <c r="Q95" s="13" t="n">
-        <v>0.2486044986892615</v>
-      </c>
-      <c r="R95" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.20479706</v>
+      </c>
+      <c r="R95" s="14" t="n">
+        <v>5.88765515847855</v>
       </c>
     </row>
     <row r="96">
@@ -7509,31 +7507,31 @@
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>2033.HK</t>
+          <t>ZEPP</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Time Watch Investments Limited</t>
+          <t>Zepp Health Corp</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>Textiles, Apparel &amp; Lu</t>
+          <t xml:space="preserve">Electronic Equipment, </t>
         </is>
       </c>
       <c r="G96" s="11" t="n">
-        <v>58301469.56463955</v>
+        <v>67165608</v>
       </c>
       <c r="H96" s="12" t="inlineStr">
         <is>
@@ -7551,10 +7549,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L96" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L96" s="14" t="n">
+        <v>57.95823362456571</v>
       </c>
       <c r="M96" s="15" t="inlineStr">
         <is>
@@ -7577,10 +7573,10 @@
         </is>
       </c>
       <c r="Q96" s="13" t="n">
-        <v>0.20479706</v>
+        <v>0.37436652</v>
       </c>
       <c r="R96" s="14" t="n">
-        <v>5.88765515847855</v>
+        <v>-39.80210722755725</v>
       </c>
     </row>
     <row r="97">
@@ -7589,31 +7585,31 @@
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>2100.HK</t>
+          <t>200521.SZ</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>BAIOO Family Interactive Limit</t>
+          <t>Changhong Meiling Co., Ltd.</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="E97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>Interactive Media &amp; Se</t>
+          <t xml:space="preserve">Electronic Equipment, </t>
         </is>
       </c>
       <c r="G97" s="11" t="n">
-        <v>100241186.0540237</v>
+        <v>385069824.3972433</v>
       </c>
       <c r="H97" s="12" t="inlineStr">
         <is>
@@ -7651,16 +7647,14 @@
           <t>–</t>
         </is>
       </c>
-      <c r="P97" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P97" s="13" t="n">
+        <v>-26.92665798819529</v>
       </c>
       <c r="Q97" s="13" t="n">
-        <v>0.4697409</v>
+        <v>0.42982808</v>
       </c>
       <c r="R97" s="14" t="n">
-        <v>-13.1060853033141</v>
+        <v>-17.48409470338235</v>
       </c>
     </row>
     <row r="98">
@@ -7669,12 +7663,12 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>ZEPP</t>
+          <t>NIOBW</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Zepp Health Corp</t>
+          <t>Niocorp Developments Ltd.</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
@@ -7684,16 +7678,16 @@
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electronic Equipment, </t>
+          <t>nan</t>
         </is>
       </c>
       <c r="G98" s="11" t="n">
-        <v>67165608</v>
+        <v>196192115.55</v>
       </c>
       <c r="H98" s="12" t="inlineStr">
         <is>
@@ -7712,17 +7706,15 @@
         </is>
       </c>
       <c r="L98" s="14" t="n">
-        <v>57.95823362456571</v>
+        <v>16.39158633355182</v>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N98" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N98" s="14" t="n">
+        <v>0.00356793135156139</v>
       </c>
       <c r="O98" s="15" t="inlineStr">
         <is>
@@ -7735,10 +7727,10 @@
         </is>
       </c>
       <c r="Q98" s="13" t="n">
-        <v>0.37436652</v>
+        <v>0.4506082204853535</v>
       </c>
       <c r="R98" s="14" t="n">
-        <v>-39.80210722755725</v>
+        <v>-15.80287766054419</v>
       </c>
     </row>
     <row r="99">
@@ -7747,12 +7739,12 @@
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>MCRB</t>
+          <t>GDHG</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>Seres Therapeutics, Inc.</t>
+          <t>Golden Heaven Group Holdings L</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
@@ -7762,16 +7754,16 @@
       </c>
       <c r="E99" s="10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t xml:space="preserve">Hotels, Restaurants &amp; </t>
         </is>
       </c>
       <c r="G99" s="11" t="n">
-        <v>50324356</v>
+        <v>69901808</v>
       </c>
       <c r="H99" s="12" t="inlineStr">
         <is>
@@ -7790,7 +7782,7 @@
         </is>
       </c>
       <c r="L99" s="14" t="n">
-        <v>617.913520840684</v>
+        <v>4.844947644272663</v>
       </c>
       <c r="M99" s="15" t="inlineStr">
         <is>
@@ -7802,21 +7794,19 @@
           <t>–</t>
         </is>
       </c>
-      <c r="O99" s="14" t="n">
-        <v>1129.056378046957</v>
-      </c>
-      <c r="P99" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="O99" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P99" s="13" t="n">
+        <v>-76.425</v>
       </c>
       <c r="Q99" s="13" t="n">
-        <v>1.4257258</v>
-      </c>
-      <c r="R99" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.3869456205617164</v>
+      </c>
+      <c r="R99" s="14" t="n">
+        <v>5.41869452105689</v>
       </c>
     </row>
     <row r="100">
@@ -7825,31 +7815,31 @@
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>CMCM</t>
+          <t>ENW.L</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Cheetah Mobile Inc.</t>
+          <t>Enwell Energy plc</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t xml:space="preserve">Oil, Gas &amp; Consumable </t>
         </is>
       </c>
       <c r="G100" s="11" t="n">
-        <v>99789184</v>
+        <v>52512980.67904043</v>
       </c>
       <c r="H100" s="12" t="inlineStr">
         <is>
@@ -7867,30 +7857,36 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L100" s="14" t="n">
-        <v>129.4819687071497</v>
+      <c r="L100" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N100" s="14" t="n">
-        <v>29.49718478507651</v>
+      <c r="N100" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O100" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="P100" s="13" t="n">
-        <v>-19.46430541052319</v>
+      <c r="P100" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q100" s="13" t="n">
-        <v>0.4287816</v>
+        <v>0.3210329</v>
       </c>
       <c r="R100" s="14" t="n">
-        <v>-0.08587525535886001</v>
+        <v>-3.33441365802889</v>
       </c>
     </row>
     <row r="101">
@@ -7899,31 +7895,31 @@
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>1122.HK</t>
+          <t>STRD</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>Qingling Motors Co., Ltd. Clas</t>
+          <t>MicroStrategy Incorporated 10.</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>Machinery</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G101" s="11" t="n">
-        <v>152039595.5916309</v>
+        <v>865764273</v>
       </c>
       <c r="H101" s="12" t="inlineStr">
         <is>
@@ -7941,10 +7937,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L101" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L101" s="14" t="n">
+        <v>531.3224561762437</v>
       </c>
       <c r="M101" s="15" t="inlineStr">
         <is>
@@ -7966,11 +7960,15 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q101" s="13" t="n">
-        <v>0.14061408</v>
-      </c>
-      <c r="R101" s="14" t="n">
-        <v>-49.45872020700714</v>
+      <c r="Q101" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R101" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -7979,31 +7977,31 @@
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>200521.SZ</t>
+          <t>MCRB</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Changhong Meiling Co., Ltd.</t>
+          <t>Seres Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electronic Equipment, </t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G102" s="11" t="n">
-        <v>385069824.3972433</v>
+        <v>50324356</v>
       </c>
       <c r="H102" s="12" t="inlineStr">
         <is>
@@ -8021,10 +8019,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L102" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L102" s="14" t="n">
+        <v>617.913520840684</v>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
@@ -8036,19 +8032,21 @@
           <t>–</t>
         </is>
       </c>
-      <c r="O102" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P102" s="13" t="n">
-        <v>-26.92665798819529</v>
+      <c r="O102" s="14" t="n">
+        <v>1129.056378046957</v>
+      </c>
+      <c r="P102" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q102" s="13" t="n">
-        <v>0.42982808</v>
-      </c>
-      <c r="R102" s="14" t="n">
-        <v>-17.48409470338235</v>
+        <v>1.4257258</v>
+      </c>
+      <c r="R102" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -8057,31 +8055,31 @@
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>VAL-WT</t>
+          <t>0JXZ.IL</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>Valaris Limited</t>
+          <t>Galapagos NV</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E103" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G103" s="11" t="n">
-        <v>663201000</v>
+        <v>1785441867.433044</v>
       </c>
       <c r="H103" s="12" t="inlineStr">
         <is>
@@ -8094,11 +8092,15 @@
       <c r="J103" s="14" t="n">
         <v>200</v>
       </c>
-      <c r="K103" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="14" t="n">
-        <v>496.4256688394619</v>
+      <c r="K103" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L103" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M103" s="15" t="inlineStr">
         <is>
@@ -8120,15 +8122,11 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q103" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R103" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="Q103" s="13" t="n">
+        <v>0.59879625</v>
+      </c>
+      <c r="R103" s="14" t="n">
+        <v>-18.94339056056228</v>
       </c>
     </row>
     <row r="104">
@@ -8137,17 +8135,17 @@
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>DQ</t>
+          <t>0909.HK</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Daqo New Energy Corp.</t>
+          <t>Ming Yuan Cloud Group Holdings</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
@@ -8157,11 +8155,11 @@
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Semic</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G104" s="11" t="n">
-        <v>780867200</v>
+        <v>256268599.1634292</v>
       </c>
       <c r="H104" s="12" t="inlineStr">
         <is>
@@ -8179,19 +8177,25 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L104" s="14" t="n">
-        <v>0.645564316185902</v>
+      <c r="L104" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N104" s="14" t="n">
-        <v>0.08772298285803271</v>
-      </c>
-      <c r="O104" s="14" t="n">
-        <v>9.317493594223155</v>
+      <c r="N104" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O104" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="P104" s="15" t="inlineStr">
         <is>
@@ -8199,10 +8203,10 @@
         </is>
       </c>
       <c r="Q104" s="13" t="n">
-        <v>0.17852724</v>
+        <v>0.401683</v>
       </c>
       <c r="R104" s="14" t="n">
-        <v>-33.48712815700289</v>
+        <v>5.22212466905032</v>
       </c>
     </row>
     <row r="105">
@@ -8289,31 +8293,31 @@
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>0JXZ.IL</t>
+          <t>BATL</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Galapagos NV</t>
+          <t>Battalion Oil Corporation</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t xml:space="preserve">Oil, Gas &amp; Consumable </t>
         </is>
       </c>
       <c r="G106" s="11" t="n">
-        <v>1785441867.433044</v>
+        <v>76758088</v>
       </c>
       <c r="H106" s="12" t="inlineStr">
         <is>
@@ -8331,36 +8335,30 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L106" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L106" s="14" t="n">
+        <v>412.2184492141075</v>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N106" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N106" s="14" t="n">
+        <v>0.01433073736802824</v>
       </c>
       <c r="O106" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="P106" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P106" s="13" t="n">
+        <v>10.712</v>
       </c>
       <c r="Q106" s="13" t="n">
-        <v>0.59879625</v>
+        <v>0.3637624472033789</v>
       </c>
       <c r="R106" s="14" t="n">
-        <v>-18.94339056056228</v>
+        <v>-2.92868160030249</v>
       </c>
     </row>
     <row r="107">
@@ -8369,31 +8367,31 @@
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>STRD</t>
+          <t>2100.HK</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>MicroStrategy Incorporated 10.</t>
+          <t>BAIOO Family Interactive Limit</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E107" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Interactive Media &amp; Se</t>
         </is>
       </c>
       <c r="G107" s="11" t="n">
-        <v>865764273</v>
+        <v>100241186.0540237</v>
       </c>
       <c r="H107" s="12" t="inlineStr">
         <is>
@@ -8411,8 +8409,10 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L107" s="14" t="n">
-        <v>531.3224561762437</v>
+      <c r="L107" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M107" s="15" t="inlineStr">
         <is>
@@ -8434,15 +8434,11 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q107" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R107" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="Q107" s="13" t="n">
+        <v>0.4697409</v>
+      </c>
+      <c r="R107" s="14" t="n">
+        <v>-13.1060853033141</v>
       </c>
     </row>
     <row r="108">
@@ -8451,12 +8447,12 @@
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>BATL</t>
+          <t>DQ</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Battalion Oil Corporation</t>
+          <t>Daqo New Energy Corp.</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
@@ -8466,16 +8462,16 @@
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oil, Gas &amp; Consumable </t>
+          <t>Semiconductors &amp; Semic</t>
         </is>
       </c>
       <c r="G108" s="11" t="n">
-        <v>76758088</v>
+        <v>780867200</v>
       </c>
       <c r="H108" s="12" t="inlineStr">
         <is>
@@ -8494,7 +8490,7 @@
         </is>
       </c>
       <c r="L108" s="14" t="n">
-        <v>412.2184492141075</v>
+        <v>0.645564316185902</v>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
@@ -8502,21 +8498,21 @@
         </is>
       </c>
       <c r="N108" s="14" t="n">
-        <v>0.01433073736802824</v>
-      </c>
-      <c r="O108" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P108" s="13" t="n">
-        <v>10.712</v>
+        <v>0.08772298285803271</v>
+      </c>
+      <c r="O108" s="14" t="n">
+        <v>9.317493594223155</v>
+      </c>
+      <c r="P108" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q108" s="13" t="n">
-        <v>0.3637624472033789</v>
+        <v>0.17852724</v>
       </c>
       <c r="R108" s="14" t="n">
-        <v>-2.92868160030249</v>
+        <v>-33.48712815700289</v>
       </c>
     </row>
     <row r="109">
@@ -8603,31 +8599,31 @@
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>001940.KS</t>
+          <t>ZH</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>KISCO Holdings Corp.</t>
+          <t>Zhihu Inc.</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Diversified Telecommun</t>
         </is>
       </c>
       <c r="G110" s="11" t="n">
-        <v>202927291.1822295</v>
+        <v>241481968</v>
       </c>
       <c r="H110" s="12" t="inlineStr">
         <is>
@@ -8671,10 +8667,10 @@
         </is>
       </c>
       <c r="Q110" s="13" t="n">
-        <v>0.2470810832653075</v>
+        <v>0.39252138</v>
       </c>
       <c r="R110" s="14" t="n">
-        <v>-5.36679090234641</v>
+        <v>-0.07052584403626</v>
       </c>
     </row>
     <row r="111">
@@ -8683,31 +8679,31 @@
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>NIOBW</t>
+          <t>1122.HK</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>Niocorp Developments Ltd.</t>
+          <t>Qingling Motors Co., Ltd. Clas</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E111" s="10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Machinery</t>
         </is>
       </c>
       <c r="G111" s="11" t="n">
-        <v>196192115.55</v>
+        <v>152039595.5916309</v>
       </c>
       <c r="H111" s="12" t="inlineStr">
         <is>
@@ -8725,16 +8721,20 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L111" s="14" t="n">
-        <v>16.39158633355182</v>
+      <c r="L111" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M111" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N111" s="14" t="n">
-        <v>0.00356793135156139</v>
+      <c r="N111" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O111" s="15" t="inlineStr">
         <is>
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="Q111" s="13" t="n">
-        <v>0.4506082204853535</v>
+        <v>0.14061408</v>
       </c>
       <c r="R111" s="14" t="n">
-        <v>-15.80287766054419</v>
+        <v>-49.45872020700714</v>
       </c>
     </row>
     <row r="112">
@@ -8759,31 +8759,31 @@
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>ENW.L</t>
+          <t>VAL-WT</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Enwell Energy plc</t>
+          <t>Valaris Limited</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oil, Gas &amp; Consumable </t>
+          <t>nan</t>
         </is>
       </c>
       <c r="G112" s="11" t="n">
-        <v>52512980.67904043</v>
+        <v>663201000</v>
       </c>
       <c r="H112" s="12" t="inlineStr">
         <is>
@@ -8796,15 +8796,11 @@
       <c r="J112" s="14" t="n">
         <v>200</v>
       </c>
-      <c r="K112" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L112" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="K112" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="14" t="n">
+        <v>496.4256688394619</v>
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
@@ -8826,11 +8822,15 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q112" s="13" t="n">
-        <v>0.3210329</v>
-      </c>
-      <c r="R112" s="14" t="n">
-        <v>-3.33441365802889</v>
+      <c r="Q112" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R112" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -11099,42 +11099,42 @@
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
-          <t>000700.KS</t>
+          <t>600636.SS</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>Eusu Holdings Co., Ltd.</t>
+          <t xml:space="preserve">China Reform Culture Holdings </t>
         </is>
       </c>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="E142" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F142" s="10" t="inlineStr">
         <is>
-          <t>Marine</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="G142" s="11" t="n">
-        <v>111908520.2591061</v>
-      </c>
-      <c r="H142" s="16" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>110866736.1118813</v>
+      </c>
+      <c r="H142" s="12" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="I142" s="13" t="n">
         <v>1.7004</v>
       </c>
       <c r="J142" s="14" t="n">
-        <v>113.36</v>
+        <v>170.04</v>
       </c>
       <c r="K142" s="15" t="inlineStr">
         <is>
@@ -11161,14 +11161,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="P142" s="13" t="n">
-        <v>1.426</v>
+      <c r="P142" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q142" s="13" t="n">
-        <v>0.4231442442328305</v>
+        <v>0.42846406</v>
       </c>
       <c r="R142" s="14" t="n">
-        <v>18.37489221292608</v>
+        <v>-15.94158732169212</v>
       </c>
     </row>
     <row r="143">
@@ -11177,42 +11179,42 @@
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>600636.SS</t>
+          <t>000700.KS</t>
         </is>
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">China Reform Culture Holdings </t>
+          <t>Eusu Holdings Co., Ltd.</t>
         </is>
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E143" s="10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F143" s="10" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Marine</t>
         </is>
       </c>
       <c r="G143" s="11" t="n">
-        <v>110866736.1118813</v>
-      </c>
-      <c r="H143" s="12" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>111908520.2591061</v>
+      </c>
+      <c r="H143" s="16" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="I143" s="13" t="n">
         <v>1.7004</v>
       </c>
       <c r="J143" s="14" t="n">
-        <v>170.04</v>
+        <v>113.36</v>
       </c>
       <c r="K143" s="15" t="inlineStr">
         <is>
@@ -11239,16 +11241,14 @@
           <t>–</t>
         </is>
       </c>
-      <c r="P143" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P143" s="13" t="n">
+        <v>1.426</v>
       </c>
       <c r="Q143" s="13" t="n">
-        <v>0.42846406</v>
+        <v>0.4231442442328305</v>
       </c>
       <c r="R143" s="14" t="n">
-        <v>-15.94158732169212</v>
+        <v>18.37489221292608</v>
       </c>
     </row>
     <row r="144">
@@ -13899,31 +13899,31 @@
       </c>
       <c r="B178" s="7" t="inlineStr">
         <is>
-          <t>9085.S</t>
+          <t>00806K.KS</t>
         </is>
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>Hokkaido Chuo Bus Co., Ltd.</t>
+          <t>Daeduck Co.,Ltd.</t>
         </is>
       </c>
       <c r="D178" s="9" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E178" s="10" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F178" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hotels, Restaurants &amp; </t>
+          <t xml:space="preserve">Electronic Equipment, </t>
         </is>
       </c>
       <c r="G178" s="11" t="n">
-        <v>65233794.31658478</v>
+        <v>217532999.5775423</v>
       </c>
       <c r="H178" s="12" t="inlineStr">
         <is>
@@ -13962,13 +13962,13 @@
         </is>
       </c>
       <c r="P178" s="13" t="n">
-        <v>0.674</v>
+        <v>3.892989341476291</v>
       </c>
       <c r="Q178" s="13" t="n">
-        <v>0.3224082</v>
+        <v>0.8024502801984631</v>
       </c>
       <c r="R178" s="14" t="n">
-        <v>16.01529251018316</v>
+        <v>19.82019773674833</v>
       </c>
     </row>
     <row r="179">
@@ -13977,31 +13977,31 @@
       </c>
       <c r="B179" s="7" t="inlineStr">
         <is>
-          <t>00806K.KS</t>
+          <t>9085.S</t>
         </is>
       </c>
       <c r="C179" s="8" t="inlineStr">
         <is>
-          <t>Daeduck Co.,Ltd.</t>
+          <t>Hokkaido Chuo Bus Co., Ltd.</t>
         </is>
       </c>
       <c r="D179" s="9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="E179" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F179" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electronic Equipment, </t>
+          <t xml:space="preserve">Hotels, Restaurants &amp; </t>
         </is>
       </c>
       <c r="G179" s="11" t="n">
-        <v>217532999.5775423</v>
+        <v>65233794.31658478</v>
       </c>
       <c r="H179" s="12" t="inlineStr">
         <is>
@@ -14040,13 +14040,13 @@
         </is>
       </c>
       <c r="P179" s="13" t="n">
-        <v>3.892989341476291</v>
+        <v>0.674</v>
       </c>
       <c r="Q179" s="13" t="n">
-        <v>0.8024502801984631</v>
+        <v>0.3224082</v>
       </c>
       <c r="R179" s="14" t="n">
-        <v>19.82019773674833</v>
+        <v>16.01529251018316</v>
       </c>
     </row>
     <row r="180">
@@ -20053,17 +20053,17 @@
       </c>
       <c r="B257" s="7" t="inlineStr">
         <is>
-          <t>XNET</t>
+          <t>NRG.PA</t>
         </is>
       </c>
       <c r="C257" s="8" t="inlineStr">
         <is>
-          <t>Xunlei Ltd</t>
+          <t>NRJ Group SA</t>
         </is>
       </c>
       <c r="D257" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E257" s="10" t="inlineStr">
@@ -20073,11 +20073,11 @@
       </c>
       <c r="F257" s="10" t="inlineStr">
         <is>
-          <t>Diversified Telecommun</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G257" s="11" t="n">
-        <v>318702240</v>
+        <v>562814031.6885223</v>
       </c>
       <c r="H257" s="12" t="inlineStr">
         <is>
@@ -20085,26 +20085,30 @@
         </is>
       </c>
       <c r="I257" s="13" t="n">
-        <v>1.2264</v>
+        <v>1.2242</v>
       </c>
       <c r="J257" s="14" t="n">
-        <v>81.76000000000001</v>
+        <v>81.61</v>
       </c>
       <c r="K257" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L257" s="14" t="n">
-        <v>16.10908037546269</v>
+      <c r="L257" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M257" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N257" s="14" t="n">
-        <v>0</v>
+      <c r="N257" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O257" s="15" t="inlineStr">
         <is>
@@ -20112,13 +20116,13 @@
         </is>
       </c>
       <c r="P257" s="13" t="n">
-        <v>5.063</v>
+        <v>2.197</v>
       </c>
       <c r="Q257" s="13" t="n">
-        <v>0.2320380985386871</v>
+        <v>0.6433824</v>
       </c>
       <c r="R257" s="14" t="n">
-        <v>7.95171435327057</v>
+        <v>9.863412864787669</v>
       </c>
     </row>
   </sheetData>

--- a/forensic_xr_book.xlsx
+++ b/forensic_xr_book.xlsx
@@ -793,10 +793,10 @@
         <v>8.86438309679353</v>
       </c>
       <c r="S8" s="13" t="n">
-        <v>-4.39412577030526</v>
+        <v>-4.39412577</v>
       </c>
       <c r="T8" s="14" t="n">
-        <v>-9.20303990747832</v>
+        <v>-9.203039907000001</v>
       </c>
       <c r="U8" s="15" t="inlineStr">
         <is>
@@ -893,13 +893,13 @@
         <v>37.04623266917117</v>
       </c>
       <c r="S9" s="13" t="n">
-        <v>-2.487497907686699</v>
+        <v>-2.487497908</v>
       </c>
       <c r="T9" s="14" t="n">
-        <v>-5.35365203107315</v>
+        <v>-5.353652031</v>
       </c>
       <c r="U9" s="13" t="n">
-        <v>2.592561619210846</v>
+        <v>2.592561619</v>
       </c>
       <c r="V9" s="13" t="n">
         <v>0</v>
@@ -985,10 +985,10 @@
         <v>37.65473555194727</v>
       </c>
       <c r="S10" s="13" t="n">
-        <v>-3.193034755467473</v>
+        <v>-3.193034755</v>
       </c>
       <c r="T10" s="14" t="n">
-        <v>-14.09829013872459</v>
+        <v>-14.09829014</v>
       </c>
       <c r="U10" s="15" t="inlineStr">
         <is>
@@ -1085,13 +1085,13 @@
         <v>39.63325301600989</v>
       </c>
       <c r="S11" s="13" t="n">
-        <v>-2.593774308137297</v>
+        <v>-2.593774308</v>
       </c>
       <c r="T11" s="14" t="n">
-        <v>-1.63055278430605</v>
+        <v>-1.630552784</v>
       </c>
       <c r="U11" s="13" t="n">
-        <v>10.06191719673139</v>
+        <v>10.0619172</v>
       </c>
       <c r="V11" s="13" t="n">
         <v>0</v>
@@ -1181,10 +1181,10 @@
         <v>43.41950981183043</v>
       </c>
       <c r="S12" s="13" t="n">
-        <v>-4.386268346199165</v>
+        <v>-4.386268346</v>
       </c>
       <c r="T12" s="14" t="n">
-        <v>-31.0336804141702</v>
+        <v>-31.03368041</v>
       </c>
       <c r="U12" s="15" t="inlineStr">
         <is>
@@ -1281,13 +1281,13 @@
         <v>66.45259291149884</v>
       </c>
       <c r="S13" s="13" t="n">
-        <v>-3.799335677153871</v>
+        <v>-3.799335677</v>
       </c>
       <c r="T13" s="14" t="n">
-        <v>-10.85595730653118</v>
+        <v>-10.85595731</v>
       </c>
       <c r="U13" s="13" t="n">
-        <v>16.37526827818598</v>
+        <v>16.37526828</v>
       </c>
       <c r="V13" s="13" t="n">
         <v>0</v>
@@ -1379,13 +1379,13 @@
         <v>22.38999653955031</v>
       </c>
       <c r="S14" s="13" t="n">
-        <v>-2.26293606280508</v>
+        <v>-2.262936063</v>
       </c>
       <c r="T14" s="14" t="n">
-        <v>-0.77385238863351</v>
+        <v>-0.7738523885999999</v>
       </c>
       <c r="U14" s="13" t="n">
-        <v>1.212661613909942</v>
+        <v>1.212661614</v>
       </c>
       <c r="V14" s="13" t="n">
         <v>0</v>
@@ -1477,13 +1477,13 @@
         <v>2.61472718142236</v>
       </c>
       <c r="S15" s="13" t="n">
-        <v>-2.253029487073428</v>
+        <v>-2.253029487</v>
       </c>
       <c r="T15" s="14" t="n">
-        <v>-2.73730801795548</v>
+        <v>-2.737308018</v>
       </c>
       <c r="U15" s="13" t="n">
-        <v>2.782840682101525</v>
+        <v>2.782840682</v>
       </c>
       <c r="V15" s="13" t="n">
         <v>0</v>
@@ -1575,13 +1575,13 @@
         <v>21.53375486044041</v>
       </c>
       <c r="S16" s="13" t="n">
-        <v>-2.853689556030607</v>
+        <v>-2.853689556</v>
       </c>
       <c r="T16" s="14" t="n">
-        <v>-4.42453237670541</v>
+        <v>-4.424532376999999</v>
       </c>
       <c r="U16" s="13" t="n">
-        <v>1.577787661060819</v>
+        <v>1.577787661</v>
       </c>
       <c r="V16" s="13" t="n">
         <v>0</v>
@@ -1673,13 +1673,13 @@
         <v>21.16964636477932</v>
       </c>
       <c r="S17" s="13" t="n">
-        <v>-2.580363332198487</v>
+        <v>-2.580363332</v>
       </c>
       <c r="T17" s="14" t="n">
-        <v>-3.7081761641262</v>
+        <v>-3.708176164</v>
       </c>
       <c r="U17" s="13" t="n">
-        <v>1.631550563863251</v>
+        <v>1.631550564</v>
       </c>
       <c r="V17" s="13" t="n">
         <v>0</v>
@@ -1771,13 +1771,13 @@
         <v>29.46091108514986</v>
       </c>
       <c r="S18" s="13" t="n">
-        <v>-2.75609704498821</v>
+        <v>-2.756097045</v>
       </c>
       <c r="T18" s="14" t="n">
-        <v>-7.11457560143953</v>
+        <v>-7.114575601</v>
       </c>
       <c r="U18" s="13" t="n">
-        <v>4.14336591577073</v>
+        <v>4.143365916</v>
       </c>
       <c r="V18" s="13" t="n">
         <v>0</v>
@@ -1869,13 +1869,13 @@
         <v>13.80142515922356</v>
       </c>
       <c r="S19" s="13" t="n">
-        <v>-2.236761084610325</v>
+        <v>-2.236761085</v>
       </c>
       <c r="T19" s="14" t="n">
-        <v>1.89328246040004</v>
+        <v>1.89328246</v>
       </c>
       <c r="U19" s="13" t="n">
-        <v>0.7293947531501755</v>
+        <v>0.7293947532</v>
       </c>
       <c r="V19" s="13" t="n">
         <v>0</v>
@@ -1967,10 +1967,10 @@
         <v>25.15386227734993</v>
       </c>
       <c r="S20" s="13" t="n">
-        <v>-2.903284763967113</v>
+        <v>-2.903284764</v>
       </c>
       <c r="T20" s="14" t="n">
-        <v>-63.88686072859065</v>
+        <v>-63.88686073</v>
       </c>
       <c r="U20" s="15" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="T21" s="14" t="n">
-        <v>26.91665480599999</v>
+        <v>26.91665481</v>
       </c>
       <c r="U21" s="15" t="inlineStr">
         <is>
@@ -2169,13 +2169,13 @@
         </is>
       </c>
       <c r="S22" s="13" t="n">
-        <v>-1.009759798558854</v>
+        <v>-1.009759799</v>
       </c>
       <c r="T22" s="14" t="n">
-        <v>14.17858875880861</v>
+        <v>14.17858876</v>
       </c>
       <c r="U22" s="13" t="n">
-        <v>-15.93577567163382</v>
+        <v>-15.93577567</v>
       </c>
       <c r="V22" s="13" t="n">
         <v>2</v>
@@ -2269,13 +2269,13 @@
         <v>-32.71958452610624</v>
       </c>
       <c r="S23" s="13" t="n">
-        <v>-2.269762967586669</v>
+        <v>-2.269762968</v>
       </c>
       <c r="T23" s="14" t="n">
-        <v>8.74819182674284</v>
+        <v>8.748191826999999</v>
       </c>
       <c r="U23" s="13" t="n">
-        <v>-2.671282804786927</v>
+        <v>-2.671282805</v>
       </c>
       <c r="V23" s="13" t="n">
         <v>0</v>
@@ -2363,13 +2363,13 @@
         <v>-1.49828078875518</v>
       </c>
       <c r="S24" s="13" t="n">
-        <v>-1.521098003145181</v>
+        <v>-1.521098003</v>
       </c>
       <c r="T24" s="14" t="n">
-        <v>24.21660815436931</v>
+        <v>24.21660815</v>
       </c>
       <c r="U24" s="13" t="n">
-        <v>-0.0121153376723886</v>
+        <v>-0.01211533767</v>
       </c>
       <c r="V24" s="13" t="n">
         <v>2</v>
@@ -2461,13 +2461,13 @@
         <v>-11.56907985022138</v>
       </c>
       <c r="S25" s="13" t="n">
-        <v>-2.102535343726942</v>
+        <v>-2.102535344</v>
       </c>
       <c r="T25" s="14" t="n">
-        <v>3.28227837712115</v>
+        <v>3.282278377</v>
       </c>
       <c r="U25" s="13" t="n">
-        <v>-0.3725603710194092</v>
+        <v>-0.372560371</v>
       </c>
       <c r="V25" s="13" t="n">
         <v>0</v>
@@ -2557,13 +2557,13 @@
         </is>
       </c>
       <c r="S26" s="13" t="n">
-        <v>-1.506554119245246</v>
+        <v>-1.506554119</v>
       </c>
       <c r="T26" s="14" t="n">
-        <v>-2.48843016029814</v>
+        <v>-2.48843016</v>
       </c>
       <c r="U26" s="13" t="n">
-        <v>7.680526366703112</v>
+        <v>7.680526367</v>
       </c>
       <c r="V26" s="13" t="n">
         <v>0</v>
@@ -2651,13 +2651,13 @@
         </is>
       </c>
       <c r="S27" s="13" t="n">
-        <v>-1.018282639818201</v>
+        <v>-1.01828264</v>
       </c>
       <c r="T27" s="14" t="n">
-        <v>-5.91762657099095</v>
+        <v>-5.917626571</v>
       </c>
       <c r="U27" s="13" t="n">
-        <v>1.126115652220573</v>
+        <v>1.126115652</v>
       </c>
       <c r="V27" s="13" t="n">
         <v>2</v>
@@ -2747,13 +2747,13 @@
         <v>0.03494303267047</v>
       </c>
       <c r="S28" s="13" t="n">
-        <v>-2.401264355199933</v>
+        <v>-2.401264355</v>
       </c>
       <c r="T28" s="14" t="n">
-        <v>3.37594750781244</v>
+        <v>3.375947508</v>
       </c>
       <c r="U28" s="13" t="n">
-        <v>0.5232374373702857</v>
+        <v>0.5232374373999999</v>
       </c>
       <c r="V28" s="13" t="n">
         <v>0</v>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="T30" s="14" t="n">
-        <v>-7.3590949836296</v>
+        <v>-7.359094984</v>
       </c>
       <c r="U30" s="13" t="n">
-        <v>1.236438216786408</v>
+        <v>1.236438217</v>
       </c>
       <c r="V30" s="13" t="n">
         <v>0</v>
@@ -3137,13 +3137,13 @@
         <v>41.66640904663798</v>
       </c>
       <c r="S32" s="13" t="n">
-        <v>-2.134336787646643</v>
+        <v>-2.134336788</v>
       </c>
       <c r="T32" s="14" t="n">
-        <v>-4.60848633381161</v>
+        <v>-4.608486333999999</v>
       </c>
       <c r="U32" s="13" t="n">
-        <v>2.834704504253627</v>
+        <v>2.834704504</v>
       </c>
       <c r="V32" s="13" t="n">
         <v>0</v>
@@ -3331,13 +3331,13 @@
         <v>20.94380126436537</v>
       </c>
       <c r="S34" s="13" t="n">
-        <v>-2.564030435448247</v>
+        <v>-2.564030435</v>
       </c>
       <c r="T34" s="14" t="n">
-        <v>-2.52520280094697</v>
+        <v>-2.525202801</v>
       </c>
       <c r="U34" s="13" t="n">
-        <v>1.338137265297392</v>
+        <v>1.338137265</v>
       </c>
       <c r="V34" s="13" t="n">
         <v>0</v>
@@ -3425,13 +3425,13 @@
         <v>41.63159677303595</v>
       </c>
       <c r="S35" s="13" t="n">
-        <v>-1.888825130302963</v>
+        <v>-1.88882513</v>
       </c>
       <c r="T35" s="14" t="n">
-        <v>-17.6340649527659</v>
+        <v>-17.63406495</v>
       </c>
       <c r="U35" s="13" t="n">
-        <v>18.57377049180328</v>
+        <v>18.57377049</v>
       </c>
       <c r="V35" s="13" t="n">
         <v>0</v>
@@ -3519,13 +3519,13 @@
         <v>18.28184430168729</v>
       </c>
       <c r="S36" s="13" t="n">
-        <v>-2.597586869550986</v>
+        <v>-2.59758687</v>
       </c>
       <c r="T36" s="14" t="n">
-        <v>-2.95634080125069</v>
+        <v>-2.956340801</v>
       </c>
       <c r="U36" s="13" t="n">
-        <v>1.576657763529952</v>
+        <v>1.576657764</v>
       </c>
       <c r="V36" s="13" t="n">
         <v>0</v>
@@ -3617,13 +3617,13 @@
         <v>16.48902767594668</v>
       </c>
       <c r="S37" s="13" t="n">
-        <v>-1.813247368484788</v>
+        <v>-1.813247368</v>
       </c>
       <c r="T37" s="14" t="n">
-        <v>-1.6387095183207</v>
+        <v>-1.638709518</v>
       </c>
       <c r="U37" s="13" t="n">
-        <v>1.414892230519857</v>
+        <v>1.414892231</v>
       </c>
       <c r="V37" s="13" t="n">
         <v>0</v>
@@ -3711,13 +3711,13 @@
         <v>8.273822214057889</v>
       </c>
       <c r="S38" s="13" t="n">
-        <v>-1.622202054027305</v>
+        <v>-1.622202054</v>
       </c>
       <c r="T38" s="14" t="n">
-        <v>0.9714577594072601</v>
+        <v>0.9714577594</v>
       </c>
       <c r="U38" s="13" t="n">
-        <v>0.8414489398193569</v>
+        <v>0.8414489398</v>
       </c>
       <c r="V38" s="13" t="n">
         <v>1</v>
@@ -3809,13 +3809,13 @@
         <v>19.77089345517098</v>
       </c>
       <c r="S39" s="13" t="n">
-        <v>-2.900498482219698</v>
+        <v>-2.900498482</v>
       </c>
       <c r="T39" s="14" t="n">
-        <v>-3.54043826358348</v>
+        <v>-3.540438264</v>
       </c>
       <c r="U39" s="13" t="n">
-        <v>1.661286747999775</v>
+        <v>1.661286748</v>
       </c>
       <c r="V39" s="13" t="n">
         <v>0</v>
@@ -3905,10 +3905,10 @@
         <v>20.88112286937462</v>
       </c>
       <c r="S40" s="13" t="n">
-        <v>-3.955059654243775</v>
+        <v>-3.955059654</v>
       </c>
       <c r="T40" s="14" t="n">
-        <v>-23.33410513269274</v>
+        <v>-23.33410513</v>
       </c>
       <c r="U40" s="15" t="inlineStr">
         <is>
@@ -4003,10 +4003,10 @@
         <v>-32.50904453448516</v>
       </c>
       <c r="S41" s="13" t="n">
-        <v>-0.539281509554925</v>
+        <v>-0.5392815096</v>
       </c>
       <c r="T41" s="14" t="n">
-        <v>-1.19508555687761</v>
+        <v>-1.195085557</v>
       </c>
       <c r="U41" s="15" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>31.64514479457069</v>
       </c>
       <c r="S42" s="13" t="n">
-        <v>-2.415262997027154</v>
+        <v>-2.415262997</v>
       </c>
       <c r="T42" s="14" t="n">
-        <v>-2.61537962843875</v>
+        <v>-2.615379628</v>
       </c>
       <c r="U42" s="13" t="n">
-        <v>2.020203942895989</v>
+        <v>2.020203943</v>
       </c>
       <c r="V42" s="13" t="n">
         <v>0</v>
@@ -4201,13 +4201,13 @@
         <v>74.56133863205552</v>
       </c>
       <c r="S43" s="13" t="n">
-        <v>-3.539994539717774</v>
+        <v>-3.53999454</v>
       </c>
       <c r="T43" s="14" t="n">
-        <v>-13.07293318520452</v>
+        <v>-13.07293319</v>
       </c>
       <c r="U43" s="13" t="n">
-        <v>5.162561371308396</v>
+        <v>5.162561371</v>
       </c>
       <c r="V43" s="13" t="n">
         <v>1</v>
@@ -4299,13 +4299,13 @@
         <v>20.07137064026483</v>
       </c>
       <c r="S44" s="13" t="n">
-        <v>-2.464797220223432</v>
+        <v>-2.46479722</v>
       </c>
       <c r="T44" s="14" t="n">
-        <v>-3.37613279668043</v>
+        <v>-3.376132797</v>
       </c>
       <c r="U44" s="13" t="n">
-        <v>3.333200473650932</v>
+        <v>3.333200474</v>
       </c>
       <c r="V44" s="13" t="n">
         <v>0</v>
@@ -4397,13 +4397,13 @@
         <v>-6.288390804467669</v>
       </c>
       <c r="S45" s="13" t="n">
-        <v>-2.266460097343455</v>
+        <v>-2.266460097</v>
       </c>
       <c r="T45" s="14" t="n">
-        <v>-1.27103907815265</v>
+        <v>-1.271039078</v>
       </c>
       <c r="U45" s="13" t="n">
-        <v>2.340699667657862</v>
+        <v>2.340699668</v>
       </c>
       <c r="V45" s="13" t="n">
         <v>0</v>
@@ -4493,13 +4493,13 @@
         <v>4.71491443732356</v>
       </c>
       <c r="S46" s="13" t="n">
-        <v>-2.12233867234492</v>
+        <v>-2.122338672</v>
       </c>
       <c r="T46" s="14" t="n">
-        <v>-7.55288046334616</v>
+        <v>-7.552880463</v>
       </c>
       <c r="U46" s="13" t="n">
-        <v>7.867915465898175</v>
+        <v>7.867915466</v>
       </c>
       <c r="V46" s="13" t="n">
         <v>0</v>
@@ -4587,13 +4587,13 @@
         <v>-14.37127256435016</v>
       </c>
       <c r="S47" s="13" t="n">
-        <v>-3.033126884083533</v>
+        <v>-3.033126884</v>
       </c>
       <c r="T47" s="14" t="n">
-        <v>-13.55918630855546</v>
+        <v>-13.55918631</v>
       </c>
       <c r="U47" s="13" t="n">
-        <v>4.472602860714508</v>
+        <v>4.472602861</v>
       </c>
       <c r="V47" s="13" t="n">
         <v>0</v>
@@ -4685,13 +4685,13 @@
         <v>33.75258674992358</v>
       </c>
       <c r="S48" s="13" t="n">
-        <v>-1.547576703773172</v>
+        <v>-1.547576704</v>
       </c>
       <c r="T48" s="14" t="n">
-        <v>-4.23253296344304</v>
+        <v>-4.232532963</v>
       </c>
       <c r="U48" s="13" t="n">
-        <v>7.304712583948644</v>
+        <v>7.304712584</v>
       </c>
       <c r="V48" s="13" t="n">
         <v>0</v>
@@ -4785,13 +4785,13 @@
         <v>-53.84157050148208</v>
       </c>
       <c r="S49" s="13" t="n">
-        <v>-1.19054060192728</v>
+        <v>-1.190540602</v>
       </c>
       <c r="T49" s="14" t="n">
-        <v>8.306245669699889</v>
+        <v>8.306245669999999</v>
       </c>
       <c r="U49" s="13" t="n">
-        <v>-2.37152796025354</v>
+        <v>-2.37152796</v>
       </c>
       <c r="V49" s="13" t="n">
         <v>2</v>
@@ -4883,13 +4883,13 @@
         <v>19.99107056150671</v>
       </c>
       <c r="S50" s="13" t="n">
-        <v>-2.786757030694751</v>
+        <v>-2.786757031</v>
       </c>
       <c r="T50" s="14" t="n">
-        <v>-1.47520503608841</v>
+        <v>-1.475205036</v>
       </c>
       <c r="U50" s="13" t="n">
-        <v>1.190317224042762</v>
+        <v>1.190317224</v>
       </c>
       <c r="V50" s="13" t="n">
         <v>0</v>
@@ -4981,13 +4981,13 @@
         <v>-23.09652103056119</v>
       </c>
       <c r="S51" s="13" t="n">
-        <v>-1.594030953435576</v>
+        <v>-1.594030953</v>
       </c>
       <c r="T51" s="14" t="n">
-        <v>10.95343633810448</v>
+        <v>10.95343634</v>
       </c>
       <c r="U51" s="13" t="n">
-        <v>0.1433587537173075</v>
+        <v>0.1433587537</v>
       </c>
       <c r="V51" s="13" t="n">
         <v>3</v>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="T52" s="14" t="n">
-        <v>0.52375844008329</v>
+        <v>0.5237584400999999</v>
       </c>
       <c r="U52" s="15" t="inlineStr">
         <is>
@@ -5179,10 +5179,10 @@
         <v>10.10651828310898</v>
       </c>
       <c r="S53" s="13" t="n">
-        <v>-5.110505794665974</v>
+        <v>-5.110505795</v>
       </c>
       <c r="T53" s="14" t="n">
-        <v>-34.83572197622183</v>
+        <v>-34.83572198</v>
       </c>
       <c r="U53" s="15" t="inlineStr">
         <is>
@@ -5275,10 +5275,10 @@
         <v>64.10263948586179</v>
       </c>
       <c r="S54" s="13" t="n">
-        <v>-3.655310895526517</v>
+        <v>-3.655310896</v>
       </c>
       <c r="T54" s="14" t="n">
-        <v>-19.1852058721071</v>
+        <v>-19.18520587</v>
       </c>
       <c r="U54" s="15" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>20.31337854120659</v>
       </c>
       <c r="S55" s="13" t="n">
-        <v>-2.915767544915927</v>
+        <v>-2.915767545</v>
       </c>
       <c r="T55" s="14" t="n">
-        <v>-7.694947517719259</v>
+        <v>-7.694947518</v>
       </c>
       <c r="U55" s="13" t="n">
-        <v>5.40915150352493</v>
+        <v>5.409151504</v>
       </c>
       <c r="V55" s="13" t="n">
         <v>0</v>
@@ -5473,13 +5473,13 @@
         <v>-12.1481312689599</v>
       </c>
       <c r="S56" s="13" t="n">
-        <v>-2.397091308269596</v>
+        <v>-2.397091308</v>
       </c>
       <c r="T56" s="14" t="n">
-        <v>4.24596287367906</v>
+        <v>4.245962874</v>
       </c>
       <c r="U56" s="13" t="n">
-        <v>-0.6145844712279552</v>
+        <v>-0.6145844712</v>
       </c>
       <c r="V56" s="13" t="n">
         <v>0</v>
@@ -5567,13 +5567,13 @@
         <v>45.17405957249845</v>
       </c>
       <c r="S57" s="13" t="n">
-        <v>-2.187318440315736</v>
+        <v>-2.18731844</v>
       </c>
       <c r="T57" s="14" t="n">
-        <v>-10.4550251586428</v>
+        <v>-10.45502516</v>
       </c>
       <c r="U57" s="13" t="n">
-        <v>9.761624594799772</v>
+        <v>9.761624595000001</v>
       </c>
       <c r="V57" s="13" t="n">
         <v>0</v>
@@ -5661,13 +5661,13 @@
         <v>-20.12284630158316</v>
       </c>
       <c r="S58" s="13" t="n">
-        <v>-2.218858354961893</v>
+        <v>-2.218858355</v>
       </c>
       <c r="T58" s="14" t="n">
-        <v>1.9824855673355</v>
+        <v>1.982485567</v>
       </c>
       <c r="U58" s="13" t="n">
-        <v>-0.4112771984162799</v>
+        <v>-0.4112771984</v>
       </c>
       <c r="V58" s="13" t="n">
         <v>0</v>
@@ -5951,13 +5951,13 @@
         <v>15.60904020523187</v>
       </c>
       <c r="S61" s="13" t="n">
-        <v>-3.10391346091711</v>
+        <v>-3.103913461</v>
       </c>
       <c r="T61" s="14" t="n">
-        <v>-3.44713733346922</v>
+        <v>-3.447137333</v>
       </c>
       <c r="U61" s="13" t="n">
-        <v>1.69158863487549</v>
+        <v>1.691588635</v>
       </c>
       <c r="V61" s="13" t="n">
         <v>0</v>
@@ -6049,13 +6049,13 @@
         <v>19.70145509137191</v>
       </c>
       <c r="S62" s="13" t="n">
-        <v>-1.71750773878683</v>
+        <v>-1.717507739</v>
       </c>
       <c r="T62" s="14" t="n">
-        <v>-3.24920277425568</v>
+        <v>-3.249202774</v>
       </c>
       <c r="U62" s="13" t="n">
-        <v>2.878789439248119</v>
+        <v>2.878789439</v>
       </c>
       <c r="V62" s="13" t="n">
         <v>2</v>
@@ -6149,13 +6149,13 @@
         <v>42.0548197766043</v>
       </c>
       <c r="S63" s="13" t="n">
-        <v>-2.273921311576543</v>
+        <v>-2.273921312</v>
       </c>
       <c r="T63" s="14" t="n">
-        <v>-4.970641742763529</v>
+        <v>-4.970641743</v>
       </c>
       <c r="U63" s="13" t="n">
-        <v>4.13753650491572</v>
+        <v>4.137536505</v>
       </c>
       <c r="V63" s="13" t="n">
         <v>0</v>
@@ -6239,13 +6239,13 @@
         <v>2.87339886762939</v>
       </c>
       <c r="S64" s="13" t="n">
-        <v>-3.017540559069912</v>
+        <v>-3.017540559</v>
       </c>
       <c r="T64" s="14" t="n">
-        <v>-10.41398480622095</v>
+        <v>-10.41398481</v>
       </c>
       <c r="U64" s="13" t="n">
-        <v>3.347595010319696</v>
+        <v>3.34759501</v>
       </c>
       <c r="V64" s="13" t="n">
         <v>0</v>
@@ -6337,13 +6337,13 @@
         <v>28.15266433787464</v>
       </c>
       <c r="S65" s="13" t="n">
-        <v>-2.406443945481648</v>
+        <v>-2.406443945</v>
       </c>
       <c r="T65" s="14" t="n">
-        <v>-7.49041723814598</v>
+        <v>-7.490417237999999</v>
       </c>
       <c r="U65" s="13" t="n">
-        <v>8.625723127634025</v>
+        <v>8.625723128000001</v>
       </c>
       <c r="V65" s="13" t="n">
         <v>1</v>
@@ -6429,13 +6429,13 @@
         <v>26.51907448672242</v>
       </c>
       <c r="S66" s="13" t="n">
-        <v>-1.891212564582076</v>
+        <v>-1.891212565</v>
       </c>
       <c r="T66" s="14" t="n">
-        <v>-12.02911738686017</v>
+        <v>-12.02911739</v>
       </c>
       <c r="U66" s="13" t="n">
-        <v>2.22729893131042</v>
+        <v>2.227298931</v>
       </c>
       <c r="V66" s="13" t="n">
         <v>0</v>
@@ -6523,13 +6523,13 @@
         <v>16.27984485454658</v>
       </c>
       <c r="S67" s="13" t="n">
-        <v>-3.083713325618227</v>
+        <v>-3.083713326</v>
       </c>
       <c r="T67" s="14" t="n">
-        <v>-10.25272874637451</v>
+        <v>-10.25272875</v>
       </c>
       <c r="U67" s="13" t="n">
-        <v>6.041894776729522</v>
+        <v>6.041894777</v>
       </c>
       <c r="V67" s="13" t="n">
         <v>0</v>
@@ -6625,13 +6625,13 @@
         </is>
       </c>
       <c r="S68" s="13" t="n">
-        <v>-2.83115164929172</v>
+        <v>-2.831151649</v>
       </c>
       <c r="T68" s="14" t="n">
-        <v>-0.27710248857647</v>
+        <v>-0.2771024886</v>
       </c>
       <c r="U68" s="13" t="n">
-        <v>1.540084632785256</v>
+        <v>1.540084633</v>
       </c>
       <c r="V68" s="13" t="n">
         <v>0</v>
@@ -6723,13 +6723,13 @@
         <v>-6.960172812293069</v>
       </c>
       <c r="S69" s="13" t="n">
-        <v>-2.572814048890368</v>
+        <v>-2.572814049</v>
       </c>
       <c r="T69" s="14" t="n">
-        <v>1.21472033813956</v>
+        <v>1.214720338</v>
       </c>
       <c r="U69" s="13" t="n">
-        <v>0.6897252278543528</v>
+        <v>0.6897252279</v>
       </c>
       <c r="V69" s="13" t="n">
         <v>0</v>
@@ -6821,13 +6821,13 @@
         <v>11.1128588832898</v>
       </c>
       <c r="S70" s="13" t="n">
-        <v>-2.032138385342544</v>
+        <v>-2.032138385</v>
       </c>
       <c r="T70" s="14" t="n">
-        <v>-3.35239639417357</v>
+        <v>-3.352396394</v>
       </c>
       <c r="U70" s="13" t="n">
-        <v>12.81857719788754</v>
+        <v>12.8185772</v>
       </c>
       <c r="V70" s="13" t="n">
         <v>0</v>
@@ -6919,13 +6919,13 @@
         <v>-1.36426494994613</v>
       </c>
       <c r="S71" s="13" t="n">
-        <v>-2.338860176704115</v>
+        <v>-2.338860177</v>
       </c>
       <c r="T71" s="14" t="n">
-        <v>1.66375692498187</v>
+        <v>1.663756925</v>
       </c>
       <c r="U71" s="13" t="n">
-        <v>0.1093208892793883</v>
+        <v>0.1093208893</v>
       </c>
       <c r="V71" s="13" t="n">
         <v>1</v>
@@ -7017,13 +7017,13 @@
         <v>-67.27614765804543</v>
       </c>
       <c r="S72" s="13" t="n">
-        <v>-1.9892148802657</v>
+        <v>-1.98921488</v>
       </c>
       <c r="T72" s="14" t="n">
-        <v>10.59859238457214</v>
+        <v>10.59859238</v>
       </c>
       <c r="U72" s="13" t="n">
-        <v>-11.26446850303838</v>
+        <v>-11.2644685</v>
       </c>
       <c r="V72" s="13" t="n">
         <v>0</v>
@@ -7111,10 +7111,10 @@
         <v>-39.80210722755725</v>
       </c>
       <c r="S73" s="13" t="n">
-        <v>-2.64345738063497</v>
+        <v>-2.643457381</v>
       </c>
       <c r="T73" s="14" t="n">
-        <v>-2.61945490328657</v>
+        <v>-2.619454903</v>
       </c>
       <c r="U73" s="15" t="inlineStr">
         <is>
@@ -7207,10 +7207,10 @@
         <v>-2.92868160030249</v>
       </c>
       <c r="S74" s="13" t="n">
-        <v>-2.470435792113804</v>
+        <v>-2.470435792</v>
       </c>
       <c r="T74" s="14" t="n">
-        <v>-14.14739211008346</v>
+        <v>-14.14739211</v>
       </c>
       <c r="U74" s="15" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="T75" s="14" t="n">
-        <v>-2.74560638368316</v>
+        <v>-2.745606384</v>
       </c>
       <c r="U75" s="15" t="inlineStr">
         <is>
@@ -7411,13 +7411,13 @@
         <v>23.55565129475746</v>
       </c>
       <c r="S76" s="13" t="n">
-        <v>-1.850188073053291</v>
+        <v>-1.850188073</v>
       </c>
       <c r="T76" s="14" t="n">
-        <v>-3.41456031481761</v>
+        <v>-3.414560315</v>
       </c>
       <c r="U76" s="13" t="n">
-        <v>1.412305817849528</v>
+        <v>1.412305818</v>
       </c>
       <c r="V76" s="13" t="n">
         <v>0</v>
@@ -7609,10 +7609,10 @@
         </is>
       </c>
       <c r="S78" s="13" t="n">
-        <v>-2.340301703200382</v>
+        <v>-2.340301703</v>
       </c>
       <c r="T78" s="14" t="n">
-        <v>-3.88769836650107</v>
+        <v>-3.887698367</v>
       </c>
       <c r="U78" s="15" t="inlineStr">
         <is>
@@ -7705,13 +7705,13 @@
         <v>5.18977421651165</v>
       </c>
       <c r="S79" s="13" t="n">
-        <v>-2.444797287228033</v>
+        <v>-2.444797287</v>
       </c>
       <c r="T79" s="14" t="n">
-        <v>1.69785352430551</v>
+        <v>1.697853524</v>
       </c>
       <c r="U79" s="13" t="n">
-        <v>0.4925352622965156</v>
+        <v>0.4925352623</v>
       </c>
       <c r="V79" s="13" t="n">
         <v>0</v>
@@ -7999,13 +7999,13 @@
         <v>10.50849759768003</v>
       </c>
       <c r="S82" s="13" t="n">
-        <v>-1.397461824669871</v>
+        <v>-1.397461825</v>
       </c>
       <c r="T82" s="14" t="n">
-        <v>-4.289167778248991</v>
+        <v>-4.289167777999999</v>
       </c>
       <c r="U82" s="13" t="n">
-        <v>2.572525537976883</v>
+        <v>2.572525538</v>
       </c>
       <c r="V82" s="13" t="n">
         <v>0</v>
@@ -8091,10 +8091,10 @@
         <v>-45.3968729102715</v>
       </c>
       <c r="S83" s="13" t="n">
-        <v>-3.120047630661008</v>
+        <v>-3.120047631</v>
       </c>
       <c r="T83" s="14" t="n">
-        <v>-3.30002323960027</v>
+        <v>-3.30002324</v>
       </c>
       <c r="U83" s="15" t="inlineStr">
         <is>
@@ -8191,13 +8191,13 @@
         <v>17.0180685132255</v>
       </c>
       <c r="S84" s="13" t="n">
-        <v>-2.759198687787279</v>
+        <v>-2.759198688</v>
       </c>
       <c r="T84" s="14" t="n">
-        <v>-2.53646867261901</v>
+        <v>-2.536468673</v>
       </c>
       <c r="U84" s="13" t="n">
-        <v>6.937621487895388</v>
+        <v>6.937621488</v>
       </c>
       <c r="V84" s="13" t="n">
         <v>0</v>
@@ -8285,13 +8285,13 @@
         <v>14.32846190262853</v>
       </c>
       <c r="S85" s="13" t="n">
-        <v>-2.84499841235601</v>
+        <v>-2.844998412</v>
       </c>
       <c r="T85" s="14" t="n">
-        <v>-7.08707865168539</v>
+        <v>-7.087078652000001</v>
       </c>
       <c r="U85" s="13" t="n">
-        <v>4.165621079046424</v>
+        <v>4.165621079</v>
       </c>
       <c r="V85" s="13" t="n">
         <v>0</v>
@@ -8383,13 +8383,13 @@
         <v>9.2155036493676</v>
       </c>
       <c r="S86" s="13" t="n">
-        <v>-2.694778095656921</v>
+        <v>-2.694778096</v>
       </c>
       <c r="T86" s="14" t="n">
-        <v>1.198970535987</v>
+        <v>1.198970536</v>
       </c>
       <c r="U86" s="13" t="n">
-        <v>0.829957359823134</v>
+        <v>0.8299573598</v>
       </c>
       <c r="V86" s="13" t="n">
         <v>0</v>
@@ -8581,10 +8581,10 @@
         <v>-3.2004042478271</v>
       </c>
       <c r="S88" s="13" t="n">
-        <v>-2.350087004720808</v>
+        <v>-2.350087005</v>
       </c>
       <c r="T88" s="14" t="n">
-        <v>1.91097143974711</v>
+        <v>1.91097144</v>
       </c>
       <c r="U88" s="13" t="n">
         <v>0</v>
@@ -8679,13 +8679,13 @@
         <v>23.08105232049102</v>
       </c>
       <c r="S89" s="13" t="n">
-        <v>-2.868320461072519</v>
+        <v>-2.868320461</v>
       </c>
       <c r="T89" s="14" t="n">
-        <v>-2.65663936463396</v>
+        <v>-2.656639365</v>
       </c>
       <c r="U89" s="13" t="n">
-        <v>1.251214855166556</v>
+        <v>1.251214855</v>
       </c>
       <c r="V89" s="13" t="n">
         <v>0</v>
@@ -8773,13 +8773,13 @@
         <v>20.77303497364105</v>
       </c>
       <c r="S90" s="13" t="n">
-        <v>-2.1295126623623</v>
+        <v>-2.129512662</v>
       </c>
       <c r="T90" s="14" t="n">
-        <v>4.1399586322581</v>
+        <v>4.139958632</v>
       </c>
       <c r="U90" s="13" t="n">
-        <v>0.5138134878477995</v>
+        <v>0.5138134878</v>
       </c>
       <c r="V90" s="13" t="n">
         <v>0</v>
@@ -8867,13 +8867,13 @@
         <v>27.56625747476087</v>
       </c>
       <c r="S91" s="13" t="n">
-        <v>-1.82603559471419</v>
+        <v>-1.826035595</v>
       </c>
       <c r="T91" s="14" t="n">
-        <v>-6.14810102247291</v>
+        <v>-6.148101022</v>
       </c>
       <c r="U91" s="13" t="n">
-        <v>2.641228883798384</v>
+        <v>2.641228884</v>
       </c>
       <c r="V91" s="13" t="n">
         <v>0</v>
@@ -8961,13 +8961,13 @@
         <v>56.1341955303911</v>
       </c>
       <c r="S92" s="13" t="n">
-        <v>-2.60514903619115</v>
+        <v>-2.605149036</v>
       </c>
       <c r="T92" s="14" t="n">
-        <v>-6.74357798713483</v>
+        <v>-6.743577987</v>
       </c>
       <c r="U92" s="13" t="n">
-        <v>4.06564940636471</v>
+        <v>4.065649406</v>
       </c>
       <c r="V92" s="13" t="n">
         <v>0</v>
@@ -9057,13 +9057,13 @@
         <v>28.89971000890849</v>
       </c>
       <c r="S93" s="13" t="n">
-        <v>-2.555213751289213</v>
+        <v>-2.555213751</v>
       </c>
       <c r="T93" s="14" t="n">
-        <v>-1.01236261564495</v>
+        <v>-1.012362616</v>
       </c>
       <c r="U93" s="13" t="n">
-        <v>1.153865617519124</v>
+        <v>1.153865618</v>
       </c>
       <c r="V93" s="13" t="n">
         <v>0</v>
@@ -9157,10 +9157,10 @@
         <v>82.43615074039568</v>
       </c>
       <c r="S94" s="13" t="n">
-        <v>-3.581838434563143</v>
+        <v>-3.581838435</v>
       </c>
       <c r="T94" s="14" t="n">
-        <v>-24.59375334822069</v>
+        <v>-24.59375335</v>
       </c>
       <c r="U94" s="15" t="inlineStr">
         <is>
@@ -9459,13 +9459,13 @@
         <v>5.22212466905032</v>
       </c>
       <c r="S97" s="13" t="n">
-        <v>-2.007615302231857</v>
+        <v>-2.007615302</v>
       </c>
       <c r="T97" s="14" t="n">
-        <v>-0.94689602584207</v>
+        <v>-0.9468960258</v>
       </c>
       <c r="U97" s="13" t="n">
-        <v>2.63525139847558</v>
+        <v>2.635251398</v>
       </c>
       <c r="V97" s="13" t="n">
         <v>2</v>
@@ -9659,10 +9659,10 @@
         <v>-0.07052584403626</v>
       </c>
       <c r="S99" s="13" t="n">
-        <v>-2.336748850821629</v>
+        <v>-2.336748851</v>
       </c>
       <c r="T99" s="14" t="n">
-        <v>4.21930319538247</v>
+        <v>4.219303195</v>
       </c>
       <c r="U99" s="15" t="inlineStr">
         <is>
@@ -9757,10 +9757,10 @@
         <v>-13.1060853033141</v>
       </c>
       <c r="S100" s="13" t="n">
-        <v>-1.50004040483074</v>
+        <v>-1.500040405</v>
       </c>
       <c r="T100" s="14" t="n">
-        <v>-6.35724071404901</v>
+        <v>-6.357240714</v>
       </c>
       <c r="U100" s="15" t="inlineStr">
         <is>
@@ -9857,13 +9857,13 @@
         <v>-17.48409470338235</v>
       </c>
       <c r="S101" s="13" t="n">
-        <v>-2.109318872320537</v>
+        <v>-2.109318872</v>
       </c>
       <c r="T101" s="14" t="n">
-        <v>-0.0656990334309</v>
+        <v>-0.06569903343</v>
       </c>
       <c r="U101" s="13" t="n">
-        <v>1.34842529711449</v>
+        <v>1.348425297</v>
       </c>
       <c r="V101" s="13" t="n">
         <v>1</v>
@@ -9960,7 +9960,7 @@
         </is>
       </c>
       <c r="T102" s="14" t="n">
-        <v>3.77339501313751</v>
+        <v>3.773395013</v>
       </c>
       <c r="U102" s="15" t="inlineStr">
         <is>
@@ -10055,10 +10055,10 @@
         <v>-49.45872020700714</v>
       </c>
       <c r="S103" s="13" t="n">
-        <v>-2.239091206578989</v>
+        <v>-2.239091207</v>
       </c>
       <c r="T103" s="14" t="n">
-        <v>-3.6558091995071</v>
+        <v>-3.6558092</v>
       </c>
       <c r="U103" s="15" t="inlineStr">
         <is>
@@ -10151,10 +10151,10 @@
         <v>-0.08587525535886001</v>
       </c>
       <c r="S104" s="13" t="n">
-        <v>-2.174580805007552</v>
+        <v>-2.174580805</v>
       </c>
       <c r="T104" s="14" t="n">
-        <v>-1.7298305026421</v>
+        <v>-1.729830503</v>
       </c>
       <c r="U104" s="15" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         </is>
       </c>
       <c r="T105" s="14" t="n">
-        <v>23.4689552871371</v>
+        <v>23.46895529</v>
       </c>
       <c r="U105" s="15" t="inlineStr">
         <is>
@@ -10351,10 +10351,10 @@
         <v>5.88765515847855</v>
       </c>
       <c r="S106" s="13" t="n">
-        <v>-2.179280574088794</v>
+        <v>-2.179280574</v>
       </c>
       <c r="T106" s="14" t="n">
-        <v>-4.48430271211064</v>
+        <v>-4.484302712</v>
       </c>
       <c r="U106" s="15" t="inlineStr">
         <is>
@@ -10451,10 +10451,10 @@
         <v>-0.01770960934256</v>
       </c>
       <c r="S107" s="13" t="n">
-        <v>-2.561637716689408</v>
+        <v>-2.561637717</v>
       </c>
       <c r="T107" s="14" t="n">
-        <v>0.73251124757929</v>
+        <v>0.7325112476</v>
       </c>
       <c r="U107" s="15" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="T109" s="14" t="n">
-        <v>-1.22297804480268</v>
+        <v>-1.222978045</v>
       </c>
       <c r="U109" s="15" t="inlineStr">
         <is>
@@ -10743,10 +10743,10 @@
         <v>5.41869452105689</v>
       </c>
       <c r="S110" s="13" t="n">
-        <v>0.0264563698090616</v>
+        <v>0.02645636981</v>
       </c>
       <c r="T110" s="14" t="n">
-        <v>-4.264219668733</v>
+        <v>-4.264219669</v>
       </c>
       <c r="U110" s="15" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
         </is>
       </c>
       <c r="T112" s="14" t="n">
-        <v>-2.50413597459744</v>
+        <v>-2.504135975</v>
       </c>
       <c r="U112" s="15" t="inlineStr">
         <is>
@@ -11049,13 +11049,13 @@
         <v>8.4966969254048</v>
       </c>
       <c r="S113" s="13" t="n">
-        <v>-2.029296398696578</v>
+        <v>-2.029296399</v>
       </c>
       <c r="T113" s="14" t="n">
-        <v>-3.78627595621825</v>
+        <v>-3.786275956</v>
       </c>
       <c r="U113" s="13" t="n">
-        <v>6.433646371762406</v>
+        <v>6.433646372</v>
       </c>
       <c r="V113" s="13" t="n">
         <v>0</v>
@@ -11147,13 +11147,13 @@
         <v>13.31159657511799</v>
       </c>
       <c r="S114" s="13" t="n">
-        <v>-2.579489952690022</v>
+        <v>-2.579489953</v>
       </c>
       <c r="T114" s="14" t="n">
-        <v>-2.07085799331451</v>
+        <v>-2.070857993</v>
       </c>
       <c r="U114" s="13" t="n">
-        <v>1.480845132054703</v>
+        <v>1.480845132</v>
       </c>
       <c r="V114" s="13" t="n">
         <v>0</v>
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="T115" s="14" t="n">
-        <v>-5.72654621500689</v>
+        <v>-5.726546215</v>
       </c>
       <c r="U115" s="15" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         </is>
       </c>
       <c r="T116" s="14" t="n">
-        <v>2.12771632834339</v>
+        <v>2.127716328</v>
       </c>
       <c r="U116" s="15" t="inlineStr">
         <is>
@@ -11445,13 +11445,13 @@
         <v>18.37489221292608</v>
       </c>
       <c r="S117" s="13" t="n">
-        <v>-2.778307688048026</v>
+        <v>-2.778307688</v>
       </c>
       <c r="T117" s="14" t="n">
-        <v>-6.332213787431599</v>
+        <v>-6.332213787000001</v>
       </c>
       <c r="U117" s="13" t="n">
-        <v>2.996280707709857</v>
+        <v>2.996280708</v>
       </c>
       <c r="V117" s="13" t="n">
         <v>0</v>
@@ -11545,10 +11545,10 @@
         <v>-15.94158732169212</v>
       </c>
       <c r="S118" s="13" t="n">
-        <v>-2.934119241031321</v>
+        <v>-2.934119241</v>
       </c>
       <c r="T118" s="14" t="n">
-        <v>-10.66472665917669</v>
+        <v>-10.66472666</v>
       </c>
       <c r="U118" s="15" t="inlineStr">
         <is>
@@ -11647,10 +11647,10 @@
         <v>-2.88310643745674</v>
       </c>
       <c r="S119" s="13" t="n">
-        <v>-2.698656556148066</v>
+        <v>-2.698656556</v>
       </c>
       <c r="T119" s="14" t="n">
-        <v>-2.08999385905122</v>
+        <v>-2.089993859</v>
       </c>
       <c r="U119" s="15" t="inlineStr">
         <is>
@@ -11747,13 +11747,13 @@
         <v>2.51941313424669</v>
       </c>
       <c r="S120" s="13" t="n">
-        <v>-1.284522990958467</v>
+        <v>-1.284522991</v>
       </c>
       <c r="T120" s="14" t="n">
-        <v>0.53842982142132</v>
+        <v>0.5384298214</v>
       </c>
       <c r="U120" s="13" t="n">
-        <v>0.8422449688047844</v>
+        <v>0.8422449688</v>
       </c>
       <c r="V120" s="13" t="n">
         <v>0</v>
@@ -11841,13 +11841,13 @@
         <v>10.13005666406702</v>
       </c>
       <c r="S121" s="13" t="n">
-        <v>-2.759283868022472</v>
+        <v>-2.759283868</v>
       </c>
       <c r="T121" s="14" t="n">
-        <v>-8.142823441586609</v>
+        <v>-8.142823441999999</v>
       </c>
       <c r="U121" s="13" t="n">
-        <v>2.545015594509398</v>
+        <v>2.545015595</v>
       </c>
       <c r="V121" s="13" t="n">
         <v>0</v>
@@ -11939,13 +11939,13 @@
         <v>5.83530359957682</v>
       </c>
       <c r="S122" s="13" t="n">
-        <v>-2.73662871028983</v>
+        <v>-2.73662871</v>
       </c>
       <c r="T122" s="14" t="n">
-        <v>-1.48522908304314</v>
+        <v>-1.485229083</v>
       </c>
       <c r="U122" s="13" t="n">
-        <v>1.374232617759218</v>
+        <v>1.374232618</v>
       </c>
       <c r="V122" s="13" t="n">
         <v>0</v>
@@ -12037,13 +12037,13 @@
         <v>45.26381769111611</v>
       </c>
       <c r="S123" s="13" t="n">
-        <v>-3.065773572575873</v>
+        <v>-3.065773573</v>
       </c>
       <c r="T123" s="14" t="n">
-        <v>-9.11577592890082</v>
+        <v>-9.115775929</v>
       </c>
       <c r="U123" s="13" t="n">
-        <v>4.510991970859092</v>
+        <v>4.510991971</v>
       </c>
       <c r="V123" s="13" t="n">
         <v>0</v>
@@ -12135,13 +12135,13 @@
         <v>15.64004610904716</v>
       </c>
       <c r="S124" s="13" t="n">
-        <v>-2.471102317670937</v>
+        <v>-2.471102318</v>
       </c>
       <c r="T124" s="14" t="n">
-        <v>-0.79961487777166</v>
+        <v>-0.7996148778</v>
       </c>
       <c r="U124" s="13" t="n">
-        <v>1.10201726935953</v>
+        <v>1.102017269</v>
       </c>
       <c r="V124" s="13" t="n">
         <v>0</v>
@@ -12233,13 +12233,13 @@
         <v>17.29941120876121</v>
       </c>
       <c r="S125" s="13" t="n">
-        <v>-1.110949839889436</v>
+        <v>-1.11094984</v>
       </c>
       <c r="T125" s="14" t="n">
-        <v>-3.62422455086337</v>
+        <v>-3.624224551</v>
       </c>
       <c r="U125" s="13" t="n">
-        <v>2.324624969428222</v>
+        <v>2.324624969</v>
       </c>
       <c r="V125" s="13" t="n">
         <v>2</v>
@@ -12331,13 +12331,13 @@
         <v>37.68573976219297</v>
       </c>
       <c r="S126" s="13" t="n">
-        <v>-3.778177664153858</v>
+        <v>-3.778177664</v>
       </c>
       <c r="T126" s="14" t="n">
-        <v>-9.03662837341248</v>
+        <v>-9.036628372999999</v>
       </c>
       <c r="U126" s="13" t="n">
-        <v>4.45647980103508</v>
+        <v>4.456479801</v>
       </c>
       <c r="V126" s="13" t="n">
         <v>0</v>
@@ -12429,13 +12429,13 @@
         <v>31.05041066738988</v>
       </c>
       <c r="S127" s="13" t="n">
-        <v>-3.197729263328707</v>
+        <v>-3.197729263</v>
       </c>
       <c r="T127" s="14" t="n">
-        <v>-4.24987177968791</v>
+        <v>-4.24987178</v>
       </c>
       <c r="U127" s="13" t="n">
-        <v>1.575003519639589</v>
+        <v>1.57500352</v>
       </c>
       <c r="V127" s="13" t="n">
         <v>0</v>
@@ -12527,13 +12527,13 @@
         <v>4.28036525989522</v>
       </c>
       <c r="S128" s="13" t="n">
-        <v>-2.290918471386604</v>
+        <v>-2.290918471</v>
       </c>
       <c r="T128" s="14" t="n">
-        <v>1.78635181917696</v>
+        <v>1.786351819</v>
       </c>
       <c r="U128" s="13" t="n">
-        <v>0.6421491654592014</v>
+        <v>0.6421491655</v>
       </c>
       <c r="V128" s="13" t="n">
         <v>0</v>
@@ -12621,10 +12621,10 @@
         <v>10.67041810112654</v>
       </c>
       <c r="S129" s="13" t="n">
-        <v>-3.634305013182785</v>
+        <v>-3.634305013</v>
       </c>
       <c r="T129" s="14" t="n">
-        <v>-16.803148451441</v>
+        <v>-16.80314845</v>
       </c>
       <c r="U129" s="15" t="inlineStr">
         <is>
@@ -12719,13 +12719,13 @@
         <v>91.25740021643644</v>
       </c>
       <c r="S130" s="13" t="n">
-        <v>-3.010751462743358</v>
+        <v>-3.010751463</v>
       </c>
       <c r="T130" s="14" t="n">
-        <v>-22.38172362107296</v>
+        <v>-22.38172362</v>
       </c>
       <c r="U130" s="13" t="n">
-        <v>20.94531600179292</v>
+        <v>20.945316</v>
       </c>
       <c r="V130" s="13" t="n">
         <v>1</v>
@@ -12817,13 +12817,13 @@
         <v>-12.27244927369035</v>
       </c>
       <c r="S131" s="13" t="n">
-        <v>-2.172264097773123</v>
+        <v>-2.172264098</v>
       </c>
       <c r="T131" s="14" t="n">
-        <v>0.43251151898519</v>
+        <v>0.432511519</v>
       </c>
       <c r="U131" s="13" t="n">
-        <v>-1.319393996312838</v>
+        <v>-1.319393996</v>
       </c>
       <c r="V131" s="13" t="n">
         <v>1</v>
@@ -12915,13 +12915,13 @@
         <v>9.217169839441199</v>
       </c>
       <c r="S132" s="13" t="n">
-        <v>-2.616706336539075</v>
+        <v>-2.616706337</v>
       </c>
       <c r="T132" s="14" t="n">
-        <v>0.49455685896082</v>
+        <v>0.494556859</v>
       </c>
       <c r="U132" s="13" t="n">
-        <v>0.9122368890474492</v>
+        <v>0.912236889</v>
       </c>
       <c r="V132" s="13" t="n">
         <v>0</v>
@@ -13013,13 +13013,13 @@
         <v>42.88036165428956</v>
       </c>
       <c r="S133" s="13" t="n">
-        <v>-3.012801149260425</v>
+        <v>-3.012801149</v>
       </c>
       <c r="T133" s="14" t="n">
-        <v>-11.70996876238516</v>
+        <v>-11.70996876</v>
       </c>
       <c r="U133" s="13" t="n">
-        <v>7.664384908313171</v>
+        <v>7.664384908</v>
       </c>
       <c r="V133" s="13" t="n">
         <v>0</v>
@@ -13112,7 +13112,7 @@
         </is>
       </c>
       <c r="T134" s="14" t="n">
-        <v>-36.15360285440495</v>
+        <v>-36.15360285</v>
       </c>
       <c r="U134" s="15" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         </is>
       </c>
       <c r="T135" s="14" t="n">
-        <v>-8.73750523274216</v>
+        <v>-8.737505233</v>
       </c>
       <c r="U135" s="15" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         </is>
       </c>
       <c r="T136" s="14" t="n">
-        <v>-172.0680665087247</v>
+        <v>-172.0680665</v>
       </c>
       <c r="U136" s="15" t="inlineStr">
         <is>
@@ -13403,13 +13403,13 @@
         <v>0.57248041378731</v>
       </c>
       <c r="S137" s="13" t="n">
-        <v>-2.196047003706723</v>
+        <v>-2.196047004</v>
       </c>
       <c r="T137" s="14" t="n">
-        <v>4.27504884335666</v>
+        <v>4.275048843</v>
       </c>
       <c r="U137" s="13" t="n">
-        <v>0.0595058689256865</v>
+        <v>0.05950586893</v>
       </c>
       <c r="V137" s="13" t="n">
         <v>0</v>
@@ -13499,10 +13499,10 @@
         <v>-7.526063375308591</v>
       </c>
       <c r="S138" s="13" t="n">
-        <v>-2.491443692092051</v>
+        <v>-2.491443692</v>
       </c>
       <c r="T138" s="14" t="n">
-        <v>1.85366756486852</v>
+        <v>1.853667565</v>
       </c>
       <c r="U138" s="15" t="inlineStr">
         <is>
@@ -13595,13 +13595,13 @@
         <v>-6.53325236167032</v>
       </c>
       <c r="S139" s="13" t="n">
-        <v>-2.282827387326704</v>
+        <v>-2.282827387</v>
       </c>
       <c r="T139" s="14" t="n">
-        <v>3.05396268189857</v>
+        <v>3.053962682</v>
       </c>
       <c r="U139" s="13" t="n">
-        <v>0.3296415727254221</v>
+        <v>0.3296415727</v>
       </c>
       <c r="V139" s="13" t="n">
         <v>1</v>
@@ -13795,13 +13795,13 @@
         <v>-0.10085463897419</v>
       </c>
       <c r="S141" s="13" t="n">
-        <v>-2.148891520709846</v>
+        <v>-2.148891521</v>
       </c>
       <c r="T141" s="14" t="n">
-        <v>9.709109258039319</v>
+        <v>9.709109258</v>
       </c>
       <c r="U141" s="13" t="n">
-        <v>0.3600719373853067</v>
+        <v>0.3600719374</v>
       </c>
       <c r="V141" s="13" t="n">
         <v>0</v>
@@ -13889,13 +13889,13 @@
         <v>14.09780450650098</v>
       </c>
       <c r="S142" s="13" t="n">
-        <v>-3.008828956302724</v>
+        <v>-3.008828956</v>
       </c>
       <c r="T142" s="14" t="n">
-        <v>-5.56039604864298</v>
+        <v>-5.560396049</v>
       </c>
       <c r="U142" s="13" t="n">
-        <v>2.242063818520789</v>
+        <v>2.242063819</v>
       </c>
       <c r="V142" s="13" t="n">
         <v>0</v>
@@ -13987,13 +13987,13 @@
         <v>1.27950049947798</v>
       </c>
       <c r="S143" s="13" t="n">
-        <v>-1.682265373968202</v>
+        <v>-1.682265374</v>
       </c>
       <c r="T143" s="14" t="n">
-        <v>11.52788205641223</v>
+        <v>11.52788206</v>
       </c>
       <c r="U143" s="13" t="n">
-        <v>-1.946109371981569</v>
+        <v>-1.946109372</v>
       </c>
       <c r="V143" s="13" t="n">
         <v>2</v>
@@ -14085,13 +14085,13 @@
         <v>-0.99428287025673</v>
       </c>
       <c r="S144" s="13" t="n">
-        <v>-2.620472019944004</v>
+        <v>-2.62047202</v>
       </c>
       <c r="T144" s="14" t="n">
-        <v>-3.51274180078098</v>
+        <v>-3.512741801</v>
       </c>
       <c r="U144" s="13" t="n">
-        <v>2.115791360458863</v>
+        <v>2.11579136</v>
       </c>
       <c r="V144" s="13" t="n">
         <v>0</v>
@@ -14188,7 +14188,7 @@
         </is>
       </c>
       <c r="T145" s="14" t="n">
-        <v>-2.84183867858983</v>
+        <v>-2.841838679</v>
       </c>
       <c r="U145" s="15" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         </is>
       </c>
       <c r="T147" s="14" t="n">
-        <v>-16.55590717299578</v>
+        <v>-16.55590717</v>
       </c>
       <c r="U147" s="15" t="inlineStr">
         <is>
@@ -14479,13 +14479,13 @@
         <v>7.586819833962901</v>
       </c>
       <c r="S148" s="13" t="n">
-        <v>-2.713413619483628</v>
+        <v>-2.713413619</v>
       </c>
       <c r="T148" s="14" t="n">
-        <v>-0.31738635952646</v>
+        <v>-0.3173863595</v>
       </c>
       <c r="U148" s="13" t="n">
-        <v>1.05599723402785</v>
+        <v>1.055997234</v>
       </c>
       <c r="V148" s="13" t="n">
         <v>0</v>
@@ -14580,10 +14580,10 @@
         </is>
       </c>
       <c r="T149" s="14" t="n">
-        <v>1.39142870364948</v>
+        <v>1.391428704</v>
       </c>
       <c r="U149" s="13" t="n">
-        <v>0.9179250914589204</v>
+        <v>0.9179250915</v>
       </c>
       <c r="V149" s="13" t="n">
         <v>0</v>
@@ -14775,13 +14775,13 @@
         <v>6.655436185731239</v>
       </c>
       <c r="S151" s="13" t="n">
-        <v>-2.651531112243157</v>
+        <v>-2.651531112</v>
       </c>
       <c r="T151" s="14" t="n">
-        <v>-0.37290335090951</v>
+        <v>-0.3729033509</v>
       </c>
       <c r="U151" s="13" t="n">
-        <v>1.076640098099326</v>
+        <v>1.076640098</v>
       </c>
       <c r="V151" s="13" t="n">
         <v>0</v>
@@ -14875,10 +14875,10 @@
         </is>
       </c>
       <c r="S152" s="13" t="n">
-        <v>-5.85684007251814</v>
+        <v>-5.856840073</v>
       </c>
       <c r="T152" s="14" t="n">
-        <v>-61.92955429553982</v>
+        <v>-61.9295543</v>
       </c>
       <c r="U152" s="15" t="inlineStr">
         <is>
@@ -14975,13 +14975,13 @@
         <v>12.89968251048677</v>
       </c>
       <c r="S153" s="13" t="n">
-        <v>-2.330154719448644</v>
+        <v>-2.330154719</v>
       </c>
       <c r="T153" s="14" t="n">
-        <v>1.72376230640697</v>
+        <v>1.723762306</v>
       </c>
       <c r="U153" s="13" t="n">
-        <v>0.7172301511307546</v>
+        <v>0.7172301511</v>
       </c>
       <c r="V153" s="13" t="n">
         <v>0</v>
@@ -15173,13 +15173,13 @@
         <v>-3.50351724026233</v>
       </c>
       <c r="S155" s="13" t="n">
-        <v>-2.272182452057624</v>
+        <v>-2.272182452</v>
       </c>
       <c r="T155" s="14" t="n">
-        <v>2.93642226869341</v>
+        <v>2.936422269</v>
       </c>
       <c r="U155" s="13" t="n">
-        <v>0.466424366620591</v>
+        <v>0.4664243666</v>
       </c>
       <c r="V155" s="13" t="n">
         <v>0</v>
@@ -15271,13 +15271,13 @@
         <v>19.3820394699907</v>
       </c>
       <c r="S156" s="13" t="n">
-        <v>-2.828170143856845</v>
+        <v>-2.828170144</v>
       </c>
       <c r="T156" s="14" t="n">
-        <v>-6.724709245663039</v>
+        <v>-6.724709246000001</v>
       </c>
       <c r="U156" s="13" t="n">
-        <v>2.536178107606679</v>
+        <v>2.536178108</v>
       </c>
       <c r="V156" s="13" t="n">
         <v>0</v>
@@ -15361,13 +15361,13 @@
         <v>-22.7100997019229</v>
       </c>
       <c r="S157" s="13" t="n">
-        <v>-0.427490703934539</v>
+        <v>-0.4274907039</v>
       </c>
       <c r="T157" s="14" t="n">
-        <v>44.4419431530099</v>
+        <v>44.44194315</v>
       </c>
       <c r="U157" s="13" t="n">
-        <v>-0.1061832124034006</v>
+        <v>-0.1061832124</v>
       </c>
       <c r="V157" s="13" t="n">
         <v>2</v>
@@ -15459,13 +15459,13 @@
         <v>2.15224373121313</v>
       </c>
       <c r="S158" s="13" t="n">
-        <v>-2.129699332839016</v>
+        <v>-2.129699333</v>
       </c>
       <c r="T158" s="14" t="n">
-        <v>2.10240862901628</v>
+        <v>2.102408629</v>
       </c>
       <c r="U158" s="13" t="n">
-        <v>0.2923076923076923</v>
+        <v>0.2923076923</v>
       </c>
       <c r="V158" s="13" t="n">
         <v>0</v>
@@ -15653,13 +15653,13 @@
         <v>4.56842880538298</v>
       </c>
       <c r="S160" s="13" t="n">
-        <v>-2.663661536279651</v>
+        <v>-2.663661536</v>
       </c>
       <c r="T160" s="14" t="n">
-        <v>-3.91788151364764</v>
+        <v>-3.917881514</v>
       </c>
       <c r="U160" s="13" t="n">
-        <v>4.118827160493828</v>
+        <v>4.11882716</v>
       </c>
       <c r="V160" s="13" t="n">
         <v>1</v>
@@ -15756,10 +15756,10 @@
         </is>
       </c>
       <c r="T161" s="14" t="n">
-        <v>25.77515999624327</v>
+        <v>25.77516</v>
       </c>
       <c r="U161" s="13" t="n">
-        <v>0.5782529472459441</v>
+        <v>0.5782529472</v>
       </c>
       <c r="V161" s="13" t="n">
         <v>1</v>
@@ -15851,13 +15851,13 @@
         <v>5.61202266922335</v>
       </c>
       <c r="S162" s="13" t="n">
-        <v>-2.276110698446209</v>
+        <v>-2.276110698</v>
       </c>
       <c r="T162" s="14" t="n">
-        <v>-0.01460558103244</v>
+        <v>-0.01460558103</v>
       </c>
       <c r="U162" s="13" t="n">
-        <v>1.003073425207195</v>
+        <v>1.003073425</v>
       </c>
       <c r="V162" s="13" t="n">
         <v>0</v>
@@ -15949,13 +15949,13 @@
         <v>29.84741698924731</v>
       </c>
       <c r="S163" s="13" t="n">
-        <v>-3.320908768266181</v>
+        <v>-3.320908768</v>
       </c>
       <c r="T163" s="14" t="n">
-        <v>-14.38768644717639</v>
+        <v>-14.38768645</v>
       </c>
       <c r="U163" s="13" t="n">
-        <v>8.330146502429471</v>
+        <v>8.330146502</v>
       </c>
       <c r="V163" s="13" t="n">
         <v>0</v>
@@ -16047,13 +16047,13 @@
         <v>11.29480107049915</v>
       </c>
       <c r="S164" s="13" t="n">
-        <v>-2.209557333525585</v>
+        <v>-2.209557334</v>
       </c>
       <c r="T164" s="14" t="n">
-        <v>0.74813627491824</v>
+        <v>0.7481362749</v>
       </c>
       <c r="U164" s="13" t="n">
-        <v>0.8362881319128553</v>
+        <v>0.8362881319</v>
       </c>
       <c r="V164" s="13" t="n">
         <v>0</v>
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="T166" s="14" t="n">
-        <v>-5.32859836802312</v>
+        <v>-5.328598368000001</v>
       </c>
       <c r="U166" s="15" t="inlineStr">
         <is>
@@ -16339,10 +16339,10 @@
         <v>30.61531878874247</v>
       </c>
       <c r="S167" s="13" t="n">
-        <v>-2.096435817173475</v>
+        <v>-2.096435817</v>
       </c>
       <c r="T167" s="14" t="n">
-        <v>3.22437861529322</v>
+        <v>3.224378615</v>
       </c>
       <c r="U167" s="13" t="n">
         <v>0</v>
@@ -16433,13 +16433,13 @@
         <v>8.626452817392121</v>
       </c>
       <c r="S168" s="13" t="n">
-        <v>-2.065062358316639</v>
+        <v>-2.065062358</v>
       </c>
       <c r="T168" s="14" t="n">
-        <v>3.10334625741499</v>
+        <v>3.103346257</v>
       </c>
       <c r="U168" s="13" t="n">
-        <v>0.6617185860478229</v>
+        <v>0.661718586</v>
       </c>
       <c r="V168" s="13" t="n">
         <v>0</v>
@@ -16532,7 +16532,7 @@
         </is>
       </c>
       <c r="T169" s="14" t="n">
-        <v>1.21633633259001</v>
+        <v>1.216336333</v>
       </c>
       <c r="U169" s="15" t="inlineStr">
         <is>
@@ -16625,13 +16625,13 @@
         <v>50.0609576727145</v>
       </c>
       <c r="S170" s="13" t="n">
-        <v>-3.126055689617853</v>
+        <v>-3.12605569</v>
       </c>
       <c r="T170" s="14" t="n">
-        <v>-23.05234663094824</v>
+        <v>-23.05234663</v>
       </c>
       <c r="U170" s="13" t="n">
-        <v>4.524942488238586</v>
+        <v>4.524942488</v>
       </c>
       <c r="V170" s="13" t="n">
         <v>0</v>
@@ -16723,10 +16723,10 @@
         <v>24.93998495390208</v>
       </c>
       <c r="S171" s="13" t="n">
-        <v>-2.543559389363076</v>
+        <v>-2.543559389</v>
       </c>
       <c r="T171" s="14" t="n">
-        <v>-12.23811459342974</v>
+        <v>-12.23811459</v>
       </c>
       <c r="U171" s="15" t="inlineStr">
         <is>
@@ -16823,13 +16823,13 @@
         <v>3.81877431688942</v>
       </c>
       <c r="S172" s="13" t="n">
-        <v>-2.85432131068956</v>
+        <v>-2.854321311</v>
       </c>
       <c r="T172" s="14" t="n">
-        <v>1.83846806785417</v>
+        <v>1.838468068</v>
       </c>
       <c r="U172" s="13" t="n">
-        <v>0.7459311966632659</v>
+        <v>0.7459311967</v>
       </c>
       <c r="V172" s="13" t="n">
         <v>0</v>
@@ -16917,13 +16917,13 @@
         <v>25.24656770901743</v>
       </c>
       <c r="S173" s="13" t="n">
-        <v>-1.867846691411665</v>
+        <v>-1.867846691</v>
       </c>
       <c r="T173" s="14" t="n">
-        <v>19.01574551844175</v>
+        <v>19.01574552</v>
       </c>
       <c r="U173" s="13" t="n">
-        <v>0.4238454801132283</v>
+        <v>0.4238454801</v>
       </c>
       <c r="V173" s="13" t="n">
         <v>1</v>
@@ -17015,13 +17015,13 @@
         <v>15.96522635134936</v>
       </c>
       <c r="S174" s="13" t="n">
-        <v>-2.6043339372014</v>
+        <v>-2.604333937</v>
       </c>
       <c r="T174" s="14" t="n">
-        <v>1.75592675906143</v>
+        <v>1.755926759</v>
       </c>
       <c r="U174" s="13" t="n">
-        <v>0.7715117893122156</v>
+        <v>0.7715117893</v>
       </c>
       <c r="V174" s="13" t="n">
         <v>0</v>
@@ -17313,13 +17313,13 @@
         <v>19.82019773674833</v>
       </c>
       <c r="S177" s="13" t="n">
-        <v>-2.800605970345969</v>
+        <v>-2.80060597</v>
       </c>
       <c r="T177" s="14" t="n">
-        <v>-10.30470748183011</v>
+        <v>-10.30470748</v>
       </c>
       <c r="U177" s="13" t="n">
-        <v>6.152081916194092</v>
+        <v>6.152081916</v>
       </c>
       <c r="V177" s="13" t="n">
         <v>1</v>
@@ -17518,7 +17518,7 @@
         </is>
       </c>
       <c r="T179" s="14" t="n">
-        <v>-12.67503707506274</v>
+        <v>-12.67503708</v>
       </c>
       <c r="U179" s="15" t="inlineStr">
         <is>
@@ -17611,13 +17611,13 @@
         <v>4.863136918225091</v>
       </c>
       <c r="S180" s="13" t="n">
-        <v>-2.175664232182845</v>
+        <v>-2.175664232</v>
       </c>
       <c r="T180" s="14" t="n">
-        <v>0.69968182341564</v>
+        <v>0.6996818234</v>
       </c>
       <c r="U180" s="13" t="n">
-        <v>0.8090301262583925</v>
+        <v>0.8090301263</v>
       </c>
       <c r="V180" s="13" t="n">
         <v>1</v>
@@ -17709,13 +17709,13 @@
         <v>12.82839116862447</v>
       </c>
       <c r="S181" s="13" t="n">
-        <v>-3.041666588676601</v>
+        <v>-3.041666589</v>
       </c>
       <c r="T181" s="14" t="n">
-        <v>-6.10575845556636</v>
+        <v>-6.105758456</v>
       </c>
       <c r="U181" s="13" t="n">
-        <v>2.293684663194304</v>
+        <v>2.293684663</v>
       </c>
       <c r="V181" s="13" t="n">
         <v>0</v>
@@ -17905,10 +17905,10 @@
         <v>18.80116414972911</v>
       </c>
       <c r="S183" s="13" t="n">
-        <v>-2.674223850296329</v>
+        <v>-2.67422385</v>
       </c>
       <c r="T183" s="14" t="n">
-        <v>-6.03540320314695</v>
+        <v>-6.035403203</v>
       </c>
       <c r="U183" s="13" t="n">
         <v>12.1875</v>
@@ -18001,10 +18001,10 @@
         <v>75.04068475170423</v>
       </c>
       <c r="S184" s="13" t="n">
-        <v>-4.491530408958325</v>
+        <v>-4.491530409</v>
       </c>
       <c r="T184" s="14" t="n">
-        <v>-28.45139013409631</v>
+        <v>-28.45139013</v>
       </c>
       <c r="U184" s="15" t="inlineStr">
         <is>
@@ -18101,13 +18101,13 @@
         <v>2.51688288419865</v>
       </c>
       <c r="S185" s="13" t="n">
-        <v>-1.836608730623069</v>
+        <v>-1.836608731</v>
       </c>
       <c r="T185" s="14" t="n">
-        <v>-0.159709085859</v>
+        <v>-0.1597090859</v>
       </c>
       <c r="U185" s="13" t="n">
-        <v>1.053098607540765</v>
+        <v>1.053098608</v>
       </c>
       <c r="V185" s="13" t="n">
         <v>0</v>
@@ -18195,13 +18195,13 @@
         <v>-6.361455537859779</v>
       </c>
       <c r="S186" s="13" t="n">
-        <v>-2.058823484403833</v>
+        <v>-2.058823484</v>
       </c>
       <c r="T186" s="14" t="n">
-        <v>4.82649883219654</v>
+        <v>4.826498832</v>
       </c>
       <c r="U186" s="13" t="n">
-        <v>0.2596583643183067</v>
+        <v>0.2596583643</v>
       </c>
       <c r="V186" s="13" t="n">
         <v>0</v>
@@ -18293,13 +18293,13 @@
         <v>8.05445110996609</v>
       </c>
       <c r="S187" s="13" t="n">
-        <v>-2.587184277139168</v>
+        <v>-2.587184277</v>
       </c>
       <c r="T187" s="14" t="n">
-        <v>-2.67903405005484</v>
+        <v>-2.67903405</v>
       </c>
       <c r="U187" s="13" t="n">
-        <v>2.133143476398095</v>
+        <v>2.133143476</v>
       </c>
       <c r="V187" s="13" t="n">
         <v>0</v>
@@ -18391,13 +18391,13 @@
         <v>16.54744550722191</v>
       </c>
       <c r="S188" s="13" t="n">
-        <v>-2.898157312786473</v>
+        <v>-2.898157313</v>
       </c>
       <c r="T188" s="14" t="n">
-        <v>-3.45534897937682</v>
+        <v>-3.455348979</v>
       </c>
       <c r="U188" s="13" t="n">
-        <v>1.81404317167921</v>
+        <v>1.814043172</v>
       </c>
       <c r="V188" s="13" t="n">
         <v>0</v>
@@ -18585,13 +18585,13 @@
         <v>-45.5060069909903</v>
       </c>
       <c r="S190" s="13" t="n">
-        <v>2.699195858445373</v>
+        <v>2.699195858</v>
       </c>
       <c r="T190" s="14" t="n">
-        <v>27.30371118404443</v>
+        <v>27.30371118</v>
       </c>
       <c r="U190" s="13" t="n">
-        <v>-22.25806451612903</v>
+        <v>-22.25806452</v>
       </c>
       <c r="V190" s="13" t="n">
         <v>2</v>
@@ -18683,13 +18683,13 @@
         <v>29.26685369926984</v>
       </c>
       <c r="S191" s="13" t="n">
-        <v>-2.783259346050712</v>
+        <v>-2.783259346</v>
       </c>
       <c r="T191" s="14" t="n">
-        <v>-4.40583277248982</v>
+        <v>-4.405832772</v>
       </c>
       <c r="U191" s="13" t="n">
-        <v>2.561508405270332</v>
+        <v>2.561508405</v>
       </c>
       <c r="V191" s="13" t="n">
         <v>1</v>
@@ -18783,13 +18783,13 @@
         <v>15.12058285182725</v>
       </c>
       <c r="S192" s="13" t="n">
-        <v>-2.386456049184507</v>
+        <v>-2.386456049</v>
       </c>
       <c r="T192" s="14" t="n">
-        <v>-8.52506143582251</v>
+        <v>-8.525061436</v>
       </c>
       <c r="U192" s="13" t="n">
-        <v>8.665755213647309</v>
+        <v>8.665755214000001</v>
       </c>
       <c r="V192" s="13" t="n">
         <v>0</v>
@@ -18879,13 +18879,13 @@
         <v>10.35220845063016</v>
       </c>
       <c r="S193" s="13" t="n">
-        <v>-4.293869042148248</v>
+        <v>-4.293869042</v>
       </c>
       <c r="T193" s="14" t="n">
-        <v>-1.07904646352625</v>
+        <v>-1.079046464</v>
       </c>
       <c r="U193" s="13" t="n">
-        <v>1.149160371267095</v>
+        <v>1.149160371</v>
       </c>
       <c r="V193" s="13" t="n">
         <v>0</v>
@@ -18973,13 +18973,13 @@
         <v>18.76992956492909</v>
       </c>
       <c r="S194" s="13" t="n">
-        <v>-3.515064072784987</v>
+        <v>-3.515064073</v>
       </c>
       <c r="T194" s="14" t="n">
-        <v>-6.495709064964849</v>
+        <v>-6.495709065</v>
       </c>
       <c r="U194" s="13" t="n">
-        <v>1.93689526003278</v>
+        <v>1.93689526</v>
       </c>
       <c r="V194" s="13" t="n">
         <v>0</v>
@@ -19071,13 +19071,13 @@
         <v>27.01503544203232</v>
       </c>
       <c r="S195" s="13" t="n">
-        <v>-2.882269626820924</v>
+        <v>-2.882269627</v>
       </c>
       <c r="T195" s="14" t="n">
-        <v>-5.91776017838208</v>
+        <v>-5.917760178</v>
       </c>
       <c r="U195" s="13" t="n">
-        <v>1.920765986588495</v>
+        <v>1.920765987</v>
       </c>
       <c r="V195" s="13" t="n">
         <v>0</v>
@@ -19169,13 +19169,13 @@
         <v>15.69464724869351</v>
       </c>
       <c r="S196" s="13" t="n">
-        <v>-2.278674096990552</v>
+        <v>-2.278674097</v>
       </c>
       <c r="T196" s="14" t="n">
-        <v>-1.6105802008343</v>
+        <v>-1.610580201</v>
       </c>
       <c r="U196" s="13" t="n">
-        <v>1.296100375601217</v>
+        <v>1.296100376</v>
       </c>
       <c r="V196" s="13" t="n">
         <v>0</v>
@@ -19267,10 +19267,10 @@
         <v>3.91075966169833</v>
       </c>
       <c r="S197" s="13" t="n">
-        <v>-1.720119846694105</v>
+        <v>-1.720119847</v>
       </c>
       <c r="T197" s="14" t="n">
-        <v>-6.50427751271215</v>
+        <v>-6.504277512999999</v>
       </c>
       <c r="U197" s="15" t="inlineStr">
         <is>
@@ -19369,10 +19369,10 @@
         <v>3.32218004455735</v>
       </c>
       <c r="S198" s="13" t="n">
-        <v>0.6956833662367963</v>
+        <v>0.6956833662</v>
       </c>
       <c r="T198" s="14" t="n">
-        <v>-7.667633207454171</v>
+        <v>-7.667633207000001</v>
       </c>
       <c r="U198" s="15" t="inlineStr">
         <is>
@@ -19469,13 +19469,13 @@
         <v>7.006957596949031</v>
       </c>
       <c r="S199" s="13" t="n">
-        <v>-2.394912027160873</v>
+        <v>-2.394912027</v>
       </c>
       <c r="T199" s="14" t="n">
-        <v>-3.54778411272524</v>
+        <v>-3.547784113</v>
       </c>
       <c r="U199" s="13" t="n">
-        <v>2.901760642793626</v>
+        <v>2.901760643</v>
       </c>
       <c r="V199" s="13" t="n">
         <v>0</v>
@@ -19567,13 +19567,13 @@
         <v>11.30091593873676</v>
       </c>
       <c r="S200" s="13" t="n">
-        <v>-2.271568800940273</v>
+        <v>-2.271568801</v>
       </c>
       <c r="T200" s="14" t="n">
-        <v>-1.35333470994629</v>
+        <v>-1.35333471</v>
       </c>
       <c r="U200" s="13" t="n">
-        <v>1.753441290679362</v>
+        <v>1.753441291</v>
       </c>
       <c r="V200" s="13" t="n">
         <v>0</v>
@@ -19665,13 +19665,13 @@
         <v>0.592170032283</v>
       </c>
       <c r="S201" s="13" t="n">
-        <v>-2.67113507790955</v>
+        <v>-2.671135078</v>
       </c>
       <c r="T201" s="14" t="n">
-        <v>-1.78155790063177</v>
+        <v>-1.781557901</v>
       </c>
       <c r="U201" s="13" t="n">
-        <v>1.740363636363636</v>
+        <v>1.740363636</v>
       </c>
       <c r="V201" s="13" t="n">
         <v>0</v>
@@ -19763,13 +19763,13 @@
         <v>22.37528559324966</v>
       </c>
       <c r="S202" s="13" t="n">
-        <v>-2.285278450507819</v>
+        <v>-2.285278451</v>
       </c>
       <c r="T202" s="14" t="n">
-        <v>-4.5408752766206</v>
+        <v>-4.540875277</v>
       </c>
       <c r="U202" s="13" t="n">
-        <v>1.473444569578555</v>
+        <v>1.47344457</v>
       </c>
       <c r="V202" s="13" t="n">
         <v>0</v>
@@ -19859,13 +19859,13 @@
         <v>45.69247556520861</v>
       </c>
       <c r="S203" s="13" t="n">
-        <v>-2.815716483299779</v>
+        <v>-2.815716483</v>
       </c>
       <c r="T203" s="14" t="n">
-        <v>-8.13406968474955</v>
+        <v>-8.134069685</v>
       </c>
       <c r="U203" s="13" t="n">
-        <v>2.360628755551685</v>
+        <v>2.360628756</v>
       </c>
       <c r="V203" s="13" t="n">
         <v>0</v>
@@ -19957,13 +19957,13 @@
         <v>27.73014144535261</v>
       </c>
       <c r="S204" s="13" t="n">
-        <v>-2.471743263712613</v>
+        <v>-2.471743264</v>
       </c>
       <c r="T204" s="14" t="n">
-        <v>-3.32985291447249</v>
+        <v>-3.329852914</v>
       </c>
       <c r="U204" s="13" t="n">
-        <v>2.360853432282004</v>
+        <v>2.360853432</v>
       </c>
       <c r="V204" s="13" t="n">
         <v>0</v>
@@ -20057,13 +20057,13 @@
         <v>-3.84531481517366</v>
       </c>
       <c r="S205" s="13" t="n">
-        <v>-2.199569924171544</v>
+        <v>-2.199569924</v>
       </c>
       <c r="T205" s="14" t="n">
-        <v>-0.39086399675769</v>
+        <v>-0.3908639968</v>
       </c>
       <c r="U205" s="13" t="n">
-        <v>1.27604456549221</v>
+        <v>1.276044565</v>
       </c>
       <c r="V205" s="13" t="n">
         <v>0</v>
@@ -20151,13 +20151,13 @@
         <v>37.83421293525399</v>
       </c>
       <c r="S206" s="13" t="n">
-        <v>-2.173389320651632</v>
+        <v>-2.173389321</v>
       </c>
       <c r="T206" s="14" t="n">
-        <v>-0.95208525757065</v>
+        <v>-0.9520852576</v>
       </c>
       <c r="U206" s="13" t="n">
-        <v>1.274500494287335</v>
+        <v>1.274500494</v>
       </c>
       <c r="V206" s="13" t="n">
         <v>0</v>
@@ -20245,13 +20245,13 @@
         <v>85.05703962677774</v>
       </c>
       <c r="S207" s="13" t="n">
-        <v>-2.985835514542073</v>
+        <v>-2.985835515</v>
       </c>
       <c r="T207" s="14" t="n">
-        <v>-21.44077101378553</v>
+        <v>-21.44077101</v>
       </c>
       <c r="U207" s="13" t="n">
-        <v>9.955414012738853</v>
+        <v>9.955414013</v>
       </c>
       <c r="V207" s="13" t="n">
         <v>0</v>
@@ -20343,13 +20343,13 @@
         <v>11.24941922463203</v>
       </c>
       <c r="S208" s="13" t="n">
-        <v>-2.726408458144991</v>
+        <v>-2.726408458</v>
       </c>
       <c r="T208" s="14" t="n">
-        <v>-4.34509895896628</v>
+        <v>-4.345098959</v>
       </c>
       <c r="U208" s="13" t="n">
-        <v>2.380358587374393</v>
+        <v>2.380358587</v>
       </c>
       <c r="V208" s="13" t="n">
         <v>0</v>
@@ -20441,13 +20441,13 @@
         <v>-5.94487112325419</v>
       </c>
       <c r="S209" s="13" t="n">
-        <v>-2.321933205518042</v>
+        <v>-2.321933206</v>
       </c>
       <c r="T209" s="14" t="n">
-        <v>-0.10131428904853</v>
+        <v>-0.101314289</v>
       </c>
       <c r="U209" s="13" t="n">
-        <v>1.026736911341804</v>
+        <v>1.026736911</v>
       </c>
       <c r="V209" s="13" t="n">
         <v>0</v>
@@ -20533,13 +20533,13 @@
         <v>-3.30729480634787</v>
       </c>
       <c r="S210" s="13" t="n">
-        <v>-3.058473957800916</v>
+        <v>-3.058473958</v>
       </c>
       <c r="T210" s="14" t="n">
-        <v>-5.019490260888991</v>
+        <v>-5.019490261000001</v>
       </c>
       <c r="U210" s="13" t="n">
-        <v>34.12392410411034</v>
+        <v>34.1239241</v>
       </c>
       <c r="V210" s="13" t="n">
         <v>0</v>
@@ -20629,13 +20629,13 @@
         <v>6.22326852208734</v>
       </c>
       <c r="S211" s="13" t="n">
-        <v>-2.198526500259545</v>
+        <v>-2.1985265</v>
       </c>
       <c r="T211" s="14" t="n">
-        <v>-0.30965990975479</v>
+        <v>-0.3096599098</v>
       </c>
       <c r="U211" s="13" t="n">
-        <v>1.430801987224982</v>
+        <v>1.430801987</v>
       </c>
       <c r="V211" s="13" t="n">
         <v>0</v>
@@ -20728,10 +20728,10 @@
         </is>
       </c>
       <c r="T212" s="14" t="n">
-        <v>5.78270135751235</v>
+        <v>5.782701358000001</v>
       </c>
       <c r="U212" s="13" t="n">
-        <v>-0.7870002253119844</v>
+        <v>-0.7870002253</v>
       </c>
       <c r="V212" s="13" t="n">
         <v>0</v>
@@ -20926,7 +20926,7 @@
         </is>
       </c>
       <c r="T214" s="14" t="n">
-        <v>-3.30118790232733</v>
+        <v>-3.301187902</v>
       </c>
       <c r="U214" s="15" t="inlineStr">
         <is>
@@ -21023,13 +21023,13 @@
         <v>-5.94208056549854</v>
       </c>
       <c r="S215" s="13" t="n">
-        <v>-2.449469351514515</v>
+        <v>-2.449469352</v>
       </c>
       <c r="T215" s="14" t="n">
-        <v>-1.51985954218703</v>
+        <v>-1.519859542</v>
       </c>
       <c r="U215" s="13" t="n">
-        <v>1.373981089012064</v>
+        <v>1.373981089</v>
       </c>
       <c r="V215" s="13" t="n">
         <v>0</v>
@@ -21221,10 +21221,10 @@
         <v>-0.5506910035049</v>
       </c>
       <c r="S217" s="13" t="n">
-        <v>-2.043348321389874</v>
+        <v>-2.043348321</v>
       </c>
       <c r="T217" s="14" t="n">
-        <v>0.7552194804534</v>
+        <v>0.7552194805</v>
       </c>
       <c r="U217" s="15" t="inlineStr">
         <is>
@@ -21321,10 +21321,10 @@
         <v>47.9281845231092</v>
       </c>
       <c r="S218" s="13" t="n">
-        <v>-2.895981250477484</v>
+        <v>-2.89598125</v>
       </c>
       <c r="T218" s="14" t="n">
-        <v>-8.147180489011379</v>
+        <v>-8.147180489</v>
       </c>
       <c r="U218" s="15" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         </is>
       </c>
       <c r="T219" s="14" t="n">
-        <v>-7.23575394455997</v>
+        <v>-7.235753944999999</v>
       </c>
       <c r="U219" s="15" t="inlineStr">
         <is>
@@ -21519,10 +21519,10 @@
         <v>-21.89328873237808</v>
       </c>
       <c r="S220" s="13" t="n">
-        <v>-2.583806049852292</v>
+        <v>-2.58380605</v>
       </c>
       <c r="T220" s="14" t="n">
-        <v>-6.731848788962109</v>
+        <v>-6.731848789</v>
       </c>
       <c r="U220" s="15" t="inlineStr">
         <is>
@@ -21619,13 +21619,13 @@
         <v>41.04110897596826</v>
       </c>
       <c r="S221" s="13" t="n">
-        <v>-2.607860376796028</v>
+        <v>-2.607860377</v>
       </c>
       <c r="T221" s="14" t="n">
-        <v>-7.292554407040091</v>
+        <v>-7.292554407</v>
       </c>
       <c r="U221" s="13" t="n">
-        <v>2.563846618113305</v>
+        <v>2.563846618</v>
       </c>
       <c r="V221" s="13" t="n">
         <v>0</v>
@@ -21717,13 +21717,13 @@
         <v>21.12711486323631</v>
       </c>
       <c r="S222" s="13" t="n">
-        <v>-2.778899332032088</v>
+        <v>-2.778899332</v>
       </c>
       <c r="T222" s="14" t="n">
-        <v>-7.027944399777949</v>
+        <v>-7.0279444</v>
       </c>
       <c r="U222" s="13" t="n">
-        <v>3.205456039884726</v>
+        <v>3.20545604</v>
       </c>
       <c r="V222" s="13" t="n">
         <v>0</v>
@@ -21915,13 +21915,13 @@
         <v>57.95855402982794</v>
       </c>
       <c r="S224" s="13" t="n">
-        <v>-3.669916894787224</v>
+        <v>-3.669916895</v>
       </c>
       <c r="T224" s="14" t="n">
-        <v>-22.25850638321188</v>
+        <v>-22.25850638</v>
       </c>
       <c r="U224" s="13" t="n">
-        <v>5.417572857764245</v>
+        <v>5.417572858</v>
       </c>
       <c r="V224" s="13" t="n">
         <v>0</v>
@@ -22013,13 +22013,13 @@
         <v>8.32593232260518</v>
       </c>
       <c r="S225" s="13" t="n">
-        <v>-2.278400249205083</v>
+        <v>-2.278400249</v>
       </c>
       <c r="T225" s="14" t="n">
-        <v>-1.59777756287835</v>
+        <v>-1.597777563</v>
       </c>
       <c r="U225" s="13" t="n">
-        <v>1.418916768057395</v>
+        <v>1.418916768</v>
       </c>
       <c r="V225" s="13" t="n">
         <v>0</v>
@@ -22111,13 +22111,13 @@
         <v>-14.25577933625047</v>
       </c>
       <c r="S226" s="13" t="n">
-        <v>-1.395041415256867</v>
+        <v>-1.395041415</v>
       </c>
       <c r="T226" s="14" t="n">
-        <v>10.59634783397614</v>
+        <v>10.59634783</v>
       </c>
       <c r="U226" s="13" t="n">
-        <v>-0.8595348837209302</v>
+        <v>-0.8595348837</v>
       </c>
       <c r="V226" s="13" t="n">
         <v>3</v>
@@ -22209,13 +22209,13 @@
         <v>6.682013752519091</v>
       </c>
       <c r="S227" s="13" t="n">
-        <v>-2.254409973713274</v>
+        <v>-2.254409974</v>
       </c>
       <c r="T227" s="14" t="n">
-        <v>-1.29784123325313</v>
+        <v>-1.297841233</v>
       </c>
       <c r="U227" s="13" t="n">
-        <v>2.545962258345126</v>
+        <v>2.545962258</v>
       </c>
       <c r="V227" s="13" t="n">
         <v>0</v>
@@ -22303,10 +22303,10 @@
         <v>-23.69587656996822</v>
       </c>
       <c r="S228" s="13" t="n">
-        <v>0.863329273401956</v>
+        <v>0.8633292734</v>
       </c>
       <c r="T228" s="14" t="n">
-        <v>16.63165912072102</v>
+        <v>16.63165912</v>
       </c>
       <c r="U228" s="15" t="inlineStr">
         <is>
@@ -22403,13 +22403,13 @@
         <v>9.552834159002661</v>
       </c>
       <c r="S229" s="13" t="n">
-        <v>-2.301431756704989</v>
+        <v>-2.301431757</v>
       </c>
       <c r="T229" s="14" t="n">
-        <v>-0.2537345615557</v>
+        <v>-0.2537345616</v>
       </c>
       <c r="U229" s="13" t="n">
-        <v>1.041299379693111</v>
+        <v>1.04129938</v>
       </c>
       <c r="V229" s="13" t="n">
         <v>0</v>
@@ -22501,13 +22501,13 @@
         <v>2.70345201622709</v>
       </c>
       <c r="S230" s="13" t="n">
-        <v>-2.730345533503422</v>
+        <v>-2.730345534</v>
       </c>
       <c r="T230" s="14" t="n">
-        <v>-0.9089027390122499</v>
+        <v>-0.9089027390000001</v>
       </c>
       <c r="U230" s="13" t="n">
-        <v>1.208944828042747</v>
+        <v>1.208944828</v>
       </c>
       <c r="V230" s="13" t="n">
         <v>0</v>
@@ -22599,13 +22599,13 @@
         <v>17.13424908712922</v>
       </c>
       <c r="S231" s="13" t="n">
-        <v>-2.02404216307573</v>
+        <v>-2.024042163</v>
       </c>
       <c r="T231" s="14" t="n">
-        <v>-9.80601307081248</v>
+        <v>-9.806013071000001</v>
       </c>
       <c r="U231" s="13" t="n">
-        <v>4.048085391290912</v>
+        <v>4.048085391</v>
       </c>
       <c r="V231" s="13" t="n">
         <v>1</v>
@@ -22697,13 +22697,13 @@
         <v>8.06414937975277</v>
       </c>
       <c r="S232" s="13" t="n">
-        <v>-2.462648011306148</v>
+        <v>-2.462648011</v>
       </c>
       <c r="T232" s="14" t="n">
-        <v>-0.27682562873534</v>
+        <v>-0.2768256287</v>
       </c>
       <c r="U232" s="13" t="n">
-        <v>1.078696732222529</v>
+        <v>1.078696732</v>
       </c>
       <c r="V232" s="13" t="n">
         <v>0</v>
@@ -22795,13 +22795,13 @@
         <v>0.04163176281222999</v>
       </c>
       <c r="S233" s="13" t="n">
-        <v>-2.20887480012904</v>
+        <v>-2.2088748</v>
       </c>
       <c r="T233" s="14" t="n">
-        <v>0.8809732606724</v>
+        <v>0.8809732606999999</v>
       </c>
       <c r="U233" s="13" t="n">
-        <v>0.9049429310329072</v>
+        <v>0.904942931</v>
       </c>
       <c r="V233" s="13" t="n">
         <v>1</v>
@@ -22895,13 +22895,13 @@
         <v>2.67179029631159</v>
       </c>
       <c r="S234" s="13" t="n">
-        <v>-2.335899934258819</v>
+        <v>-2.335899934</v>
       </c>
       <c r="T234" s="14" t="n">
-        <v>0.71227900905247</v>
+        <v>0.7122790091</v>
       </c>
       <c r="U234" s="13" t="n">
-        <v>0.7015457788347206</v>
+        <v>0.7015457788</v>
       </c>
       <c r="V234" s="13" t="n">
         <v>0</v>
@@ -22993,13 +22993,13 @@
         <v>6.603627306991871</v>
       </c>
       <c r="S235" s="13" t="n">
-        <v>-2.396403168903409</v>
+        <v>-2.396403169</v>
       </c>
       <c r="T235" s="14" t="n">
-        <v>-4.17526460028161</v>
+        <v>-4.175264599999999</v>
       </c>
       <c r="U235" s="13" t="n">
-        <v>4.997931034482758</v>
+        <v>4.997931034</v>
       </c>
       <c r="V235" s="13" t="n">
         <v>0</v>
@@ -23093,10 +23093,10 @@
         <v>0.04990297079128</v>
       </c>
       <c r="S236" s="13" t="n">
-        <v>-3.254667802157313</v>
+        <v>-3.254667802</v>
       </c>
       <c r="T236" s="14" t="n">
-        <v>-11.91015695925369</v>
+        <v>-11.91015696</v>
       </c>
       <c r="U236" s="15" t="inlineStr">
         <is>
@@ -23193,13 +23193,13 @@
         <v>14.00404851956707</v>
       </c>
       <c r="S237" s="13" t="n">
-        <v>-2.648591222704716</v>
+        <v>-2.648591223</v>
       </c>
       <c r="T237" s="14" t="n">
-        <v>-0.47100720642952</v>
+        <v>-0.4710072064</v>
       </c>
       <c r="U237" s="13" t="n">
-        <v>1.090792316480943</v>
+        <v>1.090792316</v>
       </c>
       <c r="V237" s="13" t="n">
         <v>0</v>
@@ -23287,10 +23287,10 @@
         <v>2.8285103457102</v>
       </c>
       <c r="S238" s="13" t="n">
-        <v>-2.564144609560466</v>
+        <v>-2.56414461</v>
       </c>
       <c r="T238" s="14" t="n">
-        <v>-6.68165246033542</v>
+        <v>-6.68165246</v>
       </c>
       <c r="U238" s="15" t="inlineStr">
         <is>
@@ -23487,13 +23487,13 @@
         <v>-7.09262159215285</v>
       </c>
       <c r="S240" s="13" t="n">
-        <v>-2.464363854789822</v>
+        <v>-2.464363855</v>
       </c>
       <c r="T240" s="14" t="n">
-        <v>-0.9703541980105901</v>
+        <v>-0.9703541980000001</v>
       </c>
       <c r="U240" s="13" t="n">
-        <v>1.159240770405692</v>
+        <v>1.15924077</v>
       </c>
       <c r="V240" s="13" t="n">
         <v>0</v>
@@ -23583,13 +23583,13 @@
         <v>25.97695254353507</v>
       </c>
       <c r="S241" s="13" t="n">
-        <v>-2.414337586121075</v>
+        <v>-2.414337586</v>
       </c>
       <c r="T241" s="14" t="n">
-        <v>-6.75755170743403</v>
+        <v>-6.757551706999999</v>
       </c>
       <c r="U241" s="13" t="n">
-        <v>3.069501898101898</v>
+        <v>3.069501898</v>
       </c>
       <c r="V241" s="13" t="n">
         <v>0</v>
@@ -23681,13 +23681,13 @@
         <v>27.25121724197425</v>
       </c>
       <c r="S242" s="13" t="n">
-        <v>-3.411655858070257</v>
+        <v>-3.411655858</v>
       </c>
       <c r="T242" s="14" t="n">
-        <v>-14.41563421252153</v>
+        <v>-14.41563421</v>
       </c>
       <c r="U242" s="13" t="n">
-        <v>5.328766899880947</v>
+        <v>5.3287669</v>
       </c>
       <c r="V242" s="13" t="n">
         <v>0</v>
@@ -23775,13 +23775,13 @@
         <v>19.18902398387608</v>
       </c>
       <c r="S243" s="13" t="n">
-        <v>-2.687534878656339</v>
+        <v>-2.687534879</v>
       </c>
       <c r="T243" s="14" t="n">
-        <v>-2.22756096062365</v>
+        <v>-2.227560961</v>
       </c>
       <c r="U243" s="13" t="n">
-        <v>1.62371734305992</v>
+        <v>1.623717343</v>
       </c>
       <c r="V243" s="13" t="n">
         <v>0</v>
@@ -23873,13 +23873,13 @@
         <v>3.22106752958146</v>
       </c>
       <c r="S244" s="13" t="n">
-        <v>-1.414872043350259</v>
+        <v>-1.414872043</v>
       </c>
       <c r="T244" s="14" t="n">
-        <v>19.18337009100278</v>
+        <v>19.18337009</v>
       </c>
       <c r="U244" s="13" t="n">
-        <v>0.0751430198554128</v>
+        <v>0.07514301985999999</v>
       </c>
       <c r="V244" s="13" t="n">
         <v>2</v>
@@ -23971,13 +23971,13 @@
         <v>10.88943079473798</v>
       </c>
       <c r="S245" s="13" t="n">
-        <v>-2.29855860277281</v>
+        <v>-2.298558603</v>
       </c>
       <c r="T245" s="14" t="n">
-        <v>1.35603213206573</v>
+        <v>1.356032132</v>
       </c>
       <c r="U245" s="13" t="n">
-        <v>0.8283155013684996</v>
+        <v>0.8283155014</v>
       </c>
       <c r="V245" s="13" t="n">
         <v>0</v>
@@ -24069,13 +24069,13 @@
         <v>0.05843160346573</v>
       </c>
       <c r="S246" s="13" t="n">
-        <v>-2.544655777607284</v>
+        <v>-2.544655778</v>
       </c>
       <c r="T246" s="14" t="n">
-        <v>-0.6483400899739801</v>
+        <v>-0.64834009</v>
       </c>
       <c r="U246" s="13" t="n">
-        <v>1.122314311715263</v>
+        <v>1.122314312</v>
       </c>
       <c r="V246" s="13" t="n">
         <v>0</v>
@@ -24157,10 +24157,10 @@
         <v>30.74435589851317</v>
       </c>
       <c r="S247" s="13" t="n">
-        <v>-2.890809837560578</v>
+        <v>-2.890809838</v>
       </c>
       <c r="T247" s="14" t="n">
-        <v>-8.59854829704075</v>
+        <v>-8.598548297000001</v>
       </c>
       <c r="U247" s="15" t="inlineStr">
         <is>
@@ -24257,13 +24257,13 @@
         <v>12.73190753752848</v>
       </c>
       <c r="S248" s="13" t="n">
-        <v>-2.523042304756247</v>
+        <v>-2.523042305</v>
       </c>
       <c r="T248" s="14" t="n">
-        <v>-5.14591025696454</v>
+        <v>-5.145910257</v>
       </c>
       <c r="U248" s="13" t="n">
-        <v>1.708117631242432</v>
+        <v>1.708117631</v>
       </c>
       <c r="V248" s="13" t="n">
         <v>1</v>
@@ -24355,13 +24355,13 @@
         <v>1.65029306549479</v>
       </c>
       <c r="S249" s="13" t="n">
-        <v>-2.797316931363276</v>
+        <v>-2.797316931</v>
       </c>
       <c r="T249" s="14" t="n">
-        <v>-1.25708901816963</v>
+        <v>-1.257089018</v>
       </c>
       <c r="U249" s="13" t="n">
-        <v>2.294977343758719</v>
+        <v>2.294977344</v>
       </c>
       <c r="V249" s="13" t="n">
         <v>0</v>
@@ -24453,13 +24453,13 @@
         <v>7.27384198550198</v>
       </c>
       <c r="S250" s="13" t="n">
-        <v>-2.138956329966382</v>
+        <v>-2.13895633</v>
       </c>
       <c r="T250" s="14" t="n">
-        <v>8.43395338034377</v>
+        <v>8.43395338</v>
       </c>
       <c r="U250" s="13" t="n">
-        <v>0.297060288879183</v>
+        <v>0.2970602889</v>
       </c>
       <c r="V250" s="13" t="n">
         <v>1</v>
@@ -24551,13 +24551,13 @@
         <v>1.6715631537233</v>
       </c>
       <c r="S251" s="13" t="n">
-        <v>-1.40899550209764</v>
+        <v>-1.408995502</v>
       </c>
       <c r="T251" s="14" t="n">
-        <v>5.85986106003435</v>
+        <v>5.85986106</v>
       </c>
       <c r="U251" s="13" t="n">
-        <v>0.1650875681883434</v>
+        <v>0.1650875682</v>
       </c>
       <c r="V251" s="13" t="n">
         <v>1</v>
@@ -24649,13 +24649,13 @@
         <v>33.06045766991454</v>
       </c>
       <c r="S252" s="13" t="n">
-        <v>-1.946570386984923</v>
+        <v>-1.946570387</v>
       </c>
       <c r="T252" s="14" t="n">
-        <v>-4.673269102665921</v>
+        <v>-4.673269103</v>
       </c>
       <c r="U252" s="13" t="n">
-        <v>1.326588620978901</v>
+        <v>1.326588621</v>
       </c>
       <c r="V252" s="13" t="n">
         <v>0</v>
@@ -24743,13 +24743,13 @@
         <v>6.825264296713179</v>
       </c>
       <c r="S253" s="13" t="n">
-        <v>-2.338764755749013</v>
+        <v>-2.338764756</v>
       </c>
       <c r="T253" s="14" t="n">
-        <v>-1.71345845878729</v>
+        <v>-1.713458459</v>
       </c>
       <c r="U253" s="13" t="n">
-        <v>1.354199098893275</v>
+        <v>1.354199099</v>
       </c>
       <c r="V253" s="13" t="n">
         <v>0</v>
@@ -24841,13 +24841,13 @@
         <v>3.49788745538076</v>
       </c>
       <c r="S254" s="13" t="n">
-        <v>-2.273446274129419</v>
+        <v>-2.273446274</v>
       </c>
       <c r="T254" s="14" t="n">
-        <v>2.11704311038847</v>
+        <v>2.11704311</v>
       </c>
       <c r="U254" s="13" t="n">
-        <v>0.7542730135326836</v>
+        <v>0.7542730135</v>
       </c>
       <c r="V254" s="13" t="n">
         <v>0</v>
@@ -24939,13 +24939,13 @@
         <v>4.56678116930229</v>
       </c>
       <c r="S255" s="13" t="n">
-        <v>-2.204114227347174</v>
+        <v>-2.204114227</v>
       </c>
       <c r="T255" s="14" t="n">
-        <v>8.21926779749819</v>
+        <v>8.219267797000001</v>
       </c>
       <c r="U255" s="13" t="n">
-        <v>0.3412073490813648</v>
+        <v>0.3412073491</v>
       </c>
       <c r="V255" s="13" t="n">
         <v>0</v>
@@ -25138,10 +25138,10 @@
         </is>
       </c>
       <c r="T257" s="14" t="n">
-        <v>-13.92231605013842</v>
+        <v>-13.92231605</v>
       </c>
       <c r="U257" s="13" t="n">
-        <v>4.087781548904659</v>
+        <v>4.087781549</v>
       </c>
       <c r="V257" s="13" t="n">
         <v>0</v>
@@ -25311,13 +25311,13 @@
         <v>1.059467</v>
       </c>
       <c r="H6" s="20" t="n">
-        <v>-1.395041415256867</v>
+        <v>-1.395041415</v>
       </c>
       <c r="I6" s="21" t="n">
-        <v>10.59634783397614</v>
+        <v>10.59634783</v>
       </c>
       <c r="J6" s="20" t="n">
-        <v>-0.8595348837209302</v>
+        <v>-0.8595348837</v>
       </c>
       <c r="K6" s="20" t="n">
         <v>0</v>
@@ -25368,13 +25368,13 @@
         <v>1.026407</v>
       </c>
       <c r="H7" s="20" t="n">
-        <v>-1.414872043350259</v>
+        <v>-1.414872043</v>
       </c>
       <c r="I7" s="21" t="n">
-        <v>19.18337009100278</v>
+        <v>19.18337009</v>
       </c>
       <c r="J7" s="20" t="n">
-        <v>0.0751430198554128</v>
+        <v>0.07514301985999999</v>
       </c>
       <c r="K7" s="20" t="n">
         <v>6</v>
@@ -25425,13 +25425,13 @@
         <v>1.001988</v>
       </c>
       <c r="H8" s="20" t="n">
-        <v>-2.778899332032088</v>
+        <v>-2.778899332</v>
       </c>
       <c r="I8" s="21" t="n">
-        <v>-7.027944399777949</v>
+        <v>-7.0279444</v>
       </c>
       <c r="J8" s="20" t="n">
-        <v>3.205456039884726</v>
+        <v>3.20545604</v>
       </c>
       <c r="K8" s="20" t="n">
         <v>6</v>
@@ -25482,13 +25482,13 @@
         <v>0.977074</v>
       </c>
       <c r="H9" s="20" t="n">
-        <v>-3.041666588676601</v>
+        <v>-3.041666589</v>
       </c>
       <c r="I9" s="21" t="n">
-        <v>-6.10575845556636</v>
+        <v>-6.105758456</v>
       </c>
       <c r="J9" s="20" t="n">
-        <v>2.293684663194304</v>
+        <v>2.293684663</v>
       </c>
       <c r="K9" s="20" t="n">
         <v>0</v>
@@ -25549,7 +25549,7 @@
         </is>
       </c>
       <c r="J10" s="20" t="n">
-        <v>0.6799252944349184</v>
+        <v>0.6799252944</v>
       </c>
       <c r="K10" s="20" t="n">
         <v>0</v>
@@ -25596,10 +25596,10 @@
         <v>0.973873</v>
       </c>
       <c r="H11" s="20" t="n">
-        <v>-2.657527535631004</v>
+        <v>-2.657527536</v>
       </c>
       <c r="I11" s="21" t="n">
-        <v>-3.14657019088875</v>
+        <v>-3.146570191</v>
       </c>
       <c r="J11" s="23" t="inlineStr">
         <is>
@@ -25655,13 +25655,13 @@
         <v>0.9719</v>
       </c>
       <c r="H12" s="20" t="n">
-        <v>-2.593253197313953</v>
+        <v>-2.593253197</v>
       </c>
       <c r="I12" s="21" t="n">
-        <v>-0.77953898907508</v>
+        <v>-0.7795389891</v>
       </c>
       <c r="J12" s="20" t="n">
-        <v>1.118452224491904</v>
+        <v>1.118452224</v>
       </c>
       <c r="K12" s="20" t="n">
         <v>12</v>
@@ -25712,13 +25712,13 @@
         <v>0.971315</v>
       </c>
       <c r="H13" s="20" t="n">
-        <v>-2.396403168903409</v>
+        <v>-2.396403169</v>
       </c>
       <c r="I13" s="21" t="n">
-        <v>-4.17526460028161</v>
+        <v>-4.175264599999999</v>
       </c>
       <c r="J13" s="20" t="n">
-        <v>4.997931034482758</v>
+        <v>4.997931034</v>
       </c>
       <c r="K13" s="20" t="n">
         <v>12</v>
@@ -25769,13 +25769,13 @@
         <v>0.965907</v>
       </c>
       <c r="H14" s="20" t="n">
-        <v>-2.683134808398645</v>
+        <v>-2.683134808</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>-4.89757180147835</v>
+        <v>-4.897571801</v>
       </c>
       <c r="J14" s="20" t="n">
-        <v>3.482436729443561</v>
+        <v>3.482436729</v>
       </c>
       <c r="K14" s="20" t="n">
         <v>0</v>
@@ -25826,13 +25826,13 @@
         <v>0.965157</v>
       </c>
       <c r="H15" s="20" t="n">
-        <v>-2.134336787646643</v>
+        <v>-2.134336788</v>
       </c>
       <c r="I15" s="21" t="n">
-        <v>-4.60848633381161</v>
+        <v>-4.608486333999999</v>
       </c>
       <c r="J15" s="20" t="n">
-        <v>2.834704504253627</v>
+        <v>2.834704504</v>
       </c>
       <c r="K15" s="20" t="n">
         <v>0</v>
@@ -25879,13 +25879,13 @@
         <v>0.945775</v>
       </c>
       <c r="H16" s="20" t="n">
-        <v>-3.065773572575873</v>
+        <v>-3.065773573</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>-9.11577592890082</v>
+        <v>-9.115775929</v>
       </c>
       <c r="J16" s="20" t="n">
-        <v>4.510991970859092</v>
+        <v>4.510991971</v>
       </c>
       <c r="K16" s="20" t="n">
         <v>0</v>
@@ -25936,13 +25936,13 @@
         <v>0.933628</v>
       </c>
       <c r="H17" s="20" t="n">
-        <v>-1.110949839889436</v>
+        <v>-1.11094984</v>
       </c>
       <c r="I17" s="21" t="n">
-        <v>-3.62422455086337</v>
+        <v>-3.624224551</v>
       </c>
       <c r="J17" s="20" t="n">
-        <v>2.324624969428222</v>
+        <v>2.324624969</v>
       </c>
       <c r="K17" s="20" t="n">
         <v>0</v>
@@ -25993,13 +25993,13 @@
         <v>0.915076</v>
       </c>
       <c r="H18" s="20" t="n">
-        <v>-2.828170143856845</v>
+        <v>-2.828170144</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>-6.724709245663039</v>
+        <v>-6.724709246000001</v>
       </c>
       <c r="J18" s="20" t="n">
-        <v>2.536178107606679</v>
+        <v>2.536178108</v>
       </c>
       <c r="K18" s="20" t="n">
         <v>0</v>
@@ -26046,13 +26046,13 @@
         <v>0.914768</v>
       </c>
       <c r="H19" s="20" t="n">
-        <v>-2.580363332198487</v>
+        <v>-2.580363332</v>
       </c>
       <c r="I19" s="21" t="n">
-        <v>-3.7081761641262</v>
+        <v>-3.708176164</v>
       </c>
       <c r="J19" s="20" t="n">
-        <v>1.631550563863251</v>
+        <v>1.631550564</v>
       </c>
       <c r="K19" s="20" t="n">
         <v>0</v>
@@ -26103,13 +26103,13 @@
         <v>0.910185</v>
       </c>
       <c r="H20" s="20" t="n">
-        <v>-3.038626366417857</v>
+        <v>-3.038626366</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>-6.503640257810591</v>
+        <v>-6.503640258</v>
       </c>
       <c r="J20" s="20" t="n">
-        <v>4.500907659204716</v>
+        <v>4.500907659</v>
       </c>
       <c r="K20" s="20" t="n">
         <v>0</v>
@@ -26170,7 +26170,7 @@
         </is>
       </c>
       <c r="J21" s="20" t="n">
-        <v>0.3794931845692332</v>
+        <v>0.3794931846</v>
       </c>
       <c r="K21" s="20" t="n">
         <v>3</v>
@@ -26217,10 +26217,10 @@
         <v>0.894174</v>
       </c>
       <c r="H22" s="20" t="n">
-        <v>-2.027710047210017</v>
+        <v>-2.027710047</v>
       </c>
       <c r="I22" s="21" t="n">
-        <v>3.49944831120939</v>
+        <v>3.499448311</v>
       </c>
       <c r="J22" s="20" t="n">
         <v>0</v>
@@ -26274,13 +26274,13 @@
         <v>0.892697</v>
       </c>
       <c r="H23" s="20" t="n">
-        <v>-3.087488896157534</v>
+        <v>-3.087488896</v>
       </c>
       <c r="I23" s="21" t="n">
-        <v>-12.73000937487076</v>
+        <v>-12.73000937</v>
       </c>
       <c r="J23" s="20" t="n">
-        <v>8.835585833058639</v>
+        <v>8.835585833</v>
       </c>
       <c r="K23" s="20" t="n">
         <v>6</v>
@@ -26327,13 +26327,13 @@
         <v>0.892012</v>
       </c>
       <c r="H24" s="20" t="n">
-        <v>-2.464363854789822</v>
+        <v>-2.464363855</v>
       </c>
       <c r="I24" s="21" t="n">
-        <v>-0.9703541980105901</v>
+        <v>-0.9703541980000001</v>
       </c>
       <c r="J24" s="20" t="n">
-        <v>1.159240770405692</v>
+        <v>1.15924077</v>
       </c>
       <c r="K24" s="20" t="n">
         <v>18</v>
@@ -26384,13 +26384,13 @@
         <v>0.888737</v>
       </c>
       <c r="H25" s="20" t="n">
-        <v>-1.603701181519002</v>
+        <v>-1.603701182</v>
       </c>
       <c r="I25" s="21" t="n">
-        <v>-3.72513313015547</v>
+        <v>-3.72513313</v>
       </c>
       <c r="J25" s="20" t="n">
-        <v>3.855427896254304</v>
+        <v>3.855427896</v>
       </c>
       <c r="K25" s="20" t="n">
         <v>0</v>
@@ -26441,10 +26441,10 @@
         <v>0.88785</v>
       </c>
       <c r="H26" s="20" t="n">
-        <v>-3.084765058607455</v>
+        <v>-3.084765059</v>
       </c>
       <c r="I26" s="21" t="n">
-        <v>-6.591497692129799</v>
+        <v>-6.591497692000001</v>
       </c>
       <c r="J26" s="23" t="inlineStr">
         <is>
@@ -26500,13 +26500,13 @@
         <v>0.883606</v>
       </c>
       <c r="H27" s="20" t="n">
-        <v>-2.828110542207146</v>
+        <v>-2.828110542</v>
       </c>
       <c r="I27" s="21" t="n">
-        <v>-3.67546897445539</v>
+        <v>-3.675468974</v>
       </c>
       <c r="J27" s="20" t="n">
-        <v>1.27503047061354</v>
+        <v>1.275030471</v>
       </c>
       <c r="K27" s="20" t="n">
         <v>6</v>
@@ -26557,13 +26557,13 @@
         <v>0.8753649999999999</v>
       </c>
       <c r="H28" s="20" t="n">
-        <v>-2.713413619483628</v>
+        <v>-2.713413619</v>
       </c>
       <c r="I28" s="21" t="n">
-        <v>-0.31738635952646</v>
+        <v>-0.3173863595</v>
       </c>
       <c r="J28" s="20" t="n">
-        <v>1.05599723402785</v>
+        <v>1.055997234</v>
       </c>
       <c r="K28" s="20" t="n">
         <v>0</v>
@@ -26614,13 +26614,13 @@
         <v>0.86395</v>
       </c>
       <c r="H29" s="20" t="n">
-        <v>-5.034736184848962</v>
+        <v>-5.034736185</v>
       </c>
       <c r="I29" s="21" t="n">
-        <v>-55.25000985204761</v>
+        <v>-55.25000985</v>
       </c>
       <c r="J29" s="20" t="n">
-        <v>10.30076126294771</v>
+        <v>10.30076126</v>
       </c>
       <c r="K29" s="20" t="n">
         <v>0</v>
@@ -26671,13 +26671,13 @@
         <v>0.854947</v>
       </c>
       <c r="H30" s="20" t="n">
-        <v>-2.420627230432045</v>
+        <v>-2.42062723</v>
       </c>
       <c r="I30" s="21" t="n">
-        <v>-4.61638606275808</v>
+        <v>-4.616386063</v>
       </c>
       <c r="J30" s="20" t="n">
-        <v>1.718982241052652</v>
+        <v>1.718982241</v>
       </c>
       <c r="K30" s="20" t="n">
         <v>3</v>
@@ -26733,10 +26733,10 @@
         </is>
       </c>
       <c r="I31" s="21" t="n">
-        <v>-7.8806355358976</v>
+        <v>-7.880635536</v>
       </c>
       <c r="J31" s="20" t="n">
-        <v>6.530213768725804</v>
+        <v>6.530213769</v>
       </c>
       <c r="K31" s="20" t="n">
         <v>0</v>
@@ -26792,10 +26792,10 @@
         </is>
       </c>
       <c r="I32" s="21" t="n">
-        <v>17.05578963564099</v>
+        <v>17.05578964</v>
       </c>
       <c r="J32" s="20" t="n">
-        <v>0.09659947964648349</v>
+        <v>0.09659947965</v>
       </c>
       <c r="K32" s="20" t="n">
         <v>12</v>
@@ -26856,7 +26856,7 @@
         </is>
       </c>
       <c r="J33" s="20" t="n">
-        <v>0.5602495038276155</v>
+        <v>0.5602495038</v>
       </c>
       <c r="K33" s="20" t="n">
         <v>24</v>
@@ -26903,13 +26903,13 @@
         <v>0.849274</v>
       </c>
       <c r="H34" s="20" t="n">
-        <v>-2.841938928514076</v>
+        <v>-2.841938929</v>
       </c>
       <c r="I34" s="21" t="n">
-        <v>-8.219622526114009</v>
+        <v>-8.219622526</v>
       </c>
       <c r="J34" s="20" t="n">
-        <v>2.450829383886256</v>
+        <v>2.450829384</v>
       </c>
       <c r="K34" s="20" t="n">
         <v>36</v>
@@ -26960,13 +26960,13 @@
         <v>0.848414</v>
       </c>
       <c r="H35" s="20" t="n">
-        <v>-3.439993363768323</v>
+        <v>-3.439993364</v>
       </c>
       <c r="I35" s="21" t="n">
-        <v>52.00492852291939</v>
+        <v>52.00492852000001</v>
       </c>
       <c r="J35" s="20" t="n">
-        <v>0.0207143375037259</v>
+        <v>0.0207143375</v>
       </c>
       <c r="K35" s="20" t="n">
         <v>0</v>
@@ -27017,13 +27017,13 @@
         <v>0.847661</v>
       </c>
       <c r="H36" s="20" t="n">
-        <v>-2.718351176091199</v>
+        <v>-2.718351176</v>
       </c>
       <c r="I36" s="21" t="n">
-        <v>-6.11192872285313</v>
+        <v>-6.111928723</v>
       </c>
       <c r="J36" s="20" t="n">
-        <v>2.808306412739853</v>
+        <v>2.808306413</v>
       </c>
       <c r="K36" s="20" t="n">
         <v>15</v>
@@ -27074,13 +27074,13 @@
         <v>0.845853</v>
       </c>
       <c r="H37" s="20" t="n">
-        <v>-1.747668894442604</v>
+        <v>-1.747668894</v>
       </c>
       <c r="I37" s="21" t="n">
-        <v>-2.4453434344101</v>
+        <v>-2.445343434</v>
       </c>
       <c r="J37" s="20" t="n">
-        <v>1.508810757928511</v>
+        <v>1.508810758</v>
       </c>
       <c r="K37" s="20" t="n">
         <v>0</v>
@@ -27127,13 +27127,13 @@
         <v>0.842102</v>
       </c>
       <c r="H38" s="20" t="n">
-        <v>-3.409862227858828</v>
+        <v>-3.409862228</v>
       </c>
       <c r="I38" s="21" t="n">
-        <v>-9.35773058054745</v>
+        <v>-9.357730581</v>
       </c>
       <c r="J38" s="20" t="n">
-        <v>2.390981511050616</v>
+        <v>2.390981511</v>
       </c>
       <c r="K38" s="20" t="n">
         <v>48</v>
@@ -27184,13 +27184,13 @@
         <v>0.8358449999999999</v>
       </c>
       <c r="H39" s="20" t="n">
-        <v>-2.464797220223432</v>
+        <v>-2.46479722</v>
       </c>
       <c r="I39" s="21" t="n">
-        <v>-3.37613279668043</v>
+        <v>-3.376132797</v>
       </c>
       <c r="J39" s="20" t="n">
-        <v>3.333200473650932</v>
+        <v>3.333200474</v>
       </c>
       <c r="K39" s="20" t="n">
         <v>6</v>
@@ -27241,13 +27241,13 @@
         <v>0.833404</v>
       </c>
       <c r="H40" s="20" t="n">
-        <v>-2.462659013273068</v>
+        <v>-2.462659013</v>
       </c>
       <c r="I40" s="21" t="n">
-        <v>-2.58457610200871</v>
+        <v>-2.584576102</v>
       </c>
       <c r="J40" s="20" t="n">
-        <v>1.276791517838837</v>
+        <v>1.276791518</v>
       </c>
       <c r="K40" s="20" t="n">
         <v>12</v>
@@ -27298,13 +27298,13 @@
         <v>0.831732</v>
       </c>
       <c r="H41" s="20" t="n">
-        <v>-2.376280161554581</v>
+        <v>-2.376280162</v>
       </c>
       <c r="I41" s="21" t="n">
-        <v>-2.20658843000475</v>
+        <v>-2.20658843</v>
       </c>
       <c r="J41" s="20" t="n">
-        <v>1.625015683120539</v>
+        <v>1.625015683</v>
       </c>
       <c r="K41" s="20" t="n">
         <v>6</v>
@@ -27360,10 +27360,10 @@
         </is>
       </c>
       <c r="I42" s="21" t="n">
-        <v>-0.7578976594889</v>
+        <v>-0.7578976595</v>
       </c>
       <c r="J42" s="20" t="n">
-        <v>1.282012658599103</v>
+        <v>1.282012659</v>
       </c>
       <c r="K42" s="20" t="n">
         <v>0</v>
@@ -27410,13 +27410,13 @@
         <v>0.829098</v>
       </c>
       <c r="H43" s="20" t="n">
-        <v>-2.391033579261655</v>
+        <v>-2.391033579</v>
       </c>
       <c r="I43" s="21" t="n">
-        <v>-3.55969898981636</v>
+        <v>-3.55969899</v>
       </c>
       <c r="J43" s="20" t="n">
-        <v>1.93998405968331</v>
+        <v>1.93998406</v>
       </c>
       <c r="K43" s="20" t="n">
         <v>0</v>
@@ -27463,13 +27463,13 @@
         <v>0.828477</v>
       </c>
       <c r="H44" s="20" t="n">
-        <v>-1.117374469224393</v>
+        <v>-1.117374469</v>
       </c>
       <c r="I44" s="21" t="n">
-        <v>-0.47240053509369</v>
+        <v>-0.4724005351</v>
       </c>
       <c r="J44" s="20" t="n">
-        <v>1.048969584106413</v>
+        <v>1.048969584</v>
       </c>
       <c r="K44" s="20" t="n">
         <v>0</v>
@@ -27516,13 +27516,13 @@
         <v>0.827738</v>
       </c>
       <c r="H45" s="20" t="n">
-        <v>-2.454424207139954</v>
+        <v>-2.454424207</v>
       </c>
       <c r="I45" s="21" t="n">
-        <v>-1.83775052742616</v>
+        <v>-1.837750527</v>
       </c>
       <c r="J45" s="20" t="n">
-        <v>3.505430304846079</v>
+        <v>3.505430305</v>
       </c>
       <c r="K45" s="20" t="n">
         <v>0</v>
@@ -27573,13 +27573,13 @@
         <v>0.826804</v>
       </c>
       <c r="H46" s="20" t="n">
-        <v>-2.530692922549726</v>
+        <v>-2.530692923</v>
       </c>
       <c r="I46" s="21" t="n">
-        <v>-4.68613655085634</v>
+        <v>-4.686136551000001</v>
       </c>
       <c r="J46" s="20" t="n">
-        <v>2.746229916897507</v>
+        <v>2.746229917</v>
       </c>
       <c r="K46" s="20" t="n">
         <v>6</v>
@@ -27630,13 +27630,13 @@
         <v>0.824675</v>
       </c>
       <c r="H47" s="20" t="n">
-        <v>-3.163624765344716</v>
+        <v>-3.163624765</v>
       </c>
       <c r="I47" s="21" t="n">
-        <v>-9.529146649724909</v>
+        <v>-9.529146650000001</v>
       </c>
       <c r="J47" s="20" t="n">
-        <v>3.056954747133755</v>
+        <v>3.056954747</v>
       </c>
       <c r="K47" s="20" t="n">
         <v>0</v>
@@ -27687,10 +27687,10 @@
         <v>0.823274</v>
       </c>
       <c r="H48" s="20" t="n">
-        <v>-3.856373323319721</v>
+        <v>-3.856373323</v>
       </c>
       <c r="I48" s="21" t="n">
-        <v>-21.2083380488909</v>
+        <v>-21.20833805</v>
       </c>
       <c r="J48" s="23" t="inlineStr">
         <is>
@@ -27746,13 +27746,13 @@
         <v>0.822789</v>
       </c>
       <c r="H49" s="20" t="n">
-        <v>-3.320908768266181</v>
+        <v>-3.320908768</v>
       </c>
       <c r="I49" s="21" t="n">
-        <v>-14.38768644717639</v>
+        <v>-14.38768645</v>
       </c>
       <c r="J49" s="20" t="n">
-        <v>8.330146502429471</v>
+        <v>8.330146502</v>
       </c>
       <c r="K49" s="20" t="n">
         <v>0</v>
@@ -27813,7 +27813,7 @@
         </is>
       </c>
       <c r="J50" s="20" t="n">
-        <v>-30.19148936170213</v>
+        <v>-30.19148936</v>
       </c>
       <c r="K50" s="20" t="n">
         <v>0</v>
@@ -27860,13 +27860,13 @@
         <v>0.820725</v>
       </c>
       <c r="H51" s="20" t="n">
-        <v>-2.218835739799293</v>
+        <v>-2.21883574</v>
       </c>
       <c r="I51" s="21" t="n">
-        <v>3.9445056733376</v>
+        <v>3.944505673</v>
       </c>
       <c r="J51" s="20" t="n">
-        <v>0.4957150537144523</v>
+        <v>0.4957150537</v>
       </c>
       <c r="K51" s="20" t="n">
         <v>0</v>
@@ -27913,13 +27913,13 @@
         <v>0.820218</v>
       </c>
       <c r="H52" s="20" t="n">
-        <v>-2.1295126623623</v>
+        <v>-2.129512662</v>
       </c>
       <c r="I52" s="21" t="n">
-        <v>4.1399586322581</v>
+        <v>4.139958632</v>
       </c>
       <c r="J52" s="20" t="n">
-        <v>0.5138134878477995</v>
+        <v>0.5138134878</v>
       </c>
       <c r="K52" s="20" t="n">
         <v>0</v>
@@ -27966,13 +27966,13 @@
         <v>0.818034</v>
       </c>
       <c r="H53" s="20" t="n">
-        <v>-2.471102317670937</v>
+        <v>-2.471102318</v>
       </c>
       <c r="I53" s="21" t="n">
-        <v>-0.79961487777166</v>
+        <v>-0.7996148778</v>
       </c>
       <c r="J53" s="20" t="n">
-        <v>1.10201726935953</v>
+        <v>1.102017269</v>
       </c>
       <c r="K53" s="20" t="n">
         <v>0</v>
@@ -28023,13 +28023,13 @@
         <v>0.817634</v>
       </c>
       <c r="H54" s="20" t="n">
-        <v>-3.121306610999216</v>
+        <v>-3.121306611</v>
       </c>
       <c r="I54" s="21" t="n">
-        <v>-9.671098638764921</v>
+        <v>-9.671098639</v>
       </c>
       <c r="J54" s="20" t="n">
-        <v>3.511864846150517</v>
+        <v>3.511864846</v>
       </c>
       <c r="K54" s="20" t="n">
         <v>24</v>
@@ -28080,13 +28080,13 @@
         <v>0.817437</v>
       </c>
       <c r="H55" s="20" t="n">
-        <v>-2.558000252921597</v>
+        <v>-2.558000253</v>
       </c>
       <c r="I55" s="21" t="n">
-        <v>-3.07721973794692</v>
+        <v>-3.077219738</v>
       </c>
       <c r="J55" s="20" t="n">
-        <v>1.498714347877685</v>
+        <v>1.498714348</v>
       </c>
       <c r="K55" s="20" t="n">
         <v>0</v>
@@ -28137,13 +28137,13 @@
         <v>0.81731</v>
       </c>
       <c r="H56" s="20" t="n">
-        <v>-2.705266689914573</v>
+        <v>-2.70526669</v>
       </c>
       <c r="I56" s="21" t="n">
-        <v>-1.59604666573861</v>
+        <v>-1.596046666</v>
       </c>
       <c r="J56" s="20" t="n">
-        <v>1.217761319733166</v>
+        <v>1.21776132</v>
       </c>
       <c r="K56" s="20" t="n">
         <v>0</v>
@@ -28190,13 +28190,13 @@
         <v>0.816343</v>
       </c>
       <c r="H57" s="20" t="n">
-        <v>-2.338764755749013</v>
+        <v>-2.338764756</v>
       </c>
       <c r="I57" s="21" t="n">
-        <v>-1.71345845878729</v>
+        <v>-1.713458459</v>
       </c>
       <c r="J57" s="20" t="n">
-        <v>1.354199098893275</v>
+        <v>1.354199099</v>
       </c>
       <c r="K57" s="20" t="n">
         <v>3</v>
@@ -28247,13 +28247,13 @@
         <v>0.815514</v>
       </c>
       <c r="H58" s="20" t="n">
-        <v>-2.313044982742726</v>
+        <v>-2.313044983</v>
       </c>
       <c r="I58" s="21" t="n">
-        <v>-0.9204490169465099</v>
+        <v>-0.9204490169</v>
       </c>
       <c r="J58" s="20" t="n">
-        <v>1.09660917598456</v>
+        <v>1.096609176</v>
       </c>
       <c r="K58" s="20" t="n">
         <v>3</v>
@@ -28314,7 +28314,7 @@
         </is>
       </c>
       <c r="J59" s="20" t="n">
-        <v>0.2271714922048997</v>
+        <v>0.2271714922</v>
       </c>
       <c r="K59" s="20" t="n">
         <v>3</v>
@@ -28361,13 +28361,13 @@
         <v>0.810494</v>
       </c>
       <c r="H60" s="20" t="n">
-        <v>-2.615001937338421</v>
+        <v>-2.615001937</v>
       </c>
       <c r="I60" s="21" t="n">
-        <v>-4.642116000142369</v>
+        <v>-4.642116000000001</v>
       </c>
       <c r="J60" s="20" t="n">
-        <v>2.10186265044353</v>
+        <v>2.10186265</v>
       </c>
       <c r="K60" s="20" t="n">
         <v>9</v>
@@ -28418,13 +28418,13 @@
         <v>0.809284</v>
       </c>
       <c r="H61" s="20" t="n">
-        <v>-2.867955121520632</v>
+        <v>-2.867955122</v>
       </c>
       <c r="I61" s="21" t="n">
-        <v>-6.26242474638882</v>
+        <v>-6.262424746000001</v>
       </c>
       <c r="J61" s="20" t="n">
-        <v>9.629045782324331</v>
+        <v>9.629045782</v>
       </c>
       <c r="K61" s="20" t="n">
         <v>0</v>
@@ -28475,13 +28475,13 @@
         <v>0.80774</v>
       </c>
       <c r="H62" s="20" t="n">
-        <v>-2.747238742380439</v>
+        <v>-2.747238742</v>
       </c>
       <c r="I62" s="21" t="n">
-        <v>-2.87879694060416</v>
+        <v>-2.878796941</v>
       </c>
       <c r="J62" s="20" t="n">
-        <v>17.92485341637282</v>
+        <v>17.92485342</v>
       </c>
       <c r="K62" s="20" t="n">
         <v>0</v>
@@ -28532,13 +28532,13 @@
         <v>0.807287</v>
       </c>
       <c r="H63" s="20" t="n">
-        <v>-2.581553482240478</v>
+        <v>-2.581553482</v>
       </c>
       <c r="I63" s="21" t="n">
-        <v>-5.07307682550893</v>
+        <v>-5.073076826</v>
       </c>
       <c r="J63" s="20" t="n">
-        <v>3.641867685693814</v>
+        <v>3.641867686</v>
       </c>
       <c r="K63" s="20" t="n">
         <v>0</v>
@@ -28585,13 +28585,13 @@
         <v>0.804447</v>
       </c>
       <c r="H64" s="20" t="n">
-        <v>-2.375597674215067</v>
+        <v>-2.375597674</v>
       </c>
       <c r="I64" s="21" t="n">
-        <v>2.00260795909611</v>
+        <v>2.002607959</v>
       </c>
       <c r="J64" s="20" t="n">
-        <v>0.6747582368749603</v>
+        <v>0.6747582369</v>
       </c>
       <c r="K64" s="20" t="n">
         <v>6</v>
@@ -28652,7 +28652,7 @@
         </is>
       </c>
       <c r="J65" s="20" t="n">
-        <v>0.2588283602518478</v>
+        <v>0.2588283603</v>
       </c>
       <c r="K65" s="20" t="n">
         <v>3</v>
@@ -28699,13 +28699,13 @@
         <v>0.802937</v>
       </c>
       <c r="H66" s="20" t="n">
-        <v>-3.799335677153871</v>
+        <v>-3.799335677</v>
       </c>
       <c r="I66" s="21" t="n">
-        <v>-10.85595730653118</v>
+        <v>-10.85595731</v>
       </c>
       <c r="J66" s="20" t="n">
-        <v>16.37526827818598</v>
+        <v>16.37526828</v>
       </c>
       <c r="K66" s="20" t="n">
         <v>18</v>
@@ -28756,13 +28756,13 @@
         <v>0.802755</v>
       </c>
       <c r="H67" s="20" t="n">
-        <v>-2.22227109544748</v>
+        <v>-2.222271095</v>
       </c>
       <c r="I67" s="21" t="n">
-        <v>-4.0966263466327</v>
+        <v>-4.096626347</v>
       </c>
       <c r="J67" s="20" t="n">
-        <v>1.671465855850855</v>
+        <v>1.671465856</v>
       </c>
       <c r="K67" s="20" t="n">
         <v>24</v>
@@ -28809,10 +28809,10 @@
         <v>0.800063</v>
       </c>
       <c r="H68" s="20" t="n">
-        <v>-2.583806049852292</v>
+        <v>-2.58380605</v>
       </c>
       <c r="I68" s="21" t="n">
-        <v>-6.731848788962109</v>
+        <v>-6.731848789</v>
       </c>
       <c r="J68" s="23" t="inlineStr">
         <is>
@@ -28868,13 +28868,13 @@
         <v>0.797576</v>
       </c>
       <c r="H69" s="20" t="n">
-        <v>-2.743672632436942</v>
+        <v>-2.743672632</v>
       </c>
       <c r="I69" s="21" t="n">
-        <v>-6.336891889754551</v>
+        <v>-6.33689189</v>
       </c>
       <c r="J69" s="20" t="n">
-        <v>2.852372361156708</v>
+        <v>2.852372361</v>
       </c>
       <c r="K69" s="20" t="n">
         <v>6</v>
@@ -28925,13 +28925,13 @@
         <v>0.795505</v>
       </c>
       <c r="H70" s="20" t="n">
-        <v>-2.331733054336424</v>
+        <v>-2.331733054</v>
       </c>
       <c r="I70" s="21" t="n">
-        <v>-1.37530147979842</v>
+        <v>-1.37530148</v>
       </c>
       <c r="J70" s="20" t="n">
-        <v>1.560090216251592</v>
+        <v>1.560090216</v>
       </c>
       <c r="K70" s="20" t="n">
         <v>0</v>
@@ -28978,13 +28978,13 @@
         <v>0.79522</v>
       </c>
       <c r="H71" s="20" t="n">
-        <v>-2.185608293627698</v>
+        <v>-2.185608294</v>
       </c>
       <c r="I71" s="21" t="n">
-        <v>1.80843440336994</v>
+        <v>1.808434403</v>
       </c>
       <c r="J71" s="20" t="n">
-        <v>0.8106565445482694</v>
+        <v>0.8106565445</v>
       </c>
       <c r="K71" s="20" t="n">
         <v>18</v>
@@ -29035,13 +29035,13 @@
         <v>0.793055</v>
       </c>
       <c r="H72" s="20" t="n">
-        <v>-2.285887091905396</v>
+        <v>-2.285887092</v>
       </c>
       <c r="I72" s="21" t="n">
-        <v>-6.379589600829889</v>
+        <v>-6.379589601</v>
       </c>
       <c r="J72" s="20" t="n">
-        <v>2.46488539682164</v>
+        <v>2.464885397</v>
       </c>
       <c r="K72" s="20" t="n">
         <v>6</v>
@@ -29088,13 +29088,13 @@
         <v>0.791096</v>
       </c>
       <c r="H73" s="20" t="n">
-        <v>-2.598039251821294</v>
+        <v>-2.598039252</v>
       </c>
       <c r="I73" s="21" t="n">
-        <v>0.72400023638067</v>
+        <v>0.7240002364</v>
       </c>
       <c r="J73" s="20" t="n">
-        <v>0.6964892412231031</v>
+        <v>0.6964892412</v>
       </c>
       <c r="K73" s="20" t="n">
         <v>9</v>
@@ -29145,13 +29145,13 @@
         <v>0.791012</v>
       </c>
       <c r="H74" s="20" t="n">
-        <v>0.9062483312050402</v>
+        <v>0.9062483312</v>
       </c>
       <c r="I74" s="21" t="n">
-        <v>29.23504446654471</v>
+        <v>29.23504447</v>
       </c>
       <c r="J74" s="20" t="n">
-        <v>0.2917116474403037</v>
+        <v>0.2917116474</v>
       </c>
       <c r="K74" s="20" t="n">
         <v>21</v>
@@ -29198,10 +29198,10 @@
         <v>0.787788</v>
       </c>
       <c r="H75" s="20" t="n">
-        <v>-2.611061981564168</v>
+        <v>-2.611061982</v>
       </c>
       <c r="I75" s="21" t="n">
-        <v>-2.78990936887509</v>
+        <v>-2.789909369</v>
       </c>
       <c r="J75" s="23" t="inlineStr">
         <is>
@@ -29257,13 +29257,13 @@
         <v>0.7870819999999999</v>
       </c>
       <c r="H76" s="20" t="n">
-        <v>-2.769395890555588</v>
+        <v>-2.769395891</v>
       </c>
       <c r="I76" s="21" t="n">
-        <v>-3.9391363237901</v>
+        <v>-3.939136324</v>
       </c>
       <c r="J76" s="20" t="n">
-        <v>2.665975891318012</v>
+        <v>2.665975891</v>
       </c>
       <c r="K76" s="20" t="n">
         <v>0</v>
@@ -29310,13 +29310,13 @@
         <v>0.785305</v>
       </c>
       <c r="H77" s="20" t="n">
-        <v>-2.471743263712613</v>
+        <v>-2.471743264</v>
       </c>
       <c r="I77" s="21" t="n">
-        <v>-3.32985291447249</v>
+        <v>-3.329852914</v>
       </c>
       <c r="J77" s="20" t="n">
-        <v>2.360853432282004</v>
+        <v>2.360853432</v>
       </c>
       <c r="K77" s="20" t="n">
         <v>6</v>
@@ -29367,10 +29367,10 @@
         <v>0.7833059999999999</v>
       </c>
       <c r="H78" s="20" t="n">
-        <v>-2.543559389363076</v>
+        <v>-2.543559389</v>
       </c>
       <c r="I78" s="21" t="n">
-        <v>-12.23811459342974</v>
+        <v>-12.23811459</v>
       </c>
       <c r="J78" s="23" t="inlineStr">
         <is>
@@ -29426,13 +29426,13 @@
         <v>0.782175</v>
       </c>
       <c r="H79" s="20" t="n">
-        <v>-2.879552734823591</v>
+        <v>-2.879552735</v>
       </c>
       <c r="I79" s="21" t="n">
-        <v>-4.85412756337102</v>
+        <v>-4.854127563</v>
       </c>
       <c r="J79" s="20" t="n">
-        <v>1.439240049931325</v>
+        <v>1.43924005</v>
       </c>
       <c r="K79" s="20" t="n">
         <v>0</v>
@@ -29483,13 +29483,13 @@
         <v>0.781583</v>
       </c>
       <c r="H80" s="20" t="n">
-        <v>-3.352998276587603</v>
+        <v>-3.352998277</v>
       </c>
       <c r="I80" s="21" t="n">
-        <v>-3.94206065124512</v>
+        <v>-3.942060651</v>
       </c>
       <c r="J80" s="20" t="n">
-        <v>5.319225195987072</v>
+        <v>5.319225196</v>
       </c>
       <c r="K80" s="20" t="n">
         <v>0</v>
@@ -29540,13 +29540,13 @@
         <v>0.781173</v>
       </c>
       <c r="H81" s="20" t="n">
-        <v>-2.520579087533114</v>
+        <v>-2.520579088</v>
       </c>
       <c r="I81" s="21" t="n">
-        <v>1.45179226462891</v>
+        <v>1.451792265</v>
       </c>
       <c r="J81" s="20" t="n">
-        <v>0.3600101679341603</v>
+        <v>0.3600101679</v>
       </c>
       <c r="K81" s="20" t="n">
         <v>0</v>
@@ -29597,13 +29597,13 @@
         <v>0.780978</v>
       </c>
       <c r="H82" s="20" t="n">
-        <v>-2.6043339372014</v>
+        <v>-2.604333937</v>
       </c>
       <c r="I82" s="21" t="n">
-        <v>1.75592675906143</v>
+        <v>1.755926759</v>
       </c>
       <c r="J82" s="20" t="n">
-        <v>0.7715117893122156</v>
+        <v>0.7715117893</v>
       </c>
       <c r="K82" s="20" t="n">
         <v>0</v>
@@ -29654,13 +29654,13 @@
         <v>0.780494</v>
       </c>
       <c r="H83" s="20" t="n">
-        <v>-2.778307688048026</v>
+        <v>-2.778307688</v>
       </c>
       <c r="I83" s="21" t="n">
-        <v>-6.332213787431599</v>
+        <v>-6.332213787000001</v>
       </c>
       <c r="J83" s="20" t="n">
-        <v>2.996280707709857</v>
+        <v>2.996280708</v>
       </c>
       <c r="K83" s="20" t="n">
         <v>3</v>
@@ -29711,13 +29711,13 @@
         <v>0.772647</v>
       </c>
       <c r="H84" s="20" t="n">
-        <v>-1.949553927062888</v>
+        <v>-1.949553927</v>
       </c>
       <c r="I84" s="21" t="n">
-        <v>-2.18988130400604</v>
+        <v>-2.189881304</v>
       </c>
       <c r="J84" s="20" t="n">
-        <v>3.069064896831903</v>
+        <v>3.069064897</v>
       </c>
       <c r="K84" s="20" t="n">
         <v>24</v>
@@ -29764,10 +29764,10 @@
         <v>0.771821</v>
       </c>
       <c r="H85" s="20" t="n">
-        <v>-2.179280574088794</v>
+        <v>-2.179280574</v>
       </c>
       <c r="I85" s="21" t="n">
-        <v>-4.48430271211064</v>
+        <v>-4.484302712</v>
       </c>
       <c r="J85" s="23" t="inlineStr">
         <is>
@@ -29823,13 +29823,13 @@
         <v>0.7686500000000001</v>
       </c>
       <c r="H86" s="20" t="n">
-        <v>-2.637851269357438</v>
+        <v>-2.637851269</v>
       </c>
       <c r="I86" s="21" t="n">
-        <v>-4.96544132896409</v>
+        <v>-4.965441329</v>
       </c>
       <c r="J86" s="20" t="n">
-        <v>1.907527951336951</v>
+        <v>1.907527951</v>
       </c>
       <c r="K86" s="20" t="n">
         <v>3</v>
@@ -29880,13 +29880,13 @@
         <v>0.7683179999999999</v>
       </c>
       <c r="H87" s="20" t="n">
-        <v>-2.90292866167897</v>
+        <v>-2.902928662</v>
       </c>
       <c r="I87" s="21" t="n">
-        <v>-6.53886783380674</v>
+        <v>-6.538867834</v>
       </c>
       <c r="J87" s="20" t="n">
-        <v>2.423551645206492</v>
+        <v>2.423551645</v>
       </c>
       <c r="K87" s="20" t="n">
         <v>27</v>
@@ -29937,13 +29937,13 @@
         <v>0.765063</v>
       </c>
       <c r="H88" s="20" t="n">
-        <v>-2.335899934258819</v>
+        <v>-2.335899934</v>
       </c>
       <c r="I88" s="21" t="n">
-        <v>0.71227900905247</v>
+        <v>0.7122790091</v>
       </c>
       <c r="J88" s="20" t="n">
-        <v>0.7015457788347206</v>
+        <v>0.7015457788</v>
       </c>
       <c r="K88" s="20" t="n">
         <v>3</v>
@@ -29994,13 +29994,13 @@
         <v>0.7646539999999999</v>
       </c>
       <c r="H89" s="20" t="n">
-        <v>-2.55697313953516</v>
+        <v>-2.55697314</v>
       </c>
       <c r="I89" s="21" t="n">
-        <v>-1.5849594219859</v>
+        <v>-1.584959422</v>
       </c>
       <c r="J89" s="20" t="n">
-        <v>1.26865028029323</v>
+        <v>1.26865028</v>
       </c>
       <c r="K89" s="20" t="n">
         <v>12</v>
@@ -30051,13 +30051,13 @@
         <v>0.763172</v>
       </c>
       <c r="H90" s="20" t="n">
-        <v>-2.815716483299779</v>
+        <v>-2.815716483</v>
       </c>
       <c r="I90" s="21" t="n">
-        <v>-8.13406968474955</v>
+        <v>-8.134069685</v>
       </c>
       <c r="J90" s="20" t="n">
-        <v>2.360628755551685</v>
+        <v>2.360628756</v>
       </c>
       <c r="K90" s="20" t="n">
         <v>27</v>
@@ -30108,13 +30108,13 @@
         <v>0.762537</v>
       </c>
       <c r="H91" s="20" t="n">
-        <v>-2.156386026379526</v>
+        <v>-2.156386026</v>
       </c>
       <c r="I91" s="21" t="n">
-        <v>5.977842245072059</v>
+        <v>5.977842245</v>
       </c>
       <c r="J91" s="20" t="n">
-        <v>-3.478954833536457</v>
+        <v>-3.478954834</v>
       </c>
       <c r="K91" s="20" t="n">
         <v>0</v>
@@ -30161,13 +30161,13 @@
         <v>0.7625</v>
       </c>
       <c r="H92" s="20" t="n">
-        <v>-3.45059824550919</v>
+        <v>-3.450598246</v>
       </c>
       <c r="I92" s="21" t="n">
-        <v>-8.075292568151569</v>
+        <v>-8.075292568</v>
       </c>
       <c r="J92" s="20" t="n">
-        <v>6.380255941499086</v>
+        <v>6.380255941</v>
       </c>
       <c r="K92" s="20" t="n">
         <v>0</v>
@@ -30218,13 +30218,13 @@
         <v>0.761491</v>
       </c>
       <c r="H93" s="20" t="n">
-        <v>-2.338860176704115</v>
+        <v>-2.338860177</v>
       </c>
       <c r="I93" s="21" t="n">
-        <v>1.66375692498187</v>
+        <v>1.663756925</v>
       </c>
       <c r="J93" s="20" t="n">
-        <v>0.1093208892793883</v>
+        <v>0.1093208893</v>
       </c>
       <c r="K93" s="20" t="n">
         <v>0</v>
@@ -30275,13 +30275,13 @@
         <v>0.7607</v>
       </c>
       <c r="H94" s="20" t="n">
-        <v>-2.781160222601376</v>
+        <v>-2.781160223</v>
       </c>
       <c r="I94" s="21" t="n">
-        <v>-7.533173352250761</v>
+        <v>-7.533173352</v>
       </c>
       <c r="J94" s="20" t="n">
-        <v>3.917795537806337</v>
+        <v>3.917795538</v>
       </c>
       <c r="K94" s="20" t="n">
         <v>0</v>
@@ -30332,13 +30332,13 @@
         <v>0.760625</v>
       </c>
       <c r="H95" s="20" t="n">
-        <v>-3.712496319078078</v>
+        <v>-3.712496319</v>
       </c>
       <c r="I95" s="21" t="n">
-        <v>-36.89568645733485</v>
+        <v>-36.89568646</v>
       </c>
       <c r="J95" s="20" t="n">
-        <v>4.171205595137033</v>
+        <v>4.171205595</v>
       </c>
       <c r="K95" s="20" t="n">
         <v>0</v>
@@ -30385,13 +30385,13 @@
         <v>0.760446</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>-2.587674576908769</v>
+        <v>-2.587674577</v>
       </c>
       <c r="I96" s="21" t="n">
-        <v>-4.07179938500562</v>
+        <v>-4.071799385</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>1.627100320900626</v>
+        <v>1.627100321</v>
       </c>
       <c r="K96" s="20" t="n">
         <v>0</v>
@@ -30442,13 +30442,13 @@
         <v>0.75966</v>
       </c>
       <c r="H97" s="20" t="n">
-        <v>-2.759283868022472</v>
+        <v>-2.759283868</v>
       </c>
       <c r="I97" s="21" t="n">
-        <v>-8.142823441586609</v>
+        <v>-8.142823441999999</v>
       </c>
       <c r="J97" s="20" t="n">
-        <v>2.545015594509398</v>
+        <v>2.545015595</v>
       </c>
       <c r="K97" s="20" t="n">
         <v>0</v>
@@ -30499,13 +30499,13 @@
         <v>0.7588200000000001</v>
       </c>
       <c r="H98" s="20" t="n">
-        <v>-3.778177664153858</v>
+        <v>-3.778177664</v>
       </c>
       <c r="I98" s="21" t="n">
-        <v>-9.03662837341248</v>
+        <v>-9.036628372999999</v>
       </c>
       <c r="J98" s="20" t="n">
-        <v>4.45647980103508</v>
+        <v>4.456479801</v>
       </c>
       <c r="K98" s="20" t="n">
         <v>0</v>
@@ -30561,10 +30561,10 @@
         </is>
       </c>
       <c r="I99" s="21" t="n">
-        <v>5.17591616878465</v>
+        <v>5.175916169</v>
       </c>
       <c r="J99" s="20" t="n">
-        <v>0.0237844128450376</v>
+        <v>0.02378441285</v>
       </c>
       <c r="K99" s="20" t="n">
         <v>0</v>
@@ -30615,13 +30615,13 @@
         <v>0.753851</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>-2.363583804109084</v>
+        <v>-2.363583804</v>
       </c>
       <c r="I100" s="21" t="n">
-        <v>-4.76309065760763</v>
+        <v>-4.763090658</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>14.24389325298612</v>
+        <v>14.24389325</v>
       </c>
       <c r="K100" s="20" t="n">
         <v>12</v>
@@ -30672,13 +30672,13 @@
         <v>0.752348</v>
       </c>
       <c r="H101" s="20" t="n">
-        <v>-2.616706336539075</v>
+        <v>-2.616706337</v>
       </c>
       <c r="I101" s="21" t="n">
-        <v>0.49455685896082</v>
+        <v>0.494556859</v>
       </c>
       <c r="J101" s="20" t="n">
-        <v>0.9122368890474492</v>
+        <v>0.912236889</v>
       </c>
       <c r="K101" s="20" t="n">
         <v>0</v>
@@ -30788,13 +30788,13 @@
         <v>0.75092</v>
       </c>
       <c r="H103" s="20" t="n">
-        <v>-2.796545473352259</v>
+        <v>-2.796545473</v>
       </c>
       <c r="I103" s="21" t="n">
-        <v>-4.75278402369355</v>
+        <v>-4.752784024</v>
       </c>
       <c r="J103" s="20" t="n">
-        <v>1.6200457840962</v>
+        <v>1.620045784</v>
       </c>
       <c r="K103" s="20" t="n">
         <v>0</v>
@@ -30845,13 +30845,13 @@
         <v>0.750748</v>
       </c>
       <c r="H104" s="20" t="n">
-        <v>-1.339478544170577</v>
+        <v>-1.339478544</v>
       </c>
       <c r="I104" s="21" t="n">
-        <v>7.35489290634915</v>
+        <v>7.354892906000001</v>
       </c>
       <c r="J104" s="20" t="n">
-        <v>0.4105341946133486</v>
+        <v>0.4105341946</v>
       </c>
       <c r="K104" s="20" t="n">
         <v>12</v>
@@ -30898,13 +30898,13 @@
         <v>0.74883</v>
       </c>
       <c r="H105" s="20" t="n">
-        <v>-2.708645959798128</v>
+        <v>-2.70864596</v>
       </c>
       <c r="I105" s="21" t="n">
-        <v>-3.54098043014919</v>
+        <v>-3.54098043</v>
       </c>
       <c r="J105" s="20" t="n">
-        <v>1.322310405643739</v>
+        <v>1.322310406</v>
       </c>
       <c r="K105" s="20" t="n">
         <v>3</v>
@@ -30951,13 +30951,13 @@
         <v>0.748765</v>
       </c>
       <c r="H106" s="20" t="n">
-        <v>-1.638126240595175</v>
+        <v>-1.638126241</v>
       </c>
       <c r="I106" s="21" t="n">
-        <v>3.27357543596376</v>
+        <v>3.273575436</v>
       </c>
       <c r="J106" s="20" t="n">
-        <v>0.5562387941671723</v>
+        <v>0.5562387942</v>
       </c>
       <c r="K106" s="20" t="n">
         <v>6</v>
@@ -31008,10 +31008,10 @@
         <v>0.748662</v>
       </c>
       <c r="H107" s="20" t="n">
-        <v>-0.0668305867350536</v>
+        <v>-0.06683058674</v>
       </c>
       <c r="I107" s="21" t="n">
-        <v>11.17123461009596</v>
+        <v>11.17123461</v>
       </c>
       <c r="J107" s="23" t="inlineStr">
         <is>
@@ -31067,13 +31067,13 @@
         <v>0.747634</v>
       </c>
       <c r="H108" s="20" t="n">
-        <v>-2.322235203020948</v>
+        <v>-2.322235203</v>
       </c>
       <c r="I108" s="21" t="n">
-        <v>1.99565339212309</v>
+        <v>1.995653392</v>
       </c>
       <c r="J108" s="20" t="n">
-        <v>-0.2033725422110334</v>
+        <v>-0.2033725422</v>
       </c>
       <c r="K108" s="20" t="n">
         <v>6</v>
@@ -31124,13 +31124,13 @@
         <v>0.747345</v>
       </c>
       <c r="H109" s="20" t="n">
-        <v>-2.753941730642699</v>
+        <v>-2.753941731</v>
       </c>
       <c r="I109" s="21" t="n">
-        <v>-6.33859932646841</v>
+        <v>-6.338599326</v>
       </c>
       <c r="J109" s="20" t="n">
-        <v>4.202568657707337</v>
+        <v>4.202568658</v>
       </c>
       <c r="K109" s="20" t="n">
         <v>6</v>
@@ -31240,13 +31240,13 @@
         <v>0.745383</v>
       </c>
       <c r="H111" s="20" t="n">
-        <v>-1.361408793136724</v>
+        <v>-1.361408793</v>
       </c>
       <c r="I111" s="21" t="n">
-        <v>-1.35313052896115</v>
+        <v>-1.353130529</v>
       </c>
       <c r="J111" s="20" t="n">
-        <v>1.140984547017535</v>
+        <v>1.140984547</v>
       </c>
       <c r="K111" s="20" t="n">
         <v>18</v>
@@ -31297,13 +31297,13 @@
         <v>0.744889</v>
       </c>
       <c r="H112" s="20" t="n">
-        <v>-2.884831439208776</v>
+        <v>-2.884831439</v>
       </c>
       <c r="I112" s="21" t="n">
-        <v>-5.17280744794984</v>
+        <v>-5.172807447999999</v>
       </c>
       <c r="J112" s="20" t="n">
-        <v>8.131264894337138</v>
+        <v>8.131264893999999</v>
       </c>
       <c r="K112" s="20" t="n">
         <v>0</v>
@@ -31354,13 +31354,13 @@
         <v>0.743634</v>
       </c>
       <c r="H113" s="20" t="n">
-        <v>1.028639109582966</v>
+        <v>1.02863911</v>
       </c>
       <c r="I113" s="21" t="n">
-        <v>-4.19302522558833</v>
+        <v>-4.193025226</v>
       </c>
       <c r="J113" s="20" t="n">
-        <v>1.792814534414137</v>
+        <v>1.792814534</v>
       </c>
       <c r="K113" s="20" t="n">
         <v>18</v>
@@ -31411,13 +31411,13 @@
         <v>0.741555</v>
       </c>
       <c r="H114" s="20" t="n">
-        <v>-1.845102294432208</v>
+        <v>-1.845102294</v>
       </c>
       <c r="I114" s="21" t="n">
-        <v>-0.73273223245809</v>
+        <v>-0.7327322325</v>
       </c>
       <c r="J114" s="20" t="n">
-        <v>1.081054849125501</v>
+        <v>1.081054849</v>
       </c>
       <c r="K114" s="20" t="n">
         <v>3</v>
@@ -31468,13 +31468,13 @@
         <v>0.741476</v>
       </c>
       <c r="H115" s="20" t="n">
-        <v>-2.75609704498821</v>
+        <v>-2.756097045</v>
       </c>
       <c r="I115" s="21" t="n">
-        <v>-7.11457560143953</v>
+        <v>-7.114575601</v>
       </c>
       <c r="J115" s="20" t="n">
-        <v>4.14336591577073</v>
+        <v>4.143365916</v>
       </c>
       <c r="K115" s="20" t="n">
         <v>6</v>
@@ -31525,10 +31525,10 @@
         <v>0.741168</v>
       </c>
       <c r="H116" s="20" t="n">
-        <v>-2.199751261831435</v>
+        <v>-2.199751262</v>
       </c>
       <c r="I116" s="21" t="n">
-        <v>-9.92529218919478</v>
+        <v>-9.925292189</v>
       </c>
       <c r="J116" s="23" t="inlineStr">
         <is>
@@ -31584,13 +31584,13 @@
         <v>0.7393690000000001</v>
       </c>
       <c r="H117" s="20" t="n">
-        <v>-2.032138385342544</v>
+        <v>-2.032138385</v>
       </c>
       <c r="I117" s="21" t="n">
-        <v>-3.35239639417357</v>
+        <v>-3.352396394</v>
       </c>
       <c r="J117" s="20" t="n">
-        <v>12.81857719788754</v>
+        <v>12.8185772</v>
       </c>
       <c r="K117" s="20" t="n">
         <v>0</v>
@@ -31641,10 +31641,10 @@
         <v>0.736301</v>
       </c>
       <c r="H118" s="20" t="n">
-        <v>-2.286992752983946</v>
+        <v>-2.286992753</v>
       </c>
       <c r="I118" s="21" t="n">
-        <v>-2.34568010224385</v>
+        <v>-2.345680102</v>
       </c>
       <c r="J118" s="23" t="inlineStr">
         <is>
@@ -31696,13 +31696,13 @@
         <v>0.735619</v>
       </c>
       <c r="H119" s="20" t="n">
-        <v>1.694535059940906</v>
+        <v>1.69453506</v>
       </c>
       <c r="I119" s="21" t="n">
-        <v>24.32048734472443</v>
+        <v>24.32048734</v>
       </c>
       <c r="J119" s="20" t="n">
-        <v>-0.6397137300649863</v>
+        <v>-0.6397137301</v>
       </c>
       <c r="K119" s="20" t="n">
         <v>0</v>
@@ -31753,10 +31753,10 @@
         <v>0.735235</v>
       </c>
       <c r="H120" s="20" t="n">
-        <v>-4.422773410382487</v>
+        <v>-4.42277341</v>
       </c>
       <c r="I120" s="21" t="n">
-        <v>-24.15986634967551</v>
+        <v>-24.15986635</v>
       </c>
       <c r="J120" s="23" t="inlineStr">
         <is>
@@ -31812,13 +31812,13 @@
         <v>0.734993</v>
       </c>
       <c r="H121" s="20" t="n">
-        <v>-3.064162762756327</v>
+        <v>-3.064162763</v>
       </c>
       <c r="I121" s="21" t="n">
-        <v>-11.34339404680724</v>
+        <v>-11.34339405</v>
       </c>
       <c r="J121" s="20" t="n">
-        <v>2.205337036043079</v>
+        <v>2.205337036</v>
       </c>
       <c r="K121" s="20" t="n">
         <v>3</v>
@@ -31869,13 +31869,13 @@
         <v>0.73408</v>
       </c>
       <c r="H122" s="20" t="n">
-        <v>-2.281965031590225</v>
+        <v>-2.281965032</v>
       </c>
       <c r="I122" s="21" t="n">
-        <v>6.304991164222259</v>
+        <v>6.304991164</v>
       </c>
       <c r="J122" s="20" t="n">
-        <v>0.0095438550502363</v>
+        <v>0.009543855049999999</v>
       </c>
       <c r="K122" s="20" t="n">
         <v>0</v>
@@ -31922,13 +31922,13 @@
         <v>0.730799</v>
       </c>
       <c r="H123" s="20" t="n">
-        <v>-2.900498482219698</v>
+        <v>-2.900498482</v>
       </c>
       <c r="I123" s="21" t="n">
-        <v>-3.54043826358348</v>
+        <v>-3.540438264</v>
       </c>
       <c r="J123" s="20" t="n">
-        <v>1.661286747999775</v>
+        <v>1.661286748</v>
       </c>
       <c r="K123" s="20" t="n">
         <v>0</v>
@@ -31979,13 +31979,13 @@
         <v>0.7304659999999999</v>
       </c>
       <c r="H124" s="20" t="n">
-        <v>-2.801094360998515</v>
+        <v>-2.801094361</v>
       </c>
       <c r="I124" s="21" t="n">
-        <v>-7.38008315678878</v>
+        <v>-7.380083157000001</v>
       </c>
       <c r="J124" s="20" t="n">
-        <v>2.39479564614982</v>
+        <v>2.394795646</v>
       </c>
       <c r="K124" s="20" t="n">
         <v>6</v>
@@ -32036,13 +32036,13 @@
         <v>0.729731</v>
       </c>
       <c r="H125" s="20" t="n">
-        <v>-2.204114227347174</v>
+        <v>-2.204114227</v>
       </c>
       <c r="I125" s="21" t="n">
-        <v>8.21926779749819</v>
+        <v>8.219267797000001</v>
       </c>
       <c r="J125" s="20" t="n">
-        <v>0.3412073490813648</v>
+        <v>0.3412073491</v>
       </c>
       <c r="K125" s="20" t="n">
         <v>0</v>
@@ -32089,13 +32089,13 @@
         <v>0.729305</v>
       </c>
       <c r="H126" s="20" t="n">
-        <v>-2.424537349281738</v>
+        <v>-2.424537349</v>
       </c>
       <c r="I126" s="21" t="n">
-        <v>2.42107669187426</v>
+        <v>2.421076692</v>
       </c>
       <c r="J126" s="20" t="n">
-        <v>0.6669515128332988</v>
+        <v>0.6669515128</v>
       </c>
       <c r="K126" s="20" t="n">
         <v>3</v>
@@ -32146,13 +32146,13 @@
         <v>0.725758</v>
       </c>
       <c r="H127" s="20" t="n">
-        <v>-2.919527791187344</v>
+        <v>-2.919527791</v>
       </c>
       <c r="I127" s="21" t="n">
-        <v>-2.96488307979659</v>
+        <v>-2.96488308</v>
       </c>
       <c r="J127" s="20" t="n">
-        <v>2.79301935483871</v>
+        <v>2.793019355</v>
       </c>
       <c r="K127" s="20" t="n">
         <v>0</v>
@@ -32208,7 +32208,7 @@
         </is>
       </c>
       <c r="I128" s="21" t="n">
-        <v>-54.28302669242517</v>
+        <v>-54.28302669</v>
       </c>
       <c r="J128" s="23" t="inlineStr">
         <is>
@@ -32264,10 +32264,10 @@
         <v>0.723724</v>
       </c>
       <c r="H129" s="20" t="n">
-        <v>-2.395390459822167</v>
+        <v>-2.39539046</v>
       </c>
       <c r="I129" s="21" t="n">
-        <v>2.75236235323091</v>
+        <v>2.752362353</v>
       </c>
       <c r="J129" s="20" t="n">
         <v>0</v>
@@ -32321,13 +32321,13 @@
         <v>0.723506</v>
       </c>
       <c r="H130" s="20" t="n">
-        <v>-2.304196546146645</v>
+        <v>-2.304196546</v>
       </c>
       <c r="I130" s="21" t="n">
-        <v>-2.1660099096161</v>
+        <v>-2.16600991</v>
       </c>
       <c r="J130" s="20" t="n">
-        <v>1.445669508808037</v>
+        <v>1.445669509</v>
       </c>
       <c r="K130" s="20" t="n">
         <v>6</v>
@@ -32379,10 +32379,10 @@
         </is>
       </c>
       <c r="I131" s="21" t="n">
-        <v>4.42927782038821</v>
+        <v>4.42927782</v>
       </c>
       <c r="J131" s="20" t="n">
-        <v>0.3952343763249385</v>
+        <v>0.3952343763</v>
       </c>
       <c r="K131" s="20" t="n">
         <v>3</v>
@@ -32429,13 +32429,13 @@
         <v>0.722106</v>
       </c>
       <c r="H132" s="20" t="n">
-        <v>-2.276110698446209</v>
+        <v>-2.276110698</v>
       </c>
       <c r="I132" s="21" t="n">
-        <v>-0.01460558103244</v>
+        <v>-0.01460558103</v>
       </c>
       <c r="J132" s="20" t="n">
-        <v>1.003073425207195</v>
+        <v>1.003073425</v>
       </c>
       <c r="K132" s="20" t="n">
         <v>6</v>
@@ -32486,13 +32486,13 @@
         <v>0.721708</v>
       </c>
       <c r="H133" s="20" t="n">
-        <v>-1.850188073053291</v>
+        <v>-1.850188073</v>
       </c>
       <c r="I133" s="21" t="n">
-        <v>-3.41456031481761</v>
+        <v>-3.414560315</v>
       </c>
       <c r="J133" s="20" t="n">
-        <v>1.412305817849528</v>
+        <v>1.412305818</v>
       </c>
       <c r="K133" s="20" t="n">
         <v>0</v>
@@ -32543,13 +32543,13 @@
         <v>0.721018</v>
       </c>
       <c r="H134" s="20" t="n">
-        <v>-2.727747053397462</v>
+        <v>-2.727747053</v>
       </c>
       <c r="I134" s="21" t="n">
-        <v>1.15521495187714</v>
+        <v>1.155214952</v>
       </c>
       <c r="J134" s="20" t="n">
-        <v>0.7789478795202822</v>
+        <v>0.7789478795</v>
       </c>
       <c r="K134" s="20" t="n">
         <v>0</v>
@@ -32610,7 +32610,7 @@
         </is>
       </c>
       <c r="J135" s="20" t="n">
-        <v>1.043428323370081</v>
+        <v>1.043428323</v>
       </c>
       <c r="K135" s="20" t="n">
         <v>21</v>
@@ -32657,13 +32657,13 @@
         <v>0.718767</v>
       </c>
       <c r="H136" s="20" t="n">
-        <v>-2.352436432901861</v>
+        <v>-2.352436433</v>
       </c>
       <c r="I136" s="21" t="n">
-        <v>-3.15088451180752</v>
+        <v>-3.150884512</v>
       </c>
       <c r="J136" s="20" t="n">
-        <v>1.511134318766067</v>
+        <v>1.511134319</v>
       </c>
       <c r="K136" s="20" t="n">
         <v>24</v>
@@ -32714,13 +32714,13 @@
         <v>0.718423</v>
       </c>
       <c r="H137" s="20" t="n">
-        <v>-2.168004665548296</v>
+        <v>-2.168004666</v>
       </c>
       <c r="I137" s="21" t="n">
-        <v>-7.502127257256309</v>
+        <v>-7.502127257000001</v>
       </c>
       <c r="J137" s="20" t="n">
-        <v>2.159805115712546</v>
+        <v>2.159805116</v>
       </c>
       <c r="K137" s="20" t="n">
         <v>60</v>
@@ -32767,13 +32767,13 @@
         <v>0.718145</v>
       </c>
       <c r="H138" s="20" t="n">
-        <v>-2.038730887273122</v>
+        <v>-2.038730887</v>
       </c>
       <c r="I138" s="21" t="n">
-        <v>4.2993815601886</v>
+        <v>4.29938156</v>
       </c>
       <c r="J138" s="20" t="n">
-        <v>0.0831577399486481</v>
+        <v>0.08315773995</v>
       </c>
       <c r="K138" s="20" t="n">
         <v>6</v>
@@ -32824,10 +32824,10 @@
         <v>0.717909</v>
       </c>
       <c r="H139" s="20" t="n">
-        <v>-4.246271986395366</v>
+        <v>-4.246271986</v>
       </c>
       <c r="I139" s="21" t="n">
-        <v>-27.50859387788509</v>
+        <v>-27.50859388</v>
       </c>
       <c r="J139" s="23" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         </is>
       </c>
       <c r="J140" s="20" t="n">
-        <v>-12.26557440746017</v>
+        <v>-12.26557441</v>
       </c>
       <c r="K140" s="20" t="n">
         <v>12</v>
@@ -32940,10 +32940,10 @@
         <v>0.717618</v>
       </c>
       <c r="H141" s="20" t="n">
-        <v>-4.992735774652516</v>
+        <v>-4.992735775</v>
       </c>
       <c r="I141" s="21" t="n">
-        <v>-155.1368744982055</v>
+        <v>-155.1368745</v>
       </c>
       <c r="J141" s="23" t="inlineStr">
         <is>
@@ -32999,13 +32999,13 @@
         <v>0.716321</v>
       </c>
       <c r="H142" s="20" t="n">
-        <v>-2.337441786293357</v>
+        <v>-2.337441786</v>
       </c>
       <c r="I142" s="21" t="n">
-        <v>1.26547539547886</v>
+        <v>1.265475395</v>
       </c>
       <c r="J142" s="20" t="n">
-        <v>0.5105987226951042</v>
+        <v>0.5105987227</v>
       </c>
       <c r="K142" s="20" t="n">
         <v>18</v>
@@ -33052,13 +33052,13 @@
         <v>0.715496</v>
       </c>
       <c r="H143" s="20" t="n">
-        <v>-3.134595413579538</v>
+        <v>-3.134595414</v>
       </c>
       <c r="I143" s="21" t="n">
-        <v>-12.18139114675267</v>
+        <v>-12.18139115</v>
       </c>
       <c r="J143" s="20" t="n">
-        <v>5.093126871428758</v>
+        <v>5.093126871</v>
       </c>
       <c r="K143" s="20" t="n">
         <v>18</v>
@@ -33109,13 +33109,13 @@
         <v>0.715103</v>
       </c>
       <c r="H144" s="20" t="n">
-        <v>-3.515064072784987</v>
+        <v>-3.515064073</v>
       </c>
       <c r="I144" s="21" t="n">
-        <v>-6.495709064964849</v>
+        <v>-6.495709065</v>
       </c>
       <c r="J144" s="20" t="n">
-        <v>1.93689526003278</v>
+        <v>1.93689526</v>
       </c>
       <c r="K144" s="20" t="n">
         <v>66</v>
@@ -33166,13 +33166,13 @@
         <v>0.715094</v>
       </c>
       <c r="H145" s="20" t="n">
-        <v>-2.898157312786473</v>
+        <v>-2.898157313</v>
       </c>
       <c r="I145" s="21" t="n">
-        <v>-3.45534897937682</v>
+        <v>-3.455348979</v>
       </c>
       <c r="J145" s="20" t="n">
-        <v>1.81404317167921</v>
+        <v>1.814043172</v>
       </c>
       <c r="K145" s="20" t="n">
         <v>0</v>
@@ -33223,13 +33223,13 @@
         <v>0.715053</v>
       </c>
       <c r="H146" s="20" t="n">
-        <v>-2.449469351514515</v>
+        <v>-2.449469352</v>
       </c>
       <c r="I146" s="21" t="n">
-        <v>-1.51985954218703</v>
+        <v>-1.519859542</v>
       </c>
       <c r="J146" s="20" t="n">
-        <v>1.373981089012064</v>
+        <v>1.373981089</v>
       </c>
       <c r="K146" s="20" t="n">
         <v>3</v>
@@ -33280,13 +33280,13 @@
         <v>0.714665</v>
       </c>
       <c r="H147" s="20" t="n">
-        <v>-3.037788985531283</v>
+        <v>-3.037788986</v>
       </c>
       <c r="I147" s="21" t="n">
-        <v>-1.7896336303006</v>
+        <v>-1.78963363</v>
       </c>
       <c r="J147" s="20" t="n">
-        <v>1.157266696383256</v>
+        <v>1.157266696</v>
       </c>
       <c r="K147" s="20" t="n">
         <v>0</v>
@@ -33337,13 +33337,13 @@
         <v>0.714454</v>
       </c>
       <c r="H148" s="20" t="n">
-        <v>-2.476733889508112</v>
+        <v>-2.47673389</v>
       </c>
       <c r="I148" s="21" t="n">
-        <v>-1.08521978803856</v>
+        <v>-1.085219788</v>
       </c>
       <c r="J148" s="20" t="n">
-        <v>1.281137247467631</v>
+        <v>1.281137247</v>
       </c>
       <c r="K148" s="20" t="n">
         <v>6</v>
@@ -33394,13 +33394,13 @@
         <v>0.714426</v>
       </c>
       <c r="H149" s="20" t="n">
-        <v>-3.010751462743358</v>
+        <v>-3.010751463</v>
       </c>
       <c r="I149" s="21" t="n">
-        <v>-22.38172362107296</v>
+        <v>-22.38172362</v>
       </c>
       <c r="J149" s="20" t="n">
-        <v>20.94531600179292</v>
+        <v>20.945316</v>
       </c>
       <c r="K149" s="20" t="n">
         <v>0</v>
@@ -33456,7 +33456,7 @@
         </is>
       </c>
       <c r="I150" s="21" t="n">
-        <v>-28.28436018957346</v>
+        <v>-28.28436019</v>
       </c>
       <c r="J150" s="23" t="inlineStr">
         <is>
@@ -33512,13 +33512,13 @@
         <v>0.713615</v>
       </c>
       <c r="H151" s="20" t="n">
-        <v>2.051568474295593</v>
+        <v>2.051568474</v>
       </c>
       <c r="I151" s="21" t="n">
-        <v>50.54055888774288</v>
+        <v>50.54055889</v>
       </c>
       <c r="J151" s="20" t="n">
-        <v>0.0436297788054333</v>
+        <v>0.04362977881</v>
       </c>
       <c r="K151" s="20" t="n">
         <v>12</v>
@@ -33574,7 +33574,7 @@
         </is>
       </c>
       <c r="I152" s="21" t="n">
-        <v>34193.77821792196</v>
+        <v>34193.77822</v>
       </c>
       <c r="J152" s="23" t="inlineStr">
         <is>
@@ -33626,13 +33626,13 @@
         <v>0.711534</v>
       </c>
       <c r="H153" s="20" t="n">
-        <v>-2.481130650319286</v>
+        <v>-2.48113065</v>
       </c>
       <c r="I153" s="21" t="n">
-        <v>7.38739143344037</v>
+        <v>7.387391432999999</v>
       </c>
       <c r="J153" s="20" t="n">
-        <v>-0.5424850221411825</v>
+        <v>-0.5424850221</v>
       </c>
       <c r="K153" s="20" t="n">
         <v>0</v>
@@ -33683,13 +33683,13 @@
         <v>0.71135</v>
       </c>
       <c r="H154" s="20" t="n">
-        <v>-2.762145438384784</v>
+        <v>-2.762145438</v>
       </c>
       <c r="I154" s="21" t="n">
-        <v>-6.33374211467059</v>
+        <v>-6.333742115000001</v>
       </c>
       <c r="J154" s="20" t="n">
-        <v>2.60604045648517</v>
+        <v>2.606040456</v>
       </c>
       <c r="K154" s="20" t="n">
         <v>3</v>
@@ -33740,13 +33740,13 @@
         <v>0.7106749999999999</v>
       </c>
       <c r="H155" s="20" t="n">
-        <v>-2.607659843536496</v>
+        <v>-2.607659844</v>
       </c>
       <c r="I155" s="21" t="n">
-        <v>1.14955798673014</v>
+        <v>1.149557987</v>
       </c>
       <c r="J155" s="20" t="n">
-        <v>0.8172814400097728</v>
+        <v>0.81728144</v>
       </c>
       <c r="K155" s="20" t="n">
         <v>0</v>
@@ -33797,13 +33797,13 @@
         <v>0.710638</v>
       </c>
       <c r="H156" s="20" t="n">
-        <v>-2.59467718278901</v>
+        <v>-2.594677183</v>
       </c>
       <c r="I156" s="21" t="n">
-        <v>-1.19320100559078</v>
+        <v>-1.193201006</v>
       </c>
       <c r="J156" s="20" t="n">
-        <v>1.31207065750736</v>
+        <v>1.312070658</v>
       </c>
       <c r="K156" s="20" t="n">
         <v>6</v>
@@ -33850,13 +33850,13 @@
         <v>0.7093930000000001</v>
       </c>
       <c r="H157" s="20" t="n">
-        <v>-2.475317839456025</v>
+        <v>-2.475317839</v>
       </c>
       <c r="I157" s="21" t="n">
-        <v>-3.1381138401801</v>
+        <v>-3.13811384</v>
       </c>
       <c r="J157" s="20" t="n">
-        <v>1.477733202987252</v>
+        <v>1.477733203</v>
       </c>
       <c r="K157" s="20" t="n">
         <v>6</v>
@@ -33907,13 +33907,13 @@
         <v>0.709257</v>
       </c>
       <c r="H158" s="20" t="n">
-        <v>-2.440122451224093</v>
+        <v>-2.440122451</v>
       </c>
       <c r="I158" s="21" t="n">
-        <v>2.41092211983988</v>
+        <v>2.41092212</v>
       </c>
       <c r="J158" s="20" t="n">
-        <v>0.5744904013961606</v>
+        <v>0.5744904014</v>
       </c>
       <c r="K158" s="20" t="n">
         <v>0</v>
@@ -33964,13 +33964,13 @@
         <v>0.707334</v>
       </c>
       <c r="H159" s="20" t="n">
-        <v>-1.499702766437339</v>
+        <v>-1.499702766</v>
       </c>
       <c r="I159" s="21" t="n">
-        <v>1.26402285775429</v>
+        <v>1.264022858</v>
       </c>
       <c r="J159" s="20" t="n">
-        <v>0.7867210693175557</v>
+        <v>0.7867210693</v>
       </c>
       <c r="K159" s="20" t="n">
         <v>27</v>
@@ -34021,13 +34021,13 @@
         <v>0.706626</v>
       </c>
       <c r="H160" s="20" t="n">
-        <v>-1.540768888442478</v>
+        <v>-1.540768888</v>
       </c>
       <c r="I160" s="21" t="n">
-        <v>-1.1591758386249</v>
+        <v>-1.159175839</v>
       </c>
       <c r="J160" s="20" t="n">
-        <v>1.083004995532207</v>
+        <v>1.083004996</v>
       </c>
       <c r="K160" s="20" t="n">
         <v>12</v>
@@ -34078,13 +34078,13 @@
         <v>0.704163</v>
       </c>
       <c r="H161" s="20" t="n">
-        <v>-2.26247856913789</v>
+        <v>-2.262478569</v>
       </c>
       <c r="I161" s="21" t="n">
-        <v>-1.60769825065383</v>
+        <v>-1.607698251</v>
       </c>
       <c r="J161" s="20" t="n">
-        <v>1.29543139632497</v>
+        <v>1.295431396</v>
       </c>
       <c r="K161" s="20" t="n">
         <v>9</v>
@@ -34131,13 +34131,13 @@
         <v>0.703539</v>
       </c>
       <c r="H162" s="20" t="n">
-        <v>-2.934172642274297</v>
+        <v>-2.934172642</v>
       </c>
       <c r="I162" s="21" t="n">
-        <v>-7.589634252678381</v>
+        <v>-7.589634253</v>
       </c>
       <c r="J162" s="20" t="n">
-        <v>3.419950462543532</v>
+        <v>3.419950463</v>
       </c>
       <c r="K162" s="20" t="n">
         <v>3</v>
@@ -34188,13 +34188,13 @@
         <v>0.703527</v>
       </c>
       <c r="H163" s="20" t="n">
-        <v>-2.328914126446184</v>
+        <v>-2.328914126</v>
       </c>
       <c r="I163" s="21" t="n">
-        <v>-5.00546044684575</v>
+        <v>-5.005460447</v>
       </c>
       <c r="J163" s="20" t="n">
-        <v>2.020181602482205</v>
+        <v>2.020181602</v>
       </c>
       <c r="K163" s="20" t="n">
         <v>6</v>
@@ -34245,13 +34245,13 @@
         <v>0.703422</v>
       </c>
       <c r="H164" s="20" t="n">
-        <v>-2.373703929283848</v>
+        <v>-2.373703929</v>
       </c>
       <c r="I164" s="21" t="n">
-        <v>-2.96908215975479</v>
+        <v>-2.96908216</v>
       </c>
       <c r="J164" s="20" t="n">
-        <v>1.955584132950836</v>
+        <v>1.955584133</v>
       </c>
       <c r="K164" s="20" t="n">
         <v>0</v>
@@ -34302,13 +34302,13 @@
         <v>0.703387</v>
       </c>
       <c r="H165" s="20" t="n">
-        <v>-2.266973042647712</v>
+        <v>-2.266973043</v>
       </c>
       <c r="I165" s="21" t="n">
-        <v>-4.86702191152372</v>
+        <v>-4.867021911999999</v>
       </c>
       <c r="J165" s="20" t="n">
-        <v>2.902734428675186</v>
+        <v>2.902734429</v>
       </c>
       <c r="K165" s="20" t="n">
         <v>18</v>
@@ -34355,13 +34355,13 @@
         <v>0.702404</v>
       </c>
       <c r="H166" s="20" t="n">
-        <v>-2.330154719448644</v>
+        <v>-2.330154719</v>
       </c>
       <c r="I166" s="21" t="n">
-        <v>1.72376230640697</v>
+        <v>1.723762306</v>
       </c>
       <c r="J166" s="20" t="n">
-        <v>0.7172301511307546</v>
+        <v>0.7172301511</v>
       </c>
       <c r="K166" s="20" t="n">
         <v>3</v>
@@ -34412,13 +34412,13 @@
         <v>0.7015400000000001</v>
       </c>
       <c r="H167" s="20" t="n">
-        <v>-2.889004540618008</v>
+        <v>-2.889004541</v>
       </c>
       <c r="I167" s="21" t="n">
-        <v>-8.578604498982639</v>
+        <v>-8.578604499000001</v>
       </c>
       <c r="J167" s="20" t="n">
-        <v>2.074403453129952</v>
+        <v>2.074403453</v>
       </c>
       <c r="K167" s="20" t="n">
         <v>0</v>
@@ -34469,13 +34469,13 @@
         <v>0.7007139999999999</v>
       </c>
       <c r="H168" s="20" t="n">
-        <v>-2.918429066150677</v>
+        <v>-2.918429066</v>
       </c>
       <c r="I168" s="21" t="n">
-        <v>-4.19544179096227</v>
+        <v>-4.195441791</v>
       </c>
       <c r="J168" s="20" t="n">
-        <v>28.67744118824174</v>
+        <v>28.67744119</v>
       </c>
       <c r="K168" s="20" t="n">
         <v>3</v>
@@ -34522,13 +34522,13 @@
         <v>0.700668</v>
       </c>
       <c r="H169" s="20" t="n">
-        <v>-2.868320461072519</v>
+        <v>-2.868320461</v>
       </c>
       <c r="I169" s="21" t="n">
-        <v>-2.65663936463396</v>
+        <v>-2.656639365</v>
       </c>
       <c r="J169" s="20" t="n">
-        <v>1.251214855166556</v>
+        <v>1.251214855</v>
       </c>
       <c r="K169" s="20" t="n">
         <v>0</v>
@@ -34580,10 +34580,10 @@
         </is>
       </c>
       <c r="I170" s="21" t="n">
-        <v>1.39142870364948</v>
+        <v>1.391428704</v>
       </c>
       <c r="J170" s="20" t="n">
-        <v>0.9179250914589204</v>
+        <v>0.9179250915</v>
       </c>
       <c r="K170" s="20" t="n">
         <v>0</v>
@@ -34634,13 +34634,13 @@
         <v>0.700515</v>
       </c>
       <c r="H171" s="20" t="n">
-        <v>-2.586094111319166</v>
+        <v>-2.586094111</v>
       </c>
       <c r="I171" s="21" t="n">
-        <v>-2.56436473691744</v>
+        <v>-2.564364737</v>
       </c>
       <c r="J171" s="20" t="n">
-        <v>1.555112881806109</v>
+        <v>1.555112882</v>
       </c>
       <c r="K171" s="20" t="n">
         <v>15</v>
@@ -34691,13 +34691,13 @@
         <v>0.700408</v>
       </c>
       <c r="H172" s="20" t="n">
-        <v>-2.786757030694751</v>
+        <v>-2.786757031</v>
       </c>
       <c r="I172" s="21" t="n">
-        <v>-1.47520503608841</v>
+        <v>-1.475205036</v>
       </c>
       <c r="J172" s="20" t="n">
-        <v>1.190317224042762</v>
+        <v>1.190317224</v>
       </c>
       <c r="K172" s="20" t="n">
         <v>6</v>
@@ -34748,13 +34748,13 @@
         <v>0.70012</v>
       </c>
       <c r="H173" s="20" t="n">
-        <v>-1.464470760618041</v>
+        <v>-1.464470761</v>
       </c>
       <c r="I173" s="21" t="n">
-        <v>12.03452445809354</v>
+        <v>12.03452446</v>
       </c>
       <c r="J173" s="20" t="n">
-        <v>0.0940624266666666</v>
+        <v>0.09406242667</v>
       </c>
       <c r="K173" s="20" t="n">
         <v>18</v>
@@ -34805,13 +34805,13 @@
         <v>0.6995130000000001</v>
       </c>
       <c r="H174" s="20" t="n">
-        <v>-2.86839800220476</v>
+        <v>-2.868398002</v>
       </c>
       <c r="I174" s="21" t="n">
-        <v>-10.60672500683177</v>
+        <v>-10.60672501</v>
       </c>
       <c r="J174" s="20" t="n">
-        <v>3.161077301566749</v>
+        <v>3.161077302</v>
       </c>
       <c r="K174" s="20" t="n">
         <v>12</v>
@@ -34872,7 +34872,7 @@
         </is>
       </c>
       <c r="J175" s="20" t="n">
-        <v>3.314403059056791</v>
+        <v>3.314403059</v>
       </c>
       <c r="K175" s="20" t="n">
         <v>3</v>
@@ -34919,13 +34919,13 @@
         <v>0.6988839999999999</v>
       </c>
       <c r="H176" s="20" t="n">
-        <v>-2.414337586121075</v>
+        <v>-2.414337586</v>
       </c>
       <c r="I176" s="21" t="n">
-        <v>-6.75755170743403</v>
+        <v>-6.757551706999999</v>
       </c>
       <c r="J176" s="20" t="n">
-        <v>3.069501898101898</v>
+        <v>3.069501898</v>
       </c>
       <c r="K176" s="20" t="n">
         <v>0</v>
@@ -34976,10 +34976,10 @@
         <v>0.6974320000000001</v>
       </c>
       <c r="H177" s="20" t="n">
-        <v>-2.170360782583936</v>
+        <v>-2.170360783</v>
       </c>
       <c r="I177" s="21" t="n">
-        <v>0.63246650440312</v>
+        <v>0.6324665044</v>
       </c>
       <c r="J177" s="20" t="n">
         <v>0</v>
@@ -35034,7 +35034,7 @@
         </is>
       </c>
       <c r="I178" s="21" t="n">
-        <v>-3.73356714073627</v>
+        <v>-3.733567141</v>
       </c>
       <c r="J178" s="23" t="inlineStr">
         <is>
@@ -35090,13 +35090,13 @@
         <v>0.696055</v>
       </c>
       <c r="H179" s="20" t="n">
-        <v>-3.028500737077406</v>
+        <v>-3.028500737</v>
       </c>
       <c r="I179" s="21" t="n">
-        <v>-7.613903427102819</v>
+        <v>-7.613903427</v>
       </c>
       <c r="J179" s="20" t="n">
-        <v>2.36791523676722</v>
+        <v>2.367915237</v>
       </c>
       <c r="K179" s="20" t="n">
         <v>0</v>
@@ -35147,13 +35147,13 @@
         <v>0.695794</v>
       </c>
       <c r="H180" s="20" t="n">
-        <v>-2.420303869251257</v>
+        <v>-2.420303869</v>
       </c>
       <c r="I180" s="21" t="n">
-        <v>-1.58758622358123</v>
+        <v>-1.587586224</v>
       </c>
       <c r="J180" s="20" t="n">
-        <v>1.500381258565438</v>
+        <v>1.500381259</v>
       </c>
       <c r="K180" s="20" t="n">
         <v>6</v>
@@ -35204,13 +35204,13 @@
         <v>0.694509</v>
       </c>
       <c r="H181" s="20" t="n">
-        <v>-3.100296601485007</v>
+        <v>-3.100296601</v>
       </c>
       <c r="I181" s="21" t="n">
-        <v>-8.56387584261844</v>
+        <v>-8.563875843</v>
       </c>
       <c r="J181" s="20" t="n">
-        <v>2.850524467284258</v>
+        <v>2.850524467</v>
       </c>
       <c r="K181" s="20" t="n">
         <v>0</v>
@@ -35261,13 +35261,13 @@
         <v>0.693061</v>
       </c>
       <c r="H182" s="20" t="n">
-        <v>-0.6139524915040987</v>
+        <v>-0.6139524915</v>
       </c>
       <c r="I182" s="21" t="n">
-        <v>-8.79077278483242</v>
+        <v>-8.790772785000001</v>
       </c>
       <c r="J182" s="20" t="n">
-        <v>2.206647325291393</v>
+        <v>2.206647325</v>
       </c>
       <c r="K182" s="20" t="n">
         <v>0</v>
@@ -35318,13 +35318,13 @@
         <v>0.692367</v>
       </c>
       <c r="H183" s="20" t="n">
-        <v>1.590517810234654</v>
+        <v>1.59051781</v>
       </c>
       <c r="I183" s="21" t="n">
-        <v>44.86940510938599</v>
+        <v>44.86940511</v>
       </c>
       <c r="J183" s="20" t="n">
-        <v>0.1686247902211405</v>
+        <v>0.1686247902</v>
       </c>
       <c r="K183" s="20" t="n">
         <v>6</v>
@@ -35375,13 +35375,13 @@
         <v>0.692202</v>
       </c>
       <c r="H184" s="20" t="n">
-        <v>-2.245661954951786</v>
+        <v>-2.245661955</v>
       </c>
       <c r="I184" s="21" t="n">
-        <v>-0.16602276125818</v>
+        <v>-0.1660227613</v>
       </c>
       <c r="J184" s="20" t="n">
-        <v>1.060993643164464</v>
+        <v>1.060993643</v>
       </c>
       <c r="K184" s="20" t="n">
         <v>9</v>
@@ -35432,10 +35432,10 @@
         <v>0.691689</v>
       </c>
       <c r="H185" s="20" t="n">
-        <v>-3.917770771350214</v>
+        <v>-3.917770771</v>
       </c>
       <c r="I185" s="21" t="n">
-        <v>-84.48045777660703</v>
+        <v>-84.48045777999999</v>
       </c>
       <c r="J185" s="23" t="inlineStr">
         <is>
@@ -35491,13 +35491,13 @@
         <v>0.690908</v>
       </c>
       <c r="H186" s="20" t="n">
-        <v>-2.608282572243894</v>
+        <v>-2.608282572</v>
       </c>
       <c r="I186" s="21" t="n">
-        <v>-17.0060236953377</v>
+        <v>-17.0060237</v>
       </c>
       <c r="J186" s="20" t="n">
-        <v>4.43869274971977</v>
+        <v>4.43869275</v>
       </c>
       <c r="K186" s="20" t="n">
         <v>6</v>
@@ -35548,10 +35548,10 @@
         <v>0.690378</v>
       </c>
       <c r="H187" s="20" t="n">
-        <v>-2.182322665290976</v>
+        <v>-2.182322665</v>
       </c>
       <c r="I187" s="21" t="n">
-        <v>-9.53375342065908</v>
+        <v>-9.533753421</v>
       </c>
       <c r="J187" s="23" t="inlineStr">
         <is>
@@ -35607,13 +35607,13 @@
         <v>0.690219</v>
       </c>
       <c r="H188" s="20" t="n">
-        <v>-2.226721664086718</v>
+        <v>-2.226721664</v>
       </c>
       <c r="I188" s="21" t="n">
-        <v>0.60250953512796</v>
+        <v>0.6025095351</v>
       </c>
       <c r="J188" s="20" t="n">
-        <v>0.8053571428571429</v>
+        <v>0.8053571429</v>
       </c>
       <c r="K188" s="20" t="n">
         <v>9</v>
@@ -35674,7 +35674,7 @@
         </is>
       </c>
       <c r="J189" s="20" t="n">
-        <v>1.865384615384616</v>
+        <v>1.865384615</v>
       </c>
       <c r="K189" s="20" t="n">
         <v>3</v>
@@ -35721,13 +35721,13 @@
         <v>0.689122</v>
       </c>
       <c r="H190" s="20" t="n">
-        <v>-2.502187468874872</v>
+        <v>-2.502187469</v>
       </c>
       <c r="I190" s="21" t="n">
-        <v>-2.5076343894912</v>
+        <v>-2.507634389</v>
       </c>
       <c r="J190" s="20" t="n">
-        <v>3.052910052910053</v>
+        <v>3.052910053</v>
       </c>
       <c r="K190" s="20" t="n">
         <v>3</v>
@@ -35788,7 +35788,7 @@
         </is>
       </c>
       <c r="J191" s="20" t="n">
-        <v>0.9487495190457867</v>
+        <v>0.948749519</v>
       </c>
       <c r="K191" s="20" t="n">
         <v>12</v>
@@ -35835,13 +35835,13 @@
         <v>0.687418</v>
       </c>
       <c r="H192" s="20" t="n">
-        <v>-2.73662871028983</v>
+        <v>-2.73662871</v>
       </c>
       <c r="I192" s="21" t="n">
-        <v>-1.48522908304314</v>
+        <v>-1.485229083</v>
       </c>
       <c r="J192" s="20" t="n">
-        <v>1.374232617759218</v>
+        <v>1.374232618</v>
       </c>
       <c r="K192" s="20" t="n">
         <v>0</v>
@@ -35892,13 +35892,13 @@
         <v>0.686801</v>
       </c>
       <c r="H193" s="20" t="n">
-        <v>-3.335029071242707</v>
+        <v>-3.335029071</v>
       </c>
       <c r="I193" s="21" t="n">
-        <v>-8.335675070269829</v>
+        <v>-8.335675069999999</v>
       </c>
       <c r="J193" s="20" t="n">
-        <v>2.137293574645856</v>
+        <v>2.137293575</v>
       </c>
       <c r="K193" s="20" t="n">
         <v>0</v>
@@ -35949,10 +35949,10 @@
         <v>0.686739</v>
       </c>
       <c r="H194" s="20" t="n">
-        <v>-2.51436416148178</v>
+        <v>-2.514364161</v>
       </c>
       <c r="I194" s="21" t="n">
-        <v>-11.86941757627874</v>
+        <v>-11.86941758</v>
       </c>
       <c r="J194" s="23" t="inlineStr">
         <is>
@@ -36008,13 +36008,13 @@
         <v>0.686284</v>
       </c>
       <c r="H195" s="20" t="n">
-        <v>-2.242894843412413</v>
+        <v>-2.242894843</v>
       </c>
       <c r="I195" s="21" t="n">
-        <v>2.120067170445</v>
+        <v>2.12006717</v>
       </c>
       <c r="J195" s="20" t="n">
-        <v>0.479310812644146</v>
+        <v>0.4793108126</v>
       </c>
       <c r="K195" s="20" t="n">
         <v>3</v>
@@ -36070,10 +36070,10 @@
         </is>
       </c>
       <c r="I196" s="21" t="n">
-        <v>-7.3590949836296</v>
+        <v>-7.359094984</v>
       </c>
       <c r="J196" s="20" t="n">
-        <v>1.236438216786408</v>
+        <v>1.236438217</v>
       </c>
       <c r="K196" s="20" t="n">
         <v>0</v>
@@ -36120,13 +36120,13 @@
         <v>0.685311</v>
       </c>
       <c r="H197" s="20" t="n">
-        <v>-2.462648011306148</v>
+        <v>-2.462648011</v>
       </c>
       <c r="I197" s="21" t="n">
-        <v>-0.27682562873534</v>
+        <v>-0.2768256287</v>
       </c>
       <c r="J197" s="20" t="n">
-        <v>1.078696732222529</v>
+        <v>1.078696732</v>
       </c>
       <c r="K197" s="20" t="n">
         <v>3</v>
@@ -36177,13 +36177,13 @@
         <v>0.68475</v>
       </c>
       <c r="H198" s="20" t="n">
-        <v>-2.607860376796028</v>
+        <v>-2.607860377</v>
       </c>
       <c r="I198" s="21" t="n">
-        <v>-7.292554407040091</v>
+        <v>-7.292554407</v>
       </c>
       <c r="J198" s="20" t="n">
-        <v>2.563846618113305</v>
+        <v>2.563846618</v>
       </c>
       <c r="K198" s="20" t="n">
         <v>0</v>
@@ -36244,7 +36244,7 @@
         </is>
       </c>
       <c r="J199" s="20" t="n">
-        <v>0.3529839925264069</v>
+        <v>0.3529839925</v>
       </c>
       <c r="K199" s="20" t="n">
         <v>3</v>
@@ -36296,10 +36296,10 @@
         </is>
       </c>
       <c r="I200" s="21" t="n">
-        <v>-18.60713888160731</v>
+        <v>-18.60713888</v>
       </c>
       <c r="J200" s="20" t="n">
-        <v>4.500447602017132</v>
+        <v>4.500447602</v>
       </c>
       <c r="K200" s="20" t="n">
         <v>18</v>
@@ -36350,13 +36350,13 @@
         <v>0.68294</v>
       </c>
       <c r="H201" s="20" t="n">
-        <v>-2.48435188488805</v>
+        <v>-2.484351885</v>
       </c>
       <c r="I201" s="21" t="n">
-        <v>-2.39060952425661</v>
+        <v>-2.390609524</v>
       </c>
       <c r="J201" s="20" t="n">
-        <v>3.631917208728934</v>
+        <v>3.631917209</v>
       </c>
       <c r="K201" s="20" t="n">
         <v>18</v>
@@ -36407,10 +36407,10 @@
         <v>0.682854</v>
       </c>
       <c r="H202" s="20" t="n">
-        <v>-3.758838281521334</v>
+        <v>-3.758838282</v>
       </c>
       <c r="I202" s="21" t="n">
-        <v>-21.38148625077137</v>
+        <v>-21.38148625</v>
       </c>
       <c r="J202" s="23" t="inlineStr">
         <is>
@@ -36462,13 +36462,13 @@
         <v>0.682455</v>
       </c>
       <c r="H203" s="20" t="n">
-        <v>-2.278674096990552</v>
+        <v>-2.278674097</v>
       </c>
       <c r="I203" s="21" t="n">
-        <v>-1.6105802008343</v>
+        <v>-1.610580201</v>
       </c>
       <c r="J203" s="20" t="n">
-        <v>1.296100375601217</v>
+        <v>1.296100376</v>
       </c>
       <c r="K203" s="20" t="n">
         <v>12</v>
@@ -36519,10 +36519,10 @@
         <v>0.681159</v>
       </c>
       <c r="H204" s="20" t="n">
-        <v>-1.209916533798902</v>
+        <v>-1.209916534</v>
       </c>
       <c r="I204" s="21" t="n">
-        <v>1.7494935546563</v>
+        <v>1.749493555</v>
       </c>
       <c r="J204" s="23" t="inlineStr">
         <is>
@@ -36578,13 +36578,13 @@
         <v>0.680779</v>
       </c>
       <c r="H205" s="20" t="n">
-        <v>-2.506607417859025</v>
+        <v>-2.506607418</v>
       </c>
       <c r="I205" s="21" t="n">
-        <v>-5.069834264799391</v>
+        <v>-5.069834265</v>
       </c>
       <c r="J205" s="20" t="n">
-        <v>2.240894301134632</v>
+        <v>2.240894301</v>
       </c>
       <c r="K205" s="20" t="n">
         <v>6</v>
@@ -36645,7 +36645,7 @@
         </is>
       </c>
       <c r="J206" s="20" t="n">
-        <v>0.7341955624930315</v>
+        <v>0.7341955625</v>
       </c>
       <c r="K206" s="20" t="n">
         <v>3</v>
@@ -36692,13 +36692,13 @@
         <v>0.679862</v>
       </c>
       <c r="H207" s="20" t="n">
-        <v>-2.652352970772494</v>
+        <v>-2.652352971</v>
       </c>
       <c r="I207" s="21" t="n">
-        <v>-6.31082635731508</v>
+        <v>-6.310826357000001</v>
       </c>
       <c r="J207" s="20" t="n">
-        <v>2.9074726309447</v>
+        <v>2.907472631</v>
       </c>
       <c r="K207" s="20" t="n">
         <v>9</v>
@@ -36749,10 +36749,10 @@
         <v>0.679535</v>
       </c>
       <c r="H208" s="20" t="n">
-        <v>-2.411014262619897</v>
+        <v>-2.411014263</v>
       </c>
       <c r="I208" s="21" t="n">
-        <v>-12.34169747502556</v>
+        <v>-12.34169748</v>
       </c>
       <c r="J208" s="23" t="inlineStr">
         <is>
@@ -36808,10 +36808,10 @@
         <v>0.6795</v>
       </c>
       <c r="H209" s="20" t="n">
-        <v>-4.079622050390492</v>
+        <v>-4.07962205</v>
       </c>
       <c r="I209" s="21" t="n">
-        <v>-17.7075915492238</v>
+        <v>-17.70759155</v>
       </c>
       <c r="J209" s="23" t="inlineStr">
         <is>
@@ -36867,13 +36867,13 @@
         <v>0.679055</v>
       </c>
       <c r="H210" s="20" t="n">
-        <v>-3.075779918514349</v>
+        <v>-3.075779919</v>
       </c>
       <c r="I210" s="21" t="n">
-        <v>-7.30697439589784</v>
+        <v>-7.306974396</v>
       </c>
       <c r="J210" s="20" t="n">
-        <v>10.45241854818525</v>
+        <v>10.45241855</v>
       </c>
       <c r="K210" s="20" t="n">
         <v>0</v>
@@ -36924,13 +36924,13 @@
         <v>0.6784210000000001</v>
       </c>
       <c r="H211" s="20" t="n">
-        <v>-3.11842486014186</v>
+        <v>-3.11842486</v>
       </c>
       <c r="I211" s="21" t="n">
-        <v>-15.32360414976475</v>
+        <v>-15.32360415</v>
       </c>
       <c r="J211" s="20" t="n">
-        <v>4.101929390774689</v>
+        <v>4.101929391</v>
       </c>
       <c r="K211" s="20" t="n">
         <v>27</v>
@@ -36981,13 +36981,13 @@
         <v>0.678164</v>
       </c>
       <c r="H212" s="20" t="n">
-        <v>-2.166199288990756</v>
+        <v>-2.166199289</v>
       </c>
       <c r="I212" s="21" t="n">
-        <v>-4.40721689463575</v>
+        <v>-4.407216894999999</v>
       </c>
       <c r="J212" s="20" t="n">
-        <v>1.712581082028398</v>
+        <v>1.712581082</v>
       </c>
       <c r="K212" s="20" t="n">
         <v>24</v>
@@ -37034,10 +37034,10 @@
         <v>0.6781160000000001</v>
       </c>
       <c r="H213" s="20" t="n">
-        <v>-2.760194091238428</v>
+        <v>-2.760194091</v>
       </c>
       <c r="I213" s="21" t="n">
-        <v>-0.51091374316261</v>
+        <v>-0.5109137431999999</v>
       </c>
       <c r="J213" s="23" t="inlineStr">
         <is>
@@ -37093,13 +37093,13 @@
         <v>0.678005</v>
       </c>
       <c r="H214" s="20" t="n">
-        <v>-2.586866194135727</v>
+        <v>-2.586866194</v>
       </c>
       <c r="I214" s="21" t="n">
-        <v>-2.27054862736931</v>
+        <v>-2.270548627</v>
       </c>
       <c r="J214" s="20" t="n">
-        <v>1.554877654870771</v>
+        <v>1.554877655</v>
       </c>
       <c r="K214" s="20" t="n">
         <v>27</v>
@@ -37146,13 +37146,13 @@
         <v>0.6779770000000001</v>
       </c>
       <c r="H215" s="20" t="n">
-        <v>-2.909303088350763</v>
+        <v>-2.909303088</v>
       </c>
       <c r="I215" s="21" t="n">
-        <v>-8.11268325401641</v>
+        <v>-8.112683254</v>
       </c>
       <c r="J215" s="20" t="n">
-        <v>7.225490196078431</v>
+        <v>7.225490196</v>
       </c>
       <c r="K215" s="20" t="n">
         <v>0</v>
@@ -37203,10 +37203,10 @@
         <v>0.677018</v>
       </c>
       <c r="H216" s="20" t="n">
-        <v>-1.055377965664196</v>
+        <v>-1.055377966</v>
       </c>
       <c r="I216" s="21" t="n">
-        <v>-36.88879750835751</v>
+        <v>-36.88879751</v>
       </c>
       <c r="J216" s="23" t="inlineStr">
         <is>
@@ -37262,13 +37262,13 @@
         <v>0.676725</v>
       </c>
       <c r="H217" s="20" t="n">
-        <v>-2.265201878699585</v>
+        <v>-2.265201879</v>
       </c>
       <c r="I217" s="21" t="n">
-        <v>2.11108250686555</v>
+        <v>2.111082507</v>
       </c>
       <c r="J217" s="20" t="n">
-        <v>0.7498977464421289</v>
+        <v>0.7498977464</v>
       </c>
       <c r="K217" s="20" t="n">
         <v>27</v>
@@ -37319,13 +37319,13 @@
         <v>0.676248</v>
       </c>
       <c r="H218" s="20" t="n">
-        <v>-2.46933453499803</v>
+        <v>-2.469334535</v>
       </c>
       <c r="I218" s="21" t="n">
-        <v>-0.8063498201167499</v>
+        <v>-0.8063498201</v>
       </c>
       <c r="J218" s="20" t="n">
-        <v>1.177867115771174</v>
+        <v>1.177867116</v>
       </c>
       <c r="K218" s="20" t="n">
         <v>0</v>
@@ -37376,13 +37376,13 @@
         <v>0.675895</v>
       </c>
       <c r="H219" s="20" t="n">
-        <v>-1.286888337274693</v>
+        <v>-1.286888337</v>
       </c>
       <c r="I219" s="21" t="n">
-        <v>25.50288113024909</v>
+        <v>25.50288113</v>
       </c>
       <c r="J219" s="20" t="n">
-        <v>-3.269057934508816</v>
+        <v>-3.269057935</v>
       </c>
       <c r="K219" s="20" t="n">
         <v>0</v>
@@ -37433,10 +37433,10 @@
         <v>0.674909</v>
       </c>
       <c r="H220" s="20" t="n">
-        <v>-0.3271389781303014</v>
+        <v>-0.3271389781</v>
       </c>
       <c r="I220" s="21" t="n">
-        <v>-4.85259137065122</v>
+        <v>-4.852591371</v>
       </c>
       <c r="J220" s="23" t="inlineStr">
         <is>
@@ -37497,10 +37497,10 @@
         </is>
       </c>
       <c r="I221" s="21" t="n">
-        <v>1.20679907873231</v>
+        <v>1.206799079</v>
       </c>
       <c r="J221" s="20" t="n">
-        <v>0.8717595081698964</v>
+        <v>0.8717595082</v>
       </c>
       <c r="K221" s="20" t="n">
         <v>0</v>
@@ -37551,13 +37551,13 @@
         <v>0.673941</v>
       </c>
       <c r="H222" s="20" t="n">
-        <v>-2.694778095656921</v>
+        <v>-2.694778096</v>
       </c>
       <c r="I222" s="21" t="n">
-        <v>1.198970535987</v>
+        <v>1.198970536</v>
       </c>
       <c r="J222" s="20" t="n">
-        <v>0.829957359823134</v>
+        <v>0.8299573598</v>
       </c>
       <c r="K222" s="20" t="n">
         <v>6</v>
@@ -37608,13 +37608,13 @@
         <v>0.673816</v>
       </c>
       <c r="H223" s="20" t="n">
-        <v>-2.743164469204992</v>
+        <v>-2.743164469</v>
       </c>
       <c r="I223" s="21" t="n">
-        <v>-0.77306849301404</v>
+        <v>-0.7730684929999999</v>
       </c>
       <c r="J223" s="20" t="n">
-        <v>1.198946524255205</v>
+        <v>1.198946524</v>
       </c>
       <c r="K223" s="20" t="n">
         <v>0</v>
@@ -37666,10 +37666,10 @@
         </is>
       </c>
       <c r="I224" s="21" t="n">
-        <v>-1.42065557442036</v>
+        <v>-1.420655574</v>
       </c>
       <c r="J224" s="20" t="n">
-        <v>1.222158399171277</v>
+        <v>1.222158399</v>
       </c>
       <c r="K224" s="20" t="n">
         <v>15</v>
@@ -37716,10 +37716,10 @@
         <v>0.673466</v>
       </c>
       <c r="H225" s="20" t="n">
-        <v>1.223897878017083</v>
+        <v>1.223897878</v>
       </c>
       <c r="I225" s="21" t="n">
-        <v>4.53178440853874</v>
+        <v>4.531784409</v>
       </c>
       <c r="J225" s="23" t="inlineStr">
         <is>
@@ -37771,13 +37771,13 @@
         <v>0.673367</v>
       </c>
       <c r="H226" s="20" t="n">
-        <v>-3.297065822014596</v>
+        <v>-3.297065822</v>
       </c>
       <c r="I226" s="21" t="n">
-        <v>-8.9783398970009</v>
+        <v>-8.978339897</v>
       </c>
       <c r="J226" s="20" t="n">
-        <v>2.1388088376561</v>
+        <v>2.138808838</v>
       </c>
       <c r="K226" s="20" t="n">
         <v>0</v>
@@ -37828,13 +37828,13 @@
         <v>0.672438</v>
       </c>
       <c r="H227" s="20" t="n">
-        <v>-2.148891520709846</v>
+        <v>-2.148891521</v>
       </c>
       <c r="I227" s="21" t="n">
-        <v>9.709109258039319</v>
+        <v>9.709109258</v>
       </c>
       <c r="J227" s="20" t="n">
-        <v>0.3600719373853067</v>
+        <v>0.3600719374</v>
       </c>
       <c r="K227" s="20" t="n">
         <v>0</v>
@@ -37886,7 +37886,7 @@
         </is>
       </c>
       <c r="I228" s="21" t="n">
-        <v>-4.05987318627158</v>
+        <v>-4.059873186</v>
       </c>
       <c r="J228" s="23" t="inlineStr">
         <is>
@@ -37938,13 +37938,13 @@
         <v>0.672242</v>
       </c>
       <c r="H229" s="20" t="n">
-        <v>-2.321933205518042</v>
+        <v>-2.321933206</v>
       </c>
       <c r="I229" s="21" t="n">
-        <v>-0.10131428904853</v>
+        <v>-0.101314289</v>
       </c>
       <c r="J229" s="20" t="n">
-        <v>1.026736911341804</v>
+        <v>1.026736911</v>
       </c>
       <c r="K229" s="20" t="n">
         <v>3</v>
@@ -37995,13 +37995,13 @@
         <v>0.669755</v>
       </c>
       <c r="H230" s="20" t="n">
-        <v>-2.557395858776104</v>
+        <v>-2.557395859</v>
       </c>
       <c r="I230" s="21" t="n">
-        <v>0.68384568094277</v>
+        <v>0.6838456809000001</v>
       </c>
       <c r="J230" s="20" t="n">
-        <v>0.9137179754517412</v>
+        <v>0.9137179755</v>
       </c>
       <c r="K230" s="20" t="n">
         <v>27</v>
@@ -38052,13 +38052,13 @@
         <v>0.669445</v>
       </c>
       <c r="H231" s="20" t="n">
-        <v>-2.399479765020756</v>
+        <v>-2.399479765</v>
       </c>
       <c r="I231" s="21" t="n">
-        <v>-3.10831543418226</v>
+        <v>-3.108315434</v>
       </c>
       <c r="J231" s="20" t="n">
-        <v>2.188967136150235</v>
+        <v>2.188967136</v>
       </c>
       <c r="K231" s="20" t="n">
         <v>27</v>
@@ -38109,13 +38109,13 @@
         <v>0.668872</v>
       </c>
       <c r="H232" s="20" t="n">
-        <v>-2.662995916222718</v>
+        <v>-2.662995916</v>
       </c>
       <c r="I232" s="21" t="n">
-        <v>-6.491735497490881</v>
+        <v>-6.491735497</v>
       </c>
       <c r="J232" s="20" t="n">
-        <v>2.917457620578511</v>
+        <v>2.917457621</v>
       </c>
       <c r="K232" s="20" t="n">
         <v>0</v>
@@ -38162,13 +38162,13 @@
         <v>0.668557</v>
       </c>
       <c r="H233" s="20" t="n">
-        <v>-2.687534878656339</v>
+        <v>-2.687534879</v>
       </c>
       <c r="I233" s="21" t="n">
-        <v>-2.22756096062365</v>
+        <v>-2.227560961</v>
       </c>
       <c r="J233" s="20" t="n">
-        <v>1.62371734305992</v>
+        <v>1.623717343</v>
       </c>
       <c r="K233" s="20" t="n">
         <v>6</v>
@@ -38219,13 +38219,13 @@
         <v>0.668556</v>
       </c>
       <c r="H234" s="20" t="n">
-        <v>-2.065062358316639</v>
+        <v>-2.065062358</v>
       </c>
       <c r="I234" s="21" t="n">
-        <v>3.10334625741499</v>
+        <v>3.103346257</v>
       </c>
       <c r="J234" s="20" t="n">
-        <v>0.6617185860478229</v>
+        <v>0.661718586</v>
       </c>
       <c r="K234" s="20" t="n">
         <v>66</v>
@@ -38272,13 +38272,13 @@
         <v>0.6663249999999999</v>
       </c>
       <c r="H235" s="20" t="n">
-        <v>-2.337222868965199</v>
+        <v>-2.337222869</v>
       </c>
       <c r="I235" s="21" t="n">
-        <v>1.06712807156276</v>
+        <v>1.067128072</v>
       </c>
       <c r="J235" s="20" t="n">
-        <v>0.8409450960394357</v>
+        <v>0.840945096</v>
       </c>
       <c r="K235" s="20" t="n">
         <v>6</v>
@@ -38329,13 +38329,13 @@
         <v>0.665142</v>
       </c>
       <c r="H236" s="20" t="n">
-        <v>-2.910969912602727</v>
+        <v>-2.910969913</v>
       </c>
       <c r="I236" s="21" t="n">
-        <v>-5.76453106387159</v>
+        <v>-5.764531064</v>
       </c>
       <c r="J236" s="20" t="n">
-        <v>5.165039929015085</v>
+        <v>5.165039929</v>
       </c>
       <c r="K236" s="20" t="n">
         <v>6</v>
@@ -38510,7 +38510,7 @@
         </is>
       </c>
       <c r="J239" s="20" t="n">
-        <v>4.564888795193423</v>
+        <v>4.564888795</v>
       </c>
       <c r="K239" s="20" t="n">
         <v>0</v>
@@ -38557,13 +38557,13 @@
         <v>0.66351</v>
       </c>
       <c r="H240" s="20" t="n">
-        <v>-2.587978279416219</v>
+        <v>-2.587978279</v>
       </c>
       <c r="I240" s="21" t="n">
-        <v>-4.66689599816534</v>
+        <v>-4.666895998</v>
       </c>
       <c r="J240" s="20" t="n">
-        <v>1.490125240847784</v>
+        <v>1.490125241</v>
       </c>
       <c r="K240" s="20" t="n">
         <v>0</v>
@@ -38614,13 +38614,13 @@
         <v>0.663241</v>
       </c>
       <c r="H241" s="20" t="n">
-        <v>-0.4719903279113389</v>
+        <v>-0.4719903279</v>
       </c>
       <c r="I241" s="21" t="n">
-        <v>82.91619881312138</v>
+        <v>82.91619881</v>
       </c>
       <c r="J241" s="20" t="n">
-        <v>0.0309018504244772</v>
+        <v>0.03090185042</v>
       </c>
       <c r="K241" s="20" t="n">
         <v>0</v>
@@ -38671,13 +38671,13 @@
         <v>0.6630509999999999</v>
       </c>
       <c r="H242" s="20" t="n">
-        <v>-2.857864463296485</v>
+        <v>-2.857864463</v>
       </c>
       <c r="I242" s="21" t="n">
-        <v>-8.772262262775509</v>
+        <v>-8.772262263</v>
       </c>
       <c r="J242" s="20" t="n">
-        <v>4.085403337096976</v>
+        <v>4.085403337</v>
       </c>
       <c r="K242" s="20" t="n">
         <v>0</v>
@@ -38728,13 +38728,13 @@
         <v>0.662305</v>
       </c>
       <c r="H243" s="20" t="n">
-        <v>-2.402941226751197</v>
+        <v>-2.402941227</v>
       </c>
       <c r="I243" s="21" t="n">
-        <v>-0.64928691626946</v>
+        <v>-0.6492869163</v>
       </c>
       <c r="J243" s="20" t="n">
-        <v>6.547537681077849</v>
+        <v>6.547537681</v>
       </c>
       <c r="K243" s="20" t="n">
         <v>3</v>
@@ -38785,13 +38785,13 @@
         <v>0.662238</v>
       </c>
       <c r="H244" s="20" t="n">
-        <v>-2.556923961481192</v>
+        <v>-2.556923961</v>
       </c>
       <c r="I244" s="21" t="n">
-        <v>-3.80412931781099</v>
+        <v>-3.804129318</v>
       </c>
       <c r="J244" s="20" t="n">
-        <v>2.692156585590385</v>
+        <v>2.692156586</v>
       </c>
       <c r="K244" s="20" t="n">
         <v>6</v>
@@ -38847,10 +38847,10 @@
         </is>
       </c>
       <c r="I245" s="21" t="n">
-        <v>10.81418865639709</v>
+        <v>10.81418866</v>
       </c>
       <c r="J245" s="20" t="n">
-        <v>0.3905828882124327</v>
+        <v>0.3905828882</v>
       </c>
       <c r="K245" s="20" t="n">
         <v>0</v>
@@ -38901,13 +38901,13 @@
         <v>0.66186</v>
       </c>
       <c r="H246" s="20" t="n">
-        <v>-2.136213156863037</v>
+        <v>-2.136213157</v>
       </c>
       <c r="I246" s="21" t="n">
-        <v>-0.0604047115675</v>
+        <v>-0.06040471157</v>
       </c>
       <c r="J246" s="20" t="n">
-        <v>1.024778761061947</v>
+        <v>1.024778761</v>
       </c>
       <c r="K246" s="20" t="n">
         <v>3</v>
@@ -38954,13 +38954,13 @@
         <v>0.661286</v>
       </c>
       <c r="H247" s="20" t="n">
-        <v>-2.578862897881975</v>
+        <v>-2.578862898</v>
       </c>
       <c r="I247" s="21" t="n">
-        <v>-7.76986560465774</v>
+        <v>-7.769865605</v>
       </c>
       <c r="J247" s="20" t="n">
-        <v>1.572098416711847</v>
+        <v>1.572098417</v>
       </c>
       <c r="K247" s="20" t="n">
         <v>3</v>
@@ -39011,13 +39011,13 @@
         <v>0.6600240000000001</v>
       </c>
       <c r="H248" s="20" t="n">
-        <v>-3.047583736013</v>
+        <v>-3.047583736</v>
       </c>
       <c r="I248" s="21" t="n">
-        <v>-4.91299797173185</v>
+        <v>-4.912997972</v>
       </c>
       <c r="J248" s="20" t="n">
-        <v>4.044172432144758</v>
+        <v>4.044172432</v>
       </c>
       <c r="K248" s="20" t="n">
         <v>0</v>
@@ -39069,7 +39069,7 @@
         </is>
       </c>
       <c r="I249" s="21" t="n">
-        <v>-18.01713586291309</v>
+        <v>-18.01713586</v>
       </c>
       <c r="J249" s="23" t="inlineStr">
         <is>
@@ -39121,10 +39121,10 @@
         <v>0.659816</v>
       </c>
       <c r="H250" s="20" t="n">
-        <v>-3.404510926198683</v>
+        <v>-3.404510926</v>
       </c>
       <c r="I250" s="21" t="n">
-        <v>-7.903992331363479</v>
+        <v>-7.903992331</v>
       </c>
       <c r="J250" s="23" t="inlineStr">
         <is>
@@ -39176,13 +39176,13 @@
         <v>0.659786</v>
       </c>
       <c r="H251" s="20" t="n">
-        <v>-2.209557333525585</v>
+        <v>-2.209557334</v>
       </c>
       <c r="I251" s="21" t="n">
-        <v>0.74813627491824</v>
+        <v>0.7481362749</v>
       </c>
       <c r="J251" s="20" t="n">
-        <v>0.8362881319128553</v>
+        <v>0.8362881319</v>
       </c>
       <c r="K251" s="20" t="n">
         <v>27</v>
@@ -39229,13 +39229,13 @@
         <v>0.659537</v>
       </c>
       <c r="H252" s="20" t="n">
-        <v>-1.01198323332253</v>
+        <v>-1.011983233</v>
       </c>
       <c r="I252" s="21" t="n">
-        <v>-42.27439176427834</v>
+        <v>-42.27439176</v>
       </c>
       <c r="J252" s="20" t="n">
-        <v>2.814394782306127</v>
+        <v>2.814394782</v>
       </c>
       <c r="K252" s="20" t="n">
         <v>0</v>
@@ -39296,7 +39296,7 @@
         </is>
       </c>
       <c r="J253" s="20" t="n">
-        <v>0.1066674245521219</v>
+        <v>0.1066674246</v>
       </c>
       <c r="K253" s="20" t="n">
         <v>21</v>
@@ -39343,13 +39343,13 @@
         <v>0.659157</v>
       </c>
       <c r="H254" s="20" t="n">
-        <v>-2.26293606280508</v>
+        <v>-2.262936063</v>
       </c>
       <c r="I254" s="21" t="n">
-        <v>-0.77385238863351</v>
+        <v>-0.7738523885999999</v>
       </c>
       <c r="J254" s="20" t="n">
-        <v>1.212661613909942</v>
+        <v>1.212661614</v>
       </c>
       <c r="K254" s="20" t="n">
         <v>0</v>
@@ -39400,13 +39400,13 @@
         <v>0.65894</v>
       </c>
       <c r="H255" s="20" t="n">
-        <v>-2.305023553806205</v>
+        <v>-2.305023554</v>
       </c>
       <c r="I255" s="21" t="n">
-        <v>3.16279715064975</v>
+        <v>3.162797151</v>
       </c>
       <c r="J255" s="20" t="n">
-        <v>0.5138206426258106</v>
+        <v>0.5138206426</v>
       </c>
       <c r="K255" s="20" t="n">
         <v>12</v>

--- a/forensic_xr_book.xlsx
+++ b/forensic_xr_book.xlsx
@@ -117,7 +117,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -129,7 +129,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -721,12 +721,12 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>0256.HK</t>
+          <t>0538.HK</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Citychamp Watch &amp; Jewellery Gr</t>
+          <t>Ajisen (China) Holdings Limite</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -741,15 +741,15 @@
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>Textiles, Apparel &amp; Lu</t>
+          <t xml:space="preserve">Hotels, Restaurants &amp; </t>
         </is>
       </c>
       <c r="G8" s="11" t="n">
-        <v>72222697.29843518</v>
+        <v>110731994.1818532</v>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>UNRESEARCHED</t>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="I8" s="13" t="n">
@@ -784,34 +784,32 @@
         </is>
       </c>
       <c r="P8" s="13" t="n">
-        <v>-7.946</v>
+        <v>-4.256074644466831</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>0.12084257</v>
+        <v>0.27059576</v>
       </c>
       <c r="R8" s="14" t="n">
-        <v>8.86438309679353</v>
+        <v>66.45259291149884</v>
       </c>
       <c r="S8" s="13" t="n">
-        <v>-4.39412577</v>
+        <v>-3.799335677</v>
       </c>
       <c r="T8" s="14" t="n">
-        <v>-9.203039907000001</v>
-      </c>
-      <c r="U8" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-10.85595731</v>
+      </c>
+      <c r="U8" s="13" t="n">
+        <v>16.37526828</v>
       </c>
       <c r="V8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="W8" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" s="8" t="inlineStr">
         <is>
-          <t>+ WC release</t>
+          <t>clean</t>
         </is>
       </c>
     </row>
@@ -821,33 +819,33 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>214180.KQ</t>
+          <t>2355.HK</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Minwise Co., Ltd</t>
+          <t>Baoye Group Company Limited</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Construction &amp; Enginee</t>
         </is>
       </c>
       <c r="G9" s="11" t="n">
-        <v>118767246.4195844</v>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
+        <v>195982093.9629554</v>
+      </c>
+      <c r="H9" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -884,32 +882,32 @@
         </is>
       </c>
       <c r="P9" s="13" t="n">
-        <v>-0.323</v>
+        <v>-4.899369514150129</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>0.9486322725013556</v>
+        <v>0.101864375</v>
       </c>
       <c r="R9" s="14" t="n">
-        <v>37.04623266917117</v>
+        <v>39.63325301600989</v>
       </c>
       <c r="S9" s="13" t="n">
-        <v>-2.487497908</v>
+        <v>-2.593774308</v>
       </c>
       <c r="T9" s="14" t="n">
-        <v>-5.353652031</v>
+        <v>-1.630552784</v>
       </c>
       <c r="U9" s="13" t="n">
-        <v>2.592561619</v>
+        <v>10.0619172</v>
       </c>
       <c r="V9" s="13" t="n">
         <v>0</v>
       </c>
       <c r="W9" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X9" s="8" t="inlineStr">
         <is>
-          <t>+ WC release</t>
+          <t>+ FCF leads NI, WC release</t>
         </is>
       </c>
     </row>
@@ -919,17 +917,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>XRX</t>
+          <t>214180.KQ</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Xerox Holdings Corporation</t>
+          <t>Minwise Co., Ltd</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -939,13 +937,13 @@
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="G10" s="11" t="n">
-        <v>450408800</v>
-      </c>
-      <c r="H10" s="12" t="inlineStr">
+        <v>118767246.4195844</v>
+      </c>
+      <c r="H10" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -961,39 +959,43 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L10" s="14" t="n">
-        <v>429.1656823756551</v>
+      <c r="L10" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M10" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N10" s="14" t="n">
-        <v>10.2129443296845</v>
-      </c>
-      <c r="O10" s="14" t="n">
-        <v>8.487610367416689</v>
+      <c r="N10" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O10" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="P10" s="13" t="n">
-        <v>8.554</v>
+        <v>-0.323</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>1.3937424</v>
+        <v>0.9486322725013556</v>
       </c>
       <c r="R10" s="14" t="n">
-        <v>37.65473555194727</v>
+        <v>37.04623266917117</v>
       </c>
       <c r="S10" s="13" t="n">
-        <v>-3.193034755</v>
+        <v>-2.487497908</v>
       </c>
       <c r="T10" s="14" t="n">
-        <v>-14.09829014</v>
-      </c>
-      <c r="U10" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-5.353652031</v>
+      </c>
+      <c r="U10" s="13" t="n">
+        <v>2.592561619</v>
       </c>
       <c r="V10" s="13" t="n">
         <v>0</v>
@@ -1013,33 +1015,33 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>2355.HK</t>
+          <t>XRX</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Baoye Group Company Limited</t>
+          <t>Xerox Holdings Corporation</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>Construction &amp; Enginee</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G11" s="11" t="n">
-        <v>195982093.9629554</v>
-      </c>
-      <c r="H11" s="12" t="inlineStr">
+        <v>450408800</v>
+      </c>
+      <c r="H11" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -1055,53 +1057,49 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L11" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L11" s="14" t="n">
+        <v>429.1656823756551</v>
       </c>
       <c r="M11" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N11" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O11" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N11" s="14" t="n">
+        <v>10.2129443296845</v>
+      </c>
+      <c r="O11" s="14" t="n">
+        <v>8.487610367416689</v>
       </c>
       <c r="P11" s="13" t="n">
-        <v>-4.899369514150129</v>
+        <v>8.554</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0.101864375</v>
+        <v>1.3937424</v>
       </c>
       <c r="R11" s="14" t="n">
-        <v>39.63325301600989</v>
+        <v>37.65473555194727</v>
       </c>
       <c r="S11" s="13" t="n">
-        <v>-2.593774308</v>
+        <v>-3.193034755</v>
       </c>
       <c r="T11" s="14" t="n">
-        <v>-1.630552784</v>
-      </c>
-      <c r="U11" s="13" t="n">
-        <v>10.0619172</v>
+        <v>-14.09829014</v>
+      </c>
+      <c r="U11" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="V11" s="13" t="n">
         <v>0</v>
       </c>
       <c r="W11" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X11" s="8" t="inlineStr">
         <is>
-          <t>+ FCF leads NI, WC release</t>
+          <t>+ WC release</t>
         </is>
       </c>
     </row>
@@ -1111,33 +1109,33 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>UIS</t>
+          <t>0256.HK</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Unisys Corporation</t>
+          <t>Citychamp Watch &amp; Jewellery Gr</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Textiles, Apparel &amp; Lu</t>
         </is>
       </c>
       <c r="G12" s="11" t="n">
-        <v>176456608</v>
-      </c>
-      <c r="H12" s="12" t="inlineStr">
+        <v>72222697.29843518</v>
+      </c>
+      <c r="H12" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -1153,8 +1151,10 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L12" s="14" t="n">
-        <v>664.1859510299552</v>
+      <c r="L12" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M12" s="15" t="inlineStr">
         <is>
@@ -1166,25 +1166,25 @@
           <t>–</t>
         </is>
       </c>
-      <c r="O12" s="14" t="n">
-        <v>41.02353725449977</v>
+      <c r="O12" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="P12" s="13" t="n">
-        <v>14.07767730337079</v>
-      </c>
-      <c r="Q12" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-7.946</v>
+      </c>
+      <c r="Q12" s="13" t="n">
+        <v>0.12084257</v>
       </c>
       <c r="R12" s="14" t="n">
-        <v>43.41950981183043</v>
+        <v>8.86438309679353</v>
       </c>
       <c r="S12" s="13" t="n">
-        <v>-4.386268346</v>
+        <v>-4.39412577</v>
       </c>
       <c r="T12" s="14" t="n">
-        <v>-31.03368041</v>
+        <v>-9.203039907000001</v>
       </c>
       <c r="U12" s="15" t="inlineStr">
         <is>
@@ -1195,11 +1195,11 @@
         <v>0</v>
       </c>
       <c r="W12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12" s="8" t="inlineStr">
         <is>
-          <t>clean</t>
+          <t>+ WC release</t>
         </is>
       </c>
     </row>
@@ -1209,35 +1209,35 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>0538.HK</t>
+          <t>UIS</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Ajisen (China) Holdings Limite</t>
+          <t>Unisys Corporation</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hotels, Restaurants &amp; </t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G13" s="11" t="n">
-        <v>110731994.1818532</v>
+        <v>176456608</v>
       </c>
       <c r="H13" s="16" t="inlineStr">
         <is>
-          <t>YELLOW</t>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="I13" s="13" t="n">
@@ -1251,10 +1251,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L13" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L13" s="14" t="n">
+        <v>664.1859510299552</v>
       </c>
       <c r="M13" s="15" t="inlineStr">
         <is>
@@ -1266,28 +1264,30 @@
           <t>–</t>
         </is>
       </c>
-      <c r="O13" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="O13" s="14" t="n">
+        <v>41.02353725449977</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>-4.256074644466831</v>
-      </c>
-      <c r="Q13" s="13" t="n">
-        <v>0.27059576</v>
+        <v>14.07767730337079</v>
+      </c>
+      <c r="Q13" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="R13" s="14" t="n">
-        <v>66.45259291149884</v>
+        <v>43.41950981183043</v>
       </c>
       <c r="S13" s="13" t="n">
-        <v>-3.799335677</v>
+        <v>-4.386268346</v>
       </c>
       <c r="T13" s="14" t="n">
-        <v>-10.85595731</v>
-      </c>
-      <c r="U13" s="13" t="n">
-        <v>16.37526828</v>
+        <v>-31.03368041</v>
+      </c>
+      <c r="U13" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="V13" s="13" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
       <c r="G14" s="11" t="n">
         <v>86771221.75693507</v>
       </c>
-      <c r="H14" s="12" t="inlineStr">
+      <c r="H14" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -1431,7 +1431,7 @@
       <c r="G15" s="11" t="n">
         <v>137700514.4040183</v>
       </c>
-      <c r="H15" s="12" t="inlineStr">
+      <c r="H15" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -1529,7 +1529,7 @@
       <c r="G16" s="11" t="n">
         <v>766321290.3686138</v>
       </c>
-      <c r="H16" s="12" t="inlineStr">
+      <c r="H16" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -1627,7 +1627,7 @@
       <c r="G17" s="11" t="n">
         <v>190876303.7740096</v>
       </c>
-      <c r="H17" s="12" t="inlineStr">
+      <c r="H17" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -1725,7 +1725,7 @@
       <c r="G18" s="11" t="n">
         <v>102389102.5023126</v>
       </c>
-      <c r="H18" s="12" t="inlineStr">
+      <c r="H18" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -1823,7 +1823,7 @@
       <c r="G19" s="11" t="n">
         <v>319008390.1582418</v>
       </c>
-      <c r="H19" s="12" t="inlineStr">
+      <c r="H19" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -1921,7 +1921,7 @@
       <c r="G20" s="11" t="n">
         <v>105611425.0404425</v>
       </c>
-      <c r="H20" s="12" t="inlineStr">
+      <c r="H20" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -2021,7 +2021,7 @@
       <c r="G21" s="11" t="n">
         <v>58760768</v>
       </c>
-      <c r="H21" s="12" t="inlineStr">
+      <c r="H21" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>023590.KS</t>
+          <t>032190.KQ</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Daou Technology Inc.</t>
+          <t>Daou Data Corp.</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
@@ -2115,13 +2115,13 @@
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="G22" s="11" t="n">
-        <v>1148709798.626002</v>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
+        <v>512293310.7061763</v>
+      </c>
+      <c r="H22" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="P22" s="13" t="n">
-        <v>-12.852</v>
+        <v>-11.053</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.4782027784698607</v>
+        <v>0.4656302080321993</v>
       </c>
       <c r="R22" s="15" t="inlineStr">
         <is>
@@ -2169,25 +2169,21 @@
         </is>
       </c>
       <c r="S22" s="13" t="n">
-        <v>-1.009759799</v>
+        <v>-1.506554119</v>
       </c>
       <c r="T22" s="14" t="n">
-        <v>14.17858876</v>
+        <v>-2.48843016</v>
       </c>
       <c r="U22" s="13" t="n">
-        <v>-15.93577567</v>
+        <v>7.680526367</v>
       </c>
       <c r="V22" s="13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W22" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="X22" s="8" t="inlineStr">
-        <is>
-          <t>WARN: Beneish&gt;-1.78, high accruals</t>
-        </is>
-      </c>
+      <c r="X22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -2195,33 +2191,33 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>3700.HK</t>
+          <t>023590.KS</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Inke Limited</t>
+          <t>Daou Technology Inc.</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>Diversified Telecommun</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G23" s="11" t="n">
-        <v>241787776.6746577</v>
-      </c>
-      <c r="H23" s="12" t="inlineStr">
+        <v>1148709798.626002</v>
+      </c>
+      <c r="H23" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -2257,33 +2253,37 @@
           <t>–</t>
         </is>
       </c>
-      <c r="P23" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P23" s="13" t="n">
+        <v>-12.852</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.28567517</v>
-      </c>
-      <c r="R23" s="14" t="n">
-        <v>-32.71958452610624</v>
+        <v>0.4782027784698607</v>
+      </c>
+      <c r="R23" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="S23" s="13" t="n">
-        <v>-2.269762968</v>
+        <v>-1.009759799</v>
       </c>
       <c r="T23" s="14" t="n">
-        <v>8.748191826999999</v>
+        <v>14.17858876</v>
       </c>
       <c r="U23" s="13" t="n">
-        <v>-2.671282805</v>
+        <v>-15.93577567</v>
       </c>
       <c r="V23" s="13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W23" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="X23" s="8" t="inlineStr"/>
+      <c r="X23" s="8" t="inlineStr">
+        <is>
+          <t>WARN: Beneish&gt;-1.78, high accruals</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -2317,7 +2317,7 @@
       <c r="G24" s="11" t="n">
         <v>407085504</v>
       </c>
-      <c r="H24" s="12" t="inlineStr">
+      <c r="H24" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -2415,7 +2415,7 @@
       <c r="G25" s="11" t="n">
         <v>92123282.75923637</v>
       </c>
-      <c r="H25" s="12" t="inlineStr">
+      <c r="H25" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -2483,33 +2483,33 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>032190.KQ</t>
+          <t>IH</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Daou Data Corp.</t>
+          <t>Ihuman Inc.</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Consumer Stapl</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Household Products</t>
         </is>
       </c>
       <c r="G26" s="11" t="n">
-        <v>512293310.7061763</v>
-      </c>
-      <c r="H26" s="12" t="inlineStr">
+        <v>61335440</v>
+      </c>
+      <c r="H26" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -2525,10 +2525,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L26" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L26" s="14" t="n">
+        <v>36.21397352003996</v>
       </c>
       <c r="M26" s="15" t="inlineStr">
         <is>
@@ -2546,24 +2544,22 @@
         </is>
       </c>
       <c r="P26" s="13" t="n">
-        <v>-11.053</v>
+        <v>-16.30325301502349</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0.4656302080321993</v>
-      </c>
-      <c r="R26" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.42920363</v>
+      </c>
+      <c r="R26" s="14" t="n">
+        <v>0.03494303267047</v>
       </c>
       <c r="S26" s="13" t="n">
-        <v>-1.506554119</v>
+        <v>-2.401264355</v>
       </c>
       <c r="T26" s="14" t="n">
-        <v>-2.48843016</v>
+        <v>3.375947508</v>
       </c>
       <c r="U26" s="13" t="n">
-        <v>7.680526367</v>
+        <v>0.5232374373999999</v>
       </c>
       <c r="V26" s="13" t="n">
         <v>0</v>
@@ -2579,33 +2575,33 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>FBIO</t>
+          <t>3700.HK</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Fortress Biotech, Inc.</t>
+          <t>Inke Limited</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Diversified Telecommun</t>
         </is>
       </c>
       <c r="G27" s="11" t="n">
-        <v>85712048</v>
-      </c>
-      <c r="H27" s="12" t="inlineStr">
+        <v>241787776.6746577</v>
+      </c>
+      <c r="H27" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -2621,16 +2617,20 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L27" s="14" t="n">
-        <v>343.1034572875916</v>
+      <c r="L27" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M27" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N27" s="14" t="n">
-        <v>1.220365193000639</v>
+      <c r="N27" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O27" s="15" t="inlineStr">
         <is>
@@ -2643,33 +2643,27 @@
         </is>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0.52161556</v>
-      </c>
-      <c r="R27" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.28567517</v>
+      </c>
+      <c r="R27" s="14" t="n">
+        <v>-32.71958452610624</v>
       </c>
       <c r="S27" s="13" t="n">
-        <v>-1.01828264</v>
+        <v>-2.269762968</v>
       </c>
       <c r="T27" s="14" t="n">
-        <v>-5.917626571</v>
+        <v>8.748191826999999</v>
       </c>
       <c r="U27" s="13" t="n">
-        <v>1.126115652</v>
+        <v>-2.671282805</v>
       </c>
       <c r="V27" s="13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W27" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="X27" s="8" t="inlineStr">
-        <is>
-          <t>WARN: Beneish&gt;-1.78, receivables&gt;sales</t>
-        </is>
-      </c>
+      <c r="X27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -2677,17 +2671,17 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>IH</t>
+          <t>CCL.AX</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Ihuman Inc.</t>
+          <t>Coca-Cola Amatil Limited</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
@@ -2697,13 +2691,13 @@
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>Household Products</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="G28" s="11" t="n">
-        <v>61335440</v>
-      </c>
-      <c r="H28" s="12" t="inlineStr">
+        <v>757397297.131691</v>
+      </c>
+      <c r="H28" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -2719,8 +2713,10 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L28" s="14" t="n">
-        <v>36.21397352003996</v>
+      <c r="L28" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M28" s="15" t="inlineStr">
         <is>
@@ -2738,22 +2734,22 @@
         </is>
       </c>
       <c r="P28" s="13" t="n">
-        <v>-16.30325301502349</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0.42920363</v>
+        <v>2.487333</v>
       </c>
       <c r="R28" s="14" t="n">
-        <v>0.03494303267047</v>
+        <v>41.63159677303595</v>
       </c>
       <c r="S28" s="13" t="n">
-        <v>-2.401264355</v>
+        <v>-1.88882513</v>
       </c>
       <c r="T28" s="14" t="n">
-        <v>3.375947508</v>
+        <v>-17.63406495</v>
       </c>
       <c r="U28" s="13" t="n">
-        <v>0.5232374373999999</v>
+        <v>18.57377049</v>
       </c>
       <c r="V28" s="13" t="n">
         <v>0</v>
@@ -2769,17 +2765,17 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>036030.KQ</t>
+          <t>MOMO</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>KT Hitel Corporation., Limited</t>
+          <t>Hello Group Inc.</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
@@ -2789,13 +2785,13 @@
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Diversified Telecommun</t>
         </is>
       </c>
       <c r="G29" s="11" t="n">
-        <v>150050732.0442173</v>
-      </c>
-      <c r="H29" s="12" t="inlineStr">
+        <v>723205632</v>
+      </c>
+      <c r="H29" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -2832,28 +2828,22 @@
         </is>
       </c>
       <c r="P29" s="13" t="n">
-        <v>-615.858919062507</v>
+        <v>-2.728782876763296</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0.7595988387147542</v>
+        <v>0.46039647</v>
       </c>
       <c r="R29" s="14" t="n">
-        <v>19.5455356272729</v>
-      </c>
-      <c r="S29" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T29" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="U29" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>20.94380126436537</v>
+      </c>
+      <c r="S29" s="13" t="n">
+        <v>-2.564030435</v>
+      </c>
+      <c r="T29" s="14" t="n">
+        <v>-2.525202801</v>
+      </c>
+      <c r="U29" s="13" t="n">
+        <v>1.338137265</v>
       </c>
       <c r="V29" s="13" t="n">
         <v>0</v>
@@ -2869,33 +2859,33 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>SOGP</t>
+          <t>042420.KQ</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Sound Group Inc.</t>
+          <t>Z Holdings Corporation</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>Diversified Telecommun</t>
+          <t>Internet &amp; Direct Mark</t>
         </is>
       </c>
       <c r="G30" s="11" t="n">
-        <v>50852788</v>
-      </c>
-      <c r="H30" s="12" t="inlineStr">
+        <v>96779704.39330758</v>
+      </c>
+      <c r="H30" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -2932,24 +2922,22 @@
         </is>
       </c>
       <c r="P30" s="13" t="n">
-        <v>-1.272959469710062</v>
+        <v>3.135</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>0.85055774</v>
+        <v>0.3895122570757942</v>
       </c>
       <c r="R30" s="14" t="n">
-        <v>0.25686856401089</v>
-      </c>
-      <c r="S30" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>41.66640904663798</v>
+      </c>
+      <c r="S30" s="13" t="n">
+        <v>-2.134336788</v>
       </c>
       <c r="T30" s="14" t="n">
-        <v>-7.359094984</v>
+        <v>-4.608486333999999</v>
       </c>
       <c r="U30" s="13" t="n">
-        <v>1.236438217</v>
+        <v>2.834704504</v>
       </c>
       <c r="V30" s="13" t="n">
         <v>0</v>
@@ -2991,7 +2979,7 @@
       <c r="G31" s="11" t="n">
         <v>138531094.1027808</v>
       </c>
-      <c r="H31" s="12" t="inlineStr">
+      <c r="H31" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -3065,33 +3053,33 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>042420.KQ</t>
+          <t>FBIO</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Z Holdings Corporation</t>
+          <t>Fortress Biotech, Inc.</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>Internet &amp; Direct Mark</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G32" s="11" t="n">
-        <v>96779704.39330758</v>
-      </c>
-      <c r="H32" s="12" t="inlineStr">
+        <v>85712048</v>
+      </c>
+      <c r="H32" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -3107,51 +3095,55 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L32" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L32" s="14" t="n">
+        <v>343.1034572875916</v>
       </c>
       <c r="M32" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N32" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N32" s="14" t="n">
+        <v>1.220365193000639</v>
       </c>
       <c r="O32" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="P32" s="13" t="n">
-        <v>3.135</v>
+      <c r="P32" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>0.3895122570757942</v>
-      </c>
-      <c r="R32" s="14" t="n">
-        <v>41.66640904663798</v>
+        <v>0.52161556</v>
+      </c>
+      <c r="R32" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="S32" s="13" t="n">
-        <v>-2.134336788</v>
+        <v>-1.01828264</v>
       </c>
       <c r="T32" s="14" t="n">
-        <v>-4.608486333999999</v>
+        <v>-5.917626571</v>
       </c>
       <c r="U32" s="13" t="n">
-        <v>2.834704504</v>
+        <v>1.126115652</v>
       </c>
       <c r="V32" s="13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W32" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="X32" s="8" t="inlineStr"/>
+      <c r="X32" s="8" t="inlineStr">
+        <is>
+          <t>WARN: Beneish&gt;-1.78, receivables&gt;sales</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -3185,7 +3177,7 @@
       <c r="G33" s="11" t="n">
         <v>4373527361.245239</v>
       </c>
-      <c r="H33" s="12" t="inlineStr">
+      <c r="H33" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -3259,12 +3251,12 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>MOMO</t>
+          <t>SOGP</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Hello Group Inc.</t>
+          <t>Sound Group Inc.</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
@@ -3283,9 +3275,9 @@
         </is>
       </c>
       <c r="G34" s="11" t="n">
-        <v>723205632</v>
-      </c>
-      <c r="H34" s="12" t="inlineStr">
+        <v>50852788</v>
+      </c>
+      <c r="H34" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -3322,22 +3314,24 @@
         </is>
       </c>
       <c r="P34" s="13" t="n">
-        <v>-2.728782876763296</v>
+        <v>-1.272959469710062</v>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>0.46039647</v>
+        <v>0.85055774</v>
       </c>
       <c r="R34" s="14" t="n">
-        <v>20.94380126436537</v>
-      </c>
-      <c r="S34" s="13" t="n">
-        <v>-2.564030435</v>
+        <v>0.25686856401089</v>
+      </c>
+      <c r="S34" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="T34" s="14" t="n">
-        <v>-2.525202801</v>
+        <v>-7.359094984</v>
       </c>
       <c r="U34" s="13" t="n">
-        <v>1.338137265</v>
+        <v>1.236438217</v>
       </c>
       <c r="V34" s="13" t="n">
         <v>0</v>
@@ -3353,33 +3347,33 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>CCL.AX</t>
+          <t>036030.KQ</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Coca-Cola Amatil Limited</t>
+          <t>KT Hitel Corporation., Limited</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>Consumer Stapl</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="G35" s="11" t="n">
-        <v>757397297.131691</v>
-      </c>
-      <c r="H35" s="12" t="inlineStr">
+        <v>150050732.0442173</v>
+      </c>
+      <c r="H35" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -3416,22 +3410,28 @@
         </is>
       </c>
       <c r="P35" s="13" t="n">
-        <v>-8.710000000000001</v>
+        <v>-615.858919062507</v>
       </c>
       <c r="Q35" s="13" t="n">
-        <v>2.487333</v>
+        <v>0.7595988387147542</v>
       </c>
       <c r="R35" s="14" t="n">
-        <v>41.63159677303595</v>
-      </c>
-      <c r="S35" s="13" t="n">
-        <v>-1.88882513</v>
-      </c>
-      <c r="T35" s="14" t="n">
-        <v>-17.63406495</v>
-      </c>
-      <c r="U35" s="13" t="n">
-        <v>18.57377049</v>
+        <v>19.5455356272729</v>
+      </c>
+      <c r="S35" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T35" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="U35" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="V35" s="13" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
       <c r="G36" s="11" t="n">
         <v>147439191.8869889</v>
       </c>
-      <c r="H36" s="12" t="inlineStr">
+      <c r="H36" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -3571,7 +3571,7 @@
       <c r="G37" s="11" t="n">
         <v>1161809182.068069</v>
       </c>
-      <c r="H37" s="12" t="inlineStr">
+      <c r="H37" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -3665,7 +3665,7 @@
       <c r="G38" s="11" t="n">
         <v>119950341.1843873</v>
       </c>
-      <c r="H38" s="12" t="inlineStr">
+      <c r="H38" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -3763,7 +3763,7 @@
       <c r="G39" s="11" t="n">
         <v>92381342.96730712</v>
       </c>
-      <c r="H39" s="12" t="inlineStr">
+      <c r="H39" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -3861,7 +3861,7 @@
       <c r="G40" s="11" t="n">
         <v>58871488</v>
       </c>
-      <c r="H40" s="12" t="inlineStr">
+      <c r="H40" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -3959,7 +3959,7 @@
       <c r="G41" s="11" t="n">
         <v>270879392</v>
       </c>
-      <c r="H41" s="12" t="inlineStr">
+      <c r="H41" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -4057,7 +4057,7 @@
       <c r="G42" s="11" t="n">
         <v>134208652.6063451</v>
       </c>
-      <c r="H42" s="12" t="inlineStr">
+      <c r="H42" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -4155,7 +4155,7 @@
       <c r="G43" s="11" t="n">
         <v>63422331.40438554</v>
       </c>
-      <c r="H43" s="12" t="inlineStr">
+      <c r="H43" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -4253,7 +4253,7 @@
       <c r="G44" s="11" t="n">
         <v>185502384.3848075</v>
       </c>
-      <c r="H44" s="12" t="inlineStr">
+      <c r="H44" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -4351,7 +4351,7 @@
       <c r="G45" s="11" t="n">
         <v>117147191.336379</v>
       </c>
-      <c r="H45" s="12" t="inlineStr">
+      <c r="H45" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -4449,7 +4449,7 @@
       <c r="G46" s="11" t="n">
         <v>62173400</v>
       </c>
-      <c r="H46" s="12" t="inlineStr">
+      <c r="H46" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -4541,7 +4541,7 @@
       <c r="G47" s="11" t="n">
         <v>75542004.82368466</v>
       </c>
-      <c r="H47" s="12" t="inlineStr">
+      <c r="H47" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -4639,7 +4639,7 @@
       <c r="G48" s="11" t="n">
         <v>955064808.3495485</v>
       </c>
-      <c r="H48" s="12" t="inlineStr">
+      <c r="H48" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -4737,7 +4737,7 @@
       <c r="G49" s="11" t="n">
         <v>499843622.960411</v>
       </c>
-      <c r="H49" s="12" t="inlineStr">
+      <c r="H49" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -4837,7 +4837,7 @@
       <c r="G50" s="11" t="n">
         <v>50782125.30029904</v>
       </c>
-      <c r="H50" s="12" t="inlineStr">
+      <c r="H50" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -4935,7 +4935,7 @@
       <c r="G51" s="11" t="n">
         <v>252340682.5422591</v>
       </c>
-      <c r="H51" s="12" t="inlineStr">
+      <c r="H51" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -5033,7 +5033,7 @@
       <c r="G52" s="11" t="n">
         <v>54121944</v>
       </c>
-      <c r="H52" s="12" t="inlineStr">
+      <c r="H52" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -5131,7 +5131,7 @@
       <c r="G53" s="11" t="n">
         <v>55643912</v>
       </c>
-      <c r="H53" s="12" t="inlineStr">
+      <c r="H53" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -5233,7 +5233,7 @@
       <c r="G54" s="11" t="n">
         <v>63345280</v>
       </c>
-      <c r="H54" s="12" t="inlineStr">
+      <c r="H54" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -5329,7 +5329,7 @@
       <c r="G55" s="11" t="n">
         <v>829219825.0310974</v>
       </c>
-      <c r="H55" s="12" t="inlineStr">
+      <c r="H55" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -5427,7 +5427,7 @@
       <c r="G56" s="11" t="n">
         <v>79265237.49040219</v>
       </c>
-      <c r="H56" s="12" t="inlineStr">
+      <c r="H56" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -5525,7 +5525,7 @@
       <c r="G57" s="11" t="n">
         <v>8487799808</v>
       </c>
-      <c r="H57" s="12" t="inlineStr">
+      <c r="H57" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -5615,7 +5615,7 @@
       <c r="G58" s="11" t="n">
         <v>4136333262.592009</v>
       </c>
-      <c r="H58" s="12" t="inlineStr">
+      <c r="H58" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -5709,7 +5709,7 @@
       <c r="G59" s="11" t="n">
         <v>55513800</v>
       </c>
-      <c r="H59" s="12" t="inlineStr">
+      <c r="H59" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -5805,7 +5805,7 @@
       <c r="G60" s="11" t="n">
         <v>50871515.65890633</v>
       </c>
-      <c r="H60" s="12" t="inlineStr">
+      <c r="H60" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -5905,7 +5905,7 @@
       <c r="G61" s="11" t="n">
         <v>293114804.1021651</v>
       </c>
-      <c r="H61" s="12" t="inlineStr">
+      <c r="H61" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -6003,7 +6003,7 @@
       <c r="G62" s="11" t="n">
         <v>3091587172.546385</v>
       </c>
-      <c r="H62" s="12" t="inlineStr">
+      <c r="H62" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -6101,7 +6101,7 @@
       <c r="G63" s="11" t="n">
         <v>645767395.6312668</v>
       </c>
-      <c r="H63" s="12" t="inlineStr">
+      <c r="H63" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -6197,7 +6197,7 @@
       <c r="G64" s="11" t="n">
         <v>1376357376</v>
       </c>
-      <c r="H64" s="12" t="inlineStr">
+      <c r="H64" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -6291,7 +6291,7 @@
       <c r="G65" s="11" t="n">
         <v>19913480554.4624</v>
       </c>
-      <c r="H65" s="12" t="inlineStr">
+      <c r="H65" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -6389,7 +6389,7 @@
       <c r="G66" s="11" t="n">
         <v>1238640512</v>
       </c>
-      <c r="H66" s="12" t="inlineStr">
+      <c r="H66" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -6477,7 +6477,7 @@
       <c r="G67" s="11" t="n">
         <v>112030195.391613</v>
       </c>
-      <c r="H67" s="12" t="inlineStr">
+      <c r="H67" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -6575,7 +6575,7 @@
       <c r="G68" s="11" t="n">
         <v>6351379456</v>
       </c>
-      <c r="H68" s="12" t="inlineStr">
+      <c r="H68" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -6677,7 +6677,7 @@
       <c r="G69" s="11" t="n">
         <v>179442298.5907096</v>
       </c>
-      <c r="H69" s="12" t="inlineStr">
+      <c r="H69" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -6775,7 +6775,7 @@
       <c r="G70" s="11" t="n">
         <v>185447570.923518</v>
       </c>
-      <c r="H70" s="12" t="inlineStr">
+      <c r="H70" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -6971,7 +6971,7 @@
       <c r="G72" s="11" t="n">
         <v>254981771.7363948</v>
       </c>
-      <c r="H72" s="12" t="inlineStr">
+      <c r="H72" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -7065,7 +7065,7 @@
       <c r="G73" s="11" t="n">
         <v>67165608</v>
       </c>
-      <c r="H73" s="12" t="inlineStr">
+      <c r="H73" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -7165,7 +7165,7 @@
       <c r="G74" s="11" t="n">
         <v>76758088</v>
       </c>
-      <c r="H74" s="12" t="inlineStr">
+      <c r="H74" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -7261,7 +7261,7 @@
       <c r="G75" s="11" t="n">
         <v>202927291.1822295</v>
       </c>
-      <c r="H75" s="12" t="inlineStr">
+      <c r="H75" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -7339,33 +7339,33 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>S19.SI</t>
+          <t>7129.KL</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Singapore Shipping Corporation</t>
+          <t>Asia File Corporation Bhd.</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Stapl</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>Marine</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="G76" s="11" t="n">
-        <v>94740958.96377563</v>
-      </c>
-      <c r="H76" s="12" t="inlineStr">
+        <v>61101137.47886419</v>
+      </c>
+      <c r="H76" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -7402,34 +7402,36 @@
         </is>
       </c>
       <c r="P76" s="13" t="n">
-        <v>-2.075237621765811</v>
+        <v>-12.569</v>
       </c>
       <c r="Q76" s="13" t="n">
-        <v>0.67009014</v>
+        <v>0.3405251</v>
       </c>
       <c r="R76" s="14" t="n">
-        <v>23.55565129475746</v>
-      </c>
-      <c r="S76" s="13" t="n">
-        <v>-1.850188073</v>
-      </c>
-      <c r="T76" s="14" t="n">
-        <v>-3.414560315</v>
-      </c>
-      <c r="U76" s="13" t="n">
-        <v>1.412305818</v>
+        <v>9.18393088079258</v>
+      </c>
+      <c r="S76" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T76" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="U76" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="V76" s="13" t="n">
         <v>0</v>
       </c>
       <c r="W76" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="X76" s="8" t="inlineStr">
-        <is>
-          <t>+ def-rev building</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X76" s="8" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -7437,33 +7439,33 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>7129.KL</t>
+          <t>S19.SI</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>Asia File Corporation Bhd.</t>
+          <t>Singapore Shipping Corporation</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>Consumer Stapl</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Marine</t>
         </is>
       </c>
       <c r="G77" s="11" t="n">
-        <v>61101137.47886419</v>
-      </c>
-      <c r="H77" s="12" t="inlineStr">
+        <v>94740958.96377563</v>
+      </c>
+      <c r="H77" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -7500,36 +7502,34 @@
         </is>
       </c>
       <c r="P77" s="13" t="n">
-        <v>-12.569</v>
+        <v>-2.075237621765811</v>
       </c>
       <c r="Q77" s="13" t="n">
-        <v>0.3405251</v>
+        <v>0.67009014</v>
       </c>
       <c r="R77" s="14" t="n">
-        <v>9.18393088079258</v>
-      </c>
-      <c r="S77" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T77" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="U77" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>23.55565129475746</v>
+      </c>
+      <c r="S77" s="13" t="n">
+        <v>-1.850188073</v>
+      </c>
+      <c r="T77" s="14" t="n">
+        <v>-3.414560315</v>
+      </c>
+      <c r="U77" s="13" t="n">
+        <v>1.412305818</v>
       </c>
       <c r="V77" s="13" t="n">
         <v>0</v>
       </c>
       <c r="W77" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X77" s="8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X77" s="8" t="inlineStr">
+        <is>
+          <t>+ def-rev building</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
@@ -7563,7 +7563,7 @@
       <c r="G78" s="11" t="n">
         <v>83057080</v>
       </c>
-      <c r="H78" s="12" t="inlineStr">
+      <c r="H78" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -7659,7 +7659,7 @@
       <c r="G79" s="11" t="n">
         <v>123410890.7711315</v>
       </c>
-      <c r="H79" s="12" t="inlineStr">
+      <c r="H79" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -7853,7 +7853,7 @@
       <c r="G81" s="11" t="n">
         <v>113745472.5711635</v>
       </c>
-      <c r="H81" s="12" t="inlineStr">
+      <c r="H81" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -7953,7 +7953,7 @@
       <c r="G82" s="11" t="n">
         <v>376670631.4656752</v>
       </c>
-      <c r="H82" s="12" t="inlineStr">
+      <c r="H82" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -8047,7 +8047,7 @@
       <c r="G83" s="11" t="n">
         <v>411747328</v>
       </c>
-      <c r="H83" s="12" t="inlineStr">
+      <c r="H83" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -8145,7 +8145,7 @@
       <c r="G84" s="11" t="n">
         <v>53016211.98899076</v>
       </c>
-      <c r="H84" s="12" t="inlineStr">
+      <c r="H84" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -8243,7 +8243,7 @@
       <c r="G85" s="11" t="n">
         <v>1982680320</v>
       </c>
-      <c r="H85" s="12" t="inlineStr">
+      <c r="H85" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -8337,7 +8337,7 @@
       <c r="G86" s="11" t="n">
         <v>4219712035.829618</v>
       </c>
-      <c r="H86" s="12" t="inlineStr">
+      <c r="H86" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -8435,7 +8435,7 @@
       <c r="G87" s="11" t="n">
         <v>61464157.95320418</v>
       </c>
-      <c r="H87" s="12" t="inlineStr">
+      <c r="H87" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -8535,7 +8535,7 @@
       <c r="G88" s="11" t="n">
         <v>54934173.79138446</v>
       </c>
-      <c r="H88" s="12" t="inlineStr">
+      <c r="H88" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -8633,7 +8633,7 @@
       <c r="G89" s="11" t="n">
         <v>79526718.99423406</v>
       </c>
-      <c r="H89" s="12" t="inlineStr">
+      <c r="H89" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -8727,7 +8727,7 @@
       <c r="G90" s="11" t="n">
         <v>94713120.14146514</v>
       </c>
-      <c r="H90" s="12" t="inlineStr">
+      <c r="H90" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -8821,7 +8821,7 @@
       <c r="G91" s="11" t="n">
         <v>1042020893.846527</v>
       </c>
-      <c r="H91" s="12" t="inlineStr">
+      <c r="H91" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -8915,7 +8915,7 @@
       <c r="G92" s="11" t="n">
         <v>513183119.2182653</v>
       </c>
-      <c r="H92" s="12" t="inlineStr">
+      <c r="H92" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -9013,7 +9013,7 @@
       <c r="G93" s="11" t="n">
         <v>1628809216</v>
       </c>
-      <c r="H93" s="12" t="inlineStr">
+      <c r="H93" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -9109,7 +9109,7 @@
       <c r="G94" s="11" t="n">
         <v>80976308.81652638</v>
       </c>
-      <c r="H94" s="12" t="inlineStr">
+      <c r="H94" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -9211,7 +9211,7 @@
       <c r="G95" s="11" t="n">
         <v>88900659.32992949</v>
       </c>
-      <c r="H95" s="12" t="inlineStr">
+      <c r="H95" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -9311,7 +9311,7 @@
       <c r="G96" s="11" t="n">
         <v>90146910.85052596</v>
       </c>
-      <c r="H96" s="12" t="inlineStr">
+      <c r="H96" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -9385,33 +9385,33 @@
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>0909.HK</t>
+          <t>ZH</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>Ming Yuan Cloud Group Holdings</t>
+          <t>Zhihu Inc.</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E97" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Diversified Telecommun</t>
         </is>
       </c>
       <c r="G97" s="11" t="n">
-        <v>256268599.1634292</v>
-      </c>
-      <c r="H97" s="12" t="inlineStr">
+        <v>241481968</v>
+      </c>
+      <c r="H97" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -9453,31 +9453,29 @@
         </is>
       </c>
       <c r="Q97" s="13" t="n">
-        <v>0.401683</v>
+        <v>0.39252138</v>
       </c>
       <c r="R97" s="14" t="n">
-        <v>5.22212466905032</v>
+        <v>-0.07052584403626</v>
       </c>
       <c r="S97" s="13" t="n">
-        <v>-2.007615302</v>
+        <v>-2.336748851</v>
       </c>
       <c r="T97" s="14" t="n">
-        <v>-0.9468960258</v>
-      </c>
-      <c r="U97" s="13" t="n">
-        <v>2.635251398</v>
+        <v>4.219303195</v>
+      </c>
+      <c r="U97" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="V97" s="13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W97" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="X97" s="8" t="inlineStr">
-        <is>
-          <t>WARN: receivables&gt;sales, SBC&gt;=30% CFO</t>
-        </is>
-      </c>
+      <c r="X97" s="8" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
@@ -9485,33 +9483,33 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>AMJB</t>
+          <t>0909.HK</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Jpmorgan Chase &amp; Co</t>
+          <t>Ming Yuan Cloud Group Holdings</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G98" s="11" t="n">
-        <v>93126748000</v>
-      </c>
-      <c r="H98" s="12" t="inlineStr">
+        <v>256268599.1634292</v>
+      </c>
+      <c r="H98" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -9522,11 +9520,15 @@
       <c r="J98" s="14" t="n">
         <v>200</v>
       </c>
-      <c r="K98" s="14" t="n">
-        <v>9.534317680673226</v>
-      </c>
-      <c r="L98" s="14" t="n">
-        <v>0.511131345421833</v>
+      <c r="K98" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L98" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
@@ -9549,35 +9551,31 @@
         </is>
       </c>
       <c r="Q98" s="13" t="n">
-        <v>0.2486044986892615</v>
-      </c>
-      <c r="R98" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S98" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T98" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="U98" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.401683</v>
+      </c>
+      <c r="R98" s="14" t="n">
+        <v>5.22212466905032</v>
+      </c>
+      <c r="S98" s="13" t="n">
+        <v>-2.007615302</v>
+      </c>
+      <c r="T98" s="14" t="n">
+        <v>-0.9468960258</v>
+      </c>
+      <c r="U98" s="13" t="n">
+        <v>2.635251398</v>
       </c>
       <c r="V98" s="13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W98" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="X98" s="8" t="inlineStr"/>
+      <c r="X98" s="8" t="inlineStr">
+        <is>
+          <t>WARN: receivables&gt;sales, SBC&gt;=30% CFO</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
@@ -9585,12 +9583,12 @@
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>ZH</t>
+          <t>CMCM</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>Zhihu Inc.</t>
+          <t>Cheetah Mobile Inc.</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
@@ -9600,18 +9598,18 @@
       </c>
       <c r="E99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>Diversified Telecommun</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G99" s="11" t="n">
-        <v>241481968</v>
-      </c>
-      <c r="H99" s="12" t="inlineStr">
+        <v>99789184</v>
+      </c>
+      <c r="H99" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -9627,42 +9625,36 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L99" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L99" s="14" t="n">
+        <v>129.4819687071497</v>
       </c>
       <c r="M99" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N99" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N99" s="14" t="n">
+        <v>29.49718478507651</v>
       </c>
       <c r="O99" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="P99" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P99" s="13" t="n">
+        <v>-19.46430541052319</v>
       </c>
       <c r="Q99" s="13" t="n">
-        <v>0.39252138</v>
+        <v>0.4287816</v>
       </c>
       <c r="R99" s="14" t="n">
-        <v>-0.07052584403626</v>
+        <v>-0.08587525535886001</v>
       </c>
       <c r="S99" s="13" t="n">
-        <v>-2.336748851</v>
+        <v>-2.174580805</v>
       </c>
       <c r="T99" s="14" t="n">
-        <v>4.219303195</v>
+        <v>-1.729830503</v>
       </c>
       <c r="U99" s="15" t="inlineStr">
         <is>
@@ -9670,12 +9662,16 @@
         </is>
       </c>
       <c r="V99" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W99" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="X99" s="8" t="inlineStr"/>
+      <c r="X99" s="8" t="inlineStr">
+        <is>
+          <t>WARN: receivables&gt;sales</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
@@ -9683,33 +9679,33 @@
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>2100.HK</t>
+          <t>200521.SZ</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>BAIOO Family Interactive Limit</t>
+          <t>Changhong Meiling Co., Ltd.</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>Interactive Media &amp; Se</t>
+          <t xml:space="preserve">Electronic Equipment, </t>
         </is>
       </c>
       <c r="G100" s="11" t="n">
-        <v>100241186.0540237</v>
-      </c>
-      <c r="H100" s="12" t="inlineStr">
+        <v>385069824.3972433</v>
+      </c>
+      <c r="H100" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -9745,37 +9741,33 @@
           <t>–</t>
         </is>
       </c>
-      <c r="P100" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P100" s="13" t="n">
+        <v>-26.92665798819529</v>
       </c>
       <c r="Q100" s="13" t="n">
-        <v>0.4697409</v>
+        <v>0.42982808</v>
       </c>
       <c r="R100" s="14" t="n">
-        <v>-13.1060853033141</v>
+        <v>-17.48409470338235</v>
       </c>
       <c r="S100" s="13" t="n">
-        <v>-1.500040405</v>
+        <v>-2.109318872</v>
       </c>
       <c r="T100" s="14" t="n">
-        <v>-6.357240714</v>
-      </c>
-      <c r="U100" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-0.06569903343</v>
+      </c>
+      <c r="U100" s="13" t="n">
+        <v>1.348425297</v>
       </c>
       <c r="V100" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W100" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X100" s="8" t="inlineStr">
         <is>
-          <t>WARN: Beneish&gt;-1.78, receivables&gt;sales | + GM inflecting</t>
+          <t>WARN: receivables&gt;sales</t>
         </is>
       </c>
     </row>
@@ -9785,33 +9777,33 @@
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>200521.SZ</t>
+          <t>MCRB</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>Changhong Meiling Co., Ltd.</t>
+          <t>Seres Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electronic Equipment, </t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G101" s="11" t="n">
-        <v>385069824.3972433</v>
-      </c>
-      <c r="H101" s="12" t="inlineStr">
+        <v>50324356</v>
+      </c>
+      <c r="H101" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -9827,10 +9819,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L101" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L101" s="14" t="n">
+        <v>617.913520840684</v>
       </c>
       <c r="M101" s="15" t="inlineStr">
         <is>
@@ -9842,40 +9832,42 @@
           <t>–</t>
         </is>
       </c>
-      <c r="O101" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P101" s="13" t="n">
-        <v>-26.92665798819529</v>
+      <c r="O101" s="14" t="n">
+        <v>1129.056378046957</v>
+      </c>
+      <c r="P101" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q101" s="13" t="n">
-        <v>0.42982808</v>
-      </c>
-      <c r="R101" s="14" t="n">
-        <v>-17.48409470338235</v>
-      </c>
-      <c r="S101" s="13" t="n">
-        <v>-2.109318872</v>
+        <v>1.4257258</v>
+      </c>
+      <c r="R101" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S101" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="T101" s="14" t="n">
-        <v>-0.06569903343</v>
-      </c>
-      <c r="U101" s="13" t="n">
-        <v>1.348425297</v>
+        <v>23.46895529</v>
+      </c>
+      <c r="U101" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="V101" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W101" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="X101" s="8" t="inlineStr">
-        <is>
-          <t>WARN: receivables&gt;sales</t>
-        </is>
-      </c>
+      <c r="X101" s="8" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
@@ -9883,12 +9875,12 @@
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>IMA</t>
+          <t>AMJB</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>ImageneBio Inc. Common Stock</t>
+          <t>Jpmorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
@@ -9898,18 +9890,18 @@
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="G102" s="11" t="n">
-        <v>57780580</v>
-      </c>
-      <c r="H102" s="12" t="inlineStr">
+        <v>93126748000</v>
+      </c>
+      <c r="H102" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -9920,13 +9912,11 @@
       <c r="J102" s="14" t="n">
         <v>200</v>
       </c>
-      <c r="K102" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="K102" s="14" t="n">
+        <v>9.534317680673226</v>
       </c>
       <c r="L102" s="14" t="n">
-        <v>158.4546226431095</v>
+        <v>0.511131345421833</v>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
@@ -9949,18 +9939,22 @@
         </is>
       </c>
       <c r="Q102" s="13" t="n">
-        <v>0.40330264</v>
-      </c>
-      <c r="R102" s="14" t="n">
-        <v>-86.72964626834113</v>
+        <v>0.2486044986892615</v>
+      </c>
+      <c r="R102" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="S102" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="T102" s="14" t="n">
-        <v>3.773395013</v>
+      <c r="T102" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="U102" s="15" t="inlineStr">
         <is>
@@ -9981,33 +9975,33 @@
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>1122.HK</t>
+          <t>VYLD</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>Qingling Motors Co., Ltd. Clas</t>
+          <t>Jpmorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E103" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>Machinery</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="G103" s="11" t="n">
-        <v>152039595.5916309</v>
-      </c>
-      <c r="H103" s="12" t="inlineStr">
+        <v>79118101660</v>
+      </c>
+      <c r="H103" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -10018,15 +10012,11 @@
       <c r="J103" s="14" t="n">
         <v>200</v>
       </c>
-      <c r="K103" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L103" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="K103" s="14" t="n">
+        <v>11.22246339801778</v>
+      </c>
+      <c r="L103" s="14" t="n">
+        <v>0.6016322308206402</v>
       </c>
       <c r="M103" s="15" t="inlineStr">
         <is>
@@ -10049,16 +10039,22 @@
         </is>
       </c>
       <c r="Q103" s="13" t="n">
-        <v>0.14061408</v>
-      </c>
-      <c r="R103" s="14" t="n">
-        <v>-49.45872020700714</v>
-      </c>
-      <c r="S103" s="13" t="n">
-        <v>-2.239091207</v>
-      </c>
-      <c r="T103" s="14" t="n">
-        <v>-3.6558092</v>
+        <v>0.2112080194234886</v>
+      </c>
+      <c r="R103" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S103" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T103" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="U103" s="15" t="inlineStr">
         <is>
@@ -10066,16 +10062,12 @@
         </is>
       </c>
       <c r="V103" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W103" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="X103" s="8" t="inlineStr">
-        <is>
-          <t>WARN: receivables&gt;sales</t>
-        </is>
-      </c>
+      <c r="X103" s="8" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
@@ -10083,33 +10075,33 @@
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>CMCM</t>
+          <t>1122.HK</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Cheetah Mobile Inc.</t>
+          <t>Qingling Motors Co., Ltd. Clas</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Machinery</t>
         </is>
       </c>
       <c r="G104" s="11" t="n">
-        <v>99789184</v>
-      </c>
-      <c r="H104" s="12" t="inlineStr">
+        <v>152039595.5916309</v>
+      </c>
+      <c r="H104" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -10125,36 +10117,42 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L104" s="14" t="n">
-        <v>129.4819687071497</v>
+      <c r="L104" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N104" s="14" t="n">
-        <v>29.49718478507651</v>
+      <c r="N104" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O104" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="P104" s="13" t="n">
-        <v>-19.46430541052319</v>
+      <c r="P104" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q104" s="13" t="n">
-        <v>0.4287816</v>
+        <v>0.14061408</v>
       </c>
       <c r="R104" s="14" t="n">
-        <v>-0.08587525535886001</v>
+        <v>-49.45872020700714</v>
       </c>
       <c r="S104" s="13" t="n">
-        <v>-2.174580805</v>
+        <v>-2.239091207</v>
       </c>
       <c r="T104" s="14" t="n">
-        <v>-1.729830503</v>
+        <v>-3.6558092</v>
       </c>
       <c r="U104" s="15" t="inlineStr">
         <is>
@@ -10179,12 +10177,12 @@
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>MCRB</t>
+          <t>IMA</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>Seres Therapeutics, Inc.</t>
+          <t>ImageneBio Inc. Common Stock</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
@@ -10203,9 +10201,9 @@
         </is>
       </c>
       <c r="G105" s="11" t="n">
-        <v>50324356</v>
-      </c>
-      <c r="H105" s="12" t="inlineStr">
+        <v>57780580</v>
+      </c>
+      <c r="H105" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -10222,7 +10220,7 @@
         </is>
       </c>
       <c r="L105" s="14" t="n">
-        <v>617.913520840684</v>
+        <v>158.4546226431095</v>
       </c>
       <c r="M105" s="15" t="inlineStr">
         <is>
@@ -10234,8 +10232,10 @@
           <t>–</t>
         </is>
       </c>
-      <c r="O105" s="14" t="n">
-        <v>1129.056378046957</v>
+      <c r="O105" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="P105" s="15" t="inlineStr">
         <is>
@@ -10243,12 +10243,10 @@
         </is>
       </c>
       <c r="Q105" s="13" t="n">
-        <v>1.4257258</v>
-      </c>
-      <c r="R105" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.40330264</v>
+      </c>
+      <c r="R105" s="14" t="n">
+        <v>-86.72964626834113</v>
       </c>
       <c r="S105" s="15" t="inlineStr">
         <is>
@@ -10256,7 +10254,7 @@
         </is>
       </c>
       <c r="T105" s="14" t="n">
-        <v>23.46895529</v>
+        <v>3.773395013</v>
       </c>
       <c r="U105" s="15" t="inlineStr">
         <is>
@@ -10277,33 +10275,33 @@
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>2033.HK</t>
+          <t>DQ</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Time Watch Investments Limited</t>
+          <t>Daqo New Energy Corp.</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>Textiles, Apparel &amp; Lu</t>
+          <t>Semiconductors &amp; Semic</t>
         </is>
       </c>
       <c r="G106" s="11" t="n">
-        <v>58301469.56463955</v>
-      </c>
-      <c r="H106" s="12" t="inlineStr">
+        <v>780867200</v>
+      </c>
+      <c r="H106" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -10319,25 +10317,19 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L106" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L106" s="14" t="n">
+        <v>0.645564316185902</v>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N106" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O106" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N106" s="14" t="n">
+        <v>0.08772298285803271</v>
+      </c>
+      <c r="O106" s="14" t="n">
+        <v>9.317493594223155</v>
       </c>
       <c r="P106" s="15" t="inlineStr">
         <is>
@@ -10345,16 +10337,18 @@
         </is>
       </c>
       <c r="Q106" s="13" t="n">
-        <v>0.20479706</v>
+        <v>0.17852724</v>
       </c>
       <c r="R106" s="14" t="n">
-        <v>5.88765515847855</v>
-      </c>
-      <c r="S106" s="13" t="n">
-        <v>-2.179280574</v>
+        <v>-33.48712815700289</v>
+      </c>
+      <c r="S106" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="T106" s="14" t="n">
-        <v>-4.484302712</v>
+        <v>-1.222978045</v>
       </c>
       <c r="U106" s="15" t="inlineStr">
         <is>
@@ -10362,14 +10356,14 @@
         </is>
       </c>
       <c r="V106" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="W106" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="W106" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="X106" s="8" t="inlineStr">
         <is>
-          <t>WARN: receivables&gt;sales</t>
+          <t>WARN: receivables&gt;sales, inventory build | + def-rev building</t>
         </is>
       </c>
     </row>
@@ -10379,17 +10373,17 @@
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>DOYU</t>
+          <t>2100.HK</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>Douyu International Holdings L</t>
+          <t>BAIOO Family Interactive Limit</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E107" s="10" t="inlineStr">
@@ -10399,13 +10393,13 @@
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>Diversified Telecommun</t>
+          <t>Interactive Media &amp; Se</t>
         </is>
       </c>
       <c r="G107" s="11" t="n">
-        <v>137012016</v>
-      </c>
-      <c r="H107" s="12" t="inlineStr">
+        <v>100241186.0540237</v>
+      </c>
+      <c r="H107" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -10441,20 +10435,22 @@
           <t>–</t>
         </is>
       </c>
-      <c r="P107" s="13" t="n">
-        <v>-40.44178343215683</v>
+      <c r="P107" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q107" s="13" t="n">
-        <v>0.48591852</v>
+        <v>0.4697409</v>
       </c>
       <c r="R107" s="14" t="n">
-        <v>-0.01770960934256</v>
+        <v>-13.1060853033141</v>
       </c>
       <c r="S107" s="13" t="n">
-        <v>-2.561637717</v>
+        <v>-1.500040405</v>
       </c>
       <c r="T107" s="14" t="n">
-        <v>0.7325112476</v>
+        <v>-6.357240714</v>
       </c>
       <c r="U107" s="15" t="inlineStr">
         <is>
@@ -10462,12 +10458,16 @@
         </is>
       </c>
       <c r="V107" s="13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W107" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X107" s="8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X107" s="8" t="inlineStr">
+        <is>
+          <t>WARN: Beneish&gt;-1.78, receivables&gt;sales | + GM inflecting</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
@@ -10475,33 +10475,33 @@
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>VYLD</t>
+          <t>ENW.L</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Jpmorgan Chase &amp; Co</t>
+          <t>Enwell Energy plc</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t xml:space="preserve">Oil, Gas &amp; Consumable </t>
         </is>
       </c>
       <c r="G108" s="11" t="n">
-        <v>79118101660</v>
-      </c>
-      <c r="H108" s="12" t="inlineStr">
+        <v>52512980.67904043</v>
+      </c>
+      <c r="H108" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -10512,11 +10512,15 @@
       <c r="J108" s="14" t="n">
         <v>200</v>
       </c>
-      <c r="K108" s="14" t="n">
-        <v>11.22246339801778</v>
-      </c>
-      <c r="L108" s="14" t="n">
-        <v>0.6016322308206402</v>
+      <c r="K108" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L108" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
@@ -10539,22 +10543,18 @@
         </is>
       </c>
       <c r="Q108" s="13" t="n">
-        <v>0.2112080194234886</v>
-      </c>
-      <c r="R108" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.3210329</v>
+      </c>
+      <c r="R108" s="14" t="n">
+        <v>-3.33441365802889</v>
       </c>
       <c r="S108" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="T108" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="T108" s="14" t="n">
+        <v>-2.504135975</v>
       </c>
       <c r="U108" s="15" t="inlineStr">
         <is>
@@ -10562,12 +10562,16 @@
         </is>
       </c>
       <c r="V108" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W108" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="X108" s="8" t="inlineStr"/>
+      <c r="X108" s="8" t="inlineStr">
+        <is>
+          <t>WARN: inventory build</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="n">
@@ -10575,33 +10579,33 @@
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>DQ</t>
+          <t>0JXZ.IL</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>Daqo New Energy Corp.</t>
+          <t>Galapagos NV</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E109" s="10" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Semic</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G109" s="11" t="n">
-        <v>780867200</v>
-      </c>
-      <c r="H109" s="12" t="inlineStr">
+        <v>1785441867.433044</v>
+      </c>
+      <c r="H109" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -10617,19 +10621,25 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L109" s="14" t="n">
-        <v>0.645564316185902</v>
+      <c r="L109" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M109" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N109" s="14" t="n">
-        <v>0.08772298285803271</v>
-      </c>
-      <c r="O109" s="14" t="n">
-        <v>9.317493594223155</v>
+      <c r="N109" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O109" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="P109" s="15" t="inlineStr">
         <is>
@@ -10637,18 +10647,20 @@
         </is>
       </c>
       <c r="Q109" s="13" t="n">
-        <v>0.17852724</v>
+        <v>0.59879625</v>
       </c>
       <c r="R109" s="14" t="n">
-        <v>-33.48712815700289</v>
+        <v>-18.94339056056228</v>
       </c>
       <c r="S109" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="T109" s="14" t="n">
-        <v>-1.222978045</v>
+      <c r="T109" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="U109" s="15" t="inlineStr">
         <is>
@@ -10656,16 +10668,12 @@
         </is>
       </c>
       <c r="V109" s="13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W109" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="X109" s="8" t="inlineStr">
-        <is>
-          <t>WARN: receivables&gt;sales, inventory build | + def-rev building</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X109" s="8" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n">
@@ -10673,12 +10681,12 @@
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>GDHG</t>
+          <t>DOYU</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Golden Heaven Group Holdings L</t>
+          <t>Douyu International Holdings L</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
@@ -10688,18 +10696,18 @@
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hotels, Restaurants &amp; </t>
+          <t>Diversified Telecommun</t>
         </is>
       </c>
       <c r="G110" s="11" t="n">
-        <v>69901808</v>
-      </c>
-      <c r="H110" s="12" t="inlineStr">
+        <v>137012016</v>
+      </c>
+      <c r="H110" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -10715,8 +10723,10 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L110" s="14" t="n">
-        <v>4.844947644272663</v>
+      <c r="L110" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
@@ -10734,19 +10744,19 @@
         </is>
       </c>
       <c r="P110" s="13" t="n">
-        <v>-76.425</v>
+        <v>-40.44178343215683</v>
       </c>
       <c r="Q110" s="13" t="n">
-        <v>0.3869456205617164</v>
+        <v>0.48591852</v>
       </c>
       <c r="R110" s="14" t="n">
-        <v>5.41869452105689</v>
+        <v>-0.01770960934256</v>
       </c>
       <c r="S110" s="13" t="n">
-        <v>0.02645636981</v>
+        <v>-2.561637717</v>
       </c>
       <c r="T110" s="14" t="n">
-        <v>-4.264219669</v>
+        <v>0.7325112476</v>
       </c>
       <c r="U110" s="15" t="inlineStr">
         <is>
@@ -10754,16 +10764,12 @@
         </is>
       </c>
       <c r="V110" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W110" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="X110" s="8" t="inlineStr">
-        <is>
-          <t>WARN: Beneish&gt;-1.78</t>
-        </is>
-      </c>
+      <c r="X110" s="8" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="7" t="n">
@@ -10771,33 +10777,33 @@
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>0JXZ.IL</t>
+          <t>GDHG</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>Galapagos NV</t>
+          <t>Golden Heaven Group Holdings L</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E111" s="10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t xml:space="preserve">Hotels, Restaurants &amp; </t>
         </is>
       </c>
       <c r="G111" s="11" t="n">
-        <v>1785441867.433044</v>
-      </c>
-      <c r="H111" s="12" t="inlineStr">
+        <v>69901808</v>
+      </c>
+      <c r="H111" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -10813,10 +10819,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L111" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L111" s="14" t="n">
+        <v>4.844947644272663</v>
       </c>
       <c r="M111" s="15" t="inlineStr">
         <is>
@@ -10833,26 +10837,20 @@
           <t>–</t>
         </is>
       </c>
-      <c r="P111" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P111" s="13" t="n">
+        <v>-76.425</v>
       </c>
       <c r="Q111" s="13" t="n">
-        <v>0.59879625</v>
+        <v>0.3869456205617164</v>
       </c>
       <c r="R111" s="14" t="n">
-        <v>-18.94339056056228</v>
-      </c>
-      <c r="S111" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T111" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>5.41869452105689</v>
+      </c>
+      <c r="S111" s="13" t="n">
+        <v>0.02645636981</v>
+      </c>
+      <c r="T111" s="14" t="n">
+        <v>-4.264219669</v>
       </c>
       <c r="U111" s="15" t="inlineStr">
         <is>
@@ -10860,12 +10858,16 @@
         </is>
       </c>
       <c r="V111" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W111" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="X111" s="8" t="inlineStr"/>
+      <c r="X111" s="8" t="inlineStr">
+        <is>
+          <t>WARN: Beneish&gt;-1.78</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
@@ -10873,33 +10875,33 @@
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>ENW.L</t>
+          <t>2033.HK</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Enwell Energy plc</t>
+          <t>Time Watch Investments Limited</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oil, Gas &amp; Consumable </t>
+          <t>Textiles, Apparel &amp; Lu</t>
         </is>
       </c>
       <c r="G112" s="11" t="n">
-        <v>52512980.67904043</v>
-      </c>
-      <c r="H112" s="12" t="inlineStr">
+        <v>58301469.56463955</v>
+      </c>
+      <c r="H112" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -10941,18 +10943,16 @@
         </is>
       </c>
       <c r="Q112" s="13" t="n">
-        <v>0.3210329</v>
+        <v>0.20479706</v>
       </c>
       <c r="R112" s="14" t="n">
-        <v>-3.33441365802889</v>
-      </c>
-      <c r="S112" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>5.88765515847855</v>
+      </c>
+      <c r="S112" s="13" t="n">
+        <v>-2.179280574</v>
       </c>
       <c r="T112" s="14" t="n">
-        <v>-2.504135975</v>
+        <v>-4.484302712</v>
       </c>
       <c r="U112" s="15" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
       </c>
       <c r="X112" s="8" t="inlineStr">
         <is>
-          <t>WARN: inventory build</t>
+          <t>WARN: receivables&gt;sales</t>
         </is>
       </c>
     </row>
@@ -11003,7 +11003,7 @@
       <c r="G113" s="11" t="n">
         <v>153131337.1641741</v>
       </c>
-      <c r="H113" s="12" t="inlineStr">
+      <c r="H113" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -11101,7 +11101,7 @@
       <c r="G114" s="11" t="n">
         <v>106691802.0154448</v>
       </c>
-      <c r="H114" s="12" t="inlineStr">
+      <c r="H114" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -11199,7 +11199,7 @@
       <c r="G115" s="11" t="n">
         <v>62819068</v>
       </c>
-      <c r="H115" s="12" t="inlineStr">
+      <c r="H115" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -11299,7 +11299,7 @@
       <c r="G116" s="11" t="n">
         <v>270172480</v>
       </c>
-      <c r="H116" s="12" t="inlineStr">
+      <c r="H116" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -11373,42 +11373,42 @@
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>000700.KS</t>
+          <t>600636.SS</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>Eusu Holdings Co., Ltd.</t>
+          <t xml:space="preserve">China Reform Culture Holdings </t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="E117" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
-          <t>Marine</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="G117" s="11" t="n">
-        <v>111908520.2591061</v>
+        <v>110866736.1118813</v>
       </c>
       <c r="H117" s="16" t="inlineStr">
         <is>
-          <t>YELLOW</t>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="I117" s="13" t="n">
         <v>1.9555</v>
       </c>
       <c r="J117" s="14" t="n">
-        <v>113.36</v>
+        <v>170.04</v>
       </c>
       <c r="K117" s="15" t="inlineStr">
         <is>
@@ -11435,33 +11435,37 @@
           <t>–</t>
         </is>
       </c>
-      <c r="P117" s="13" t="n">
-        <v>1.426</v>
+      <c r="P117" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q117" s="13" t="n">
-        <v>0.4231442442328305</v>
+        <v>0.42846406</v>
       </c>
       <c r="R117" s="14" t="n">
-        <v>18.37489221292608</v>
+        <v>-15.94158732169212</v>
       </c>
       <c r="S117" s="13" t="n">
-        <v>-2.778307688</v>
+        <v>-2.934119241</v>
       </c>
       <c r="T117" s="14" t="n">
-        <v>-6.332213787000001</v>
-      </c>
-      <c r="U117" s="13" t="n">
-        <v>2.996280708</v>
+        <v>-10.66472666</v>
+      </c>
+      <c r="U117" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="V117" s="13" t="n">
         <v>0</v>
       </c>
       <c r="W117" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X117" s="8" t="inlineStr">
         <is>
-          <t>+ FCF leads NI</t>
+          <t>clean</t>
         </is>
       </c>
     </row>
@@ -11471,42 +11475,42 @@
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>600636.SS</t>
+          <t>000700.KS</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">China Reform Culture Holdings </t>
+          <t>Eusu Holdings Co., Ltd.</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Marine</t>
         </is>
       </c>
       <c r="G118" s="11" t="n">
-        <v>110866736.1118813</v>
+        <v>111908520.2591061</v>
       </c>
       <c r="H118" s="12" t="inlineStr">
         <is>
-          <t>UNRESEARCHED</t>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="I118" s="13" t="n">
         <v>1.9555</v>
       </c>
       <c r="J118" s="14" t="n">
-        <v>170.04</v>
+        <v>113.36</v>
       </c>
       <c r="K118" s="15" t="inlineStr">
         <is>
@@ -11533,37 +11537,33 @@
           <t>–</t>
         </is>
       </c>
-      <c r="P118" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P118" s="13" t="n">
+        <v>1.426</v>
       </c>
       <c r="Q118" s="13" t="n">
-        <v>0.42846406</v>
+        <v>0.4231442442328305</v>
       </c>
       <c r="R118" s="14" t="n">
-        <v>-15.94158732169212</v>
+        <v>18.37489221292608</v>
       </c>
       <c r="S118" s="13" t="n">
-        <v>-2.934119241</v>
+        <v>-2.778307688</v>
       </c>
       <c r="T118" s="14" t="n">
-        <v>-10.66472666</v>
-      </c>
-      <c r="U118" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-6.332213787000001</v>
+      </c>
+      <c r="U118" s="13" t="n">
+        <v>2.996280708</v>
       </c>
       <c r="V118" s="13" t="n">
         <v>0</v>
       </c>
       <c r="W118" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X118" s="8" t="inlineStr">
         <is>
-          <t>clean</t>
+          <t>+ FCF leads NI</t>
         </is>
       </c>
     </row>
@@ -11599,7 +11599,7 @@
       <c r="G119" s="11" t="n">
         <v>68425127.21561953</v>
       </c>
-      <c r="H119" s="12" t="inlineStr">
+      <c r="H119" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -11701,7 +11701,7 @@
       <c r="G120" s="11" t="n">
         <v>215222192.0983211</v>
       </c>
-      <c r="H120" s="12" t="inlineStr">
+      <c r="H120" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -11795,7 +11795,7 @@
       <c r="G121" s="11" t="n">
         <v>131529608.885231</v>
       </c>
-      <c r="H121" s="12" t="inlineStr">
+      <c r="H121" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -11893,7 +11893,7 @@
       <c r="G122" s="11" t="n">
         <v>250607546.2559808</v>
       </c>
-      <c r="H122" s="12" t="inlineStr">
+      <c r="H122" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -12089,7 +12089,7 @@
       <c r="G124" s="11" t="n">
         <v>384059537.8747862</v>
       </c>
-      <c r="H124" s="12" t="inlineStr">
+      <c r="H124" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -12187,7 +12187,7 @@
       <c r="G125" s="11" t="n">
         <v>198008171.3658428</v>
       </c>
-      <c r="H125" s="12" t="inlineStr">
+      <c r="H125" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -12285,7 +12285,7 @@
       <c r="G126" s="11" t="n">
         <v>624774879.4154508</v>
       </c>
-      <c r="H126" s="12" t="inlineStr">
+      <c r="H126" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -12383,7 +12383,7 @@
       <c r="G127" s="11" t="n">
         <v>165858082.1155147</v>
       </c>
-      <c r="H127" s="12" t="inlineStr">
+      <c r="H127" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -12481,7 +12481,7 @@
       <c r="G128" s="11" t="n">
         <v>2487798891.075561</v>
       </c>
-      <c r="H128" s="12" t="inlineStr">
+      <c r="H128" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -12579,7 +12579,7 @@
       <c r="G129" s="11" t="n">
         <v>1546016256</v>
       </c>
-      <c r="H129" s="12" t="inlineStr">
+      <c r="H129" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -12675,7 +12675,7 @@
       <c r="G130" s="11" t="n">
         <v>51385880</v>
       </c>
-      <c r="H130" s="12" t="inlineStr">
+      <c r="H130" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -12771,7 +12771,7 @@
       <c r="G131" s="11" t="n">
         <v>681998129.2183533</v>
       </c>
-      <c r="H131" s="12" t="inlineStr">
+      <c r="H131" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -12869,7 +12869,7 @@
       <c r="G132" s="11" t="n">
         <v>118910336.3754696</v>
       </c>
-      <c r="H132" s="12" t="inlineStr">
+      <c r="H132" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -12967,7 +12967,7 @@
       <c r="G133" s="11" t="n">
         <v>1200219909.118439</v>
       </c>
-      <c r="H133" s="12" t="inlineStr">
+      <c r="H133" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -13061,7 +13061,7 @@
       <c r="G134" s="11" t="n">
         <v>168998096</v>
       </c>
-      <c r="H134" s="12" t="inlineStr">
+      <c r="H134" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -13159,7 +13159,7 @@
       <c r="G135" s="11" t="n">
         <v>71860360</v>
       </c>
-      <c r="H135" s="12" t="inlineStr">
+      <c r="H135" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -13259,7 +13259,7 @@
       <c r="G136" s="11" t="n">
         <v>65197908</v>
       </c>
-      <c r="H136" s="12" t="inlineStr">
+      <c r="H136" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -13357,7 +13357,7 @@
       <c r="G137" s="11" t="n">
         <v>942040962.4710084</v>
       </c>
-      <c r="H137" s="12" t="inlineStr">
+      <c r="H137" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -13451,7 +13451,7 @@
       <c r="G138" s="11" t="n">
         <v>172599385.2923545</v>
       </c>
-      <c r="H138" s="12" t="inlineStr">
+      <c r="H138" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -13553,7 +13553,7 @@
       <c r="G139" s="11" t="n">
         <v>2793141760</v>
       </c>
-      <c r="H139" s="12" t="inlineStr">
+      <c r="H139" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -13647,7 +13647,7 @@
       <c r="G140" s="11" t="n">
         <v>67297128</v>
       </c>
-      <c r="H140" s="12" t="inlineStr">
+      <c r="H140" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -13749,7 +13749,7 @@
       <c r="G141" s="11" t="n">
         <v>54606287.47050738</v>
       </c>
-      <c r="H141" s="12" t="inlineStr">
+      <c r="H141" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -13843,7 +13843,7 @@
       <c r="G142" s="11" t="n">
         <v>67755237.57049769</v>
       </c>
-      <c r="H142" s="12" t="inlineStr">
+      <c r="H142" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -13941,7 +13941,7 @@
       <c r="G143" s="11" t="n">
         <v>73634240.58063953</v>
       </c>
-      <c r="H143" s="12" t="inlineStr">
+      <c r="H143" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -14039,7 +14039,7 @@
       <c r="G144" s="11" t="n">
         <v>277609192.5993335</v>
       </c>
-      <c r="H144" s="12" t="inlineStr">
+      <c r="H144" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -14137,7 +14137,7 @@
       <c r="G145" s="11" t="n">
         <v>66768136</v>
       </c>
-      <c r="H145" s="12" t="inlineStr">
+      <c r="H145" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -14235,7 +14235,7 @@
       <c r="G146" s="11" t="n">
         <v>104319478.0894728</v>
       </c>
-      <c r="H146" s="12" t="inlineStr">
+      <c r="H146" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -14335,7 +14335,7 @@
       <c r="G147" s="11" t="n">
         <v>69608488</v>
       </c>
-      <c r="H147" s="12" t="inlineStr">
+      <c r="H147" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -14433,7 +14433,7 @@
       <c r="G148" s="11" t="n">
         <v>125759425.1632687</v>
       </c>
-      <c r="H148" s="12" t="inlineStr">
+      <c r="H148" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -14531,7 +14531,7 @@
       <c r="G149" s="11" t="n">
         <v>827467968</v>
       </c>
-      <c r="H149" s="12" t="inlineStr">
+      <c r="H149" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -14629,7 +14629,7 @@
       <c r="G150" s="11" t="n">
         <v>88514613.86107269</v>
       </c>
-      <c r="H150" s="12" t="inlineStr">
+      <c r="H150" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -14729,7 +14729,7 @@
       <c r="G151" s="11" t="n">
         <v>251679028.1441964</v>
       </c>
-      <c r="H151" s="12" t="inlineStr">
+      <c r="H151" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -14827,7 +14827,7 @@
       <c r="G152" s="11" t="n">
         <v>59345484</v>
       </c>
-      <c r="H152" s="12" t="inlineStr">
+      <c r="H152" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -14929,7 +14929,7 @@
       <c r="G153" s="11" t="n">
         <v>93145645.10028052</v>
       </c>
-      <c r="H153" s="12" t="inlineStr">
+      <c r="H153" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -15027,7 +15027,7 @@
       <c r="G154" s="11" t="n">
         <v>112311283.219952</v>
       </c>
-      <c r="H154" s="12" t="inlineStr">
+      <c r="H154" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -15127,7 +15127,7 @@
       <c r="G155" s="11" t="n">
         <v>727225187.2049317</v>
       </c>
-      <c r="H155" s="12" t="inlineStr">
+      <c r="H155" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -15319,7 +15319,7 @@
       <c r="G157" s="11" t="n">
         <v>306372864</v>
       </c>
-      <c r="H157" s="12" t="inlineStr">
+      <c r="H157" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -15413,7 +15413,7 @@
       <c r="G158" s="11" t="n">
         <v>52354233.2174132</v>
       </c>
-      <c r="H158" s="12" t="inlineStr">
+      <c r="H158" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -15507,7 +15507,7 @@
       <c r="G159" s="11" t="n">
         <v>90115083.31770048</v>
       </c>
-      <c r="H159" s="12" t="inlineStr">
+      <c r="H159" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -15607,7 +15607,7 @@
       <c r="G160" s="11" t="n">
         <v>177022517.6883737</v>
       </c>
-      <c r="H160" s="12" t="inlineStr">
+      <c r="H160" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -15705,7 +15705,7 @@
       <c r="G161" s="11" t="n">
         <v>89614672</v>
       </c>
-      <c r="H161" s="12" t="inlineStr">
+      <c r="H161" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -15805,7 +15805,7 @@
       <c r="G162" s="11" t="n">
         <v>61559999.54910471</v>
       </c>
-      <c r="H162" s="12" t="inlineStr">
+      <c r="H162" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -15903,7 +15903,7 @@
       <c r="G163" s="11" t="n">
         <v>117253956.7947385</v>
       </c>
-      <c r="H163" s="12" t="inlineStr">
+      <c r="H163" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -16001,7 +16001,7 @@
       <c r="G164" s="11" t="n">
         <v>222272815.7774208</v>
       </c>
-      <c r="H164" s="12" t="inlineStr">
+      <c r="H164" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -16095,7 +16095,7 @@
       <c r="G165" s="11" t="n">
         <v>58413371.05213177</v>
       </c>
-      <c r="H165" s="12" t="inlineStr">
+      <c r="H165" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -16195,7 +16195,7 @@
       <c r="G166" s="11" t="n">
         <v>142019952</v>
       </c>
-      <c r="H166" s="12" t="inlineStr">
+      <c r="H166" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -16293,7 +16293,7 @@
       <c r="G167" s="11" t="n">
         <v>577025857.6757355</v>
       </c>
-      <c r="H167" s="12" t="inlineStr">
+      <c r="H167" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -16387,7 +16387,7 @@
       <c r="G168" s="11" t="n">
         <v>1211536564.668243</v>
       </c>
-      <c r="H168" s="12" t="inlineStr">
+      <c r="H168" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -16481,7 +16481,7 @@
       <c r="G169" s="11" t="n">
         <v>80460832</v>
       </c>
-      <c r="H169" s="12" t="inlineStr">
+      <c r="H169" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -16579,7 +16579,7 @@
       <c r="G170" s="11" t="n">
         <v>109420617.644927</v>
       </c>
-      <c r="H170" s="12" t="inlineStr">
+      <c r="H170" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -16777,7 +16777,7 @@
       <c r="G172" s="11" t="n">
         <v>1918573280.560824</v>
       </c>
-      <c r="H172" s="12" t="inlineStr">
+      <c r="H172" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -16871,7 +16871,7 @@
       <c r="G173" s="11" t="n">
         <v>62863042.90078065</v>
       </c>
-      <c r="H173" s="12" t="inlineStr">
+      <c r="H173" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -16969,7 +16969,7 @@
       <c r="G174" s="11" t="n">
         <v>56495738.77864098</v>
       </c>
-      <c r="H174" s="12" t="inlineStr">
+      <c r="H174" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -17067,7 +17067,7 @@
       <c r="G175" s="11" t="n">
         <v>286710084.9602571</v>
       </c>
-      <c r="H175" s="12" t="inlineStr">
+      <c r="H175" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -17167,7 +17167,7 @@
       <c r="G176" s="11" t="n">
         <v>105012840.1910658</v>
       </c>
-      <c r="H176" s="12" t="inlineStr">
+      <c r="H176" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -17267,7 +17267,7 @@
       <c r="G177" s="11" t="n">
         <v>217532999.5775423</v>
       </c>
-      <c r="H177" s="12" t="inlineStr">
+      <c r="H177" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -17365,7 +17365,7 @@
       <c r="G178" s="11" t="n">
         <v>65233794.31658478</v>
       </c>
-      <c r="H178" s="12" t="inlineStr">
+      <c r="H178" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -17465,7 +17465,7 @@
       <c r="G179" s="11" t="n">
         <v>177214464</v>
       </c>
-      <c r="H179" s="12" t="inlineStr">
+      <c r="H179" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -17565,7 +17565,7 @@
       <c r="G180" s="11" t="n">
         <v>194080437.2869432</v>
       </c>
-      <c r="H180" s="12" t="inlineStr">
+      <c r="H180" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -17761,7 +17761,7 @@
       <c r="G182" s="11" t="n">
         <v>105909941.480752</v>
       </c>
-      <c r="H182" s="12" t="inlineStr">
+      <c r="H182" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -17861,7 +17861,7 @@
       <c r="G183" s="11" t="n">
         <v>1508673536</v>
       </c>
-      <c r="H183" s="12" t="inlineStr">
+      <c r="H183" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -17957,7 +17957,7 @@
       <c r="G184" s="11" t="n">
         <v>55903008</v>
       </c>
-      <c r="H184" s="12" t="inlineStr">
+      <c r="H184" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -18055,7 +18055,7 @@
       <c r="G185" s="11" t="n">
         <v>884342369.346069</v>
       </c>
-      <c r="H185" s="12" t="inlineStr">
+      <c r="H185" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -18149,7 +18149,7 @@
       <c r="G186" s="11" t="n">
         <v>95502091.50071996</v>
       </c>
-      <c r="H186" s="12" t="inlineStr">
+      <c r="H186" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -18247,7 +18247,7 @@
       <c r="G187" s="11" t="n">
         <v>50212160.69315293</v>
       </c>
-      <c r="H187" s="12" t="inlineStr">
+      <c r="H187" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -18345,7 +18345,7 @@
       <c r="G188" s="11" t="n">
         <v>57964067.02224172</v>
       </c>
-      <c r="H188" s="12" t="inlineStr">
+      <c r="H188" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -18443,7 +18443,7 @@
       <c r="G189" s="11" t="n">
         <v>116875362.1434653</v>
       </c>
-      <c r="H189" s="12" t="inlineStr">
+      <c r="H189" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -18543,7 +18543,7 @@
       <c r="G190" s="11" t="n">
         <v>545204096</v>
       </c>
-      <c r="H190" s="12" t="inlineStr">
+      <c r="H190" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -18637,7 +18637,7 @@
       <c r="G191" s="11" t="n">
         <v>3110350472.716553</v>
       </c>
-      <c r="H191" s="12" t="inlineStr">
+      <c r="H191" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -18735,7 +18735,7 @@
       <c r="G192" s="11" t="n">
         <v>67201741.43705355</v>
       </c>
-      <c r="H192" s="12" t="inlineStr">
+      <c r="H192" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -18835,7 +18835,7 @@
       <c r="G193" s="11" t="n">
         <v>467926272</v>
       </c>
-      <c r="H193" s="12" t="inlineStr">
+      <c r="H193" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -18927,7 +18927,7 @@
       <c r="G194" s="11" t="n">
         <v>191529460.3644733</v>
       </c>
-      <c r="H194" s="12" t="inlineStr">
+      <c r="H194" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -19025,7 +19025,7 @@
       <c r="G195" s="11" t="n">
         <v>129745238.9596071</v>
       </c>
-      <c r="H195" s="12" t="inlineStr">
+      <c r="H195" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -19123,7 +19123,7 @@
       <c r="G196" s="11" t="n">
         <v>209807244.5166701</v>
       </c>
-      <c r="H196" s="12" t="inlineStr">
+      <c r="H196" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -19221,7 +19221,7 @@
       <c r="G197" s="11" t="n">
         <v>131943298.9656925</v>
       </c>
-      <c r="H197" s="12" t="inlineStr">
+      <c r="H197" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -19321,7 +19321,7 @@
       <c r="G198" s="11" t="n">
         <v>562563939.6004179</v>
       </c>
-      <c r="H198" s="12" t="inlineStr">
+      <c r="H198" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -19423,7 +19423,7 @@
       <c r="G199" s="11" t="n">
         <v>2943670429.386438</v>
       </c>
-      <c r="H199" s="16" t="inlineStr">
+      <c r="H199" s="12" t="inlineStr">
         <is>
           <t>YELLOW</t>
         </is>
@@ -19521,7 +19521,7 @@
       <c r="G200" s="11" t="n">
         <v>59064911.0160135</v>
       </c>
-      <c r="H200" s="12" t="inlineStr">
+      <c r="H200" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -19619,7 +19619,7 @@
       <c r="G201" s="11" t="n">
         <v>229224126.7182245</v>
       </c>
-      <c r="H201" s="12" t="inlineStr">
+      <c r="H201" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -19717,7 +19717,7 @@
       <c r="G202" s="11" t="n">
         <v>732676492.639092</v>
       </c>
-      <c r="H202" s="12" t="inlineStr">
+      <c r="H202" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -19815,7 +19815,7 @@
       <c r="G203" s="11" t="n">
         <v>159301312</v>
       </c>
-      <c r="H203" s="12" t="inlineStr">
+      <c r="H203" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -19911,7 +19911,7 @@
       <c r="G204" s="11" t="n">
         <v>65205302.16997118</v>
       </c>
-      <c r="H204" s="12" t="inlineStr">
+      <c r="H204" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -20009,7 +20009,7 @@
       <c r="G205" s="11" t="n">
         <v>103059115.8746573</v>
       </c>
-      <c r="H205" s="12" t="inlineStr">
+      <c r="H205" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -20105,7 +20105,7 @@
       <c r="G206" s="11" t="n">
         <v>79257340.28838441</v>
       </c>
-      <c r="H206" s="12" t="inlineStr">
+      <c r="H206" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -20199,7 +20199,7 @@
       <c r="G207" s="11" t="n">
         <v>101142964.4425459</v>
       </c>
-      <c r="H207" s="12" t="inlineStr">
+      <c r="H207" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -20297,7 +20297,7 @@
       <c r="G208" s="11" t="n">
         <v>710861291.0740051</v>
       </c>
-      <c r="H208" s="12" t="inlineStr">
+      <c r="H208" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -20395,7 +20395,7 @@
       <c r="G209" s="11" t="n">
         <v>122170111.186666</v>
       </c>
-      <c r="H209" s="12" t="inlineStr">
+      <c r="H209" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -20493,7 +20493,7 @@
       <c r="G210" s="11" t="n">
         <v>104025144</v>
       </c>
-      <c r="H210" s="12" t="inlineStr">
+      <c r="H210" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -20585,7 +20585,7 @@
       <c r="G211" s="11" t="n">
         <v>204205728</v>
       </c>
-      <c r="H211" s="12" t="inlineStr">
+      <c r="H211" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -20677,7 +20677,7 @@
       <c r="G212" s="11" t="n">
         <v>331247923.7159156</v>
       </c>
-      <c r="H212" s="12" t="inlineStr">
+      <c r="H212" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -20773,7 +20773,7 @@
       <c r="G213" s="11" t="n">
         <v>74352208.34467946</v>
       </c>
-      <c r="H213" s="12" t="inlineStr">
+      <c r="H213" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -20873,7 +20873,7 @@
       <c r="G214" s="11" t="n">
         <v>195573437.9176652</v>
       </c>
-      <c r="H214" s="12" t="inlineStr">
+      <c r="H214" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -20977,7 +20977,7 @@
       <c r="G215" s="11" t="n">
         <v>127395710.0485319</v>
       </c>
-      <c r="H215" s="12" t="inlineStr">
+      <c r="H215" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -21075,7 +21075,7 @@
       <c r="G216" s="11" t="n">
         <v>200581998.5176101</v>
       </c>
-      <c r="H216" s="16" t="inlineStr">
+      <c r="H216" s="12" t="inlineStr">
         <is>
           <t>YELLOW</t>
         </is>
@@ -21175,7 +21175,7 @@
       <c r="G217" s="11" t="n">
         <v>205733000.7223753</v>
       </c>
-      <c r="H217" s="12" t="inlineStr">
+      <c r="H217" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -21275,7 +21275,7 @@
       <c r="G218" s="11" t="n">
         <v>816091923.8290631</v>
       </c>
-      <c r="H218" s="12" t="inlineStr">
+      <c r="H218" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -21375,7 +21375,7 @@
       <c r="G219" s="11" t="n">
         <v>113457520</v>
       </c>
-      <c r="H219" s="12" t="inlineStr">
+      <c r="H219" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -21473,7 +21473,7 @@
       <c r="G220" s="11" t="n">
         <v>222956720</v>
       </c>
-      <c r="H220" s="12" t="inlineStr">
+      <c r="H220" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -21573,7 +21573,7 @@
       <c r="G221" s="11" t="n">
         <v>483229522.229424</v>
       </c>
-      <c r="H221" s="12" t="inlineStr">
+      <c r="H221" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -21769,7 +21769,7 @@
       <c r="G223" s="11" t="n">
         <v>72140270.34925747</v>
       </c>
-      <c r="H223" s="12" t="inlineStr">
+      <c r="H223" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -21869,7 +21869,7 @@
       <c r="G224" s="11" t="n">
         <v>133975231.7133373</v>
       </c>
-      <c r="H224" s="12" t="inlineStr">
+      <c r="H224" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -21967,7 +21967,7 @@
       <c r="G225" s="11" t="n">
         <v>1681734314.436417</v>
       </c>
-      <c r="H225" s="12" t="inlineStr">
+      <c r="H225" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -22163,7 +22163,7 @@
       <c r="G227" s="11" t="n">
         <v>735705190.6283264</v>
       </c>
-      <c r="H227" s="12" t="inlineStr">
+      <c r="H227" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -22257,7 +22257,7 @@
       <c r="G228" s="11" t="n">
         <v>254800752</v>
       </c>
-      <c r="H228" s="12" t="inlineStr">
+      <c r="H228" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -22357,7 +22357,7 @@
       <c r="G229" s="11" t="n">
         <v>818325962.5587237</v>
       </c>
-      <c r="H229" s="12" t="inlineStr">
+      <c r="H229" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -22455,7 +22455,7 @@
       <c r="G230" s="11" t="n">
         <v>181462913.081588</v>
       </c>
-      <c r="H230" s="12" t="inlineStr">
+      <c r="H230" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -22553,7 +22553,7 @@
       <c r="G231" s="11" t="n">
         <v>1055324584.065971</v>
       </c>
-      <c r="H231" s="12" t="inlineStr">
+      <c r="H231" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -22651,7 +22651,7 @@
       <c r="G232" s="11" t="n">
         <v>257241799.1600985</v>
       </c>
-      <c r="H232" s="12" t="inlineStr">
+      <c r="H232" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -22749,7 +22749,7 @@
       <c r="G233" s="11" t="n">
         <v>116298496</v>
       </c>
-      <c r="H233" s="12" t="inlineStr">
+      <c r="H233" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -22847,7 +22847,7 @@
       <c r="G234" s="11" t="n">
         <v>193037044.8453704</v>
       </c>
-      <c r="H234" s="12" t="inlineStr">
+      <c r="H234" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -23045,7 +23045,7 @@
       <c r="G236" s="11" t="n">
         <v>160401808</v>
       </c>
-      <c r="H236" s="12" t="inlineStr">
+      <c r="H236" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -23147,7 +23147,7 @@
       <c r="G237" s="11" t="n">
         <v>55752293.57371306</v>
       </c>
-      <c r="H237" s="16" t="inlineStr">
+      <c r="H237" s="12" t="inlineStr">
         <is>
           <t>YELLOW</t>
         </is>
@@ -23245,7 +23245,7 @@
       <c r="G238" s="11" t="n">
         <v>286546592</v>
       </c>
-      <c r="H238" s="12" t="inlineStr">
+      <c r="H238" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -23441,7 +23441,7 @@
       <c r="G240" s="11" t="n">
         <v>50524003.66617677</v>
       </c>
-      <c r="H240" s="16" t="inlineStr">
+      <c r="H240" s="12" t="inlineStr">
         <is>
           <t>YELLOW</t>
         </is>
@@ -23539,7 +23539,7 @@
       <c r="G241" s="11" t="n">
         <v>323675168</v>
       </c>
-      <c r="H241" s="12" t="inlineStr">
+      <c r="H241" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -23635,7 +23635,7 @@
       <c r="G242" s="11" t="n">
         <v>143889911.7769679</v>
       </c>
-      <c r="H242" s="12" t="inlineStr">
+      <c r="H242" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -23729,7 +23729,7 @@
       <c r="G243" s="11" t="n">
         <v>90425333.54678354</v>
       </c>
-      <c r="H243" s="12" t="inlineStr">
+      <c r="H243" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -23925,7 +23925,7 @@
       <c r="G245" s="11" t="n">
         <v>455792884.9637012</v>
       </c>
-      <c r="H245" s="12" t="inlineStr">
+      <c r="H245" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -24023,7 +24023,7 @@
       <c r="G246" s="11" t="n">
         <v>102220264</v>
       </c>
-      <c r="H246" s="12" t="inlineStr">
+      <c r="H246" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -24117,7 +24117,7 @@
       <c r="G247" s="11" t="n">
         <v>1459454976</v>
       </c>
-      <c r="H247" s="12" t="inlineStr">
+      <c r="H247" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -24211,7 +24211,7 @@
       <c r="G248" s="11" t="n">
         <v>3237362433.096281</v>
       </c>
-      <c r="H248" s="12" t="inlineStr">
+      <c r="H248" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -24309,7 +24309,7 @@
       <c r="G249" s="11" t="n">
         <v>1479694708.230896</v>
       </c>
-      <c r="H249" s="12" t="inlineStr">
+      <c r="H249" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -24407,7 +24407,7 @@
       <c r="G250" s="11" t="n">
         <v>108580292.5080679</v>
       </c>
-      <c r="H250" s="12" t="inlineStr">
+      <c r="H250" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -24505,7 +24505,7 @@
       <c r="G251" s="11" t="n">
         <v>365884949.1364559</v>
       </c>
-      <c r="H251" s="12" t="inlineStr">
+      <c r="H251" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -24603,7 +24603,7 @@
       <c r="G252" s="11" t="n">
         <v>261787072</v>
       </c>
-      <c r="H252" s="12" t="inlineStr">
+      <c r="H252" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -24697,7 +24697,7 @@
       <c r="G253" s="11" t="n">
         <v>111196261.6460032</v>
       </c>
-      <c r="H253" s="16" t="inlineStr">
+      <c r="H253" s="12" t="inlineStr">
         <is>
           <t>YELLOW</t>
         </is>
@@ -24795,7 +24795,7 @@
       <c r="G254" s="11" t="n">
         <v>255558499.6926191</v>
       </c>
-      <c r="H254" s="12" t="inlineStr">
+      <c r="H254" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -24893,7 +24893,7 @@
       <c r="G255" s="11" t="n">
         <v>133567273.379282</v>
       </c>
-      <c r="H255" s="12" t="inlineStr">
+      <c r="H255" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -24987,7 +24987,7 @@
       <c r="G256" s="11" t="n">
         <v>74108079.37993298</v>
       </c>
-      <c r="H256" s="12" t="inlineStr">
+      <c r="H256" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
@@ -25087,7 +25087,7 @@
       <c r="G257" s="11" t="n">
         <v>194515898.3174057</v>
       </c>
-      <c r="H257" s="12" t="inlineStr">
+      <c r="H257" s="16" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
